--- a/DOCUMENTATION/WEB_SCRAPE_AUTOMATIOn.xlsx
+++ b/DOCUMENTATION/WEB_SCRAPE_AUTOMATIOn.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://globaldenso-my.sharepoint.com/personal/vincent_joe_narvaez_a3n_ap_denso_com/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vincent\UNIFIED_SYSTEM_AUTOMATION\DOCUMENTATION\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="372" documentId="8_{E76025FE-EEAC-496C-BFB2-CB82C65A5A8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{536E2677-663D-47E9-A12A-0CA607198B16}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B3C70B6-5751-489C-8AB2-540C9FD92C07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="2310" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{AF954AEF-E990-4149-A50E-313C2C1CB0ED}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{AF954AEF-E990-4149-A50E-313C2C1CB0ED}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="AUTOMATION CONTROL" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -28,8 +28,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -37,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="41">
   <si>
     <t xml:space="preserve">WEB_SCRAPE Automation User's Manual </t>
   </si>
@@ -116,12 +114,57 @@
   <si>
     <t>Note: The human verification process have a 300s duration when this expired this process will skipped.</t>
   </si>
+  <si>
+    <t>Automation Control</t>
+  </si>
+  <si>
+    <t>STOP: This will automatically interrupt the ongoing execution.</t>
+  </si>
+  <si>
+    <t>START AUTOMATION: This launches the Full country along with its platforms and categories in a background thread.</t>
+  </si>
+  <si>
+    <t>SCRAPE FILES: A function that used to extract data out of the existing folder containing  a MHTML files.</t>
+  </si>
+  <si>
+    <t>FILTER INPUT &amp; LOG-LEVEL : This will highlighted all the match value selected or Inputted by the user.</t>
+  </si>
+  <si>
+    <t>CLEAR FILTER: This unfiltered all the matching lines that selected or inputted by the user.</t>
+  </si>
+  <si>
+    <t>LOG OUTPUT: This display all the activities happening in the START AUTOMATION and SCRAPE FILES functions.</t>
+  </si>
+  <si>
+    <t>How to use</t>
+  </si>
+  <si>
+    <t>1.Automate Webpages</t>
+  </si>
+  <si>
+    <t>1.To begin in automating webpages, click 'START AUTOMATION'.</t>
+  </si>
+  <si>
+    <t>4. When finished a dialog appeared containing a no. of successful and failed during automating along with the location of folder that have MHTML and excel files.</t>
+  </si>
+  <si>
+    <t>`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. The folder validated first if there are existing MHTML files, then skipped it the existing one and proceed on the next categories not yet executed. </t>
+  </si>
+  <si>
+    <t>3. When a pop-up notification showed in your screen, you need to go on the browser itself to manually solve it.</t>
+  </si>
+  <si>
+    <t>1.Scrape MHTML Files</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -180,8 +223,31 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="14"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -200,8 +266,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -280,12 +358,92 @@
     </border>
     <border>
       <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="medium">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
       </right>
       <top/>
       <bottom style="medium">
         <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -294,7 +452,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -309,26 +467,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -346,6 +496,52 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="6"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="6"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -457,8 +653,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="679549" y="1404207"/>
-          <a:ext cx="1915975" cy="1120588"/>
+          <a:off x="688061" y="1417029"/>
+          <a:ext cx="1941511" cy="1131579"/>
           <a:chOff x="609867" y="1040943"/>
           <a:chExt cx="2098967" cy="1120588"/>
         </a:xfrm>
@@ -572,8 +768,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="6094038" y="3886200"/>
-          <a:ext cx="316523" cy="497969"/>
+          <a:off x="6179160" y="3922835"/>
+          <a:ext cx="316523" cy="503464"/>
           <a:chOff x="5223049" y="6616473"/>
           <a:chExt cx="315843" cy="497969"/>
         </a:xfrm>
@@ -702,8 +898,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="6709009" y="888125"/>
-          <a:ext cx="609224" cy="315058"/>
+          <a:off x="6802643" y="895452"/>
+          <a:ext cx="617736" cy="318721"/>
           <a:chOff x="6991842" y="4402850"/>
           <a:chExt cx="615020" cy="315058"/>
         </a:xfrm>
@@ -832,8 +1028,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="13285444" y="0"/>
-          <a:ext cx="8815838" cy="5997740"/>
+          <a:off x="13464199" y="0"/>
+          <a:ext cx="8943521" cy="6054524"/>
           <a:chOff x="2469366" y="5346324"/>
           <a:chExt cx="8923895" cy="5997740"/>
         </a:xfrm>
@@ -2338,15 +2534,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>577973</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>473302</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>10467</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>317047</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>92240</xdr:rowOff>
+      <xdr:colOff>212376</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>102707</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -2361,8 +2557,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="2414937" y="2775857"/>
-          <a:ext cx="8923896" cy="5997740"/>
+          <a:off x="2291711" y="3235978"/>
+          <a:ext cx="8831120" cy="6131956"/>
           <a:chOff x="2469366" y="5346324"/>
           <a:chExt cx="8923895" cy="5997740"/>
         </a:xfrm>
@@ -3485,11 +3681,418 @@
     </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>600076</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="5355262" cy="3836355"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="35" name="Picture 34">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{10059F1D-D6B7-4776-AE6D-973711882605}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7313814" y="15417646"/>
+          <a:ext cx="5355262" cy="3836355"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>145677</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>11206</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>518967</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>114838</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="36" name="Arrow: Right 35">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8C1AF961-839B-4CD4-8ED8-AE03004D3960}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6241677" y="10107706"/>
+          <a:ext cx="982890" cy="484632"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100" kern="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>34217</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>80945</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>293760</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>175287</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="38" name="Picture 37">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD4F6D96-828F-4C76-900E-BB08356FFF17}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9793164" y="13374169"/>
+          <a:ext cx="7509006" cy="4081981"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>492638</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>48727</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>38</xdr:col>
+      <xdr:colOff>544894</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>1753</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="41" name="Picture 116">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{319A031A-E418-4E20-A1A5-30B9CC27E33F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:srcRect l="79666" t="83798"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8962165" y="18635349"/>
+          <a:ext cx="3682054" cy="1682435"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>241964</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>47369</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>42</xdr:col>
+      <xdr:colOff>484500</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>5344</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="42" name="Picture 117">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1F9461FA-CE96-4C61-BBBB-FB633E9081CA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="21500660" y="15480630"/>
+          <a:ext cx="4494275" cy="2455700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>331304</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>96631</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>97204</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>7002</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="47" name="Arrow: Right 46">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ACF57ED5-C1B0-40FE-9A50-C8A70E8E0EB7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17945652" y="14950109"/>
+          <a:ext cx="980682" cy="490154"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100" kern="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>45</xdr:col>
+      <xdr:colOff>241904</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>166310</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>47</xdr:col>
+      <xdr:colOff>7804</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>76680</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="48" name="Arrow: Right 47">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1CB3D611-3536-4C85-B330-D2CC28838BBB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="27456190" y="15481905"/>
+          <a:ext cx="975424" cy="500013"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100" kern="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>47</xdr:col>
+      <xdr:colOff>78992</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>6431</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>57</xdr:col>
+      <xdr:colOff>419017</xdr:colOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>480</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="49" name="Picture 48">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{61849501-E803-9EEF-5126-935EE3340809}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="28680450" y="13606014"/>
+          <a:ext cx="6425442" cy="4838331"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3813,49 +4416,49 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
     </row>
     <row r="2" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A2" s="24"/>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
+      <c r="A2" s="20"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
     </row>
     <row r="3" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
+      <c r="B3" s="21"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="21"/>
+      <c r="I3" s="21"/>
     </row>
     <row r="5" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="22"/>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
     </row>
     <row r="7" spans="1:42" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
@@ -3898,12 +4501,12 @@
       </c>
     </row>
     <row r="16" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A16" s="21" t="s">
+      <c r="A16" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="B16" s="21"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
       <c r="AN16" t="s">
         <v>12</v>
       </c>
@@ -3940,12 +4543,12 @@
       </c>
     </row>
     <row r="41" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A41" s="20" t="s">
+      <c r="A41" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="B41" s="20"/>
-      <c r="C41" s="20"/>
-      <c r="D41" s="20"/>
+      <c r="B41" s="16"/>
+      <c r="C41" s="16"/>
+      <c r="D41" s="16"/>
     </row>
     <row r="45" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
@@ -3980,51 +4583,204 @@
     <hyperlink ref="C19" location="Sheet1!B24" display="1. Automate Webpages " xr:uid="{5184525B-E007-4EC0-81DF-379C712E2C6C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="256" orientation="portrait" horizontalDpi="4294967292" verticalDpi="0" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;KFF0000 CONFIDENTIAL&amp;1#_x000D_</oddHeader>
   </headerFooter>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40098BD2-3A0C-4DBD-8904-60C96FC01DEF}">
-  <dimension ref="D11:AD70"/>
+  <dimension ref="C10:DJ351"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="11" spans="4:30" ht="24" x14ac:dyDescent="0.25">
-      <c r="D11" s="18" t="s">
+    <row r="10" spans="4:114" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="AD10" s="30"/>
+      <c r="AE10" s="30"/>
+      <c r="AF10" s="30"/>
+      <c r="AG10" s="30"/>
+      <c r="AH10" s="30"/>
+      <c r="AI10" s="30"/>
+      <c r="AJ10" s="30"/>
+      <c r="AK10" s="30"/>
+      <c r="AL10" s="30"/>
+      <c r="AM10" s="30"/>
+      <c r="AN10" s="30"/>
+      <c r="AO10" s="30"/>
+      <c r="AP10" s="30"/>
+      <c r="AQ10" s="30"/>
+      <c r="AR10" s="30"/>
+      <c r="AS10" s="30"/>
+      <c r="AT10" s="30"/>
+      <c r="AU10" s="30"/>
+      <c r="AV10" s="30"/>
+      <c r="AW10" s="30"/>
+      <c r="AX10" s="30"/>
+      <c r="AY10" s="30"/>
+      <c r="AZ10" s="30"/>
+      <c r="BA10" s="30"/>
+      <c r="BB10" s="30"/>
+      <c r="BC10" s="30"/>
+      <c r="BD10" s="30"/>
+      <c r="BE10" s="30"/>
+      <c r="BF10" s="30"/>
+      <c r="BG10" s="30"/>
+      <c r="BH10" s="30"/>
+      <c r="BI10" s="30"/>
+      <c r="BJ10" s="30"/>
+      <c r="BK10" s="30"/>
+      <c r="BL10" s="30"/>
+      <c r="BM10" s="30"/>
+      <c r="BN10" s="30"/>
+      <c r="BO10" s="25"/>
+      <c r="BP10" s="25"/>
+      <c r="BQ10" s="25"/>
+      <c r="BR10" s="25"/>
+      <c r="BS10" s="25"/>
+      <c r="BT10" s="25"/>
+      <c r="BU10" s="25"/>
+      <c r="BV10" s="25"/>
+      <c r="BW10" s="25"/>
+      <c r="BX10" s="25"/>
+      <c r="BY10" s="25"/>
+      <c r="BZ10" s="25"/>
+      <c r="CA10" s="25"/>
+      <c r="CB10" s="25"/>
+      <c r="CC10" s="25"/>
+      <c r="CD10" s="25"/>
+      <c r="CE10" s="25"/>
+      <c r="CF10" s="25"/>
+      <c r="CG10" s="25"/>
+      <c r="CH10" s="25"/>
+      <c r="CI10" s="25"/>
+      <c r="CJ10" s="25"/>
+      <c r="CK10" s="25"/>
+      <c r="CL10" s="25"/>
+      <c r="CM10" s="25"/>
+      <c r="CN10" s="25"/>
+      <c r="CO10" s="25"/>
+      <c r="CP10" s="25"/>
+      <c r="CQ10" s="25"/>
+      <c r="CR10" s="25"/>
+      <c r="CS10" s="25"/>
+      <c r="CT10" s="25"/>
+      <c r="CU10" s="25"/>
+      <c r="CV10" s="25"/>
+      <c r="CW10" s="25"/>
+      <c r="CX10" s="25"/>
+      <c r="CY10" s="25"/>
+      <c r="CZ10" s="25"/>
+      <c r="DA10" s="30"/>
+    </row>
+    <row r="11" spans="4:114" ht="24" x14ac:dyDescent="0.25">
+      <c r="D11" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="13"/>
-      <c r="L11" s="13"/>
-      <c r="M11" s="14"/>
-      <c r="N11" s="13"/>
-      <c r="O11" s="13"/>
-      <c r="P11" s="13"/>
-      <c r="Q11" s="13"/>
-      <c r="R11" s="13"/>
-      <c r="S11" s="13"/>
-      <c r="T11" s="13"/>
-      <c r="U11" s="13"/>
-      <c r="V11" s="14"/>
-      <c r="W11" s="13"/>
-      <c r="X11" s="13"/>
-      <c r="Y11" s="13"/>
-      <c r="Z11" s="13"/>
-      <c r="AA11" s="13"/>
-      <c r="AB11" s="13"/>
-      <c r="AC11" s="13"/>
-      <c r="AD11" s="15"/>
-    </row>
-    <row r="12" spans="4:30" x14ac:dyDescent="0.25">
-      <c r="D12" s="16"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="12"/>
+      <c r="L11" s="12"/>
+      <c r="M11" s="13"/>
+      <c r="N11" s="12"/>
+      <c r="O11" s="12"/>
+      <c r="P11" s="12"/>
+      <c r="Q11" s="12"/>
+      <c r="R11" s="12"/>
+      <c r="S11" s="12"/>
+      <c r="T11" s="12"/>
+      <c r="U11" s="12"/>
+      <c r="V11" s="13"/>
+      <c r="W11" s="12"/>
+      <c r="X11" s="12"/>
+      <c r="Y11" s="12"/>
+      <c r="Z11" s="12"/>
+      <c r="AA11" s="12"/>
+      <c r="AB11" s="12"/>
+      <c r="AC11" s="12"/>
+      <c r="AD11" s="41"/>
+      <c r="AE11" s="42"/>
+      <c r="AF11" s="43"/>
+      <c r="AG11" s="43"/>
+      <c r="AH11" s="43"/>
+      <c r="AI11" s="43"/>
+      <c r="AJ11" s="43"/>
+      <c r="AK11" s="43"/>
+      <c r="AL11" s="43"/>
+      <c r="AM11" s="43"/>
+      <c r="AN11" s="43"/>
+      <c r="AO11" s="43"/>
+      <c r="AP11" s="43"/>
+      <c r="AQ11" s="43"/>
+      <c r="AR11" s="43"/>
+      <c r="AS11" s="43"/>
+      <c r="AT11" s="43"/>
+      <c r="AU11" s="43"/>
+      <c r="AV11" s="43"/>
+      <c r="AW11" s="43"/>
+      <c r="AX11" s="43"/>
+      <c r="AY11" s="43"/>
+      <c r="AZ11" s="43"/>
+      <c r="BA11" s="43"/>
+      <c r="BB11" s="43"/>
+      <c r="BC11" s="43"/>
+      <c r="BD11" s="43"/>
+      <c r="BE11" s="43"/>
+      <c r="BF11" s="43"/>
+      <c r="BG11" s="43"/>
+      <c r="BH11" s="43"/>
+      <c r="BI11" s="43"/>
+      <c r="BJ11" s="43"/>
+      <c r="BK11" s="43"/>
+      <c r="BL11" s="43"/>
+      <c r="BM11" s="43"/>
+      <c r="BN11" s="44"/>
+      <c r="BO11" s="25"/>
+      <c r="BP11" s="25"/>
+      <c r="BQ11" s="25"/>
+      <c r="BR11" s="25"/>
+      <c r="BS11" s="25"/>
+      <c r="BT11" s="25"/>
+      <c r="BU11" s="25"/>
+      <c r="BV11" s="25"/>
+      <c r="BW11" s="25"/>
+      <c r="BX11" s="25"/>
+      <c r="BY11" s="25"/>
+      <c r="BZ11" s="25"/>
+      <c r="CA11" s="25"/>
+      <c r="CB11" s="25"/>
+      <c r="CC11" s="25"/>
+      <c r="CD11" s="25"/>
+      <c r="CE11" s="25"/>
+      <c r="CF11" s="25"/>
+      <c r="CG11" s="25"/>
+      <c r="CH11" s="25"/>
+      <c r="CI11" s="25"/>
+      <c r="CJ11" s="25"/>
+      <c r="CK11" s="25"/>
+      <c r="CL11" s="25"/>
+      <c r="CM11" s="25"/>
+      <c r="CN11" s="25"/>
+      <c r="CO11" s="25"/>
+      <c r="CP11" s="25"/>
+      <c r="CQ11" s="25"/>
+      <c r="CR11" s="25"/>
+      <c r="CS11" s="25"/>
+      <c r="CT11" s="25"/>
+      <c r="CU11" s="25"/>
+      <c r="CV11" s="25"/>
+      <c r="CW11" s="25"/>
+      <c r="CX11" s="25"/>
+      <c r="CY11" s="25"/>
+      <c r="CZ11" s="25"/>
+    </row>
+    <row r="12" spans="4:114" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D12" s="14"/>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
@@ -4044,15 +4800,99 @@
       <c r="U12" s="4"/>
       <c r="V12" s="4"/>
       <c r="W12" s="4"/>
-      <c r="X12" s="4"/>
+      <c r="X12" s="32"/>
       <c r="Y12" s="4"/>
       <c r="Z12" s="4"/>
       <c r="AA12" s="4"/>
       <c r="AB12" s="4"/>
       <c r="AC12" s="4"/>
-      <c r="AD12" s="17"/>
-    </row>
-    <row r="13" spans="4:30" x14ac:dyDescent="0.25">
+      <c r="AD12" s="41"/>
+      <c r="AE12" s="45"/>
+      <c r="AF12" s="45"/>
+      <c r="AG12" s="45"/>
+      <c r="AH12" s="45"/>
+      <c r="AI12" s="45"/>
+      <c r="AJ12" s="45"/>
+      <c r="AK12" s="45"/>
+      <c r="AL12" s="45"/>
+      <c r="AM12" s="45"/>
+      <c r="AN12" s="45"/>
+      <c r="AO12" s="45"/>
+      <c r="AP12" s="45"/>
+      <c r="AQ12" s="45"/>
+      <c r="AR12" s="45"/>
+      <c r="AS12" s="45"/>
+      <c r="AT12" s="45"/>
+      <c r="AU12" s="45"/>
+      <c r="AV12" s="45"/>
+      <c r="AW12" s="45"/>
+      <c r="AX12" s="45"/>
+      <c r="AY12" s="45"/>
+      <c r="AZ12" s="45"/>
+      <c r="BA12" s="45"/>
+      <c r="BB12" s="45"/>
+      <c r="BC12" s="45"/>
+      <c r="BD12" s="45"/>
+      <c r="BE12" s="45"/>
+      <c r="BF12" s="45"/>
+      <c r="BG12" s="45"/>
+      <c r="BH12" s="45"/>
+      <c r="BI12" s="45"/>
+      <c r="BJ12" s="45"/>
+      <c r="BK12" s="45"/>
+      <c r="BL12" s="45"/>
+      <c r="BM12" s="45"/>
+      <c r="BN12" s="46"/>
+      <c r="BO12" s="25"/>
+      <c r="BP12" s="25"/>
+      <c r="BQ12" s="25"/>
+      <c r="BR12" s="25"/>
+      <c r="BS12" s="25"/>
+      <c r="BT12" s="25"/>
+      <c r="BU12" s="25"/>
+      <c r="BV12" s="25"/>
+      <c r="BW12" s="25"/>
+      <c r="BX12" s="25"/>
+      <c r="BY12" s="25"/>
+      <c r="BZ12" s="25"/>
+      <c r="CA12" s="25"/>
+      <c r="CB12" s="25"/>
+      <c r="CC12" s="25"/>
+      <c r="CD12" s="25"/>
+      <c r="CE12" s="25"/>
+      <c r="CF12" s="25"/>
+      <c r="CG12" s="25"/>
+      <c r="CH12" s="25"/>
+      <c r="CI12" s="25"/>
+      <c r="CJ12" s="25"/>
+      <c r="CK12" s="25"/>
+      <c r="CL12" s="25"/>
+      <c r="CM12" s="25"/>
+      <c r="CN12" s="25"/>
+      <c r="CO12" s="25"/>
+      <c r="CP12" s="25"/>
+      <c r="CQ12" s="25"/>
+      <c r="CR12" s="25"/>
+      <c r="CS12" s="25"/>
+      <c r="CT12" s="25"/>
+      <c r="CU12" s="25"/>
+      <c r="CV12" s="25"/>
+      <c r="CW12" s="25"/>
+      <c r="CX12" s="25"/>
+      <c r="CY12" s="25"/>
+      <c r="CZ12" s="25"/>
+      <c r="DA12" s="30"/>
+      <c r="DB12" s="30"/>
+      <c r="DC12" s="30"/>
+      <c r="DD12" s="30"/>
+      <c r="DE12" s="30"/>
+      <c r="DF12" s="30"/>
+      <c r="DG12" s="30"/>
+      <c r="DH12" s="30"/>
+      <c r="DI12" s="30"/>
+      <c r="DJ12" s="30"/>
+    </row>
+    <row r="13" spans="4:114" x14ac:dyDescent="0.25">
       <c r="D13" s="5"/>
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
@@ -4078,803 +4918,541 @@
       <c r="AA13" s="6"/>
       <c r="AB13" s="6"/>
       <c r="AC13" s="6"/>
-      <c r="AD13" s="7"/>
-    </row>
-    <row r="14" spans="4:30" x14ac:dyDescent="0.25">
+      <c r="AD13" s="6"/>
+      <c r="AH13" s="26"/>
+      <c r="BN13" s="28"/>
+    </row>
+    <row r="14" spans="4:114" x14ac:dyDescent="0.25">
       <c r="D14" s="8"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="19"/>
-      <c r="I14" s="19"/>
-      <c r="J14" s="19"/>
-      <c r="K14" s="19"/>
-      <c r="L14" s="19"/>
-      <c r="M14" s="19"/>
-      <c r="N14" s="19"/>
-      <c r="O14" s="19"/>
-      <c r="P14" s="19"/>
-      <c r="Q14" s="19"/>
-      <c r="R14" s="19"/>
-      <c r="S14" s="19"/>
-      <c r="T14" s="19"/>
-      <c r="U14" s="19"/>
+      <c r="E14" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14" s="24"/>
+      <c r="G14" s="24"/>
+      <c r="H14" s="24"/>
+      <c r="I14" s="24"/>
       <c r="V14" s="9"/>
-      <c r="W14" s="19"/>
-      <c r="AD14" s="9"/>
-    </row>
-    <row r="15" spans="4:30" x14ac:dyDescent="0.25">
+      <c r="AD14" s="25"/>
+      <c r="AH14" s="28"/>
+      <c r="BN14" s="28"/>
+    </row>
+    <row r="15" spans="4:114" x14ac:dyDescent="0.25">
       <c r="D15" s="8"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="19"/>
-      <c r="I15" s="19"/>
-      <c r="J15" s="19"/>
-      <c r="K15" s="19"/>
-      <c r="L15" s="19"/>
-      <c r="M15" s="19"/>
-      <c r="N15" s="19"/>
-      <c r="O15" s="19"/>
-      <c r="P15" s="19"/>
-      <c r="Q15" s="19"/>
-      <c r="R15" s="19"/>
-      <c r="S15" s="19"/>
-      <c r="T15" s="19"/>
-      <c r="U15" s="19"/>
-      <c r="V15" s="9"/>
-      <c r="W15" s="19"/>
-      <c r="AD15" s="9"/>
-    </row>
-    <row r="16" spans="4:30" x14ac:dyDescent="0.25">
+      <c r="E15" s="24"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="24"/>
+      <c r="H15" s="24"/>
+      <c r="I15" s="24"/>
+      <c r="V15" s="28"/>
+      <c r="W15" s="25"/>
+      <c r="X15" s="25"/>
+      <c r="Y15" s="25"/>
+      <c r="Z15" s="25"/>
+      <c r="AA15" s="25"/>
+      <c r="AB15" s="25"/>
+      <c r="AC15" s="25"/>
+      <c r="AD15" s="25"/>
+      <c r="AE15" s="25"/>
+      <c r="AH15" s="28"/>
+      <c r="BN15" s="28"/>
+    </row>
+    <row r="16" spans="4:114" x14ac:dyDescent="0.25">
       <c r="D16" s="8"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="19"/>
-      <c r="I16" s="19"/>
-      <c r="J16" s="19"/>
-      <c r="K16" s="19"/>
-      <c r="L16" s="19"/>
-      <c r="M16" s="19"/>
-      <c r="N16" s="19"/>
-      <c r="O16" s="19"/>
-      <c r="P16" s="19"/>
-      <c r="Q16" s="19"/>
-      <c r="R16" s="19"/>
-      <c r="S16" s="19"/>
-      <c r="T16" s="19"/>
-      <c r="U16" s="19"/>
-      <c r="V16" s="9"/>
-      <c r="W16" s="19"/>
-      <c r="AD16" s="9"/>
-    </row>
-    <row r="17" spans="4:30" x14ac:dyDescent="0.25">
+      <c r="V16" s="28"/>
+      <c r="W16" s="25"/>
+      <c r="X16" s="25"/>
+      <c r="Y16" s="25"/>
+      <c r="Z16" s="25"/>
+      <c r="AA16" s="25"/>
+      <c r="AB16" s="25"/>
+      <c r="AC16" s="25"/>
+      <c r="AD16" s="25"/>
+      <c r="AE16" s="25"/>
+      <c r="AH16" s="28"/>
+      <c r="BN16" s="28"/>
+    </row>
+    <row r="17" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D17" s="8"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="19"/>
-      <c r="I17" s="19"/>
-      <c r="J17" s="19"/>
-      <c r="K17" s="19"/>
-      <c r="L17" s="19"/>
-      <c r="M17" s="19"/>
-      <c r="N17" s="19"/>
-      <c r="O17" s="19"/>
-      <c r="P17" s="19"/>
-      <c r="Q17" s="19"/>
-      <c r="R17" s="19"/>
-      <c r="S17" s="19"/>
-      <c r="T17" s="19"/>
-      <c r="U17" s="19"/>
-      <c r="V17" s="9"/>
-      <c r="W17" s="19"/>
-      <c r="AD17" s="9"/>
-    </row>
-    <row r="18" spans="4:30" x14ac:dyDescent="0.25">
+      <c r="V17" s="28"/>
+      <c r="W17" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="X17" s="22"/>
+      <c r="Y17" s="22"/>
+      <c r="Z17" s="22"/>
+      <c r="AA17" s="22"/>
+      <c r="AB17" s="22"/>
+      <c r="AC17" s="22"/>
+      <c r="AD17" s="22"/>
+      <c r="AE17" s="25"/>
+      <c r="AH17" s="28"/>
+      <c r="BN17" s="28"/>
+    </row>
+    <row r="18" spans="4:66" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D18" s="8"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="19"/>
-      <c r="I18" s="19"/>
-      <c r="J18" s="19"/>
-      <c r="K18" s="19"/>
-      <c r="L18" s="19"/>
-      <c r="M18" s="19"/>
-      <c r="N18" s="19"/>
-      <c r="O18" s="19"/>
-      <c r="P18" s="19"/>
-      <c r="Q18" s="19"/>
-      <c r="R18" s="19"/>
-      <c r="S18" s="19"/>
-      <c r="T18" s="19"/>
-      <c r="U18" s="19"/>
-      <c r="V18" s="9"/>
-      <c r="W18" t="s">
-        <v>4</v>
+      <c r="V18" s="28"/>
+      <c r="W18" s="22"/>
+      <c r="X18" s="22"/>
+      <c r="Y18" s="22"/>
+      <c r="Z18" s="22"/>
+      <c r="AA18" s="22"/>
+      <c r="AB18" s="22"/>
+      <c r="AC18" s="22"/>
+      <c r="AD18" s="22"/>
+      <c r="AE18" s="25"/>
+      <c r="AH18" s="28"/>
+      <c r="BN18" s="28"/>
+    </row>
+    <row r="19" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="D19" s="8"/>
+      <c r="V19" s="28"/>
+      <c r="W19" s="25"/>
+      <c r="X19" s="25"/>
+      <c r="Y19" s="25"/>
+      <c r="Z19" s="25"/>
+      <c r="AA19" s="25"/>
+      <c r="AB19" s="25"/>
+      <c r="AC19" s="25"/>
+      <c r="AD19" s="25"/>
+      <c r="AE19" s="25"/>
+      <c r="AH19" s="28"/>
+      <c r="BN19" s="28"/>
+    </row>
+    <row r="20" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="D20" s="8"/>
+      <c r="V20" s="28"/>
+      <c r="W20" s="23" t="s">
+        <v>27</v>
       </c>
-      <c r="AD18" s="9"/>
-    </row>
-    <row r="19" spans="4:30" x14ac:dyDescent="0.25">
-      <c r="D19" s="8"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="19"/>
-      <c r="H19" s="19"/>
-      <c r="I19" s="19"/>
-      <c r="J19" s="19"/>
-      <c r="K19" s="19"/>
-      <c r="L19" s="19"/>
-      <c r="M19" s="19"/>
-      <c r="N19" s="19"/>
-      <c r="O19" s="19"/>
-      <c r="P19" s="19"/>
-      <c r="Q19" s="19"/>
-      <c r="R19" s="19"/>
-      <c r="S19" s="19"/>
-      <c r="T19" s="19"/>
-      <c r="U19" s="19"/>
-      <c r="V19" s="9"/>
-      <c r="W19" t="s">
-        <v>4</v>
+      <c r="X20" s="23"/>
+      <c r="Y20" s="23"/>
+      <c r="Z20" s="23"/>
+      <c r="AA20" s="23"/>
+      <c r="AB20" s="23"/>
+      <c r="AC20" s="23"/>
+      <c r="AD20" s="23"/>
+      <c r="AE20" s="25"/>
+      <c r="AH20" s="28"/>
+      <c r="BN20" s="28"/>
+    </row>
+    <row r="21" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="D21" s="8"/>
+      <c r="V21" s="28"/>
+      <c r="W21" s="23"/>
+      <c r="X21" s="23"/>
+      <c r="Y21" s="23"/>
+      <c r="Z21" s="23"/>
+      <c r="AA21" s="23"/>
+      <c r="AB21" s="23"/>
+      <c r="AC21" s="23"/>
+      <c r="AD21" s="23"/>
+      <c r="AE21" s="25"/>
+      <c r="AH21" s="28"/>
+      <c r="BN21" s="28"/>
+    </row>
+    <row r="22" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="D22" s="8"/>
+      <c r="V22" s="28"/>
+      <c r="W22" s="25"/>
+      <c r="X22" s="25"/>
+      <c r="Y22" s="25"/>
+      <c r="Z22" s="25"/>
+      <c r="AA22" s="25"/>
+      <c r="AB22" s="25"/>
+      <c r="AC22" s="25"/>
+      <c r="AD22" s="25"/>
+      <c r="AE22" s="25"/>
+      <c r="AH22" s="28"/>
+      <c r="BN22" s="28"/>
+    </row>
+    <row r="23" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="D23" s="8"/>
+      <c r="V23" s="28"/>
+      <c r="W23" s="22" t="s">
+        <v>29</v>
       </c>
-      <c r="AD19" s="9"/>
-    </row>
-    <row r="20" spans="4:30" x14ac:dyDescent="0.25">
-      <c r="D20" s="8"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="19"/>
-      <c r="G20" s="19"/>
-      <c r="H20" s="19"/>
-      <c r="I20" s="19"/>
-      <c r="J20" s="19"/>
-      <c r="K20" s="19"/>
-      <c r="L20" s="19"/>
-      <c r="M20" s="19"/>
-      <c r="N20" s="19"/>
-      <c r="O20" s="19"/>
-      <c r="P20" s="19"/>
-      <c r="Q20" s="19"/>
-      <c r="R20" s="19"/>
-      <c r="S20" s="19"/>
-      <c r="T20" s="19"/>
-      <c r="U20" s="19"/>
-      <c r="V20" s="9"/>
-      <c r="W20" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD20" s="9"/>
-    </row>
-    <row r="21" spans="4:30" x14ac:dyDescent="0.25">
-      <c r="D21" s="8"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="19"/>
-      <c r="H21" s="19"/>
-      <c r="I21" s="19"/>
-      <c r="J21" s="19"/>
-      <c r="K21" s="19"/>
-      <c r="L21" s="19"/>
-      <c r="M21" s="19"/>
-      <c r="N21" s="19"/>
-      <c r="O21" s="19"/>
-      <c r="P21" s="19"/>
-      <c r="Q21" s="19"/>
-      <c r="R21" s="19"/>
-      <c r="S21" s="19"/>
-      <c r="T21" s="19"/>
-      <c r="U21" s="19"/>
-      <c r="V21" s="9"/>
-      <c r="AD21" s="9"/>
-    </row>
-    <row r="22" spans="4:30" x14ac:dyDescent="0.25">
-      <c r="D22" s="8"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="19"/>
-      <c r="G22" s="19"/>
-      <c r="H22" s="19"/>
-      <c r="I22" s="19"/>
-      <c r="J22" s="19"/>
-      <c r="K22" s="19"/>
-      <c r="L22" s="19"/>
-      <c r="M22" s="19"/>
-      <c r="N22" s="19"/>
-      <c r="O22" s="19"/>
-      <c r="P22" s="19"/>
-      <c r="Q22" s="19"/>
-      <c r="R22" s="19"/>
-      <c r="S22" s="19"/>
-      <c r="T22" s="19"/>
-      <c r="U22" s="19"/>
-      <c r="V22" s="9"/>
-      <c r="W22" t="s">
-        <v>6</v>
-      </c>
-      <c r="AD22" s="9"/>
-    </row>
-    <row r="23" spans="4:30" x14ac:dyDescent="0.25">
-      <c r="D23" s="8"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="19"/>
-      <c r="G23" s="19"/>
-      <c r="H23" s="19"/>
-      <c r="I23" s="19"/>
-      <c r="J23" s="19"/>
-      <c r="K23" s="19"/>
-      <c r="L23" s="19"/>
-      <c r="M23" s="19"/>
-      <c r="N23" s="19"/>
-      <c r="O23" s="19"/>
-      <c r="P23" s="19"/>
-      <c r="Q23" s="19"/>
-      <c r="R23" s="19"/>
-      <c r="S23" s="19"/>
-      <c r="T23" s="19"/>
-      <c r="U23" s="19"/>
-      <c r="V23" s="9"/>
-      <c r="AD23" s="9"/>
-    </row>
-    <row r="24" spans="4:30" x14ac:dyDescent="0.25">
+      <c r="X23" s="22"/>
+      <c r="Y23" s="22"/>
+      <c r="Z23" s="22"/>
+      <c r="AA23" s="22"/>
+      <c r="AB23" s="22"/>
+      <c r="AC23" s="22"/>
+      <c r="AD23" s="22"/>
+      <c r="AE23" s="25"/>
+      <c r="AH23" s="28"/>
+      <c r="BN23" s="28"/>
+    </row>
+    <row r="24" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D24" s="8"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="19"/>
-      <c r="H24" s="19"/>
-      <c r="I24" s="19"/>
-      <c r="J24" s="19"/>
-      <c r="K24" s="19"/>
-      <c r="L24" s="19"/>
-      <c r="M24" s="19"/>
-      <c r="N24" s="19"/>
-      <c r="O24" s="19"/>
-      <c r="P24" s="19"/>
-      <c r="Q24" s="19"/>
-      <c r="R24" s="19"/>
-      <c r="S24" s="19"/>
-      <c r="T24" s="19"/>
-      <c r="U24" s="19"/>
-      <c r="V24" s="9"/>
-      <c r="W24" t="s">
+      <c r="V24" s="28"/>
+      <c r="W24" s="22"/>
+      <c r="X24" s="22"/>
+      <c r="Y24" s="22"/>
+      <c r="Z24" s="22"/>
+      <c r="AA24" s="22"/>
+      <c r="AB24" s="22"/>
+      <c r="AC24" s="22"/>
+      <c r="AD24" s="22"/>
+      <c r="AE24" s="25"/>
+      <c r="AH24" s="28"/>
+      <c r="BN24" s="28"/>
+    </row>
+    <row r="25" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="D25" s="8"/>
+      <c r="V25" s="28"/>
+      <c r="W25" s="25"/>
+      <c r="X25" s="25"/>
+      <c r="Y25" s="25"/>
+      <c r="Z25" s="25"/>
+      <c r="AA25" s="25"/>
+      <c r="AB25" s="25"/>
+      <c r="AC25" s="25"/>
+      <c r="AD25" s="25"/>
+      <c r="AE25" s="25"/>
+      <c r="AH25" s="28"/>
+      <c r="BN25" s="28"/>
+    </row>
+    <row r="26" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="D26" s="8"/>
+      <c r="V26" s="28"/>
+      <c r="W26" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="AD24" s="9"/>
-    </row>
-    <row r="25" spans="4:30" x14ac:dyDescent="0.25">
-      <c r="D25" s="8"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="19"/>
-      <c r="I25" s="19"/>
-      <c r="J25" s="19"/>
-      <c r="K25" s="19"/>
-      <c r="L25" s="19"/>
-      <c r="M25" s="19"/>
-      <c r="N25" s="19"/>
-      <c r="O25" s="19"/>
-      <c r="P25" s="19"/>
-      <c r="Q25" s="19"/>
-      <c r="R25" s="19"/>
-      <c r="S25" s="19"/>
-      <c r="T25" s="19"/>
-      <c r="U25" s="19"/>
-      <c r="V25" s="9"/>
-      <c r="AD25" s="9"/>
-    </row>
-    <row r="26" spans="4:30" x14ac:dyDescent="0.25">
-      <c r="D26" s="8"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
-      <c r="G26" s="19"/>
-      <c r="H26" s="19"/>
-      <c r="I26" s="19"/>
-      <c r="J26" s="19"/>
-      <c r="K26" s="19"/>
-      <c r="L26" s="19"/>
-      <c r="M26" s="19"/>
-      <c r="N26" s="19"/>
-      <c r="O26" s="19"/>
-      <c r="P26" s="19"/>
-      <c r="Q26" s="19"/>
-      <c r="R26" s="19"/>
-      <c r="S26" s="19"/>
-      <c r="T26" s="19"/>
-      <c r="U26" s="19"/>
-      <c r="V26" s="9"/>
-      <c r="W26" t="s">
+      <c r="X26" s="23"/>
+      <c r="Y26" s="23"/>
+      <c r="Z26" s="23"/>
+      <c r="AA26" s="23"/>
+      <c r="AB26" s="23"/>
+      <c r="AC26" s="23"/>
+      <c r="AD26" s="23"/>
+      <c r="AE26" s="25"/>
+      <c r="AH26" s="28"/>
+      <c r="BN26" s="28"/>
+    </row>
+    <row r="27" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="D27" s="8"/>
+      <c r="V27" s="28"/>
+      <c r="W27" s="23"/>
+      <c r="X27" s="23"/>
+      <c r="Y27" s="23"/>
+      <c r="Z27" s="23"/>
+      <c r="AA27" s="23"/>
+      <c r="AB27" s="23"/>
+      <c r="AC27" s="23"/>
+      <c r="AD27" s="23"/>
+      <c r="AE27" s="25"/>
+      <c r="AH27" s="28"/>
+      <c r="BN27" s="28"/>
+    </row>
+    <row r="28" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="D28" s="8"/>
+      <c r="V28" s="28"/>
+      <c r="W28" s="25"/>
+      <c r="X28" s="25"/>
+      <c r="Y28" s="25"/>
+      <c r="Z28" s="25"/>
+      <c r="AA28" s="25"/>
+      <c r="AB28" s="25"/>
+      <c r="AC28" s="25"/>
+      <c r="AD28" s="25"/>
+      <c r="AE28" s="25"/>
+      <c r="AH28" s="28"/>
+      <c r="BN28" s="28"/>
+    </row>
+    <row r="29" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="D29" s="8"/>
+      <c r="V29" s="28"/>
+      <c r="W29" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="AD26" s="9"/>
-    </row>
-    <row r="27" spans="4:30" x14ac:dyDescent="0.25">
-      <c r="D27" s="8"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
-      <c r="G27" s="19"/>
-      <c r="H27" s="19"/>
-      <c r="I27" s="19"/>
-      <c r="J27" s="19"/>
-      <c r="K27" s="19"/>
-      <c r="L27" s="19"/>
-      <c r="M27" s="19"/>
-      <c r="N27" s="19"/>
-      <c r="O27" s="19"/>
-      <c r="P27" s="19"/>
-      <c r="Q27" s="19"/>
-      <c r="R27" s="19"/>
-      <c r="S27" s="19"/>
-      <c r="T27" s="19"/>
-      <c r="U27" s="19"/>
-      <c r="V27" s="9"/>
-      <c r="AD27" s="9"/>
-    </row>
-    <row r="28" spans="4:30" x14ac:dyDescent="0.25">
-      <c r="D28" s="8"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="19"/>
-      <c r="H28" s="19"/>
-      <c r="I28" s="19"/>
-      <c r="J28" s="19"/>
-      <c r="K28" s="19"/>
-      <c r="L28" s="19"/>
-      <c r="M28" s="19"/>
-      <c r="N28" s="19"/>
-      <c r="O28" s="19"/>
-      <c r="P28" s="19"/>
-      <c r="Q28" s="19"/>
-      <c r="R28" s="19"/>
-      <c r="S28" s="19"/>
-      <c r="T28" s="19"/>
-      <c r="U28" s="19"/>
-      <c r="V28" s="9"/>
-      <c r="W28" t="s">
-        <v>9</v>
+      <c r="X29" s="23"/>
+      <c r="Y29" s="23"/>
+      <c r="Z29" s="23"/>
+      <c r="AA29" s="23"/>
+      <c r="AB29" s="23"/>
+      <c r="AC29" s="23"/>
+      <c r="AD29" s="23"/>
+      <c r="AE29" s="25"/>
+      <c r="AH29" s="28"/>
+      <c r="BN29" s="28"/>
+    </row>
+    <row r="30" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="D30" s="8"/>
+      <c r="V30" s="28"/>
+      <c r="W30" s="23"/>
+      <c r="X30" s="23"/>
+      <c r="Y30" s="23"/>
+      <c r="Z30" s="23"/>
+      <c r="AA30" s="23"/>
+      <c r="AB30" s="23"/>
+      <c r="AC30" s="23"/>
+      <c r="AD30" s="23"/>
+      <c r="AE30" s="25"/>
+      <c r="AH30" s="28"/>
+      <c r="BN30" s="28"/>
+    </row>
+    <row r="31" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="D31" s="8"/>
+      <c r="V31" s="28"/>
+      <c r="W31" s="25"/>
+      <c r="X31" s="25"/>
+      <c r="Y31" s="25"/>
+      <c r="Z31" s="25"/>
+      <c r="AA31" s="25"/>
+      <c r="AB31" s="25"/>
+      <c r="AC31" s="25"/>
+      <c r="AD31" s="25"/>
+      <c r="AE31" s="25"/>
+      <c r="AH31" s="28"/>
+      <c r="BN31" s="28"/>
+    </row>
+    <row r="32" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="D32" s="8"/>
+      <c r="V32" s="28"/>
+      <c r="W32" s="38" t="s">
+        <v>30</v>
       </c>
-      <c r="AD28" s="9"/>
-    </row>
-    <row r="29" spans="4:30" x14ac:dyDescent="0.25">
-      <c r="D29" s="8"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
-      <c r="G29" s="19"/>
-      <c r="H29" s="19"/>
-      <c r="I29" s="19"/>
-      <c r="J29" s="19"/>
-      <c r="K29" s="19"/>
-      <c r="L29" s="19"/>
-      <c r="M29" s="19"/>
-      <c r="N29" s="19"/>
-      <c r="O29" s="19"/>
-      <c r="P29" s="19"/>
-      <c r="Q29" s="19"/>
-      <c r="R29" s="19"/>
-      <c r="S29" s="19"/>
-      <c r="T29" s="19"/>
-      <c r="U29" s="19"/>
-      <c r="V29" s="9"/>
-      <c r="AD29" s="9"/>
-    </row>
-    <row r="30" spans="4:30" x14ac:dyDescent="0.25">
-      <c r="D30" s="8"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="19"/>
-      <c r="I30" s="19"/>
-      <c r="J30" s="19"/>
-      <c r="K30" s="19"/>
-      <c r="L30" s="19"/>
-      <c r="M30" s="19"/>
-      <c r="N30" s="19"/>
-      <c r="O30" s="19"/>
-      <c r="P30" s="19"/>
-      <c r="Q30" s="19"/>
-      <c r="R30" s="19"/>
-      <c r="S30" s="19"/>
-      <c r="T30" s="19"/>
-      <c r="U30" s="19"/>
-      <c r="V30" s="9"/>
-      <c r="W30" t="s">
-        <v>10</v>
+      <c r="X32" s="38"/>
+      <c r="Y32" s="38"/>
+      <c r="Z32" s="38"/>
+      <c r="AA32" s="38"/>
+      <c r="AB32" s="38"/>
+      <c r="AC32" s="38"/>
+      <c r="AD32" s="38"/>
+      <c r="AE32" s="25"/>
+      <c r="AH32" s="28"/>
+      <c r="BN32" s="28"/>
+    </row>
+    <row r="33" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="D33" s="8"/>
+      <c r="V33" s="28"/>
+      <c r="W33" s="38"/>
+      <c r="X33" s="38"/>
+      <c r="Y33" s="38"/>
+      <c r="Z33" s="38"/>
+      <c r="AA33" s="38"/>
+      <c r="AB33" s="38"/>
+      <c r="AC33" s="38"/>
+      <c r="AD33" s="38"/>
+      <c r="AE33" s="25"/>
+      <c r="AH33" s="28"/>
+      <c r="BN33" s="28"/>
+    </row>
+    <row r="34" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="D34" s="8"/>
+      <c r="V34" s="28"/>
+      <c r="W34" s="25"/>
+      <c r="X34" s="25"/>
+      <c r="Y34" s="25"/>
+      <c r="Z34" s="25"/>
+      <c r="AA34" s="25"/>
+      <c r="AB34" s="25"/>
+      <c r="AC34" s="25"/>
+      <c r="AD34" s="25"/>
+      <c r="AE34" s="25"/>
+      <c r="AH34" s="28"/>
+      <c r="BN34" s="28"/>
+    </row>
+    <row r="35" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="D35" s="8"/>
+      <c r="V35" s="28"/>
+      <c r="W35" s="38" t="s">
+        <v>31</v>
       </c>
-      <c r="AD30" s="9"/>
-    </row>
-    <row r="31" spans="4:30" x14ac:dyDescent="0.25">
-      <c r="D31" s="8"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="19"/>
-      <c r="G31" s="19"/>
-      <c r="H31" s="19"/>
-      <c r="I31" s="19"/>
-      <c r="J31" s="19"/>
-      <c r="K31" s="19"/>
-      <c r="L31" s="19"/>
-      <c r="M31" s="19"/>
-      <c r="N31" s="19"/>
-      <c r="O31" s="19"/>
-      <c r="P31" s="19"/>
-      <c r="Q31" s="19"/>
-      <c r="R31" s="19"/>
-      <c r="S31" s="19"/>
-      <c r="T31" s="19"/>
-      <c r="U31" s="19"/>
-      <c r="V31" s="9"/>
-      <c r="AD31" s="9"/>
-    </row>
-    <row r="32" spans="4:30" x14ac:dyDescent="0.25">
-      <c r="D32" s="8"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="19"/>
-      <c r="I32" s="19"/>
-      <c r="J32" s="19"/>
-      <c r="K32" s="19"/>
-      <c r="L32" s="19"/>
-      <c r="M32" s="19"/>
-      <c r="N32" s="19"/>
-      <c r="O32" s="19"/>
-      <c r="P32" s="19"/>
-      <c r="Q32" s="19"/>
-      <c r="R32" s="19"/>
-      <c r="S32" s="19"/>
-      <c r="T32" s="19"/>
-      <c r="U32" s="19"/>
-      <c r="V32" s="9"/>
-      <c r="W32" t="s">
-        <v>13</v>
+      <c r="X35" s="38"/>
+      <c r="Y35" s="38"/>
+      <c r="Z35" s="38"/>
+      <c r="AA35" s="38"/>
+      <c r="AB35" s="38"/>
+      <c r="AC35" s="38"/>
+      <c r="AD35" s="38"/>
+      <c r="AE35" s="25"/>
+      <c r="AH35" s="28"/>
+      <c r="BN35" s="28"/>
+    </row>
+    <row r="36" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="D36" s="8"/>
+      <c r="V36" s="28"/>
+      <c r="W36" s="38"/>
+      <c r="X36" s="38"/>
+      <c r="Y36" s="38"/>
+      <c r="Z36" s="38"/>
+      <c r="AA36" s="38"/>
+      <c r="AB36" s="38"/>
+      <c r="AC36" s="38"/>
+      <c r="AD36" s="38"/>
+      <c r="AE36" s="25"/>
+      <c r="AH36" s="28"/>
+      <c r="BN36" s="28"/>
+    </row>
+    <row r="37" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="D37" s="8"/>
+      <c r="V37" s="28"/>
+      <c r="W37" s="25"/>
+      <c r="X37" s="25"/>
+      <c r="Y37" s="25"/>
+      <c r="Z37" s="25"/>
+      <c r="AA37" s="25"/>
+      <c r="AB37" s="25"/>
+      <c r="AC37" s="25"/>
+      <c r="AD37" s="25"/>
+      <c r="AE37" s="25"/>
+      <c r="AH37" s="28"/>
+      <c r="BN37" s="28"/>
+    </row>
+    <row r="38" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="D38" s="8"/>
+      <c r="V38" s="28"/>
+      <c r="W38" s="38" t="s">
+        <v>32</v>
       </c>
-      <c r="AD32" s="9"/>
-    </row>
-    <row r="33" spans="4:30" x14ac:dyDescent="0.25">
-      <c r="D33" s="8"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="19"/>
-      <c r="H33" s="19"/>
-      <c r="I33" s="19"/>
-      <c r="J33" s="19"/>
-      <c r="K33" s="19"/>
-      <c r="L33" s="19"/>
-      <c r="M33" s="19"/>
-      <c r="N33" s="19"/>
-      <c r="O33" s="19"/>
-      <c r="P33" s="19"/>
-      <c r="Q33" s="19"/>
-      <c r="R33" s="19"/>
-      <c r="S33" s="19"/>
-      <c r="T33" s="19"/>
-      <c r="U33" s="19"/>
-      <c r="V33" s="9"/>
-      <c r="W33" s="19"/>
-      <c r="AD33" s="9"/>
-    </row>
-    <row r="34" spans="4:30" x14ac:dyDescent="0.25">
-      <c r="D34" s="8"/>
-      <c r="E34" s="19"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="19"/>
-      <c r="H34" s="19"/>
-      <c r="I34" s="19"/>
-      <c r="J34" s="19"/>
-      <c r="K34" s="19"/>
-      <c r="L34" s="19"/>
-      <c r="M34" s="19"/>
-      <c r="N34" s="19"/>
-      <c r="O34" s="19"/>
-      <c r="P34" s="19"/>
-      <c r="Q34" s="19"/>
-      <c r="R34" s="19"/>
-      <c r="S34" s="19"/>
-      <c r="T34" s="19"/>
-      <c r="U34" s="19"/>
-      <c r="V34" s="9"/>
-      <c r="W34" s="19"/>
-      <c r="AD34" s="9"/>
-    </row>
-    <row r="35" spans="4:30" x14ac:dyDescent="0.25">
-      <c r="D35" s="8"/>
-      <c r="E35" s="19"/>
-      <c r="F35" s="19"/>
-      <c r="G35" s="19"/>
-      <c r="H35" s="19"/>
-      <c r="I35" s="19"/>
-      <c r="J35" s="19"/>
-      <c r="K35" s="19"/>
-      <c r="L35" s="19"/>
-      <c r="M35" s="19"/>
-      <c r="N35" s="19"/>
-      <c r="O35" s="19"/>
-      <c r="P35" s="19"/>
-      <c r="Q35" s="19"/>
-      <c r="R35" s="19"/>
-      <c r="S35" s="19"/>
-      <c r="T35" s="19"/>
-      <c r="U35" s="19"/>
-      <c r="V35" s="9"/>
-      <c r="W35" s="19"/>
-      <c r="AD35" s="9"/>
-    </row>
-    <row r="36" spans="4:30" x14ac:dyDescent="0.25">
-      <c r="D36" s="8"/>
-      <c r="E36" s="19"/>
-      <c r="F36" s="19"/>
-      <c r="G36" s="19"/>
-      <c r="H36" s="19"/>
-      <c r="I36" s="19"/>
-      <c r="J36" s="19"/>
-      <c r="K36" s="19"/>
-      <c r="L36" s="19"/>
-      <c r="M36" s="19"/>
-      <c r="N36" s="19"/>
-      <c r="O36" s="19"/>
-      <c r="P36" s="19"/>
-      <c r="Q36" s="19"/>
-      <c r="R36" s="19"/>
-      <c r="S36" s="19"/>
-      <c r="T36" s="19"/>
-      <c r="U36" s="19"/>
-      <c r="V36" s="9"/>
-      <c r="W36" s="19"/>
-      <c r="AD36" s="9"/>
-    </row>
-    <row r="37" spans="4:30" x14ac:dyDescent="0.25">
-      <c r="D37" s="8"/>
-      <c r="E37" s="19"/>
-      <c r="F37" s="19"/>
-      <c r="G37" s="19"/>
-      <c r="H37" s="19"/>
-      <c r="I37" s="19"/>
-      <c r="J37" s="19"/>
-      <c r="K37" s="19"/>
-      <c r="L37" s="19"/>
-      <c r="M37" s="19"/>
-      <c r="N37" s="19"/>
-      <c r="O37" s="19"/>
-      <c r="P37" s="19"/>
-      <c r="Q37" s="19"/>
-      <c r="R37" s="19"/>
-      <c r="S37" s="19"/>
-      <c r="T37" s="19"/>
-      <c r="U37" s="19"/>
-      <c r="V37" s="9"/>
-      <c r="W37" s="19"/>
-      <c r="AD37" s="9"/>
-    </row>
-    <row r="38" spans="4:30" x14ac:dyDescent="0.25">
-      <c r="D38" s="8"/>
-      <c r="E38" s="19"/>
-      <c r="F38" s="19"/>
-      <c r="G38" s="19"/>
-      <c r="H38" s="19"/>
-      <c r="I38" s="19"/>
-      <c r="J38" s="19"/>
-      <c r="K38" s="19"/>
-      <c r="L38" s="19"/>
-      <c r="M38" s="19"/>
-      <c r="N38" s="19"/>
-      <c r="O38" s="19"/>
-      <c r="P38" s="19"/>
-      <c r="Q38" s="19"/>
-      <c r="R38" s="19"/>
-      <c r="S38" s="19"/>
-      <c r="T38" s="19"/>
-      <c r="U38" s="19"/>
-      <c r="V38" s="9"/>
-      <c r="W38" s="19"/>
-      <c r="AD38" s="9"/>
-    </row>
-    <row r="39" spans="4:30" x14ac:dyDescent="0.25">
+      <c r="X38" s="38"/>
+      <c r="Y38" s="38"/>
+      <c r="Z38" s="38"/>
+      <c r="AA38" s="38"/>
+      <c r="AB38" s="38"/>
+      <c r="AC38" s="38"/>
+      <c r="AD38" s="38"/>
+      <c r="AE38" s="25"/>
+      <c r="AH38" s="28"/>
+      <c r="BN38" s="28"/>
+    </row>
+    <row r="39" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D39" s="8"/>
-      <c r="E39" s="19"/>
-      <c r="F39" s="19"/>
-      <c r="G39" s="19"/>
-      <c r="H39" s="19"/>
-      <c r="I39" s="19"/>
-      <c r="J39" s="19"/>
-      <c r="K39" s="19"/>
-      <c r="L39" s="19"/>
-      <c r="M39" s="19"/>
-      <c r="N39" s="19"/>
-      <c r="O39" s="19"/>
-      <c r="P39" s="19"/>
-      <c r="Q39" s="19"/>
-      <c r="R39" s="19"/>
-      <c r="S39" s="19"/>
-      <c r="T39" s="19"/>
-      <c r="U39" s="19"/>
-      <c r="V39" s="9"/>
-      <c r="W39" s="19"/>
-      <c r="AD39" s="9"/>
-    </row>
-    <row r="40" spans="4:30" x14ac:dyDescent="0.25">
+      <c r="V39" s="28"/>
+      <c r="W39" s="38"/>
+      <c r="X39" s="38"/>
+      <c r="Y39" s="38"/>
+      <c r="Z39" s="38"/>
+      <c r="AA39" s="38"/>
+      <c r="AB39" s="38"/>
+      <c r="AC39" s="38"/>
+      <c r="AD39" s="38"/>
+      <c r="AE39" s="25"/>
+      <c r="AH39" s="28"/>
+      <c r="BN39" s="28"/>
+    </row>
+    <row r="40" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D40" s="8"/>
-      <c r="E40" s="19"/>
-      <c r="F40" s="19"/>
-      <c r="G40" s="19"/>
-      <c r="H40" s="19"/>
-      <c r="I40" s="19"/>
-      <c r="J40" s="19"/>
-      <c r="K40" s="19"/>
-      <c r="L40" s="19"/>
-      <c r="M40" s="19"/>
-      <c r="N40" s="19"/>
-      <c r="O40" s="19"/>
-      <c r="P40" s="19"/>
-      <c r="Q40" s="19"/>
-      <c r="R40" s="19"/>
-      <c r="S40" s="19"/>
-      <c r="T40" s="19"/>
-      <c r="U40" s="19"/>
-      <c r="V40" s="9"/>
-      <c r="W40" s="19"/>
-      <c r="AD40" s="9"/>
-    </row>
-    <row r="41" spans="4:30" x14ac:dyDescent="0.25">
+      <c r="V40" s="28"/>
+      <c r="W40" s="25"/>
+      <c r="X40" s="25"/>
+      <c r="Y40" s="25"/>
+      <c r="Z40" s="25"/>
+      <c r="AA40" s="25"/>
+      <c r="AB40" s="25"/>
+      <c r="AC40" s="25"/>
+      <c r="AD40" s="25"/>
+      <c r="AE40" s="25"/>
+      <c r="AH40" s="28"/>
+      <c r="BN40" s="28"/>
+    </row>
+    <row r="41" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D41" s="8"/>
-      <c r="E41" s="19"/>
-      <c r="F41" s="19"/>
-      <c r="G41" s="19"/>
-      <c r="H41" s="19"/>
-      <c r="I41" s="19"/>
-      <c r="J41" s="19"/>
-      <c r="K41" s="19"/>
-      <c r="L41" s="19"/>
-      <c r="M41" s="19"/>
-      <c r="N41" s="19"/>
-      <c r="O41" s="19"/>
-      <c r="P41" s="19"/>
-      <c r="Q41" s="19"/>
-      <c r="R41" s="19"/>
-      <c r="S41" s="19"/>
-      <c r="T41" s="19"/>
-      <c r="U41" s="19"/>
-      <c r="V41" s="9"/>
-      <c r="W41" s="19"/>
-      <c r="AD41" s="9"/>
-    </row>
-    <row r="42" spans="4:30" x14ac:dyDescent="0.25">
+      <c r="V41" s="28"/>
+      <c r="W41" s="25"/>
+      <c r="X41" s="25"/>
+      <c r="Y41" s="25"/>
+      <c r="Z41" s="25"/>
+      <c r="AA41" s="25"/>
+      <c r="AB41" s="25"/>
+      <c r="AC41" s="25"/>
+      <c r="AD41" s="25"/>
+      <c r="AE41" s="25"/>
+      <c r="AH41" s="28"/>
+      <c r="BN41" s="28"/>
+    </row>
+    <row r="42" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D42" s="8"/>
-      <c r="E42" s="19"/>
-      <c r="F42" s="19"/>
-      <c r="G42" s="19"/>
-      <c r="H42" s="19"/>
-      <c r="I42" s="19"/>
-      <c r="J42" s="19"/>
-      <c r="K42" s="19"/>
-      <c r="L42" s="19"/>
-      <c r="M42" s="19"/>
-      <c r="N42" s="19"/>
-      <c r="O42" s="19"/>
-      <c r="P42" s="19"/>
-      <c r="Q42" s="19"/>
-      <c r="R42" s="19"/>
-      <c r="S42" s="19"/>
-      <c r="T42" s="19"/>
-      <c r="U42" s="19"/>
-      <c r="V42" s="9"/>
-      <c r="W42" s="19"/>
-      <c r="AD42" s="9"/>
-    </row>
-    <row r="43" spans="4:30" x14ac:dyDescent="0.25">
+      <c r="V42" s="28"/>
+      <c r="W42" s="25"/>
+      <c r="X42" s="25"/>
+      <c r="Y42" s="25"/>
+      <c r="Z42" s="25"/>
+      <c r="AA42" s="25"/>
+      <c r="AB42" s="25"/>
+      <c r="AC42" s="25"/>
+      <c r="AD42" s="25"/>
+      <c r="AE42" s="25"/>
+      <c r="AH42" s="28"/>
+      <c r="BN42" s="28"/>
+    </row>
+    <row r="43" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D43" s="8"/>
-      <c r="E43" s="19"/>
-      <c r="F43" s="19"/>
-      <c r="G43" s="19"/>
-      <c r="H43" s="19"/>
-      <c r="I43" s="19"/>
-      <c r="J43" s="19"/>
-      <c r="K43" s="19"/>
-      <c r="L43" s="19"/>
-      <c r="M43" s="19"/>
-      <c r="N43" s="19"/>
-      <c r="O43" s="19"/>
-      <c r="P43" s="19"/>
-      <c r="Q43" s="19"/>
-      <c r="R43" s="19"/>
-      <c r="S43" s="19"/>
-      <c r="T43" s="19"/>
-      <c r="U43" s="19"/>
-      <c r="V43" s="9"/>
-      <c r="W43" s="19"/>
-      <c r="AD43" s="9"/>
-    </row>
-    <row r="44" spans="4:30" x14ac:dyDescent="0.25">
+      <c r="V43" s="28"/>
+      <c r="W43" s="25"/>
+      <c r="X43" s="25"/>
+      <c r="Y43" s="25"/>
+      <c r="Z43" s="25"/>
+      <c r="AA43" s="25"/>
+      <c r="AB43" s="25"/>
+      <c r="AC43" s="25"/>
+      <c r="AD43" s="25"/>
+      <c r="AE43" s="25"/>
+      <c r="AH43" s="28"/>
+      <c r="BN43" s="28"/>
+    </row>
+    <row r="44" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D44" s="8"/>
-      <c r="E44" s="19"/>
-      <c r="F44" s="19"/>
-      <c r="G44" s="19"/>
-      <c r="H44" s="19"/>
-      <c r="I44" s="19"/>
-      <c r="J44" s="19"/>
-      <c r="K44" s="19"/>
-      <c r="L44" s="19"/>
-      <c r="M44" s="19"/>
-      <c r="N44" s="19"/>
-      <c r="O44" s="19"/>
-      <c r="P44" s="19"/>
-      <c r="Q44" s="19"/>
-      <c r="R44" s="19"/>
-      <c r="S44" s="19"/>
-      <c r="T44" s="19"/>
-      <c r="U44" s="19"/>
-      <c r="V44" s="9"/>
-      <c r="W44" s="19"/>
-      <c r="AD44" s="9"/>
-    </row>
-    <row r="45" spans="4:30" x14ac:dyDescent="0.25">
+      <c r="V44" s="28"/>
+      <c r="W44" s="25"/>
+      <c r="X44" s="25"/>
+      <c r="Y44" s="25"/>
+      <c r="Z44" s="25"/>
+      <c r="AA44" s="25"/>
+      <c r="AB44" s="25"/>
+      <c r="AC44" s="25"/>
+      <c r="AD44" s="25"/>
+      <c r="AE44" s="25"/>
+      <c r="AH44" s="28"/>
+      <c r="BN44" s="28"/>
+    </row>
+    <row r="45" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D45" s="8"/>
-      <c r="E45" s="19"/>
-      <c r="F45" s="19"/>
-      <c r="G45" s="19"/>
-      <c r="H45" s="19"/>
-      <c r="I45" s="19"/>
-      <c r="J45" s="19"/>
-      <c r="K45" s="19"/>
-      <c r="L45" s="19"/>
-      <c r="M45" s="19"/>
-      <c r="N45" s="19"/>
-      <c r="O45" s="19"/>
-      <c r="P45" s="19"/>
-      <c r="Q45" s="19"/>
-      <c r="R45" s="19"/>
-      <c r="S45" s="19"/>
-      <c r="T45" s="19"/>
-      <c r="U45" s="19"/>
-      <c r="V45" s="9"/>
-      <c r="W45" s="19"/>
-      <c r="AD45" s="9"/>
-    </row>
-    <row r="46" spans="4:30" x14ac:dyDescent="0.25">
+      <c r="V45" s="28"/>
+      <c r="W45" s="25"/>
+      <c r="X45" s="25"/>
+      <c r="Y45" s="25"/>
+      <c r="Z45" s="25"/>
+      <c r="AA45" s="25"/>
+      <c r="AB45" s="25"/>
+      <c r="AC45" s="25"/>
+      <c r="AD45" s="25"/>
+      <c r="AE45" s="25"/>
+      <c r="AH45" s="28"/>
+      <c r="BN45" s="28"/>
+    </row>
+    <row r="46" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D46" s="8"/>
-      <c r="E46" s="19"/>
-      <c r="F46" s="19"/>
-      <c r="G46" s="19"/>
-      <c r="H46" s="19"/>
-      <c r="I46" s="19"/>
-      <c r="J46" s="19"/>
-      <c r="K46" s="19"/>
-      <c r="L46" s="19"/>
-      <c r="M46" s="19"/>
-      <c r="N46" s="19"/>
-      <c r="O46" s="19"/>
-      <c r="P46" s="19"/>
-      <c r="Q46" s="19"/>
-      <c r="R46" s="19"/>
-      <c r="S46" s="19"/>
-      <c r="T46" s="19"/>
-      <c r="U46" s="19"/>
-      <c r="V46" s="9"/>
-      <c r="W46" s="19"/>
-      <c r="AD46" s="9"/>
-    </row>
-    <row r="47" spans="4:30" x14ac:dyDescent="0.25">
+      <c r="V46" s="28"/>
+      <c r="W46" s="25"/>
+      <c r="X46" s="25"/>
+      <c r="Y46" s="25"/>
+      <c r="Z46" s="25"/>
+      <c r="AA46" s="25"/>
+      <c r="AB46" s="25"/>
+      <c r="AC46" s="25"/>
+      <c r="AD46" s="25"/>
+      <c r="AE46" s="25"/>
+      <c r="AH46" s="28"/>
+      <c r="BN46" s="28"/>
+    </row>
+    <row r="47" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D47" s="8"/>
-      <c r="E47" s="19"/>
-      <c r="F47" s="19"/>
-      <c r="G47" s="19"/>
-      <c r="H47" s="19"/>
-      <c r="I47" s="19"/>
-      <c r="J47" s="19"/>
-      <c r="K47" s="19"/>
-      <c r="L47" s="19"/>
-      <c r="M47" s="19"/>
-      <c r="N47" s="19"/>
-      <c r="O47" s="19"/>
-      <c r="P47" s="19"/>
-      <c r="Q47" s="19"/>
-      <c r="R47" s="19"/>
-      <c r="S47" s="19"/>
-      <c r="T47" s="19"/>
-      <c r="U47" s="19"/>
-      <c r="V47" s="9"/>
-      <c r="W47" s="19"/>
-      <c r="AD47" s="9"/>
-    </row>
-    <row r="48" spans="4:30" x14ac:dyDescent="0.25">
+      <c r="V47" s="28"/>
+      <c r="W47" s="25"/>
+      <c r="X47" s="25"/>
+      <c r="Y47" s="25"/>
+      <c r="Z47" s="25"/>
+      <c r="AA47" s="25"/>
+      <c r="AB47" s="25"/>
+      <c r="AC47" s="25"/>
+      <c r="AD47" s="25"/>
+      <c r="AE47" s="25"/>
+      <c r="AH47" s="28"/>
+      <c r="BN47" s="28"/>
+    </row>
+    <row r="48" spans="4:66" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D48" s="10"/>
       <c r="E48" s="11"/>
       <c r="F48" s="11"/>
@@ -4893,131 +5471,3152 @@
       <c r="S48" s="11"/>
       <c r="T48" s="11"/>
       <c r="U48" s="11"/>
-      <c r="V48" s="12"/>
-      <c r="W48" s="11"/>
-      <c r="X48" s="11"/>
-      <c r="Y48" s="11"/>
-      <c r="Z48" s="11"/>
-      <c r="AA48" s="11"/>
-      <c r="AB48" s="11"/>
-      <c r="AC48" s="11"/>
-      <c r="AD48" s="12"/>
-    </row>
-    <row r="49" spans="4:30" x14ac:dyDescent="0.25">
+      <c r="V48" s="39"/>
+      <c r="W48" s="30"/>
+      <c r="X48" s="30"/>
+      <c r="Y48" s="30"/>
+      <c r="Z48" s="30"/>
+      <c r="AA48" s="30"/>
+      <c r="AB48" s="30"/>
+      <c r="AC48" s="30"/>
+      <c r="AD48" s="30"/>
+      <c r="AE48" s="30"/>
+      <c r="AF48" s="30"/>
+      <c r="AG48" s="30"/>
+      <c r="AH48" s="31"/>
+      <c r="AI48" s="30"/>
+      <c r="AJ48" s="30"/>
+      <c r="AK48" s="30"/>
+      <c r="AL48" s="30"/>
+      <c r="AM48" s="30"/>
+      <c r="AN48" s="30"/>
+      <c r="AO48" s="30"/>
+      <c r="AP48" s="30"/>
+      <c r="AQ48" s="30"/>
+      <c r="AR48" s="30"/>
+      <c r="AS48" s="30"/>
+      <c r="AT48" s="30"/>
+      <c r="AU48" s="30"/>
+      <c r="AV48" s="30"/>
+      <c r="AW48" s="30"/>
+      <c r="AX48" s="30"/>
+      <c r="AY48" s="30"/>
+      <c r="AZ48" s="30"/>
+      <c r="BA48" s="30"/>
+      <c r="BB48" s="30"/>
+      <c r="BC48" s="30"/>
+      <c r="BD48" s="30"/>
+      <c r="BE48" s="30"/>
+      <c r="BF48" s="30"/>
+      <c r="BG48" s="30"/>
+      <c r="BH48" s="30"/>
+      <c r="BI48" s="30"/>
+      <c r="BJ48" s="30"/>
+      <c r="BK48" s="30"/>
+      <c r="BL48" s="30"/>
+      <c r="BM48" s="30"/>
+      <c r="BN48" s="31"/>
+    </row>
+    <row r="49" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D49" s="8"/>
-      <c r="AD49" s="9"/>
-    </row>
-    <row r="50" spans="4:30" x14ac:dyDescent="0.25">
-      <c r="D50" s="8"/>
-      <c r="AD50" s="9"/>
-    </row>
-    <row r="51" spans="4:30" x14ac:dyDescent="0.25">
+      <c r="W49" s="25"/>
+      <c r="X49" s="25"/>
+      <c r="Y49" s="25"/>
+      <c r="Z49" s="25"/>
+      <c r="AA49" s="25"/>
+      <c r="AB49" s="25"/>
+      <c r="AC49" s="25"/>
+      <c r="AD49" s="25"/>
+      <c r="AE49" s="25"/>
+      <c r="BN49" s="28"/>
+    </row>
+    <row r="50" spans="4:66" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="D50" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="E50" s="34"/>
+      <c r="F50" s="34"/>
+      <c r="G50" s="34"/>
+      <c r="W50" s="25"/>
+      <c r="X50" s="25"/>
+      <c r="Y50" s="25"/>
+      <c r="Z50" s="25"/>
+      <c r="AA50" s="25"/>
+      <c r="AB50" s="25"/>
+      <c r="AC50" s="25"/>
+      <c r="AD50" s="25"/>
+      <c r="AE50" s="25"/>
+      <c r="BN50" s="28"/>
+    </row>
+    <row r="51" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D51" s="8"/>
-      <c r="AD51" s="9"/>
-    </row>
-    <row r="52" spans="4:30" x14ac:dyDescent="0.25">
+      <c r="W51" s="25"/>
+      <c r="X51" s="25"/>
+      <c r="Y51" s="25"/>
+      <c r="Z51" s="25"/>
+      <c r="AA51" s="25"/>
+      <c r="AB51" s="25"/>
+      <c r="AC51" s="25"/>
+      <c r="AD51" s="25"/>
+      <c r="AE51" s="25"/>
+      <c r="BN51" s="28"/>
+    </row>
+    <row r="52" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D52" s="8"/>
-      <c r="AD52" s="9"/>
-    </row>
-    <row r="53" spans="4:30" x14ac:dyDescent="0.25">
+      <c r="W52" s="25"/>
+      <c r="X52" s="25"/>
+      <c r="Y52" s="25"/>
+      <c r="Z52" s="25"/>
+      <c r="AA52" s="25"/>
+      <c r="AB52" s="25"/>
+      <c r="AC52" s="25"/>
+      <c r="AD52" s="25"/>
+      <c r="AE52" s="25"/>
+      <c r="BN52" s="28"/>
+    </row>
+    <row r="53" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D53" s="8"/>
-      <c r="AD53" s="9"/>
-    </row>
-    <row r="54" spans="4:30" x14ac:dyDescent="0.25">
+      <c r="W53" s="25"/>
+      <c r="X53" s="25"/>
+      <c r="Y53" s="25"/>
+      <c r="Z53" s="25"/>
+      <c r="AA53" s="25"/>
+      <c r="AB53" s="25"/>
+      <c r="AC53" s="25"/>
+      <c r="AD53" s="25"/>
+      <c r="AE53" s="25"/>
+      <c r="BN53" s="28"/>
+    </row>
+    <row r="54" spans="4:66" ht="18.75" x14ac:dyDescent="0.3">
       <c r="D54" s="8"/>
-      <c r="AD54" s="9"/>
-    </row>
-    <row r="55" spans="4:30" x14ac:dyDescent="0.25">
+      <c r="E54" s="35" t="s">
+        <v>14</v>
+      </c>
+      <c r="F54" s="35"/>
+      <c r="G54" s="35"/>
+      <c r="H54" s="35"/>
+      <c r="I54" s="35"/>
+      <c r="W54" s="25"/>
+      <c r="X54" s="25"/>
+      <c r="Y54" s="25"/>
+      <c r="Z54" s="25"/>
+      <c r="AA54" s="25"/>
+      <c r="AB54" s="25"/>
+      <c r="AC54" s="25"/>
+      <c r="AD54" s="25"/>
+      <c r="AE54" s="25"/>
+      <c r="BN54" s="28"/>
+    </row>
+    <row r="55" spans="4:66" ht="18.75" x14ac:dyDescent="0.3">
       <c r="D55" s="8"/>
-      <c r="AD55" s="9"/>
-    </row>
-    <row r="56" spans="4:30" x14ac:dyDescent="0.25">
+      <c r="E55" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="F55" s="36" t="s">
+        <v>16</v>
+      </c>
+      <c r="G55" s="35"/>
+      <c r="H55" s="35"/>
+      <c r="I55" s="35"/>
+      <c r="W55" s="25"/>
+      <c r="X55" s="25"/>
+      <c r="Y55" s="25"/>
+      <c r="Z55" s="25"/>
+      <c r="AA55" s="25"/>
+      <c r="AB55" s="25"/>
+      <c r="AC55" s="25"/>
+      <c r="AD55" s="25"/>
+      <c r="AE55" s="25"/>
+      <c r="BN55" s="28"/>
+    </row>
+    <row r="56" spans="4:66" ht="18.75" x14ac:dyDescent="0.3">
       <c r="D56" s="8"/>
-      <c r="AD56" s="9"/>
-    </row>
-    <row r="57" spans="4:30" x14ac:dyDescent="0.25">
+      <c r="E56" s="35"/>
+      <c r="F56" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="G56" s="35"/>
+      <c r="H56" s="35"/>
+      <c r="I56" s="35"/>
+      <c r="W56" s="25"/>
+      <c r="X56" s="25"/>
+      <c r="Y56" s="25"/>
+      <c r="Z56" s="25"/>
+      <c r="AA56" s="25"/>
+      <c r="AB56" s="25"/>
+      <c r="AC56" s="25"/>
+      <c r="AD56" s="25"/>
+      <c r="AE56" s="25"/>
+      <c r="BN56" s="28"/>
+    </row>
+    <row r="57" spans="4:66" ht="18.75" x14ac:dyDescent="0.3">
       <c r="D57" s="8"/>
-      <c r="AD57" s="9"/>
-    </row>
-    <row r="58" spans="4:30" x14ac:dyDescent="0.25">
+      <c r="E57" s="35"/>
+      <c r="F57" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="G57" s="35"/>
+      <c r="H57" s="35"/>
+      <c r="I57" s="35"/>
+      <c r="W57" s="25"/>
+      <c r="X57" s="25"/>
+      <c r="Y57" s="25"/>
+      <c r="Z57" s="25"/>
+      <c r="AA57" s="25"/>
+      <c r="AB57" s="25"/>
+      <c r="AC57" s="25"/>
+      <c r="AD57" s="25"/>
+      <c r="AE57" s="25"/>
+      <c r="BN57" s="28"/>
+    </row>
+    <row r="58" spans="4:66" ht="18.75" x14ac:dyDescent="0.3">
       <c r="D58" s="8"/>
-      <c r="AD58" s="9"/>
-    </row>
-    <row r="59" spans="4:30" x14ac:dyDescent="0.25">
-      <c r="D59" s="8"/>
-      <c r="AD59" s="9"/>
-    </row>
-    <row r="60" spans="4:30" x14ac:dyDescent="0.25">
+      <c r="E58" s="35"/>
+      <c r="F58" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="G58" s="35"/>
+      <c r="H58" s="35"/>
+      <c r="I58" s="35"/>
+      <c r="W58" s="25"/>
+      <c r="X58" s="25"/>
+      <c r="Y58" s="25"/>
+      <c r="Z58" s="25"/>
+      <c r="AA58" s="25"/>
+      <c r="AB58" s="25"/>
+      <c r="AC58" s="25"/>
+      <c r="AD58" s="25"/>
+      <c r="AE58" s="25"/>
+      <c r="BN58" s="28"/>
+    </row>
+    <row r="59" spans="4:66" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D59" s="40"/>
+      <c r="E59" s="30"/>
+      <c r="F59" s="30"/>
+      <c r="G59" s="30"/>
+      <c r="H59" s="30"/>
+      <c r="I59" s="30"/>
+      <c r="J59" s="30"/>
+      <c r="K59" s="30"/>
+      <c r="L59" s="30"/>
+      <c r="M59" s="30"/>
+      <c r="N59" s="30"/>
+      <c r="O59" s="30"/>
+      <c r="P59" s="30"/>
+      <c r="Q59" s="30"/>
+      <c r="R59" s="30"/>
+      <c r="S59" s="30"/>
+      <c r="T59" s="30"/>
+      <c r="U59" s="30"/>
+      <c r="V59" s="30"/>
+      <c r="W59" s="30"/>
+      <c r="X59" s="30"/>
+      <c r="Y59" s="30"/>
+      <c r="Z59" s="30"/>
+      <c r="AA59" s="30"/>
+      <c r="AB59" s="30"/>
+      <c r="AC59" s="30"/>
+      <c r="AD59" s="30"/>
+      <c r="AE59" s="30"/>
+      <c r="AF59" s="30"/>
+      <c r="AG59" s="30"/>
+      <c r="AH59" s="30"/>
+      <c r="AI59" s="30"/>
+      <c r="AJ59" s="30"/>
+      <c r="AK59" s="30"/>
+      <c r="AL59" s="30"/>
+      <c r="AM59" s="30"/>
+      <c r="AN59" s="30"/>
+      <c r="AO59" s="30"/>
+      <c r="AP59" s="30"/>
+      <c r="AQ59" s="30"/>
+      <c r="AR59" s="30"/>
+      <c r="AS59" s="30"/>
+      <c r="AT59" s="30"/>
+      <c r="AU59" s="30"/>
+      <c r="AV59" s="30"/>
+      <c r="AW59" s="30"/>
+      <c r="AX59" s="30"/>
+      <c r="AY59" s="30"/>
+      <c r="AZ59" s="30"/>
+      <c r="BA59" s="30"/>
+      <c r="BB59" s="30"/>
+      <c r="BC59" s="30"/>
+      <c r="BD59" s="30"/>
+      <c r="BE59" s="30"/>
+      <c r="BF59" s="30"/>
+      <c r="BG59" s="30"/>
+      <c r="BH59" s="30"/>
+      <c r="BI59" s="30"/>
+      <c r="BJ59" s="30"/>
+      <c r="BK59" s="30"/>
+      <c r="BL59" s="30"/>
+      <c r="BM59" s="30"/>
+      <c r="BN59" s="31"/>
+    </row>
+    <row r="60" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D60" s="8"/>
-      <c r="AD60" s="9"/>
-    </row>
-    <row r="61" spans="4:30" x14ac:dyDescent="0.25">
+      <c r="W60" s="25"/>
+      <c r="X60" s="25"/>
+      <c r="Y60" s="25"/>
+      <c r="Z60" s="25"/>
+      <c r="AA60" s="25"/>
+      <c r="AB60" s="25"/>
+      <c r="AC60" s="25"/>
+      <c r="AD60" s="25"/>
+      <c r="AE60" s="25"/>
+      <c r="BN60" s="28"/>
+    </row>
+    <row r="61" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D61" s="8"/>
-      <c r="AD61" s="9"/>
-    </row>
-    <row r="62" spans="4:30" x14ac:dyDescent="0.25">
-      <c r="D62" s="8"/>
-      <c r="AD62" s="9"/>
-    </row>
-    <row r="63" spans="4:30" x14ac:dyDescent="0.25">
+      <c r="W61" s="25"/>
+      <c r="X61" s="25"/>
+      <c r="Y61" s="25"/>
+      <c r="Z61" s="25"/>
+      <c r="AA61" s="25"/>
+      <c r="AB61" s="25"/>
+      <c r="AC61" s="25"/>
+      <c r="AD61" s="25"/>
+      <c r="AE61" s="25"/>
+      <c r="BN61" s="28"/>
+    </row>
+    <row r="62" spans="4:66" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="D62" s="47" t="s">
+        <v>34</v>
+      </c>
+      <c r="E62" s="47"/>
+      <c r="F62" s="47"/>
+      <c r="G62" s="47"/>
+      <c r="W62" s="25"/>
+      <c r="X62" s="25"/>
+      <c r="Y62" s="25"/>
+      <c r="Z62" s="25"/>
+      <c r="AA62" s="25"/>
+      <c r="AB62" s="25"/>
+      <c r="AC62" s="25"/>
+      <c r="AD62" s="25"/>
+      <c r="AE62" s="25"/>
+      <c r="BN62" s="28"/>
+    </row>
+    <row r="63" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D63" s="8"/>
-      <c r="AD63" s="9"/>
-    </row>
-    <row r="64" spans="4:30" x14ac:dyDescent="0.25">
+      <c r="W63" s="25"/>
+      <c r="X63" s="25"/>
+      <c r="Y63" s="25"/>
+      <c r="Z63" s="25"/>
+      <c r="AA63" s="25"/>
+      <c r="AB63" s="25"/>
+      <c r="AC63" s="25"/>
+      <c r="AD63" s="25"/>
+      <c r="AE63" s="25"/>
+      <c r="BN63" s="28"/>
+    </row>
+    <row r="64" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D64" s="8"/>
-      <c r="AD64" s="9"/>
-    </row>
-    <row r="65" spans="4:30" x14ac:dyDescent="0.25">
+      <c r="W64" s="25"/>
+      <c r="X64" s="25"/>
+      <c r="Y64" s="25"/>
+      <c r="Z64" s="25"/>
+      <c r="AA64" s="25"/>
+      <c r="AB64" s="25"/>
+      <c r="AC64" s="25"/>
+      <c r="AD64" s="25"/>
+      <c r="AE64" s="25"/>
+      <c r="BN64" s="28"/>
+    </row>
+    <row r="65" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D65" s="8"/>
-      <c r="AD65" s="9"/>
-    </row>
-    <row r="66" spans="4:30" x14ac:dyDescent="0.25">
+      <c r="W65" s="25"/>
+      <c r="X65" s="25"/>
+      <c r="Y65" s="25"/>
+      <c r="Z65" s="25"/>
+      <c r="AA65" s="25"/>
+      <c r="AB65" s="25"/>
+      <c r="AC65" s="25"/>
+      <c r="AD65" s="25"/>
+      <c r="AE65" s="25"/>
+      <c r="BN65" s="28"/>
+    </row>
+    <row r="66" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D66" s="8"/>
-      <c r="AD66" s="9"/>
-    </row>
-    <row r="67" spans="4:30" x14ac:dyDescent="0.25">
+      <c r="W66" s="25"/>
+      <c r="X66" s="25"/>
+      <c r="Y66" s="25"/>
+      <c r="Z66" s="25"/>
+      <c r="AA66" s="25"/>
+      <c r="AB66" s="25"/>
+      <c r="AC66" s="25"/>
+      <c r="AD66" s="25"/>
+      <c r="AE66" s="25"/>
+      <c r="AO66" s="25"/>
+      <c r="AP66" s="25"/>
+      <c r="AQ66" s="25"/>
+      <c r="AR66" s="25"/>
+      <c r="AS66" s="25"/>
+      <c r="BN66" s="28"/>
+    </row>
+    <row r="67" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D67" s="8"/>
-      <c r="AD67" s="9"/>
-    </row>
-    <row r="68" spans="4:30" x14ac:dyDescent="0.25">
+      <c r="F67" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>38</v>
+      </c>
+      <c r="W67" s="25"/>
+      <c r="X67" s="25"/>
+      <c r="Y67" s="25"/>
+      <c r="Z67" s="25"/>
+      <c r="AA67" s="25"/>
+      <c r="AB67" s="25"/>
+      <c r="AC67" s="25"/>
+      <c r="AD67" s="25"/>
+      <c r="AE67" s="25"/>
+      <c r="AH67" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO67" s="25"/>
+      <c r="AP67" s="25"/>
+      <c r="AQ67" s="25"/>
+      <c r="AR67" s="25"/>
+      <c r="AS67" s="25"/>
+      <c r="AV67" t="s">
+        <v>36</v>
+      </c>
+      <c r="BN67" s="28"/>
+    </row>
+    <row r="68" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D68" s="8"/>
-      <c r="AD68" s="9"/>
-    </row>
-    <row r="69" spans="4:30" x14ac:dyDescent="0.25">
+      <c r="W68" s="25"/>
+      <c r="X68" s="25"/>
+      <c r="Y68" s="25"/>
+      <c r="Z68" s="25"/>
+      <c r="AA68" s="25"/>
+      <c r="AB68" s="25"/>
+      <c r="AC68" s="25"/>
+      <c r="AD68" s="25"/>
+      <c r="AE68" s="25"/>
+      <c r="AO68" s="25"/>
+      <c r="AP68" s="25"/>
+      <c r="AQ68" s="25"/>
+      <c r="AR68" s="25"/>
+      <c r="AS68" s="25"/>
+      <c r="BG68" t="s">
+        <v>37</v>
+      </c>
+      <c r="BN68" s="28"/>
+    </row>
+    <row r="69" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D69" s="8"/>
-      <c r="AD69" s="9"/>
-    </row>
-    <row r="70" spans="4:30" x14ac:dyDescent="0.25">
-      <c r="D70" s="10"/>
-      <c r="E70" s="11"/>
-      <c r="F70" s="11"/>
-      <c r="G70" s="11"/>
-      <c r="H70" s="11"/>
-      <c r="I70" s="11"/>
-      <c r="J70" s="11"/>
-      <c r="K70" s="11"/>
-      <c r="L70" s="11"/>
-      <c r="M70" s="11"/>
-      <c r="N70" s="11"/>
-      <c r="O70" s="11"/>
-      <c r="P70" s="11"/>
-      <c r="Q70" s="11"/>
-      <c r="R70" s="11"/>
-      <c r="S70" s="11"/>
-      <c r="T70" s="11"/>
-      <c r="U70" s="11"/>
-      <c r="V70" s="11"/>
-      <c r="W70" s="11"/>
-      <c r="X70" s="11"/>
-      <c r="Y70" s="11"/>
-      <c r="Z70" s="11"/>
-      <c r="AA70" s="11"/>
-      <c r="AB70" s="11"/>
-      <c r="AC70" s="11"/>
-      <c r="AD70" s="12"/>
+      <c r="W69" s="25"/>
+      <c r="X69" s="25"/>
+      <c r="Y69" s="25"/>
+      <c r="Z69" s="25"/>
+      <c r="AA69" s="25"/>
+      <c r="AB69" s="25"/>
+      <c r="AC69" s="25"/>
+      <c r="AD69" s="25"/>
+      <c r="AE69" s="25"/>
+      <c r="AO69" s="25"/>
+      <c r="AP69" s="25"/>
+      <c r="AQ69" s="25"/>
+      <c r="AR69" s="25"/>
+      <c r="AS69" s="25"/>
+      <c r="BN69" s="28"/>
+    </row>
+    <row r="70" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="D70" s="27"/>
+      <c r="W70" s="25"/>
+      <c r="X70" s="25"/>
+      <c r="Y70" s="25"/>
+      <c r="Z70" s="25"/>
+      <c r="AA70" s="25"/>
+      <c r="AB70" s="25"/>
+      <c r="AC70" s="25"/>
+      <c r="AD70" s="25"/>
+      <c r="AE70" s="25"/>
+      <c r="AO70" s="25"/>
+      <c r="AP70" s="25"/>
+      <c r="AQ70" s="25"/>
+      <c r="AR70" s="25"/>
+      <c r="AS70" s="25"/>
+      <c r="BN70" s="28"/>
+    </row>
+    <row r="71" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="D71" s="27"/>
+      <c r="W71" s="25"/>
+      <c r="X71" s="25"/>
+      <c r="Y71" s="25"/>
+      <c r="Z71" s="25"/>
+      <c r="AA71" s="25"/>
+      <c r="AB71" s="25"/>
+      <c r="AC71" s="25"/>
+      <c r="AD71" s="25"/>
+      <c r="AE71" s="25"/>
+      <c r="AO71" s="25"/>
+      <c r="AP71" s="25"/>
+      <c r="AQ71" s="25"/>
+      <c r="AR71" s="25"/>
+      <c r="AS71" s="25"/>
+      <c r="BN71" s="28"/>
+    </row>
+    <row r="72" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="D72" s="27"/>
+      <c r="W72" s="25"/>
+      <c r="X72" s="25"/>
+      <c r="Y72" s="25"/>
+      <c r="Z72" s="25"/>
+      <c r="AA72" s="25"/>
+      <c r="AB72" s="25"/>
+      <c r="AC72" s="25"/>
+      <c r="AD72" s="25"/>
+      <c r="AE72" s="25"/>
+      <c r="AO72" s="25"/>
+      <c r="AP72" s="25"/>
+      <c r="AQ72" s="25"/>
+      <c r="AR72" s="25"/>
+      <c r="AS72" s="25"/>
+      <c r="BN72" s="28"/>
+    </row>
+    <row r="73" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="D73" s="27"/>
+      <c r="W73" s="25"/>
+      <c r="X73" s="25"/>
+      <c r="Y73" s="25"/>
+      <c r="Z73" s="25"/>
+      <c r="AA73" s="25"/>
+      <c r="AB73" s="25"/>
+      <c r="AC73" s="25"/>
+      <c r="AD73" s="25"/>
+      <c r="AE73" s="25"/>
+      <c r="AO73" s="25"/>
+      <c r="AP73" s="25"/>
+      <c r="AQ73" s="25"/>
+      <c r="AR73" s="25"/>
+      <c r="AS73" s="25"/>
+      <c r="BN73" s="28"/>
+    </row>
+    <row r="74" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="D74" s="27"/>
+      <c r="W74" s="25"/>
+      <c r="X74" s="25"/>
+      <c r="Y74" s="25"/>
+      <c r="Z74" s="25"/>
+      <c r="AA74" s="25"/>
+      <c r="AB74" s="25"/>
+      <c r="AC74" s="25"/>
+      <c r="AD74" s="25"/>
+      <c r="AE74" s="25"/>
+      <c r="AO74" s="25"/>
+      <c r="AP74" s="25"/>
+      <c r="AQ74" s="25"/>
+      <c r="AR74" s="25"/>
+      <c r="AS74" s="25"/>
+      <c r="BN74" s="28"/>
+    </row>
+    <row r="75" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="D75" s="27"/>
+      <c r="W75" s="25"/>
+      <c r="X75" s="25"/>
+      <c r="Y75" s="25"/>
+      <c r="Z75" s="25"/>
+      <c r="AA75" s="25"/>
+      <c r="AB75" s="25"/>
+      <c r="AC75" s="25"/>
+      <c r="AD75" s="25"/>
+      <c r="AE75" s="25"/>
+      <c r="AO75" s="25"/>
+      <c r="AP75" s="25"/>
+      <c r="AQ75" s="25"/>
+      <c r="AR75" s="25"/>
+      <c r="AS75" s="25"/>
+      <c r="BN75" s="28"/>
+    </row>
+    <row r="76" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="D76" s="27"/>
+      <c r="W76" s="25"/>
+      <c r="X76" s="25"/>
+      <c r="Y76" s="25"/>
+      <c r="Z76" s="25"/>
+      <c r="AA76" s="25"/>
+      <c r="AB76" s="25"/>
+      <c r="AC76" s="25"/>
+      <c r="AD76" s="25"/>
+      <c r="AE76" s="25"/>
+      <c r="AO76" s="25"/>
+      <c r="AP76" s="25"/>
+      <c r="AQ76" s="25"/>
+      <c r="AR76" s="25"/>
+      <c r="AS76" s="25"/>
+      <c r="BN76" s="28"/>
+    </row>
+    <row r="77" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="D77" s="27"/>
+      <c r="W77" s="25"/>
+      <c r="X77" s="25"/>
+      <c r="Y77" s="25"/>
+      <c r="Z77" s="25"/>
+      <c r="AA77" s="25"/>
+      <c r="AB77" s="25"/>
+      <c r="AC77" s="25"/>
+      <c r="AD77" s="25"/>
+      <c r="AE77" s="25"/>
+      <c r="AO77" s="25"/>
+      <c r="AP77" s="25"/>
+      <c r="AQ77" s="25"/>
+      <c r="AR77" s="25"/>
+      <c r="AS77" s="25"/>
+      <c r="BN77" s="28"/>
+    </row>
+    <row r="78" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="D78" s="27"/>
+      <c r="W78" s="25"/>
+      <c r="X78" s="25"/>
+      <c r="Y78" s="25"/>
+      <c r="Z78" s="25"/>
+      <c r="AA78" s="25"/>
+      <c r="AB78" s="25"/>
+      <c r="AC78" s="25"/>
+      <c r="AD78" s="25"/>
+      <c r="AE78" s="25"/>
+      <c r="AG78" s="25"/>
+      <c r="AH78" s="25"/>
+      <c r="AO78" s="25"/>
+      <c r="AP78" s="25"/>
+      <c r="AQ78" s="25"/>
+      <c r="AR78" s="25"/>
+      <c r="AS78" s="25"/>
+      <c r="BN78" s="28"/>
+    </row>
+    <row r="79" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="D79" s="27"/>
+      <c r="W79" s="25"/>
+      <c r="X79" s="25"/>
+      <c r="Y79" s="25"/>
+      <c r="Z79" s="25"/>
+      <c r="AA79" s="25"/>
+      <c r="AB79" s="25"/>
+      <c r="AC79" s="25"/>
+      <c r="AD79" s="25"/>
+      <c r="AE79" s="25"/>
+      <c r="AG79" s="25"/>
+      <c r="AH79" s="25"/>
+      <c r="AO79" s="25"/>
+      <c r="AP79" s="25"/>
+      <c r="AQ79" s="25"/>
+      <c r="AR79" s="25"/>
+      <c r="AS79" s="25"/>
+      <c r="BN79" s="28"/>
+    </row>
+    <row r="80" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="D80" s="27"/>
+      <c r="W80" s="25"/>
+      <c r="X80" s="25"/>
+      <c r="Y80" s="25"/>
+      <c r="Z80" s="25"/>
+      <c r="AA80" s="25"/>
+      <c r="AB80" s="25"/>
+      <c r="AC80" s="25"/>
+      <c r="AD80" s="25"/>
+      <c r="AE80" s="25"/>
+      <c r="AG80" s="25"/>
+      <c r="AH80" s="25"/>
+      <c r="AO80" s="25"/>
+      <c r="AP80" s="25"/>
+      <c r="AQ80" s="25"/>
+      <c r="AR80" s="25"/>
+      <c r="AS80" s="25"/>
+      <c r="BN80" s="28"/>
+    </row>
+    <row r="81" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="D81" s="27"/>
+      <c r="W81" s="25"/>
+      <c r="X81" s="25"/>
+      <c r="Y81" s="25"/>
+      <c r="Z81" s="25"/>
+      <c r="AA81" s="25"/>
+      <c r="AB81" s="25"/>
+      <c r="AC81" s="25"/>
+      <c r="AD81" s="25"/>
+      <c r="AE81" s="25"/>
+      <c r="AG81" s="25"/>
+      <c r="AH81" s="25"/>
+      <c r="AO81" s="25"/>
+      <c r="AP81" s="25"/>
+      <c r="AQ81" s="25"/>
+      <c r="AR81" s="25"/>
+      <c r="AS81" s="25"/>
+      <c r="BN81" s="28"/>
+    </row>
+    <row r="82" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="D82" s="27"/>
+      <c r="W82" s="25"/>
+      <c r="X82" s="25"/>
+      <c r="Y82" s="25"/>
+      <c r="Z82" s="25"/>
+      <c r="AA82" s="25"/>
+      <c r="AB82" s="25"/>
+      <c r="AC82" s="25"/>
+      <c r="AD82" s="25"/>
+      <c r="AE82" s="25"/>
+      <c r="AG82" s="25"/>
+      <c r="AH82" s="25"/>
+      <c r="AO82" s="25"/>
+      <c r="AP82" s="25"/>
+      <c r="AQ82" s="25"/>
+      <c r="AR82" s="25"/>
+      <c r="AS82" s="25"/>
+      <c r="BN82" s="28"/>
+    </row>
+    <row r="83" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="D83" s="27"/>
+      <c r="W83" s="25"/>
+      <c r="X83" s="25"/>
+      <c r="Y83" s="25"/>
+      <c r="Z83" s="25"/>
+      <c r="AA83" s="25"/>
+      <c r="AB83" s="25"/>
+      <c r="AC83" s="25"/>
+      <c r="AD83" s="25"/>
+      <c r="AE83" s="25"/>
+      <c r="AG83" s="25"/>
+      <c r="AH83" s="25"/>
+      <c r="AO83" s="25"/>
+      <c r="AP83" s="25"/>
+      <c r="AQ83" s="25"/>
+      <c r="AR83" s="25"/>
+      <c r="AS83" s="25"/>
+      <c r="BN83" s="28"/>
+    </row>
+    <row r="84" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="D84" s="27"/>
+      <c r="W84" s="25"/>
+      <c r="X84" s="25"/>
+      <c r="Y84" s="25"/>
+      <c r="Z84" s="25"/>
+      <c r="AA84" s="25"/>
+      <c r="AB84" s="25"/>
+      <c r="AC84" s="25"/>
+      <c r="AD84" s="25"/>
+      <c r="AE84" s="25"/>
+      <c r="AG84" s="25"/>
+      <c r="AH84" s="25"/>
+      <c r="AO84" s="25"/>
+      <c r="AP84" s="25"/>
+      <c r="AQ84" s="25"/>
+      <c r="AR84" s="25"/>
+      <c r="AS84" s="25"/>
+      <c r="BN84" s="28"/>
+    </row>
+    <row r="85" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="D85" s="27"/>
+      <c r="W85" s="25"/>
+      <c r="X85" s="25"/>
+      <c r="Y85" s="25"/>
+      <c r="Z85" s="25"/>
+      <c r="AA85" s="25"/>
+      <c r="AB85" s="25"/>
+      <c r="AC85" s="25"/>
+      <c r="AD85" s="25"/>
+      <c r="AE85" s="25"/>
+      <c r="AG85" s="25"/>
+      <c r="AH85" s="25"/>
+      <c r="AO85" s="25"/>
+      <c r="AP85" s="25"/>
+      <c r="AQ85" s="25"/>
+      <c r="AR85" s="25"/>
+      <c r="AS85" s="25"/>
+      <c r="BN85" s="28"/>
+    </row>
+    <row r="86" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="D86" s="27"/>
+      <c r="W86" s="25"/>
+      <c r="X86" s="25"/>
+      <c r="Y86" s="25"/>
+      <c r="Z86" s="25"/>
+      <c r="AA86" s="25"/>
+      <c r="AB86" s="25"/>
+      <c r="AC86" s="25"/>
+      <c r="AD86" s="25"/>
+      <c r="AE86" s="25"/>
+      <c r="AG86" s="25"/>
+      <c r="AH86" s="25"/>
+      <c r="AO86" s="25"/>
+      <c r="AP86" s="25"/>
+      <c r="AQ86" s="25"/>
+      <c r="AR86" s="25"/>
+      <c r="AS86" s="25"/>
+      <c r="BN86" s="28"/>
+    </row>
+    <row r="87" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="D87" s="27"/>
+      <c r="W87" s="25"/>
+      <c r="X87" s="25"/>
+      <c r="Y87" s="25"/>
+      <c r="Z87" s="25"/>
+      <c r="AA87" s="25"/>
+      <c r="AB87" s="25"/>
+      <c r="AC87" s="25"/>
+      <c r="AD87" s="25"/>
+      <c r="AE87" s="25"/>
+      <c r="AG87" s="25"/>
+      <c r="AH87" s="25"/>
+      <c r="AO87" s="25"/>
+      <c r="AP87" s="25"/>
+      <c r="AQ87" s="25"/>
+      <c r="AR87" s="25"/>
+      <c r="AS87" s="25"/>
+      <c r="BN87" s="28"/>
+    </row>
+    <row r="88" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="D88" s="27"/>
+      <c r="W88" s="25"/>
+      <c r="X88" s="25"/>
+      <c r="Y88" s="25"/>
+      <c r="Z88" s="25"/>
+      <c r="AA88" s="25"/>
+      <c r="AB88" s="25"/>
+      <c r="AC88" s="25"/>
+      <c r="AD88" s="25"/>
+      <c r="AE88" s="25"/>
+      <c r="AG88" s="25"/>
+      <c r="AH88" s="25"/>
+      <c r="AO88" s="25"/>
+      <c r="AP88" s="25"/>
+      <c r="AQ88" s="25"/>
+      <c r="AR88" s="25"/>
+      <c r="AS88" s="25"/>
+      <c r="BN88" s="28"/>
+    </row>
+    <row r="89" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="D89" s="27"/>
+      <c r="W89" s="25"/>
+      <c r="X89" s="25"/>
+      <c r="Y89" s="25"/>
+      <c r="Z89" s="25"/>
+      <c r="AA89" s="25"/>
+      <c r="AB89" s="25"/>
+      <c r="AC89" s="25"/>
+      <c r="AD89" s="25"/>
+      <c r="AE89" s="25"/>
+      <c r="AO89" s="25"/>
+      <c r="AP89" s="25"/>
+      <c r="AQ89" s="25"/>
+      <c r="AR89" s="25"/>
+      <c r="AS89" s="25"/>
+      <c r="BN89" s="28"/>
+    </row>
+    <row r="90" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="D90" s="27"/>
+      <c r="F90" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q90" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="W90" s="25"/>
+      <c r="X90" s="25"/>
+      <c r="Y90" s="25"/>
+      <c r="Z90" s="25"/>
+      <c r="AA90" s="25"/>
+      <c r="AB90" s="25"/>
+      <c r="AC90" s="25"/>
+      <c r="AD90" s="25"/>
+      <c r="AE90" s="25"/>
+      <c r="AO90" s="25"/>
+      <c r="AP90" s="25"/>
+      <c r="AQ90" s="25"/>
+      <c r="AR90" s="25"/>
+      <c r="AS90" s="25"/>
+      <c r="BN90" s="28"/>
+    </row>
+    <row r="91" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="D91" s="27"/>
+      <c r="W91" s="25"/>
+      <c r="X91" s="25"/>
+      <c r="Y91" s="25"/>
+      <c r="Z91" s="25"/>
+      <c r="AA91" s="25"/>
+      <c r="AB91" s="25"/>
+      <c r="AC91" s="25"/>
+      <c r="AD91" s="25"/>
+      <c r="AE91" s="25"/>
+      <c r="AO91" s="25"/>
+      <c r="AP91" s="25"/>
+      <c r="AQ91" s="25"/>
+      <c r="AR91" s="25"/>
+      <c r="AS91" s="25"/>
+      <c r="BN91" s="28"/>
+    </row>
+    <row r="92" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="D92" s="27"/>
+      <c r="W92" s="25"/>
+      <c r="X92" s="25"/>
+      <c r="Y92" s="25"/>
+      <c r="Z92" s="25"/>
+      <c r="AA92" s="25"/>
+      <c r="AB92" s="25"/>
+      <c r="AC92" s="25"/>
+      <c r="AD92" s="25"/>
+      <c r="AE92" s="25"/>
+      <c r="AH92" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO92" s="25"/>
+      <c r="AP92" s="25"/>
+      <c r="AQ92" s="25"/>
+      <c r="AR92" s="25"/>
+      <c r="AS92" s="25"/>
+      <c r="BN92" s="28"/>
+    </row>
+    <row r="93" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="D93" s="27"/>
+      <c r="AB93" s="25"/>
+      <c r="AC93" s="25"/>
+      <c r="AD93" s="25"/>
+      <c r="AE93" s="25"/>
+      <c r="AO93" s="25"/>
+      <c r="AP93" s="25"/>
+      <c r="AQ93" s="25"/>
+      <c r="AR93" s="25"/>
+      <c r="AS93" s="25"/>
+      <c r="BN93" s="28"/>
+    </row>
+    <row r="94" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="D94" s="27"/>
+      <c r="AB94" s="25"/>
+      <c r="AC94" s="25"/>
+      <c r="AD94" s="25"/>
+      <c r="AE94" s="25"/>
+      <c r="AO94" s="25"/>
+      <c r="AP94" s="25"/>
+      <c r="AQ94" s="25"/>
+      <c r="AR94" s="25"/>
+      <c r="AS94" s="25"/>
+      <c r="BN94" s="28"/>
+    </row>
+    <row r="95" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="D95" s="27"/>
+      <c r="AB95" s="25"/>
+      <c r="AC95" s="25"/>
+      <c r="AD95" s="25"/>
+      <c r="AE95" s="25"/>
+      <c r="AO95" s="25"/>
+      <c r="AP95" s="25"/>
+      <c r="AQ95" s="25"/>
+      <c r="AR95" s="25"/>
+      <c r="AS95" s="25"/>
+      <c r="BN95" s="28"/>
+    </row>
+    <row r="96" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="D96" s="27"/>
+      <c r="AB96" s="25"/>
+      <c r="AC96" s="25"/>
+      <c r="AD96" s="25"/>
+      <c r="AE96" s="25"/>
+      <c r="AO96" s="25"/>
+      <c r="AP96" s="25"/>
+      <c r="AQ96" s="25"/>
+      <c r="AR96" s="25"/>
+      <c r="AS96" s="25"/>
+      <c r="BN96" s="28"/>
+    </row>
+    <row r="97" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="D97" s="27"/>
+      <c r="AB97" s="25"/>
+      <c r="AC97" s="25"/>
+      <c r="AD97" s="25"/>
+      <c r="AE97" s="25"/>
+      <c r="AO97" s="25"/>
+      <c r="AP97" s="25"/>
+      <c r="AQ97" s="25"/>
+      <c r="AR97" s="25"/>
+      <c r="AS97" s="25"/>
+      <c r="BN97" s="28"/>
+    </row>
+    <row r="98" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="D98" s="27"/>
+      <c r="E98" s="25"/>
+      <c r="F98" s="25"/>
+      <c r="G98" s="25"/>
+      <c r="H98" s="25"/>
+      <c r="I98" s="25"/>
+      <c r="J98" s="25"/>
+      <c r="K98" s="25"/>
+      <c r="AB98" s="25"/>
+      <c r="AC98" s="25"/>
+      <c r="AD98" s="25"/>
+      <c r="AE98" s="25"/>
+      <c r="AO98" s="25"/>
+      <c r="AP98" s="25"/>
+      <c r="AQ98" s="25"/>
+      <c r="AR98" s="25"/>
+      <c r="AS98" s="25"/>
+      <c r="BN98" s="28"/>
+    </row>
+    <row r="99" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="D99" s="27"/>
+      <c r="E99" s="25"/>
+      <c r="F99" s="25"/>
+      <c r="G99" s="25"/>
+      <c r="H99" s="25"/>
+      <c r="I99" s="25"/>
+      <c r="J99" s="25"/>
+      <c r="K99" s="25"/>
+      <c r="AB99" s="25"/>
+      <c r="AC99" s="25"/>
+      <c r="AD99" s="25"/>
+      <c r="AE99" s="25"/>
+      <c r="AO99" s="25"/>
+      <c r="AP99" s="25"/>
+      <c r="AQ99" s="25"/>
+      <c r="AR99" s="25"/>
+      <c r="AS99" s="25"/>
+      <c r="BN99" s="28"/>
+    </row>
+    <row r="100" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="D100" s="27"/>
+      <c r="E100" s="25"/>
+      <c r="F100" s="25"/>
+      <c r="G100" s="25"/>
+      <c r="H100" s="25"/>
+      <c r="I100" s="25"/>
+      <c r="J100" s="25"/>
+      <c r="K100" s="25"/>
+      <c r="AB100" s="25"/>
+      <c r="AC100" s="25"/>
+      <c r="AD100" s="25"/>
+      <c r="AE100" s="25"/>
+      <c r="AO100" s="25"/>
+      <c r="AP100" s="25"/>
+      <c r="AQ100" s="25"/>
+      <c r="AR100" s="25"/>
+      <c r="AS100" s="25"/>
+      <c r="BN100" s="28"/>
+    </row>
+    <row r="101" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="D101" s="27"/>
+      <c r="E101" s="25"/>
+      <c r="F101" s="25"/>
+      <c r="G101" s="25"/>
+      <c r="H101" s="25"/>
+      <c r="I101" s="25"/>
+      <c r="J101" s="25"/>
+      <c r="K101" s="25"/>
+      <c r="AB101" s="25"/>
+      <c r="AC101" s="25"/>
+      <c r="AD101" s="25"/>
+      <c r="AE101" s="25"/>
+      <c r="AO101" s="25"/>
+      <c r="AP101" s="25"/>
+      <c r="AQ101" s="25"/>
+      <c r="AR101" s="25"/>
+      <c r="AS101" s="25"/>
+      <c r="BN101" s="28"/>
+    </row>
+    <row r="102" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="D102" s="27"/>
+      <c r="E102" s="25"/>
+      <c r="F102" s="25"/>
+      <c r="G102" s="25"/>
+      <c r="H102" s="25"/>
+      <c r="I102" s="25"/>
+      <c r="J102" s="25"/>
+      <c r="K102" s="25"/>
+      <c r="AB102" s="25"/>
+      <c r="AC102" s="25"/>
+      <c r="AD102" s="25"/>
+      <c r="AE102" s="25"/>
+      <c r="AO102" s="25"/>
+      <c r="AP102" s="25"/>
+      <c r="AQ102" s="25"/>
+      <c r="AR102" s="25"/>
+      <c r="AS102" s="25"/>
+      <c r="BN102" s="28"/>
+    </row>
+    <row r="103" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="D103" s="27"/>
+      <c r="E103" s="25"/>
+      <c r="F103" s="25"/>
+      <c r="G103" s="25"/>
+      <c r="H103" s="25"/>
+      <c r="I103" s="25"/>
+      <c r="J103" s="25"/>
+      <c r="K103" s="25"/>
+      <c r="AB103" s="25"/>
+      <c r="AC103" s="25"/>
+      <c r="AD103" s="25"/>
+      <c r="AE103" s="25"/>
+      <c r="BN103" s="28"/>
+    </row>
+    <row r="104" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="D104" s="27"/>
+      <c r="E104" s="25"/>
+      <c r="F104" s="25"/>
+      <c r="G104" s="25"/>
+      <c r="H104" s="25"/>
+      <c r="I104" s="25"/>
+      <c r="J104" s="25"/>
+      <c r="K104" s="25"/>
+      <c r="AB104" s="25"/>
+      <c r="AC104" s="25"/>
+      <c r="AD104" s="25"/>
+      <c r="AE104" s="25"/>
+      <c r="AO104" s="25"/>
+      <c r="AP104" s="25"/>
+      <c r="AQ104" s="25"/>
+      <c r="AR104" s="25"/>
+      <c r="AS104" s="25"/>
+      <c r="BN104" s="28"/>
+    </row>
+    <row r="105" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="D105" s="27"/>
+      <c r="E105" s="25"/>
+      <c r="F105" s="25"/>
+      <c r="G105" s="25"/>
+      <c r="H105" s="25"/>
+      <c r="I105" s="25"/>
+      <c r="J105" s="25"/>
+      <c r="K105" s="25"/>
+      <c r="L105" s="25"/>
+      <c r="M105" s="25"/>
+      <c r="N105" s="25"/>
+      <c r="AB105" s="25"/>
+      <c r="AC105" s="25"/>
+      <c r="AD105" s="25"/>
+      <c r="AE105" s="25"/>
+      <c r="AO105" s="25"/>
+      <c r="AP105" s="25"/>
+      <c r="AQ105" s="25"/>
+      <c r="AR105" s="25"/>
+      <c r="AS105" s="25"/>
+      <c r="BN105" s="28"/>
+    </row>
+    <row r="106" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="D106" s="27"/>
+      <c r="E106" s="25"/>
+      <c r="F106" s="25"/>
+      <c r="G106" s="25"/>
+      <c r="H106" s="25"/>
+      <c r="I106" s="25"/>
+      <c r="J106" s="25"/>
+      <c r="K106" s="25"/>
+      <c r="L106" s="25"/>
+      <c r="M106" s="25"/>
+      <c r="N106" s="25"/>
+      <c r="AB106" s="25"/>
+      <c r="AC106" s="25"/>
+      <c r="AD106" s="25"/>
+      <c r="AE106" s="25"/>
+      <c r="BN106" s="28"/>
+    </row>
+    <row r="107" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="D107" s="27"/>
+      <c r="E107" s="25"/>
+      <c r="F107" s="25"/>
+      <c r="G107" s="25"/>
+      <c r="H107" s="25"/>
+      <c r="I107" s="25"/>
+      <c r="J107" s="25"/>
+      <c r="K107" s="25"/>
+      <c r="L107" s="25"/>
+      <c r="M107" s="25"/>
+      <c r="N107" s="25"/>
+      <c r="AB107" s="25"/>
+      <c r="AC107" s="25"/>
+      <c r="AD107" s="25"/>
+      <c r="AE107" s="25"/>
+      <c r="BN107" s="28"/>
+    </row>
+    <row r="108" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="D108" s="27"/>
+      <c r="E108" s="25"/>
+      <c r="F108" s="25"/>
+      <c r="G108" s="25"/>
+      <c r="H108" s="25"/>
+      <c r="I108" s="25"/>
+      <c r="J108" s="25"/>
+      <c r="K108" s="25"/>
+      <c r="L108" s="25"/>
+      <c r="M108" s="25"/>
+      <c r="N108" s="25"/>
+      <c r="AB108" s="25"/>
+      <c r="AC108" s="25"/>
+      <c r="AD108" s="25"/>
+      <c r="AE108" s="25"/>
+      <c r="BN108" s="28"/>
+    </row>
+    <row r="109" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="D109" s="27"/>
+      <c r="E109" s="25"/>
+      <c r="F109" s="25"/>
+      <c r="G109" s="25"/>
+      <c r="H109" s="25"/>
+      <c r="I109" s="25"/>
+      <c r="J109" s="25"/>
+      <c r="K109" s="25"/>
+      <c r="L109" s="25"/>
+      <c r="M109" s="25"/>
+      <c r="N109" s="25"/>
+      <c r="AB109" s="25"/>
+      <c r="AC109" s="25"/>
+      <c r="AD109" s="25"/>
+      <c r="AE109" s="25"/>
+      <c r="BN109" s="28"/>
+    </row>
+    <row r="110" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="D110" s="27"/>
+      <c r="E110" s="25"/>
+      <c r="F110" s="25"/>
+      <c r="G110" s="25"/>
+      <c r="H110" s="25"/>
+      <c r="I110" s="25"/>
+      <c r="J110" s="25"/>
+      <c r="K110" s="25"/>
+      <c r="L110" s="25"/>
+      <c r="M110" s="25"/>
+      <c r="N110" s="25"/>
+      <c r="AB110" s="25"/>
+      <c r="AC110" s="25"/>
+      <c r="AD110" s="25"/>
+      <c r="AE110" s="25"/>
+      <c r="BN110" s="28"/>
+    </row>
+    <row r="111" spans="3:66" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D111" s="29"/>
+      <c r="E111" s="30"/>
+      <c r="F111" s="30"/>
+      <c r="G111" s="30"/>
+      <c r="H111" s="30"/>
+      <c r="I111" s="30"/>
+      <c r="J111" s="30"/>
+      <c r="K111" s="30"/>
+      <c r="L111" s="30"/>
+      <c r="M111" s="30"/>
+      <c r="N111" s="30"/>
+      <c r="O111" s="30"/>
+      <c r="P111" s="30"/>
+      <c r="Q111" s="30"/>
+      <c r="R111" s="30"/>
+      <c r="S111" s="30"/>
+      <c r="T111" s="30"/>
+      <c r="U111" s="30"/>
+      <c r="V111" s="30"/>
+      <c r="W111" s="30"/>
+      <c r="X111" s="30"/>
+      <c r="Y111" s="30"/>
+      <c r="Z111" s="30"/>
+      <c r="AA111" s="30"/>
+      <c r="AB111" s="30"/>
+      <c r="AC111" s="30"/>
+      <c r="AD111" s="30"/>
+      <c r="AE111" s="30"/>
+      <c r="AF111" s="30"/>
+      <c r="AG111" s="30"/>
+      <c r="AH111" s="30"/>
+      <c r="AI111" s="30"/>
+      <c r="AJ111" s="30"/>
+      <c r="AK111" s="30"/>
+      <c r="AL111" s="30"/>
+      <c r="AM111" s="30"/>
+      <c r="AN111" s="30"/>
+      <c r="AO111" s="30"/>
+      <c r="AP111" s="30"/>
+      <c r="AQ111" s="30"/>
+      <c r="AR111" s="30"/>
+      <c r="AS111" s="30"/>
+      <c r="AT111" s="30"/>
+      <c r="AU111" s="30"/>
+      <c r="AV111" s="30"/>
+      <c r="AW111" s="30"/>
+      <c r="AX111" s="30"/>
+      <c r="AY111" s="30"/>
+      <c r="AZ111" s="30"/>
+      <c r="BA111" s="30"/>
+      <c r="BB111" s="30"/>
+      <c r="BC111" s="30"/>
+      <c r="BD111" s="30"/>
+      <c r="BE111" s="30"/>
+      <c r="BF111" s="30"/>
+      <c r="BG111" s="30"/>
+      <c r="BH111" s="30"/>
+      <c r="BI111" s="30"/>
+      <c r="BJ111" s="30"/>
+      <c r="BK111" s="30"/>
+      <c r="BL111" s="30"/>
+      <c r="BM111" s="30"/>
+      <c r="BN111" s="31"/>
+    </row>
+    <row r="112" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C112" s="28"/>
+      <c r="D112" s="25"/>
+      <c r="E112" s="25"/>
+      <c r="F112" s="25"/>
+      <c r="G112" s="25"/>
+      <c r="H112" s="25"/>
+      <c r="I112" s="25"/>
+      <c r="J112" s="25"/>
+      <c r="K112" s="25"/>
+      <c r="L112" s="25"/>
+      <c r="M112" s="25"/>
+      <c r="N112" s="25"/>
+      <c r="AB112" s="25"/>
+      <c r="AC112" s="25"/>
+      <c r="AD112" s="25"/>
+      <c r="AE112" s="25"/>
+      <c r="BN112" s="28"/>
+    </row>
+    <row r="113" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C113" s="28"/>
+      <c r="E113" s="25"/>
+      <c r="F113" s="25"/>
+      <c r="G113" s="25"/>
+      <c r="H113" s="25"/>
+      <c r="I113" s="25"/>
+      <c r="J113" s="25"/>
+      <c r="K113" s="25"/>
+      <c r="L113" s="25"/>
+      <c r="M113" s="25"/>
+      <c r="N113" s="25"/>
+      <c r="AB113" s="25"/>
+      <c r="AC113" s="25"/>
+      <c r="AD113" s="25"/>
+      <c r="AE113" s="25"/>
+      <c r="BN113" s="28"/>
+    </row>
+    <row r="114" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C114" s="28"/>
+      <c r="E114" s="25"/>
+      <c r="F114" s="25"/>
+      <c r="G114" s="25"/>
+      <c r="H114" s="25"/>
+      <c r="I114" s="25"/>
+      <c r="J114" s="25"/>
+      <c r="K114" s="25"/>
+      <c r="L114" s="25"/>
+      <c r="M114" s="25"/>
+      <c r="N114" s="25"/>
+      <c r="AB114" s="25"/>
+      <c r="AC114" s="25"/>
+      <c r="AD114" s="25"/>
+      <c r="AE114" s="25"/>
+      <c r="BN114" s="28"/>
+    </row>
+    <row r="115" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C115" s="28"/>
+      <c r="E115" s="25"/>
+      <c r="F115" s="25"/>
+      <c r="G115" s="25"/>
+      <c r="H115" s="25"/>
+      <c r="I115" s="25"/>
+      <c r="J115" s="25"/>
+      <c r="K115" s="25"/>
+      <c r="L115" s="25"/>
+      <c r="M115" s="25"/>
+      <c r="N115" s="25"/>
+      <c r="AB115" s="25"/>
+      <c r="AC115" s="25"/>
+      <c r="AD115" s="25"/>
+      <c r="AE115" s="25"/>
+      <c r="BN115" s="28"/>
+    </row>
+    <row r="116" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C116" s="28"/>
+      <c r="D116" s="37" t="s">
+        <v>40</v>
+      </c>
+      <c r="E116" s="37"/>
+      <c r="F116" s="37"/>
+      <c r="G116" s="37"/>
+      <c r="AB116" s="25"/>
+      <c r="AC116" s="25"/>
+      <c r="AD116" s="25"/>
+      <c r="AE116" s="25"/>
+      <c r="BN116" s="28"/>
+    </row>
+    <row r="117" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C117" s="28"/>
+      <c r="AB117" s="25"/>
+      <c r="AC117" s="25"/>
+      <c r="AD117" s="25"/>
+      <c r="AE117" s="25"/>
+      <c r="BN117" s="28"/>
+    </row>
+    <row r="118" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C118" s="28"/>
+      <c r="AB118" s="25"/>
+      <c r="AC118" s="25"/>
+      <c r="AD118" s="25"/>
+      <c r="AE118" s="25"/>
+      <c r="BN118" s="28"/>
+    </row>
+    <row r="119" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C119" s="28"/>
+      <c r="AB119" s="25"/>
+      <c r="AC119" s="25"/>
+      <c r="AD119" s="25"/>
+      <c r="AE119" s="25"/>
+      <c r="BN119" s="28"/>
+    </row>
+    <row r="120" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C120" s="28"/>
+      <c r="AB120" s="25"/>
+      <c r="AC120" s="25"/>
+      <c r="AD120" s="25"/>
+      <c r="AE120" s="25"/>
+      <c r="BN120" s="28"/>
+    </row>
+    <row r="121" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C121" s="28"/>
+      <c r="AB121" s="25"/>
+      <c r="AC121" s="25"/>
+      <c r="AD121" s="25"/>
+      <c r="AE121" s="25"/>
+      <c r="BN121" s="28"/>
+    </row>
+    <row r="122" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C122" s="28"/>
+      <c r="AB122" s="25"/>
+      <c r="AC122" s="25"/>
+      <c r="AD122" s="25"/>
+      <c r="AE122" s="25"/>
+      <c r="BN122" s="28"/>
+    </row>
+    <row r="123" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C123" s="28"/>
+      <c r="AB123" s="25"/>
+      <c r="AC123" s="25"/>
+      <c r="AD123" s="25"/>
+      <c r="AE123" s="25"/>
+      <c r="BN123" s="28"/>
+    </row>
+    <row r="124" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C124" s="28"/>
+      <c r="AB124" s="25"/>
+      <c r="AC124" s="25"/>
+      <c r="AD124" s="25"/>
+      <c r="AE124" s="25"/>
+      <c r="BN124" s="28"/>
+    </row>
+    <row r="125" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C125" s="28"/>
+      <c r="AB125" s="25"/>
+      <c r="AC125" s="25"/>
+      <c r="AD125" s="25"/>
+      <c r="AE125" s="25"/>
+      <c r="BN125" s="28"/>
+    </row>
+    <row r="126" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C126" s="28"/>
+      <c r="AB126" s="25"/>
+      <c r="AC126" s="25"/>
+      <c r="AD126" s="25"/>
+      <c r="AE126" s="25"/>
+      <c r="BN126" s="28"/>
+    </row>
+    <row r="127" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C127" s="28"/>
+      <c r="AB127" s="25"/>
+      <c r="AC127" s="25"/>
+      <c r="AD127" s="25"/>
+      <c r="AE127" s="25"/>
+      <c r="BN127" s="28"/>
+    </row>
+    <row r="128" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C128" s="28"/>
+      <c r="AB128" s="25"/>
+      <c r="AC128" s="25"/>
+      <c r="AD128" s="25"/>
+      <c r="AE128" s="25"/>
+      <c r="BN128" s="28"/>
+    </row>
+    <row r="129" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C129" s="28"/>
+      <c r="AB129" s="25"/>
+      <c r="AC129" s="25"/>
+      <c r="AD129" s="25"/>
+      <c r="AE129" s="25"/>
+      <c r="BN129" s="28"/>
+    </row>
+    <row r="130" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C130" s="28"/>
+      <c r="AB130" s="25"/>
+      <c r="AC130" s="25"/>
+      <c r="AD130" s="25"/>
+      <c r="AE130" s="25"/>
+      <c r="BN130" s="28"/>
+    </row>
+    <row r="131" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C131" s="28"/>
+      <c r="AB131" s="25"/>
+      <c r="AC131" s="25"/>
+      <c r="AD131" s="25"/>
+      <c r="AE131" s="25"/>
+      <c r="BN131" s="28"/>
+    </row>
+    <row r="132" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C132" s="28"/>
+      <c r="W132" s="25"/>
+      <c r="X132" s="25"/>
+      <c r="Y132" s="25"/>
+      <c r="Z132" s="25"/>
+      <c r="AA132" s="25"/>
+      <c r="AB132" s="25"/>
+      <c r="AC132" s="25"/>
+      <c r="AD132" s="25"/>
+      <c r="AE132" s="25"/>
+      <c r="BN132" s="28"/>
+    </row>
+    <row r="133" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C133" s="28"/>
+      <c r="W133" s="25"/>
+      <c r="X133" s="25"/>
+      <c r="Y133" s="25"/>
+      <c r="Z133" s="25"/>
+      <c r="AA133" s="25"/>
+      <c r="AB133" s="25"/>
+      <c r="AC133" s="25"/>
+      <c r="AD133" s="25"/>
+      <c r="AE133" s="25"/>
+      <c r="BN133" s="28"/>
+    </row>
+    <row r="134" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C134" s="28"/>
+      <c r="W134" s="25"/>
+      <c r="X134" s="25"/>
+      <c r="Y134" s="25"/>
+      <c r="Z134" s="25"/>
+      <c r="AA134" s="25"/>
+      <c r="AB134" s="25"/>
+      <c r="AC134" s="25"/>
+      <c r="AD134" s="25"/>
+      <c r="AE134" s="25"/>
+      <c r="BN134" s="28"/>
+    </row>
+    <row r="135" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C135" s="28"/>
+      <c r="W135" s="25"/>
+      <c r="X135" s="25"/>
+      <c r="Y135" s="25"/>
+      <c r="Z135" s="25"/>
+      <c r="AA135" s="25"/>
+      <c r="AB135" s="25"/>
+      <c r="AC135" s="25"/>
+      <c r="AD135" s="25"/>
+      <c r="AE135" s="25"/>
+      <c r="BN135" s="28"/>
+    </row>
+    <row r="136" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C136" s="28"/>
+      <c r="W136" s="25"/>
+      <c r="X136" s="25"/>
+      <c r="Y136" s="25"/>
+      <c r="Z136" s="25"/>
+      <c r="AA136" s="25"/>
+      <c r="AB136" s="25"/>
+      <c r="AC136" s="25"/>
+      <c r="AD136" s="25"/>
+      <c r="AE136" s="25"/>
+      <c r="BN136" s="28"/>
+    </row>
+    <row r="137" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C137" s="28"/>
+      <c r="W137" s="25"/>
+      <c r="X137" s="25"/>
+      <c r="Y137" s="25"/>
+      <c r="Z137" s="25"/>
+      <c r="AA137" s="25"/>
+      <c r="AB137" s="25"/>
+      <c r="AC137" s="25"/>
+      <c r="AD137" s="25"/>
+      <c r="AE137" s="25"/>
+      <c r="BN137" s="28"/>
+    </row>
+    <row r="138" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C138" s="28"/>
+      <c r="W138" s="25"/>
+      <c r="X138" s="25"/>
+      <c r="Y138" s="25"/>
+      <c r="Z138" s="25"/>
+      <c r="AA138" s="25"/>
+      <c r="AB138" s="25"/>
+      <c r="AC138" s="25"/>
+      <c r="AD138" s="25"/>
+      <c r="AE138" s="25"/>
+      <c r="BN138" s="28"/>
+    </row>
+    <row r="139" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C139" s="28"/>
+      <c r="W139" s="25"/>
+      <c r="X139" s="25"/>
+      <c r="Y139" s="25"/>
+      <c r="Z139" s="25"/>
+      <c r="AA139" s="25"/>
+      <c r="AB139" s="25"/>
+      <c r="AC139" s="25"/>
+      <c r="AD139" s="25"/>
+      <c r="AE139" s="25"/>
+      <c r="BN139" s="28"/>
+    </row>
+    <row r="140" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C140" s="28"/>
+      <c r="W140" s="25"/>
+      <c r="X140" s="25"/>
+      <c r="Y140" s="25"/>
+      <c r="Z140" s="25"/>
+      <c r="AA140" s="25"/>
+      <c r="AB140" s="25"/>
+      <c r="AC140" s="25"/>
+      <c r="AD140" s="25"/>
+      <c r="AE140" s="25"/>
+      <c r="BN140" s="28"/>
+    </row>
+    <row r="141" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C141" s="28"/>
+      <c r="W141" s="25"/>
+      <c r="X141" s="25"/>
+      <c r="Y141" s="25"/>
+      <c r="Z141" s="25"/>
+      <c r="AA141" s="25"/>
+      <c r="AB141" s="25"/>
+      <c r="AC141" s="25"/>
+      <c r="AD141" s="25"/>
+      <c r="AE141" s="25"/>
+      <c r="BN141" s="28"/>
+    </row>
+    <row r="142" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C142" s="28"/>
+      <c r="W142" s="25"/>
+      <c r="X142" s="25"/>
+      <c r="Y142" s="25"/>
+      <c r="Z142" s="25"/>
+      <c r="AA142" s="25"/>
+      <c r="AB142" s="25"/>
+      <c r="AC142" s="25"/>
+      <c r="AD142" s="25"/>
+      <c r="AE142" s="25"/>
+      <c r="BN142" s="28"/>
+    </row>
+    <row r="143" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C143" s="28"/>
+      <c r="W143" s="25"/>
+      <c r="X143" s="25"/>
+      <c r="Y143" s="25"/>
+      <c r="Z143" s="25"/>
+      <c r="AA143" s="25"/>
+      <c r="AB143" s="25"/>
+      <c r="AC143" s="25"/>
+      <c r="AD143" s="25"/>
+      <c r="AE143" s="25"/>
+      <c r="BN143" s="28"/>
+    </row>
+    <row r="144" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C144" s="28"/>
+      <c r="W144" s="25"/>
+      <c r="X144" s="25"/>
+      <c r="Y144" s="25"/>
+      <c r="Z144" s="25"/>
+      <c r="AA144" s="25"/>
+      <c r="AB144" s="25"/>
+      <c r="AC144" s="25"/>
+      <c r="AD144" s="25"/>
+      <c r="AE144" s="25"/>
+      <c r="BN144" s="28"/>
+    </row>
+    <row r="145" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C145" s="28"/>
+      <c r="W145" s="25"/>
+      <c r="X145" s="25"/>
+      <c r="Y145" s="25"/>
+      <c r="Z145" s="25"/>
+      <c r="AA145" s="25"/>
+      <c r="AB145" s="25"/>
+      <c r="AC145" s="25"/>
+      <c r="AD145" s="25"/>
+      <c r="AE145" s="25"/>
+      <c r="BN145" s="28"/>
+    </row>
+    <row r="146" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C146" s="28"/>
+      <c r="W146" s="25"/>
+      <c r="X146" s="25"/>
+      <c r="Y146" s="25"/>
+      <c r="Z146" s="25"/>
+      <c r="AA146" s="25"/>
+      <c r="AB146" s="25"/>
+      <c r="AC146" s="25"/>
+      <c r="AD146" s="25"/>
+      <c r="AE146" s="25"/>
+      <c r="BN146" s="28"/>
+    </row>
+    <row r="147" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C147" s="28"/>
+      <c r="W147" s="25"/>
+      <c r="X147" s="25"/>
+      <c r="Y147" s="25"/>
+      <c r="Z147" s="25"/>
+      <c r="AA147" s="25"/>
+      <c r="AB147" s="25"/>
+      <c r="AC147" s="25"/>
+      <c r="AD147" s="25"/>
+      <c r="AE147" s="25"/>
+      <c r="BN147" s="28"/>
+    </row>
+    <row r="148" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C148" s="28"/>
+      <c r="W148" s="25"/>
+      <c r="X148" s="25"/>
+      <c r="Y148" s="25"/>
+      <c r="Z148" s="25"/>
+      <c r="AA148" s="25"/>
+      <c r="AB148" s="25"/>
+      <c r="AC148" s="25"/>
+      <c r="AD148" s="25"/>
+      <c r="AE148" s="25"/>
+      <c r="BN148" s="28"/>
+    </row>
+    <row r="149" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C149" s="28"/>
+      <c r="W149" s="25"/>
+      <c r="X149" s="25"/>
+      <c r="Y149" s="25"/>
+      <c r="Z149" s="25"/>
+      <c r="AA149" s="25"/>
+      <c r="AB149" s="25"/>
+      <c r="AC149" s="25"/>
+      <c r="AD149" s="25"/>
+      <c r="AE149" s="25"/>
+      <c r="BN149" s="28"/>
+    </row>
+    <row r="150" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C150" s="28"/>
+      <c r="W150" s="25"/>
+      <c r="X150" s="25"/>
+      <c r="Y150" s="25"/>
+      <c r="Z150" s="25"/>
+      <c r="AA150" s="25"/>
+      <c r="AB150" s="25"/>
+      <c r="AC150" s="25"/>
+      <c r="AD150" s="25"/>
+      <c r="AE150" s="25"/>
+      <c r="BN150" s="28"/>
+    </row>
+    <row r="151" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C151" s="28"/>
+      <c r="W151" s="25"/>
+      <c r="X151" s="25"/>
+      <c r="Y151" s="25"/>
+      <c r="Z151" s="25"/>
+      <c r="AA151" s="25"/>
+      <c r="AB151" s="25"/>
+      <c r="AC151" s="25"/>
+      <c r="AD151" s="25"/>
+      <c r="AE151" s="25"/>
+      <c r="BN151" s="28"/>
+    </row>
+    <row r="152" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C152" s="28"/>
+      <c r="W152" s="25"/>
+      <c r="X152" s="25"/>
+      <c r="Y152" s="25"/>
+      <c r="Z152" s="25"/>
+      <c r="AA152" s="25"/>
+      <c r="AB152" s="25"/>
+      <c r="AC152" s="25"/>
+      <c r="AD152" s="25"/>
+      <c r="AE152" s="25"/>
+      <c r="BN152" s="28"/>
+    </row>
+    <row r="153" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C153" s="28"/>
+      <c r="W153" s="25"/>
+      <c r="X153" s="25"/>
+      <c r="Y153" s="25"/>
+      <c r="Z153" s="25"/>
+      <c r="AA153" s="25"/>
+      <c r="AB153" s="25"/>
+      <c r="AC153" s="25"/>
+      <c r="AD153" s="25"/>
+      <c r="AE153" s="25"/>
+      <c r="BN153" s="28"/>
+    </row>
+    <row r="154" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C154" s="28"/>
+      <c r="W154" s="25"/>
+      <c r="X154" s="25"/>
+      <c r="Y154" s="25"/>
+      <c r="Z154" s="25"/>
+      <c r="AA154" s="25"/>
+      <c r="AB154" s="25"/>
+      <c r="AC154" s="25"/>
+      <c r="AD154" s="25"/>
+      <c r="AE154" s="25"/>
+      <c r="BN154" s="28"/>
+    </row>
+    <row r="155" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C155" s="28"/>
+      <c r="W155" s="25"/>
+      <c r="X155" s="25"/>
+      <c r="Y155" s="25"/>
+      <c r="Z155" s="25"/>
+      <c r="AA155" s="25"/>
+      <c r="AB155" s="25"/>
+      <c r="AC155" s="25"/>
+      <c r="AD155" s="25"/>
+      <c r="AE155" s="25"/>
+      <c r="BN155" s="28"/>
+    </row>
+    <row r="156" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C156" s="28"/>
+      <c r="W156" s="25"/>
+      <c r="X156" s="25"/>
+      <c r="Y156" s="25"/>
+      <c r="Z156" s="25"/>
+      <c r="AA156" s="25"/>
+      <c r="AB156" s="25"/>
+      <c r="AC156" s="25"/>
+      <c r="AD156" s="25"/>
+      <c r="AE156" s="25"/>
+      <c r="BN156" s="28"/>
+    </row>
+    <row r="157" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C157" s="28"/>
+      <c r="W157" s="25"/>
+      <c r="X157" s="25"/>
+      <c r="Y157" s="25"/>
+      <c r="Z157" s="25"/>
+      <c r="AA157" s="25"/>
+      <c r="AB157" s="25"/>
+      <c r="AC157" s="25"/>
+      <c r="AD157" s="25"/>
+      <c r="AE157" s="25"/>
+      <c r="BN157" s="28"/>
+    </row>
+    <row r="158" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C158" s="28"/>
+      <c r="W158" s="25"/>
+      <c r="X158" s="25"/>
+      <c r="Y158" s="25"/>
+      <c r="Z158" s="25"/>
+      <c r="AA158" s="25"/>
+      <c r="AB158" s="25"/>
+      <c r="AC158" s="25"/>
+      <c r="AD158" s="25"/>
+      <c r="AE158" s="25"/>
+      <c r="BN158" s="28"/>
+    </row>
+    <row r="159" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C159" s="28"/>
+      <c r="W159" s="25"/>
+      <c r="X159" s="25"/>
+      <c r="Y159" s="25"/>
+      <c r="Z159" s="25"/>
+      <c r="AA159" s="25"/>
+      <c r="AB159" s="25"/>
+      <c r="AC159" s="25"/>
+      <c r="AD159" s="25"/>
+      <c r="AE159" s="25"/>
+      <c r="BN159" s="28"/>
+    </row>
+    <row r="160" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C160" s="28"/>
+      <c r="W160" s="25"/>
+      <c r="X160" s="25"/>
+      <c r="Y160" s="25"/>
+      <c r="Z160" s="25"/>
+      <c r="AA160" s="25"/>
+      <c r="AB160" s="25"/>
+      <c r="AC160" s="25"/>
+      <c r="AD160" s="25"/>
+      <c r="AE160" s="25"/>
+      <c r="BN160" s="28"/>
+    </row>
+    <row r="161" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C161" s="28"/>
+      <c r="W161" s="25"/>
+      <c r="X161" s="25"/>
+      <c r="Y161" s="25"/>
+      <c r="Z161" s="25"/>
+      <c r="AA161" s="25"/>
+      <c r="AB161" s="25"/>
+      <c r="AC161" s="25"/>
+      <c r="AD161" s="25"/>
+      <c r="AE161" s="25"/>
+      <c r="BN161" s="28"/>
+    </row>
+    <row r="162" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C162" s="28"/>
+      <c r="W162" s="25"/>
+      <c r="X162" s="25"/>
+      <c r="Y162" s="25"/>
+      <c r="Z162" s="25"/>
+      <c r="AA162" s="25"/>
+      <c r="AB162" s="25"/>
+      <c r="AC162" s="25"/>
+      <c r="AD162" s="25"/>
+      <c r="AE162" s="25"/>
+      <c r="BN162" s="28"/>
+    </row>
+    <row r="163" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C163" s="28"/>
+      <c r="W163" s="25"/>
+      <c r="X163" s="25"/>
+      <c r="Y163" s="25"/>
+      <c r="Z163" s="25"/>
+      <c r="AA163" s="25"/>
+      <c r="AB163" s="25"/>
+      <c r="AC163" s="25"/>
+      <c r="AD163" s="25"/>
+      <c r="AE163" s="25"/>
+      <c r="BN163" s="28"/>
+    </row>
+    <row r="164" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C164" s="28"/>
+      <c r="W164" s="25"/>
+      <c r="X164" s="25"/>
+      <c r="Y164" s="25"/>
+      <c r="Z164" s="25"/>
+      <c r="AA164" s="25"/>
+      <c r="AB164" s="25"/>
+      <c r="AC164" s="25"/>
+      <c r="AD164" s="25"/>
+      <c r="AE164" s="25"/>
+      <c r="BN164" s="28"/>
+    </row>
+    <row r="165" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C165" s="28"/>
+      <c r="W165" s="25"/>
+      <c r="X165" s="25"/>
+      <c r="Y165" s="25"/>
+      <c r="Z165" s="25"/>
+      <c r="AA165" s="25"/>
+      <c r="AB165" s="25"/>
+      <c r="AC165" s="25"/>
+      <c r="AD165" s="25"/>
+      <c r="AE165" s="25"/>
+      <c r="BN165" s="28"/>
+    </row>
+    <row r="166" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C166" s="28"/>
+      <c r="W166" s="25"/>
+      <c r="X166" s="25"/>
+      <c r="Y166" s="25"/>
+      <c r="Z166" s="25"/>
+      <c r="AA166" s="25"/>
+      <c r="AB166" s="25"/>
+      <c r="AC166" s="25"/>
+      <c r="AD166" s="25"/>
+      <c r="AE166" s="25"/>
+      <c r="BN166" s="28"/>
+    </row>
+    <row r="167" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C167" s="28"/>
+      <c r="W167" s="25"/>
+      <c r="X167" s="25"/>
+      <c r="Y167" s="25"/>
+      <c r="Z167" s="25"/>
+      <c r="AA167" s="25"/>
+      <c r="AB167" s="25"/>
+      <c r="AC167" s="25"/>
+      <c r="AD167" s="25"/>
+      <c r="AE167" s="25"/>
+      <c r="BN167" s="28"/>
+    </row>
+    <row r="168" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C168" s="28"/>
+      <c r="W168" s="25"/>
+      <c r="X168" s="25"/>
+      <c r="Y168" s="25"/>
+      <c r="Z168" s="25"/>
+      <c r="AA168" s="25"/>
+      <c r="AB168" s="25"/>
+      <c r="AC168" s="25"/>
+      <c r="AD168" s="25"/>
+      <c r="AE168" s="25"/>
+      <c r="BN168" s="28"/>
+    </row>
+    <row r="169" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C169" s="28"/>
+      <c r="W169" s="25"/>
+      <c r="X169" s="25"/>
+      <c r="Y169" s="25"/>
+      <c r="Z169" s="25"/>
+      <c r="AA169" s="25"/>
+      <c r="AB169" s="25"/>
+      <c r="AC169" s="25"/>
+      <c r="AD169" s="25"/>
+      <c r="AE169" s="25"/>
+      <c r="BN169" s="28"/>
+    </row>
+    <row r="170" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C170" s="28"/>
+      <c r="W170" s="25"/>
+      <c r="X170" s="25"/>
+      <c r="Y170" s="25"/>
+      <c r="Z170" s="25"/>
+      <c r="AA170" s="25"/>
+      <c r="AB170" s="25"/>
+      <c r="AC170" s="25"/>
+      <c r="AD170" s="25"/>
+      <c r="AE170" s="25"/>
+      <c r="BN170" s="28"/>
+    </row>
+    <row r="171" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C171" s="28"/>
+      <c r="W171" s="25"/>
+      <c r="X171" s="25"/>
+      <c r="Y171" s="25"/>
+      <c r="Z171" s="25"/>
+      <c r="AA171" s="25"/>
+      <c r="AB171" s="25"/>
+      <c r="AC171" s="25"/>
+      <c r="AD171" s="25"/>
+      <c r="AE171" s="25"/>
+      <c r="BN171" s="28"/>
+    </row>
+    <row r="172" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C172" s="28"/>
+      <c r="W172" s="25"/>
+      <c r="X172" s="25"/>
+      <c r="Y172" s="25"/>
+      <c r="Z172" s="25"/>
+      <c r="AA172" s="25"/>
+      <c r="AB172" s="25"/>
+      <c r="AC172" s="25"/>
+      <c r="AD172" s="25"/>
+      <c r="AE172" s="25"/>
+      <c r="BN172" s="28"/>
+    </row>
+    <row r="173" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C173" s="28"/>
+      <c r="W173" s="25"/>
+      <c r="X173" s="25"/>
+      <c r="Y173" s="25"/>
+      <c r="Z173" s="25"/>
+      <c r="AA173" s="25"/>
+      <c r="AB173" s="25"/>
+      <c r="AC173" s="25"/>
+      <c r="AD173" s="25"/>
+      <c r="AE173" s="25"/>
+      <c r="BN173" s="28"/>
+    </row>
+    <row r="174" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C174" s="28"/>
+      <c r="W174" s="25"/>
+      <c r="X174" s="25"/>
+      <c r="Y174" s="25"/>
+      <c r="Z174" s="25"/>
+      <c r="AA174" s="25"/>
+      <c r="AB174" s="25"/>
+      <c r="AC174" s="25"/>
+      <c r="AD174" s="25"/>
+      <c r="AE174" s="25"/>
+      <c r="BN174" s="28"/>
+    </row>
+    <row r="175" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C175" s="28"/>
+      <c r="W175" s="25"/>
+      <c r="X175" s="25"/>
+      <c r="Y175" s="25"/>
+      <c r="Z175" s="25"/>
+      <c r="AA175" s="25"/>
+      <c r="AB175" s="25"/>
+      <c r="AC175" s="25"/>
+      <c r="AD175" s="25"/>
+      <c r="AE175" s="25"/>
+      <c r="BN175" s="28"/>
+    </row>
+    <row r="176" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C176" s="28"/>
+      <c r="W176" s="25"/>
+      <c r="X176" s="25"/>
+      <c r="Y176" s="25"/>
+      <c r="Z176" s="25"/>
+      <c r="AA176" s="25"/>
+      <c r="AB176" s="25"/>
+      <c r="AC176" s="25"/>
+      <c r="AD176" s="25"/>
+      <c r="AE176" s="25"/>
+      <c r="BN176" s="28"/>
+    </row>
+    <row r="177" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C177" s="28"/>
+      <c r="W177" s="25"/>
+      <c r="X177" s="25"/>
+      <c r="Y177" s="25"/>
+      <c r="Z177" s="25"/>
+      <c r="AA177" s="25"/>
+      <c r="AB177" s="25"/>
+      <c r="AC177" s="25"/>
+      <c r="AD177" s="25"/>
+      <c r="AE177" s="25"/>
+      <c r="BN177" s="28"/>
+    </row>
+    <row r="178" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C178" s="28"/>
+      <c r="W178" s="25"/>
+      <c r="X178" s="25"/>
+      <c r="Y178" s="25"/>
+      <c r="Z178" s="25"/>
+      <c r="AA178" s="25"/>
+      <c r="AB178" s="25"/>
+      <c r="AC178" s="25"/>
+      <c r="AD178" s="25"/>
+      <c r="AE178" s="25"/>
+      <c r="BN178" s="28"/>
+    </row>
+    <row r="179" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C179" s="28"/>
+      <c r="W179" s="25"/>
+      <c r="X179" s="25"/>
+      <c r="Y179" s="25"/>
+      <c r="Z179" s="25"/>
+      <c r="AA179" s="25"/>
+      <c r="AB179" s="25"/>
+      <c r="AC179" s="25"/>
+      <c r="AD179" s="25"/>
+      <c r="AE179" s="25"/>
+      <c r="BN179" s="28"/>
+    </row>
+    <row r="180" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C180" s="28"/>
+      <c r="W180" s="25"/>
+      <c r="X180" s="25"/>
+      <c r="Y180" s="25"/>
+      <c r="Z180" s="25"/>
+      <c r="AA180" s="25"/>
+      <c r="AB180" s="25"/>
+      <c r="AC180" s="25"/>
+      <c r="AD180" s="25"/>
+      <c r="AE180" s="25"/>
+      <c r="BN180" s="28"/>
+    </row>
+    <row r="181" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C181" s="28"/>
+      <c r="W181" s="25"/>
+      <c r="X181" s="25"/>
+      <c r="Y181" s="25"/>
+      <c r="Z181" s="25"/>
+      <c r="AA181" s="25"/>
+      <c r="AB181" s="25"/>
+      <c r="AC181" s="25"/>
+      <c r="AD181" s="25"/>
+      <c r="AE181" s="25"/>
+      <c r="BN181" s="28"/>
+    </row>
+    <row r="182" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C182" s="28"/>
+      <c r="W182" s="25"/>
+      <c r="X182" s="25"/>
+      <c r="Y182" s="25"/>
+      <c r="Z182" s="25"/>
+      <c r="AA182" s="25"/>
+      <c r="AB182" s="25"/>
+      <c r="AC182" s="25"/>
+      <c r="AD182" s="25"/>
+      <c r="AE182" s="25"/>
+      <c r="BN182" s="28"/>
+    </row>
+    <row r="183" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C183" s="28"/>
+      <c r="W183" s="25"/>
+      <c r="X183" s="25"/>
+      <c r="Y183" s="25"/>
+      <c r="Z183" s="25"/>
+      <c r="AA183" s="25"/>
+      <c r="AB183" s="25"/>
+      <c r="AC183" s="25"/>
+      <c r="AD183" s="25"/>
+      <c r="AE183" s="25"/>
+      <c r="BN183" s="28"/>
+    </row>
+    <row r="184" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C184" s="28"/>
+      <c r="W184" s="25"/>
+      <c r="X184" s="25"/>
+      <c r="Y184" s="25"/>
+      <c r="Z184" s="25"/>
+      <c r="AA184" s="25"/>
+      <c r="AB184" s="25"/>
+      <c r="AC184" s="25"/>
+      <c r="AD184" s="25"/>
+      <c r="AE184" s="25"/>
+      <c r="BN184" s="28"/>
+    </row>
+    <row r="185" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C185" s="28"/>
+      <c r="W185" s="25"/>
+      <c r="X185" s="25"/>
+      <c r="Y185" s="25"/>
+      <c r="Z185" s="25"/>
+      <c r="AA185" s="25"/>
+      <c r="AB185" s="25"/>
+      <c r="AC185" s="25"/>
+      <c r="AD185" s="25"/>
+      <c r="AE185" s="25"/>
+      <c r="BN185" s="28"/>
+    </row>
+    <row r="186" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C186" s="28"/>
+      <c r="W186" s="25"/>
+      <c r="X186" s="25"/>
+      <c r="Y186" s="25"/>
+      <c r="Z186" s="25"/>
+      <c r="AA186" s="25"/>
+      <c r="AB186" s="25"/>
+      <c r="AC186" s="25"/>
+      <c r="AD186" s="25"/>
+      <c r="AE186" s="25"/>
+      <c r="BN186" s="28"/>
+    </row>
+    <row r="187" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C187" s="28"/>
+      <c r="W187" s="25"/>
+      <c r="X187" s="25"/>
+      <c r="Y187" s="25"/>
+      <c r="Z187" s="25"/>
+      <c r="AA187" s="25"/>
+      <c r="AB187" s="25"/>
+      <c r="AC187" s="25"/>
+      <c r="AD187" s="25"/>
+      <c r="AE187" s="25"/>
+      <c r="BN187" s="28"/>
+    </row>
+    <row r="188" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C188" s="28"/>
+      <c r="W188" s="25"/>
+      <c r="X188" s="25"/>
+      <c r="Y188" s="25"/>
+      <c r="Z188" s="25"/>
+      <c r="AA188" s="25"/>
+      <c r="AB188" s="25"/>
+      <c r="AC188" s="25"/>
+      <c r="AD188" s="25"/>
+      <c r="AE188" s="25"/>
+      <c r="BN188" s="28"/>
+    </row>
+    <row r="189" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C189" s="28"/>
+      <c r="W189" s="25"/>
+      <c r="X189" s="25"/>
+      <c r="Y189" s="25"/>
+      <c r="Z189" s="25"/>
+      <c r="AA189" s="25"/>
+      <c r="AB189" s="25"/>
+      <c r="AC189" s="25"/>
+      <c r="AD189" s="25"/>
+      <c r="AE189" s="25"/>
+      <c r="BN189" s="28"/>
+    </row>
+    <row r="190" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C190" s="28"/>
+      <c r="W190" s="25"/>
+      <c r="X190" s="25"/>
+      <c r="Y190" s="25"/>
+      <c r="Z190" s="25"/>
+      <c r="AA190" s="25"/>
+      <c r="AB190" s="25"/>
+      <c r="AC190" s="25"/>
+      <c r="AD190" s="25"/>
+      <c r="AE190" s="25"/>
+      <c r="BN190" s="28"/>
+    </row>
+    <row r="191" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C191" s="28"/>
+      <c r="W191" s="25"/>
+      <c r="X191" s="25"/>
+      <c r="Y191" s="25"/>
+      <c r="Z191" s="25"/>
+      <c r="AA191" s="25"/>
+      <c r="AB191" s="25"/>
+      <c r="AC191" s="25"/>
+      <c r="AD191" s="25"/>
+      <c r="AE191" s="25"/>
+      <c r="BN191" s="28"/>
+    </row>
+    <row r="192" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C192" s="28"/>
+      <c r="W192" s="25"/>
+      <c r="X192" s="25"/>
+      <c r="Y192" s="25"/>
+      <c r="Z192" s="25"/>
+      <c r="AA192" s="25"/>
+      <c r="AB192" s="25"/>
+      <c r="AC192" s="25"/>
+      <c r="AD192" s="25"/>
+      <c r="AE192" s="25"/>
+      <c r="BN192" s="28"/>
+    </row>
+    <row r="193" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C193" s="28"/>
+      <c r="W193" s="25"/>
+      <c r="X193" s="25"/>
+      <c r="Y193" s="25"/>
+      <c r="Z193" s="25"/>
+      <c r="AA193" s="25"/>
+      <c r="AB193" s="25"/>
+      <c r="AC193" s="25"/>
+      <c r="AD193" s="25"/>
+      <c r="AE193" s="25"/>
+      <c r="BN193" s="28"/>
+    </row>
+    <row r="194" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C194" s="28"/>
+      <c r="W194" s="25"/>
+      <c r="X194" s="25"/>
+      <c r="Y194" s="25"/>
+      <c r="Z194" s="25"/>
+      <c r="AA194" s="25"/>
+      <c r="AB194" s="25"/>
+      <c r="AC194" s="25"/>
+      <c r="AD194" s="25"/>
+      <c r="AE194" s="25"/>
+      <c r="BN194" s="28"/>
+    </row>
+    <row r="195" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C195" s="28"/>
+      <c r="W195" s="25"/>
+      <c r="X195" s="25"/>
+      <c r="Y195" s="25"/>
+      <c r="Z195" s="25"/>
+      <c r="AA195" s="25"/>
+      <c r="AB195" s="25"/>
+      <c r="AC195" s="25"/>
+      <c r="AD195" s="25"/>
+      <c r="AE195" s="25"/>
+      <c r="BN195" s="28"/>
+    </row>
+    <row r="196" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C196" s="28"/>
+      <c r="W196" s="25"/>
+      <c r="X196" s="25"/>
+      <c r="Y196" s="25"/>
+      <c r="Z196" s="25"/>
+      <c r="AA196" s="25"/>
+      <c r="AB196" s="25"/>
+      <c r="AC196" s="25"/>
+      <c r="AD196" s="25"/>
+      <c r="AE196" s="25"/>
+      <c r="BN196" s="28"/>
+    </row>
+    <row r="197" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="W197" s="25"/>
+      <c r="X197" s="25"/>
+      <c r="Y197" s="25"/>
+      <c r="Z197" s="25"/>
+      <c r="AA197" s="25"/>
+      <c r="AB197" s="25"/>
+      <c r="AC197" s="25"/>
+      <c r="AD197" s="25"/>
+      <c r="AE197" s="25"/>
+      <c r="BN197" s="28"/>
+    </row>
+    <row r="198" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="W198" s="25"/>
+      <c r="X198" s="25"/>
+      <c r="Y198" s="25"/>
+      <c r="Z198" s="25"/>
+      <c r="AA198" s="25"/>
+      <c r="AB198" s="25"/>
+      <c r="AC198" s="25"/>
+      <c r="AD198" s="25"/>
+      <c r="AE198" s="25"/>
+      <c r="BN198" s="28"/>
+    </row>
+    <row r="199" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="W199" s="25"/>
+      <c r="X199" s="25"/>
+      <c r="Y199" s="25"/>
+      <c r="Z199" s="25"/>
+      <c r="AA199" s="25"/>
+      <c r="AB199" s="25"/>
+      <c r="AC199" s="25"/>
+      <c r="AD199" s="25"/>
+      <c r="AE199" s="25"/>
+      <c r="BN199" s="28"/>
+    </row>
+    <row r="200" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="W200" s="25"/>
+      <c r="X200" s="25"/>
+      <c r="Y200" s="25"/>
+      <c r="Z200" s="25"/>
+      <c r="AA200" s="25"/>
+      <c r="AB200" s="25"/>
+      <c r="AC200" s="25"/>
+      <c r="AD200" s="25"/>
+      <c r="AE200" s="25"/>
+      <c r="BN200" s="28"/>
+    </row>
+    <row r="201" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="W201" s="25"/>
+      <c r="X201" s="25"/>
+      <c r="Y201" s="25"/>
+      <c r="Z201" s="25"/>
+      <c r="AA201" s="25"/>
+      <c r="AB201" s="25"/>
+      <c r="AC201" s="25"/>
+      <c r="AD201" s="25"/>
+      <c r="AE201" s="25"/>
+      <c r="BN201" s="28"/>
+    </row>
+    <row r="202" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="W202" s="25"/>
+      <c r="X202" s="25"/>
+      <c r="Y202" s="25"/>
+      <c r="Z202" s="25"/>
+      <c r="AA202" s="25"/>
+      <c r="AB202" s="25"/>
+      <c r="AC202" s="25"/>
+      <c r="AD202" s="25"/>
+      <c r="AE202" s="25"/>
+      <c r="BN202" s="28"/>
+    </row>
+    <row r="203" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="W203" s="25"/>
+      <c r="X203" s="25"/>
+      <c r="Y203" s="25"/>
+      <c r="Z203" s="25"/>
+      <c r="AA203" s="25"/>
+      <c r="AB203" s="25"/>
+      <c r="AC203" s="25"/>
+      <c r="AD203" s="25"/>
+      <c r="AE203" s="25"/>
+      <c r="BN203" s="28"/>
+    </row>
+    <row r="204" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="W204" s="25"/>
+      <c r="X204" s="25"/>
+      <c r="Y204" s="25"/>
+      <c r="Z204" s="25"/>
+      <c r="AA204" s="25"/>
+      <c r="AB204" s="25"/>
+      <c r="AC204" s="25"/>
+      <c r="AD204" s="25"/>
+      <c r="AE204" s="25"/>
+      <c r="BN204" s="28"/>
+    </row>
+    <row r="205" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="W205" s="25"/>
+      <c r="X205" s="25"/>
+      <c r="Y205" s="25"/>
+      <c r="Z205" s="25"/>
+      <c r="AA205" s="25"/>
+      <c r="AB205" s="25"/>
+      <c r="AC205" s="25"/>
+      <c r="AD205" s="25"/>
+      <c r="AE205" s="25"/>
+      <c r="BN205" s="28"/>
+    </row>
+    <row r="206" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="W206" s="25"/>
+      <c r="X206" s="25"/>
+      <c r="Y206" s="25"/>
+      <c r="Z206" s="25"/>
+      <c r="AA206" s="25"/>
+      <c r="AB206" s="25"/>
+      <c r="AC206" s="25"/>
+      <c r="AD206" s="25"/>
+      <c r="AE206" s="25"/>
+      <c r="BN206" s="28"/>
+    </row>
+    <row r="207" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="W207" s="25"/>
+      <c r="X207" s="25"/>
+      <c r="Y207" s="25"/>
+      <c r="Z207" s="25"/>
+      <c r="AA207" s="25"/>
+      <c r="AB207" s="25"/>
+      <c r="AC207" s="25"/>
+      <c r="AD207" s="25"/>
+      <c r="AE207" s="25"/>
+      <c r="BN207" s="28"/>
+    </row>
+    <row r="208" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="W208" s="25"/>
+      <c r="X208" s="25"/>
+      <c r="Y208" s="25"/>
+      <c r="Z208" s="25"/>
+      <c r="AA208" s="25"/>
+      <c r="AB208" s="25"/>
+      <c r="AC208" s="25"/>
+      <c r="AD208" s="25"/>
+      <c r="AE208" s="25"/>
+      <c r="BN208" s="28"/>
+    </row>
+    <row r="209" spans="23:66" x14ac:dyDescent="0.25">
+      <c r="W209" s="25"/>
+      <c r="X209" s="25"/>
+      <c r="Y209" s="25"/>
+      <c r="Z209" s="25"/>
+      <c r="AA209" s="25"/>
+      <c r="AB209" s="25"/>
+      <c r="AC209" s="25"/>
+      <c r="AD209" s="25"/>
+      <c r="AE209" s="25"/>
+      <c r="BN209" s="28"/>
+    </row>
+    <row r="210" spans="23:66" x14ac:dyDescent="0.25">
+      <c r="W210" s="25"/>
+      <c r="X210" s="25"/>
+      <c r="Y210" s="25"/>
+      <c r="Z210" s="25"/>
+      <c r="AA210" s="25"/>
+      <c r="AB210" s="25"/>
+      <c r="AC210" s="25"/>
+      <c r="AD210" s="25"/>
+      <c r="AE210" s="25"/>
+      <c r="BN210" s="28"/>
+    </row>
+    <row r="211" spans="23:66" x14ac:dyDescent="0.25">
+      <c r="W211" s="25"/>
+      <c r="X211" s="25"/>
+      <c r="Y211" s="25"/>
+      <c r="Z211" s="25"/>
+      <c r="AA211" s="25"/>
+      <c r="AB211" s="25"/>
+      <c r="AC211" s="25"/>
+      <c r="AD211" s="25"/>
+      <c r="AE211" s="25"/>
+      <c r="BN211" s="28"/>
+    </row>
+    <row r="212" spans="23:66" x14ac:dyDescent="0.25">
+      <c r="W212" s="25"/>
+      <c r="X212" s="25"/>
+      <c r="Y212" s="25"/>
+      <c r="Z212" s="25"/>
+      <c r="AA212" s="25"/>
+      <c r="AB212" s="25"/>
+      <c r="AC212" s="25"/>
+      <c r="AD212" s="25"/>
+      <c r="AE212" s="25"/>
+      <c r="BN212" s="28"/>
+    </row>
+    <row r="213" spans="23:66" x14ac:dyDescent="0.25">
+      <c r="W213" s="25"/>
+      <c r="X213" s="25"/>
+      <c r="Y213" s="25"/>
+      <c r="Z213" s="25"/>
+      <c r="AA213" s="25"/>
+      <c r="AB213" s="25"/>
+      <c r="AC213" s="25"/>
+      <c r="AD213" s="25"/>
+      <c r="AE213" s="25"/>
+      <c r="BN213" s="28"/>
+    </row>
+    <row r="214" spans="23:66" x14ac:dyDescent="0.25">
+      <c r="W214" s="25"/>
+      <c r="X214" s="25"/>
+      <c r="Y214" s="25"/>
+      <c r="Z214" s="25"/>
+      <c r="AA214" s="25"/>
+      <c r="AB214" s="25"/>
+      <c r="AC214" s="25"/>
+      <c r="AD214" s="25"/>
+      <c r="AE214" s="25"/>
+      <c r="BN214" s="28"/>
+    </row>
+    <row r="215" spans="23:66" x14ac:dyDescent="0.25">
+      <c r="W215" s="25"/>
+      <c r="X215" s="25"/>
+      <c r="Y215" s="25"/>
+      <c r="Z215" s="25"/>
+      <c r="AA215" s="25"/>
+      <c r="AB215" s="25"/>
+      <c r="AC215" s="25"/>
+      <c r="AD215" s="25"/>
+      <c r="AE215" s="25"/>
+      <c r="BN215" s="28"/>
+    </row>
+    <row r="216" spans="23:66" x14ac:dyDescent="0.25">
+      <c r="W216" s="25"/>
+      <c r="X216" s="25"/>
+      <c r="Y216" s="25"/>
+      <c r="Z216" s="25"/>
+      <c r="AA216" s="25"/>
+      <c r="AB216" s="25"/>
+      <c r="AC216" s="25"/>
+      <c r="AD216" s="25"/>
+      <c r="AE216" s="25"/>
+      <c r="BN216" s="28"/>
+    </row>
+    <row r="217" spans="23:66" x14ac:dyDescent="0.25">
+      <c r="W217" s="25"/>
+      <c r="X217" s="25"/>
+      <c r="Y217" s="25"/>
+      <c r="Z217" s="25"/>
+      <c r="AA217" s="25"/>
+      <c r="AB217" s="25"/>
+      <c r="AC217" s="25"/>
+      <c r="AD217" s="25"/>
+      <c r="AE217" s="25"/>
+      <c r="BN217" s="28"/>
+    </row>
+    <row r="218" spans="23:66" x14ac:dyDescent="0.25">
+      <c r="W218" s="25"/>
+      <c r="X218" s="25"/>
+      <c r="Y218" s="25"/>
+      <c r="Z218" s="25"/>
+      <c r="AA218" s="25"/>
+      <c r="AB218" s="25"/>
+      <c r="AC218" s="25"/>
+      <c r="AD218" s="25"/>
+      <c r="AE218" s="25"/>
+      <c r="BN218" s="28"/>
+    </row>
+    <row r="219" spans="23:66" x14ac:dyDescent="0.25">
+      <c r="W219" s="25"/>
+      <c r="X219" s="25"/>
+      <c r="Y219" s="25"/>
+      <c r="Z219" s="25"/>
+      <c r="AA219" s="25"/>
+      <c r="AB219" s="25"/>
+      <c r="AC219" s="25"/>
+      <c r="AD219" s="25"/>
+      <c r="AE219" s="25"/>
+      <c r="BN219" s="28"/>
+    </row>
+    <row r="220" spans="23:66" x14ac:dyDescent="0.25">
+      <c r="W220" s="25"/>
+      <c r="X220" s="25"/>
+      <c r="Y220" s="25"/>
+      <c r="Z220" s="25"/>
+      <c r="AA220" s="25"/>
+      <c r="AB220" s="25"/>
+      <c r="AC220" s="25"/>
+      <c r="AD220" s="25"/>
+      <c r="AE220" s="25"/>
+      <c r="BN220" s="28"/>
+    </row>
+    <row r="221" spans="23:66" x14ac:dyDescent="0.25">
+      <c r="W221" s="25"/>
+      <c r="X221" s="25"/>
+      <c r="Y221" s="25"/>
+      <c r="Z221" s="25"/>
+      <c r="AA221" s="25"/>
+      <c r="AB221" s="25"/>
+      <c r="AC221" s="25"/>
+      <c r="AD221" s="25"/>
+      <c r="AE221" s="25"/>
+      <c r="BN221" s="28"/>
+    </row>
+    <row r="222" spans="23:66" x14ac:dyDescent="0.25">
+      <c r="W222" s="25"/>
+      <c r="X222" s="25"/>
+      <c r="Y222" s="25"/>
+      <c r="Z222" s="25"/>
+      <c r="AA222" s="25"/>
+      <c r="AB222" s="25"/>
+      <c r="AC222" s="25"/>
+      <c r="AD222" s="25"/>
+      <c r="AE222" s="25"/>
+      <c r="BN222" s="28"/>
+    </row>
+    <row r="223" spans="23:66" x14ac:dyDescent="0.25">
+      <c r="W223" s="25"/>
+      <c r="X223" s="25"/>
+      <c r="Y223" s="25"/>
+      <c r="Z223" s="25"/>
+      <c r="AA223" s="25"/>
+      <c r="AB223" s="25"/>
+      <c r="AC223" s="25"/>
+      <c r="AD223" s="25"/>
+      <c r="AE223" s="25"/>
+      <c r="BN223" s="28"/>
+    </row>
+    <row r="224" spans="23:66" x14ac:dyDescent="0.25">
+      <c r="W224" s="25"/>
+      <c r="X224" s="25"/>
+      <c r="Y224" s="25"/>
+      <c r="Z224" s="25"/>
+      <c r="AA224" s="25"/>
+      <c r="AB224" s="25"/>
+      <c r="AC224" s="25"/>
+      <c r="AD224" s="25"/>
+      <c r="AE224" s="25"/>
+      <c r="BN224" s="28"/>
+    </row>
+    <row r="225" spans="23:66" x14ac:dyDescent="0.25">
+      <c r="W225" s="25"/>
+      <c r="X225" s="25"/>
+      <c r="Y225" s="25"/>
+      <c r="Z225" s="25"/>
+      <c r="AA225" s="25"/>
+      <c r="AB225" s="25"/>
+      <c r="AC225" s="25"/>
+      <c r="AD225" s="25"/>
+      <c r="AE225" s="25"/>
+      <c r="BN225" s="28"/>
+    </row>
+    <row r="226" spans="23:66" x14ac:dyDescent="0.25">
+      <c r="W226" s="25"/>
+      <c r="X226" s="25"/>
+      <c r="Y226" s="25"/>
+      <c r="Z226" s="25"/>
+      <c r="AA226" s="25"/>
+      <c r="AB226" s="25"/>
+      <c r="AC226" s="25"/>
+      <c r="AD226" s="25"/>
+      <c r="AE226" s="25"/>
+      <c r="BN226" s="28"/>
+    </row>
+    <row r="227" spans="23:66" x14ac:dyDescent="0.25">
+      <c r="W227" s="25"/>
+      <c r="X227" s="25"/>
+      <c r="Y227" s="25"/>
+      <c r="Z227" s="25"/>
+      <c r="AA227" s="25"/>
+      <c r="AB227" s="25"/>
+      <c r="AC227" s="25"/>
+      <c r="AD227" s="25"/>
+      <c r="AE227" s="25"/>
+      <c r="BN227" s="28"/>
+    </row>
+    <row r="228" spans="23:66" x14ac:dyDescent="0.25">
+      <c r="W228" s="25"/>
+      <c r="X228" s="25"/>
+      <c r="Y228" s="25"/>
+      <c r="Z228" s="25"/>
+      <c r="AA228" s="25"/>
+      <c r="AB228" s="25"/>
+      <c r="AC228" s="25"/>
+      <c r="AD228" s="25"/>
+      <c r="AE228" s="25"/>
+      <c r="BN228" s="28"/>
+    </row>
+    <row r="229" spans="23:66" x14ac:dyDescent="0.25">
+      <c r="W229" s="25"/>
+      <c r="X229" s="25"/>
+      <c r="Y229" s="25"/>
+      <c r="Z229" s="25"/>
+      <c r="AA229" s="25"/>
+      <c r="AB229" s="25"/>
+      <c r="AC229" s="25"/>
+      <c r="AD229" s="25"/>
+      <c r="AE229" s="25"/>
+      <c r="BN229" s="28"/>
+    </row>
+    <row r="230" spans="23:66" x14ac:dyDescent="0.25">
+      <c r="W230" s="25"/>
+      <c r="X230" s="25"/>
+      <c r="Y230" s="25"/>
+      <c r="Z230" s="25"/>
+      <c r="AA230" s="25"/>
+      <c r="AB230" s="25"/>
+      <c r="AC230" s="25"/>
+      <c r="AD230" s="25"/>
+      <c r="AE230" s="25"/>
+      <c r="BN230" s="28"/>
+    </row>
+    <row r="231" spans="23:66" x14ac:dyDescent="0.25">
+      <c r="W231" s="25"/>
+      <c r="X231" s="25"/>
+      <c r="Y231" s="25"/>
+      <c r="Z231" s="25"/>
+      <c r="AA231" s="25"/>
+      <c r="AB231" s="25"/>
+      <c r="AC231" s="25"/>
+      <c r="AD231" s="25"/>
+      <c r="AE231" s="25"/>
+      <c r="BN231" s="28"/>
+    </row>
+    <row r="232" spans="23:66" x14ac:dyDescent="0.25">
+      <c r="W232" s="25"/>
+      <c r="X232" s="25"/>
+      <c r="Y232" s="25"/>
+      <c r="Z232" s="25"/>
+      <c r="AA232" s="25"/>
+      <c r="AB232" s="25"/>
+      <c r="AC232" s="25"/>
+      <c r="AD232" s="25"/>
+      <c r="AE232" s="25"/>
+      <c r="BN232" s="28"/>
+    </row>
+    <row r="233" spans="23:66" x14ac:dyDescent="0.25">
+      <c r="W233" s="25"/>
+      <c r="X233" s="25"/>
+      <c r="Y233" s="25"/>
+      <c r="Z233" s="25"/>
+      <c r="AA233" s="25"/>
+      <c r="AB233" s="25"/>
+      <c r="AC233" s="25"/>
+      <c r="AD233" s="25"/>
+      <c r="AE233" s="25"/>
+      <c r="BN233" s="28"/>
+    </row>
+    <row r="234" spans="23:66" x14ac:dyDescent="0.25">
+      <c r="BN234" s="28"/>
+    </row>
+    <row r="235" spans="23:66" x14ac:dyDescent="0.25">
+      <c r="BN235" s="28"/>
+    </row>
+    <row r="236" spans="23:66" x14ac:dyDescent="0.25">
+      <c r="BN236" s="28"/>
+    </row>
+    <row r="237" spans="23:66" x14ac:dyDescent="0.25">
+      <c r="BN237" s="28"/>
+    </row>
+    <row r="238" spans="23:66" x14ac:dyDescent="0.25">
+      <c r="BN238" s="28"/>
+    </row>
+    <row r="239" spans="23:66" x14ac:dyDescent="0.25">
+      <c r="BN239" s="28"/>
+    </row>
+    <row r="240" spans="23:66" x14ac:dyDescent="0.25">
+      <c r="BN240" s="28"/>
+    </row>
+    <row r="241" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN241" s="28"/>
+    </row>
+    <row r="242" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN242" s="28"/>
+    </row>
+    <row r="243" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN243" s="28"/>
+    </row>
+    <row r="244" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN244" s="28"/>
+    </row>
+    <row r="245" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN245" s="28"/>
+    </row>
+    <row r="246" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN246" s="28"/>
+    </row>
+    <row r="247" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN247" s="28"/>
+    </row>
+    <row r="248" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN248" s="28"/>
+    </row>
+    <row r="249" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN249" s="28"/>
+    </row>
+    <row r="250" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN250" s="28"/>
+    </row>
+    <row r="251" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN251" s="28"/>
+    </row>
+    <row r="252" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN252" s="28"/>
+    </row>
+    <row r="253" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN253" s="28"/>
+    </row>
+    <row r="254" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN254" s="28"/>
+    </row>
+    <row r="255" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN255" s="28"/>
+    </row>
+    <row r="256" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN256" s="28"/>
+    </row>
+    <row r="257" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN257" s="28"/>
+    </row>
+    <row r="258" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN258" s="28"/>
+    </row>
+    <row r="259" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN259" s="28"/>
+    </row>
+    <row r="260" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN260" s="28"/>
+    </row>
+    <row r="261" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN261" s="28"/>
+    </row>
+    <row r="262" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN262" s="28"/>
+    </row>
+    <row r="263" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN263" s="28"/>
+    </row>
+    <row r="264" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN264" s="28"/>
+    </row>
+    <row r="265" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN265" s="28"/>
+    </row>
+    <row r="266" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN266" s="28"/>
+    </row>
+    <row r="267" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN267" s="28"/>
+    </row>
+    <row r="268" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN268" s="28"/>
+    </row>
+    <row r="269" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN269" s="28"/>
+    </row>
+    <row r="270" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN270" s="28"/>
+    </row>
+    <row r="271" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN271" s="28"/>
+    </row>
+    <row r="272" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN272" s="28"/>
+    </row>
+    <row r="273" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN273" s="28"/>
+    </row>
+    <row r="274" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN274" s="28"/>
+    </row>
+    <row r="275" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN275" s="28"/>
+    </row>
+    <row r="276" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN276" s="28"/>
+    </row>
+    <row r="277" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN277" s="28"/>
+    </row>
+    <row r="278" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN278" s="28"/>
+    </row>
+    <row r="279" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN279" s="28"/>
+    </row>
+    <row r="280" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN280" s="28"/>
+    </row>
+    <row r="281" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN281" s="28"/>
+    </row>
+    <row r="282" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN282" s="28"/>
+    </row>
+    <row r="283" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN283" s="28"/>
+    </row>
+    <row r="284" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN284" s="28"/>
+    </row>
+    <row r="285" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN285" s="28"/>
+    </row>
+    <row r="286" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN286" s="28"/>
+    </row>
+    <row r="287" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN287" s="28"/>
+    </row>
+    <row r="288" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN288" s="28"/>
+    </row>
+    <row r="289" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN289" s="28"/>
+    </row>
+    <row r="290" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN290" s="28"/>
+    </row>
+    <row r="291" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN291" s="28"/>
+    </row>
+    <row r="292" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN292" s="28"/>
+    </row>
+    <row r="293" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN293" s="28"/>
+    </row>
+    <row r="294" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN294" s="28"/>
+    </row>
+    <row r="295" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN295" s="28"/>
+    </row>
+    <row r="296" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN296" s="28"/>
+    </row>
+    <row r="297" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN297" s="28"/>
+    </row>
+    <row r="298" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN298" s="28"/>
+    </row>
+    <row r="299" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN299" s="28"/>
+    </row>
+    <row r="300" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN300" s="28"/>
+    </row>
+    <row r="301" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN301" s="28"/>
+    </row>
+    <row r="302" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN302" s="28"/>
+    </row>
+    <row r="303" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN303" s="28"/>
+    </row>
+    <row r="304" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN304" s="28"/>
+    </row>
+    <row r="305" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN305" s="28"/>
+    </row>
+    <row r="306" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN306" s="28"/>
+    </row>
+    <row r="307" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN307" s="28"/>
+    </row>
+    <row r="308" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN308" s="28"/>
+    </row>
+    <row r="309" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN309" s="28"/>
+    </row>
+    <row r="310" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN310" s="28"/>
+    </row>
+    <row r="311" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN311" s="28"/>
+    </row>
+    <row r="312" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN312" s="28"/>
+    </row>
+    <row r="313" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN313" s="28"/>
+    </row>
+    <row r="314" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN314" s="28"/>
+    </row>
+    <row r="315" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN315" s="28"/>
+    </row>
+    <row r="316" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN316" s="28"/>
+    </row>
+    <row r="317" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN317" s="28"/>
+    </row>
+    <row r="318" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN318" s="28"/>
+    </row>
+    <row r="319" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN319" s="28"/>
+    </row>
+    <row r="320" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN320" s="28"/>
+    </row>
+    <row r="321" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN321" s="28"/>
+    </row>
+    <row r="322" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN322" s="28"/>
+    </row>
+    <row r="323" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN323" s="28"/>
+    </row>
+    <row r="324" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN324" s="28"/>
+    </row>
+    <row r="325" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN325" s="28"/>
+    </row>
+    <row r="326" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN326" s="28"/>
+    </row>
+    <row r="327" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN327" s="28"/>
+    </row>
+    <row r="328" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN328" s="28"/>
+    </row>
+    <row r="329" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN329" s="28"/>
+    </row>
+    <row r="330" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN330" s="28"/>
+    </row>
+    <row r="331" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN331" s="28"/>
+    </row>
+    <row r="332" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN332" s="28"/>
+    </row>
+    <row r="333" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN333" s="28"/>
+    </row>
+    <row r="334" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN334" s="28"/>
+    </row>
+    <row r="335" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN335" s="28"/>
+    </row>
+    <row r="336" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN336" s="28"/>
+    </row>
+    <row r="337" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN337" s="28"/>
+    </row>
+    <row r="338" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN338" s="28"/>
+    </row>
+    <row r="339" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN339" s="28"/>
+    </row>
+    <row r="340" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN340" s="28"/>
+    </row>
+    <row r="341" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN341" s="28"/>
+    </row>
+    <row r="342" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN342" s="28"/>
+    </row>
+    <row r="343" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN343" s="28"/>
+    </row>
+    <row r="344" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN344" s="28"/>
+    </row>
+    <row r="345" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN345" s="28"/>
+    </row>
+    <row r="346" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN346" s="28"/>
+    </row>
+    <row r="347" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN347" s="28"/>
+    </row>
+    <row r="348" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN348" s="28"/>
+    </row>
+    <row r="349" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN349" s="28"/>
+    </row>
+    <row r="350" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN350" s="28"/>
+    </row>
+    <row r="351" spans="66:66" x14ac:dyDescent="0.25">
+      <c r="BN351" s="28"/>
     </row>
   </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="D116:G116"/>
+    <mergeCell ref="W29:AD30"/>
+    <mergeCell ref="W32:AD33"/>
+    <mergeCell ref="W35:AD36"/>
+    <mergeCell ref="W38:AD39"/>
+    <mergeCell ref="D50:G50"/>
+    <mergeCell ref="D62:G62"/>
+    <mergeCell ref="E14:I15"/>
+    <mergeCell ref="W17:AD18"/>
+    <mergeCell ref="W20:AD21"/>
+    <mergeCell ref="W23:AD24"/>
+    <mergeCell ref="W26:AD27"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="F55" location="'AUTOMATION CONTROL'!D62" display="1. Automate Webpages " xr:uid="{D0968135-C58E-46C6-9C10-12729229DAC1}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="256" orientation="portrait" horizontalDpi="4294967292" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/DOCUMENTATION/WEB_SCRAPE_AUTOMATIOn.xlsx
+++ b/DOCUMENTATION/WEB_SCRAPE_AUTOMATIOn.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vincent\UNIFIED_SYSTEM_AUTOMATION\DOCUMENTATION\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UNIFIED_SYSTEM_AUTOMATION\DOCUMENTATION\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B3C70B6-5751-489C-8AB2-540C9FD92C07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DFB2F0C-A621-485A-AAB9-CACF82B7AC2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{AF954AEF-E990-4149-A50E-313C2C1CB0ED}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{AF954AEF-E990-4149-A50E-313C2C1CB0ED}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="55">
   <si>
     <t xml:space="preserve">WEB_SCRAPE Automation User's Manual </t>
   </si>
@@ -118,24 +118,6 @@
     <t>Automation Control</t>
   </si>
   <si>
-    <t>STOP: This will automatically interrupt the ongoing execution.</t>
-  </si>
-  <si>
-    <t>START AUTOMATION: This launches the Full country along with its platforms and categories in a background thread.</t>
-  </si>
-  <si>
-    <t>SCRAPE FILES: A function that used to extract data out of the existing folder containing  a MHTML files.</t>
-  </si>
-  <si>
-    <t>FILTER INPUT &amp; LOG-LEVEL : This will highlighted all the match value selected or Inputted by the user.</t>
-  </si>
-  <si>
-    <t>CLEAR FILTER: This unfiltered all the matching lines that selected or inputted by the user.</t>
-  </si>
-  <si>
-    <t>LOG OUTPUT: This display all the activities happening in the START AUTOMATION and SCRAPE FILES functions.</t>
-  </si>
-  <si>
     <t>How to use</t>
   </si>
   <si>
@@ -143,9 +125,6 @@
   </si>
   <si>
     <t>1.To begin in automating webpages, click 'START AUTOMATION'.</t>
-  </si>
-  <si>
-    <t>4. When finished a dialog appeared containing a no. of successful and failed during automating along with the location of folder that have MHTML and excel files.</t>
   </si>
   <si>
     <t>`</t>
@@ -159,12 +138,121 @@
   <si>
     <t>1.Scrape MHTML Files</t>
   </si>
+  <si>
+    <t>4. When finished a dialog appeared containing a no. of successful and failed during automation along with the location of folder that have MHTML and excel files.</t>
+  </si>
+  <si>
+    <t>Overview</t>
+  </si>
+  <si>
+    <t>The Automation Control tab is the main operational screen. It automatically visits multiple app store intelligence platforms across 22 countries, captures each page as an MHTML snapshot, and extracts the top app rankings into an Excel file — all without manual intervention.</t>
+  </si>
+  <si>
+    <t>What it does:</t>
+  </si>
+  <si>
+    <t>Opens Google Chrome automatically and navigates to each configured platform</t>
+  </si>
+  <si>
+    <t>Visits every combination of country, app platform (Android / Apple), and category</t>
+  </si>
+  <si>
+    <t>Saves each page as an MHTML file to your local drive</t>
+  </si>
+  <si>
+    <t>Immediately extracts app ranking data into All_platforms.xlsx</t>
+  </si>
+  <si>
+    <t>Skips any country/category already captured in a previous session</t>
+  </si>
+  <si>
+    <t>Before you start:</t>
+  </si>
+  <si>
+    <t>⚠️ Do NOT close the application or the Chrome browser while running.
+Use the STOP button inside the app if you need to end the session early.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">⚠️ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>WARNING — Set Power &amp; Sleep to NEVER before starting</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Go to: Settings → System → Power &amp; Sleep → set both Screen and Sleep to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Never</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. The automation runs for several hours. If the PC sleeps, the browser may close itself and the session will fail.</t>
+    </r>
+  </si>
+  <si>
+    <t>📝 Make sure Google Chrome is installed.
+ChromeDriver is downloaded automatically — no manual installation needed.</t>
+  </si>
+  <si>
+    <t>START AUTOMATION: Launches the full automation loop in a background thread. The GUI stays responsive while it runs.</t>
+  </si>
+  <si>
+    <t>STOP: Sends a stop signal. The current page capture finishes first, then the loop exits cleanly.</t>
+  </si>
+  <si>
+    <t>SCRAPE FILES: Extracts data from an existing folder of MHTML files without re-running the browser.</t>
+  </si>
+  <si>
+    <t>Automation Control - Summary</t>
+  </si>
+  <si>
+    <t>CLEAR LOGS: Wipes the log display. Does not affect the automation.</t>
+  </si>
+  <si>
+    <t>COPY ALL: Copies full log text to clipboard for troubleshooting.</t>
+  </si>
+  <si>
+    <t>FILTER INPUT &amp; LOG-LEVEL : Type a keyword to highlight matching lines in yellow and Filter by ALL, INFO, WARNING, or ERROR.</t>
+  </si>
+  <si>
+    <t>CLEAR FILTER: Removes all filters and restores the full log view.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -242,6 +330,22 @@
       <u/>
       <sz val="14"/>
       <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -438,13 +542,13 @@
     </border>
     <border>
       <left style="medium">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </left>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="medium">
         <color indexed="64"/>
-      </bottom>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -452,7 +556,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -479,6 +583,27 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -497,24 +622,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="6"/>
@@ -522,26 +637,58 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="6"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2557,8 +2704,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="2291711" y="3235978"/>
-          <a:ext cx="8831120" cy="6131956"/>
+          <a:off x="2291711" y="3214331"/>
+          <a:ext cx="8831120" cy="5997740"/>
           <a:chOff x="2469366" y="5346324"/>
           <a:chExt cx="8923895" cy="5997740"/>
         </a:xfrm>
@@ -3685,7 +3832,7 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>600076</xdr:colOff>
-      <xdr:row>68</xdr:row>
+      <xdr:row>79</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="5355262" cy="3836355"/>
@@ -3730,13 +3877,13 @@
     <xdr:from>
       <xdr:col>14</xdr:col>
       <xdr:colOff>145677</xdr:colOff>
-      <xdr:row>75</xdr:row>
+      <xdr:row>86</xdr:row>
       <xdr:rowOff>11206</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>518967</xdr:colOff>
-      <xdr:row>77</xdr:row>
+      <xdr:row>88</xdr:row>
       <xdr:rowOff>114838</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -3793,13 +3940,13 @@
     <xdr:from>
       <xdr:col>16</xdr:col>
       <xdr:colOff>34217</xdr:colOff>
-      <xdr:row>67</xdr:row>
+      <xdr:row>78</xdr:row>
       <xdr:rowOff>80945</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>28</xdr:col>
       <xdr:colOff>293760</xdr:colOff>
-      <xdr:row>87</xdr:row>
+      <xdr:row>98</xdr:row>
       <xdr:rowOff>175287</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3837,13 +3984,13 @@
     <xdr:from>
       <xdr:col>32</xdr:col>
       <xdr:colOff>492638</xdr:colOff>
-      <xdr:row>67</xdr:row>
+      <xdr:row>78</xdr:row>
       <xdr:rowOff>48727</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>38</xdr:col>
       <xdr:colOff>544894</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>87</xdr:row>
       <xdr:rowOff>1753</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3882,13 +4029,13 @@
     <xdr:from>
       <xdr:col>35</xdr:col>
       <xdr:colOff>241964</xdr:colOff>
-      <xdr:row>78</xdr:row>
+      <xdr:row>89</xdr:row>
       <xdr:rowOff>47369</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>42</xdr:col>
       <xdr:colOff>484500</xdr:colOff>
-      <xdr:row>91</xdr:row>
+      <xdr:row>102</xdr:row>
       <xdr:rowOff>5344</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3926,13 +4073,13 @@
     <xdr:from>
       <xdr:col>29</xdr:col>
       <xdr:colOff>331304</xdr:colOff>
-      <xdr:row>75</xdr:row>
+      <xdr:row>86</xdr:row>
       <xdr:rowOff>96631</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>31</xdr:col>
       <xdr:colOff>97204</xdr:colOff>
-      <xdr:row>78</xdr:row>
+      <xdr:row>89</xdr:row>
       <xdr:rowOff>7002</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -3989,13 +4136,13 @@
     <xdr:from>
       <xdr:col>45</xdr:col>
       <xdr:colOff>241904</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>87</xdr:row>
       <xdr:rowOff>166310</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>47</xdr:col>
       <xdr:colOff>7804</xdr:colOff>
-      <xdr:row>79</xdr:row>
+      <xdr:row>90</xdr:row>
       <xdr:rowOff>76680</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -4052,13 +4199,13 @@
     <xdr:from>
       <xdr:col>47</xdr:col>
       <xdr:colOff>78992</xdr:colOff>
-      <xdr:row>68</xdr:row>
+      <xdr:row>79</xdr:row>
       <xdr:rowOff>6431</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>57</xdr:col>
       <xdr:colOff>419017</xdr:colOff>
-      <xdr:row>93</xdr:row>
+      <xdr:row>104</xdr:row>
       <xdr:rowOff>480</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4416,49 +4563,49 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
     </row>
     <row r="2" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A2" s="20"/>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
+      <c r="A2" s="37"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
     </row>
     <row r="3" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
+      <c r="B3" s="38"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="38"/>
+      <c r="I3" s="38"/>
     </row>
     <row r="5" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
+      <c r="B5" s="35"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35"/>
     </row>
     <row r="7" spans="1:42" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
@@ -4501,12 +4648,12 @@
       </c>
     </row>
     <row r="16" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
+      <c r="B16" s="34"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="34"/>
       <c r="AN16" t="s">
         <v>12</v>
       </c>
@@ -4543,12 +4690,12 @@
       </c>
     </row>
     <row r="41" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A41" s="16" t="s">
+      <c r="A41" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="B41" s="16"/>
-      <c r="C41" s="16"/>
-      <c r="D41" s="16"/>
+      <c r="B41" s="33"/>
+      <c r="C41" s="33"/>
+      <c r="D41" s="33"/>
     </row>
     <row r="45" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
@@ -4597,82 +4744,82 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="10" spans="4:114" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="AD10" s="30"/>
-      <c r="AE10" s="30"/>
-      <c r="AF10" s="30"/>
-      <c r="AG10" s="30"/>
-      <c r="AH10" s="30"/>
-      <c r="AI10" s="30"/>
-      <c r="AJ10" s="30"/>
-      <c r="AK10" s="30"/>
-      <c r="AL10" s="30"/>
-      <c r="AM10" s="30"/>
-      <c r="AN10" s="30"/>
-      <c r="AO10" s="30"/>
-      <c r="AP10" s="30"/>
-      <c r="AQ10" s="30"/>
-      <c r="AR10" s="30"/>
-      <c r="AS10" s="30"/>
-      <c r="AT10" s="30"/>
-      <c r="AU10" s="30"/>
-      <c r="AV10" s="30"/>
-      <c r="AW10" s="30"/>
-      <c r="AX10" s="30"/>
-      <c r="AY10" s="30"/>
-      <c r="AZ10" s="30"/>
-      <c r="BA10" s="30"/>
-      <c r="BB10" s="30"/>
-      <c r="BC10" s="30"/>
-      <c r="BD10" s="30"/>
-      <c r="BE10" s="30"/>
-      <c r="BF10" s="30"/>
-      <c r="BG10" s="30"/>
-      <c r="BH10" s="30"/>
-      <c r="BI10" s="30"/>
-      <c r="BJ10" s="30"/>
-      <c r="BK10" s="30"/>
-      <c r="BL10" s="30"/>
-      <c r="BM10" s="30"/>
-      <c r="BN10" s="30"/>
-      <c r="BO10" s="25"/>
-      <c r="BP10" s="25"/>
-      <c r="BQ10" s="25"/>
-      <c r="BR10" s="25"/>
-      <c r="BS10" s="25"/>
-      <c r="BT10" s="25"/>
-      <c r="BU10" s="25"/>
-      <c r="BV10" s="25"/>
-      <c r="BW10" s="25"/>
-      <c r="BX10" s="25"/>
-      <c r="BY10" s="25"/>
-      <c r="BZ10" s="25"/>
-      <c r="CA10" s="25"/>
-      <c r="CB10" s="25"/>
-      <c r="CC10" s="25"/>
-      <c r="CD10" s="25"/>
-      <c r="CE10" s="25"/>
-      <c r="CF10" s="25"/>
-      <c r="CG10" s="25"/>
-      <c r="CH10" s="25"/>
-      <c r="CI10" s="25"/>
-      <c r="CJ10" s="25"/>
-      <c r="CK10" s="25"/>
-      <c r="CL10" s="25"/>
-      <c r="CM10" s="25"/>
-      <c r="CN10" s="25"/>
-      <c r="CO10" s="25"/>
-      <c r="CP10" s="25"/>
-      <c r="CQ10" s="25"/>
-      <c r="CR10" s="25"/>
-      <c r="CS10" s="25"/>
-      <c r="CT10" s="25"/>
-      <c r="CU10" s="25"/>
-      <c r="CV10" s="25"/>
-      <c r="CW10" s="25"/>
-      <c r="CX10" s="25"/>
-      <c r="CY10" s="25"/>
-      <c r="CZ10" s="25"/>
-      <c r="DA10" s="30"/>
+      <c r="AD10" s="21"/>
+      <c r="AE10" s="21"/>
+      <c r="AF10" s="21"/>
+      <c r="AG10" s="21"/>
+      <c r="AH10" s="21"/>
+      <c r="AI10" s="21"/>
+      <c r="AJ10" s="21"/>
+      <c r="AK10" s="21"/>
+      <c r="AL10" s="21"/>
+      <c r="AM10" s="21"/>
+      <c r="AN10" s="21"/>
+      <c r="AO10" s="21"/>
+      <c r="AP10" s="21"/>
+      <c r="AQ10" s="21"/>
+      <c r="AR10" s="21"/>
+      <c r="AS10" s="21"/>
+      <c r="AT10" s="21"/>
+      <c r="AU10" s="21"/>
+      <c r="AV10" s="21"/>
+      <c r="AW10" s="21"/>
+      <c r="AX10" s="21"/>
+      <c r="AY10" s="21"/>
+      <c r="AZ10" s="21"/>
+      <c r="BA10" s="21"/>
+      <c r="BB10" s="21"/>
+      <c r="BC10" s="21"/>
+      <c r="BD10" s="21"/>
+      <c r="BE10" s="21"/>
+      <c r="BF10" s="21"/>
+      <c r="BG10" s="21"/>
+      <c r="BH10" s="21"/>
+      <c r="BI10" s="21"/>
+      <c r="BJ10" s="21"/>
+      <c r="BK10" s="21"/>
+      <c r="BL10" s="21"/>
+      <c r="BM10" s="21"/>
+      <c r="BN10" s="21"/>
+      <c r="BO10" s="16"/>
+      <c r="BP10" s="16"/>
+      <c r="BQ10" s="16"/>
+      <c r="BR10" s="16"/>
+      <c r="BS10" s="16"/>
+      <c r="BT10" s="16"/>
+      <c r="BU10" s="16"/>
+      <c r="BV10" s="16"/>
+      <c r="BW10" s="16"/>
+      <c r="BX10" s="16"/>
+      <c r="BY10" s="16"/>
+      <c r="BZ10" s="16"/>
+      <c r="CA10" s="16"/>
+      <c r="CB10" s="16"/>
+      <c r="CC10" s="16"/>
+      <c r="CD10" s="16"/>
+      <c r="CE10" s="16"/>
+      <c r="CF10" s="16"/>
+      <c r="CG10" s="16"/>
+      <c r="CH10" s="16"/>
+      <c r="CI10" s="16"/>
+      <c r="CJ10" s="16"/>
+      <c r="CK10" s="16"/>
+      <c r="CL10" s="16"/>
+      <c r="CM10" s="16"/>
+      <c r="CN10" s="16"/>
+      <c r="CO10" s="16"/>
+      <c r="CP10" s="16"/>
+      <c r="CQ10" s="16"/>
+      <c r="CR10" s="16"/>
+      <c r="CS10" s="16"/>
+      <c r="CT10" s="16"/>
+      <c r="CU10" s="16"/>
+      <c r="CV10" s="16"/>
+      <c r="CW10" s="16"/>
+      <c r="CX10" s="16"/>
+      <c r="CY10" s="16"/>
+      <c r="CZ10" s="16"/>
+      <c r="DA10" s="21"/>
     </row>
     <row r="11" spans="4:114" ht="24" x14ac:dyDescent="0.25">
       <c r="D11" s="15" t="s">
@@ -4703,81 +4850,81 @@
       <c r="AA11" s="12"/>
       <c r="AB11" s="12"/>
       <c r="AC11" s="12"/>
-      <c r="AD11" s="41"/>
-      <c r="AE11" s="42"/>
-      <c r="AF11" s="43"/>
-      <c r="AG11" s="43"/>
-      <c r="AH11" s="43"/>
-      <c r="AI11" s="43"/>
-      <c r="AJ11" s="43"/>
-      <c r="AK11" s="43"/>
-      <c r="AL11" s="43"/>
-      <c r="AM11" s="43"/>
-      <c r="AN11" s="43"/>
-      <c r="AO11" s="43"/>
-      <c r="AP11" s="43"/>
-      <c r="AQ11" s="43"/>
-      <c r="AR11" s="43"/>
-      <c r="AS11" s="43"/>
-      <c r="AT11" s="43"/>
-      <c r="AU11" s="43"/>
-      <c r="AV11" s="43"/>
-      <c r="AW11" s="43"/>
-      <c r="AX11" s="43"/>
-      <c r="AY11" s="43"/>
-      <c r="AZ11" s="43"/>
-      <c r="BA11" s="43"/>
-      <c r="BB11" s="43"/>
-      <c r="BC11" s="43"/>
-      <c r="BD11" s="43"/>
-      <c r="BE11" s="43"/>
-      <c r="BF11" s="43"/>
-      <c r="BG11" s="43"/>
-      <c r="BH11" s="43"/>
-      <c r="BI11" s="43"/>
-      <c r="BJ11" s="43"/>
-      <c r="BK11" s="43"/>
-      <c r="BL11" s="43"/>
-      <c r="BM11" s="43"/>
-      <c r="BN11" s="44"/>
-      <c r="BO11" s="25"/>
-      <c r="BP11" s="25"/>
-      <c r="BQ11" s="25"/>
-      <c r="BR11" s="25"/>
-      <c r="BS11" s="25"/>
-      <c r="BT11" s="25"/>
-      <c r="BU11" s="25"/>
-      <c r="BV11" s="25"/>
-      <c r="BW11" s="25"/>
-      <c r="BX11" s="25"/>
-      <c r="BY11" s="25"/>
-      <c r="BZ11" s="25"/>
-      <c r="CA11" s="25"/>
-      <c r="CB11" s="25"/>
-      <c r="CC11" s="25"/>
-      <c r="CD11" s="25"/>
-      <c r="CE11" s="25"/>
-      <c r="CF11" s="25"/>
-      <c r="CG11" s="25"/>
-      <c r="CH11" s="25"/>
-      <c r="CI11" s="25"/>
-      <c r="CJ11" s="25"/>
-      <c r="CK11" s="25"/>
-      <c r="CL11" s="25"/>
-      <c r="CM11" s="25"/>
-      <c r="CN11" s="25"/>
-      <c r="CO11" s="25"/>
-      <c r="CP11" s="25"/>
-      <c r="CQ11" s="25"/>
-      <c r="CR11" s="25"/>
-      <c r="CS11" s="25"/>
-      <c r="CT11" s="25"/>
-      <c r="CU11" s="25"/>
-      <c r="CV11" s="25"/>
-      <c r="CW11" s="25"/>
-      <c r="CX11" s="25"/>
-      <c r="CY11" s="25"/>
-      <c r="CZ11" s="25"/>
+      <c r="AD11" s="27"/>
+      <c r="AE11" s="28"/>
+      <c r="AF11" s="29"/>
+      <c r="AG11" s="29"/>
+      <c r="AH11" s="29"/>
+      <c r="AI11" s="29"/>
+      <c r="AJ11" s="29"/>
+      <c r="AK11" s="29"/>
+      <c r="AL11" s="29"/>
+      <c r="AM11" s="29"/>
+      <c r="AN11" s="29"/>
+      <c r="AO11" s="29"/>
+      <c r="AP11" s="29"/>
+      <c r="AQ11" s="29"/>
+      <c r="AR11" s="29"/>
+      <c r="AS11" s="29"/>
+      <c r="AT11" s="29"/>
+      <c r="AU11" s="29"/>
+      <c r="AV11" s="29"/>
+      <c r="AW11" s="29"/>
+      <c r="AX11" s="29"/>
+      <c r="AY11" s="29"/>
+      <c r="AZ11" s="29"/>
+      <c r="BA11" s="29"/>
+      <c r="BB11" s="29"/>
+      <c r="BC11" s="29"/>
+      <c r="BD11" s="29"/>
+      <c r="BE11" s="29"/>
+      <c r="BF11" s="29"/>
+      <c r="BG11" s="29"/>
+      <c r="BH11" s="29"/>
+      <c r="BI11" s="29"/>
+      <c r="BJ11" s="29"/>
+      <c r="BK11" s="29"/>
+      <c r="BL11" s="29"/>
+      <c r="BM11" s="29"/>
+      <c r="BN11" s="30"/>
+      <c r="BO11" s="16"/>
+      <c r="BP11" s="16"/>
+      <c r="BQ11" s="16"/>
+      <c r="BR11" s="16"/>
+      <c r="BS11" s="16"/>
+      <c r="BT11" s="16"/>
+      <c r="BU11" s="16"/>
+      <c r="BV11" s="16"/>
+      <c r="BW11" s="16"/>
+      <c r="BX11" s="16"/>
+      <c r="BY11" s="16"/>
+      <c r="BZ11" s="16"/>
+      <c r="CA11" s="16"/>
+      <c r="CB11" s="16"/>
+      <c r="CC11" s="16"/>
+      <c r="CD11" s="16"/>
+      <c r="CE11" s="16"/>
+      <c r="CF11" s="16"/>
+      <c r="CG11" s="16"/>
+      <c r="CH11" s="16"/>
+      <c r="CI11" s="16"/>
+      <c r="CJ11" s="16"/>
+      <c r="CK11" s="16"/>
+      <c r="CL11" s="16"/>
+      <c r="CM11" s="16"/>
+      <c r="CN11" s="16"/>
+      <c r="CO11" s="16"/>
+      <c r="CP11" s="16"/>
+      <c r="CQ11" s="16"/>
+      <c r="CR11" s="16"/>
+      <c r="CS11" s="16"/>
+      <c r="CT11" s="16"/>
+      <c r="CU11" s="16"/>
+      <c r="CV11" s="16"/>
+      <c r="CW11" s="16"/>
+      <c r="CX11" s="16"/>
+      <c r="CY11" s="16"/>
+      <c r="CZ11" s="16"/>
     </row>
     <row r="12" spans="4:114" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D12" s="14"/>
@@ -4800,99 +4947,99 @@
       <c r="U12" s="4"/>
       <c r="V12" s="4"/>
       <c r="W12" s="4"/>
-      <c r="X12" s="32"/>
+      <c r="X12" s="23"/>
       <c r="Y12" s="4"/>
       <c r="Z12" s="4"/>
       <c r="AA12" s="4"/>
       <c r="AB12" s="4"/>
       <c r="AC12" s="4"/>
-      <c r="AD12" s="41"/>
-      <c r="AE12" s="45"/>
-      <c r="AF12" s="45"/>
-      <c r="AG12" s="45"/>
-      <c r="AH12" s="45"/>
-      <c r="AI12" s="45"/>
-      <c r="AJ12" s="45"/>
-      <c r="AK12" s="45"/>
-      <c r="AL12" s="45"/>
-      <c r="AM12" s="45"/>
-      <c r="AN12" s="45"/>
-      <c r="AO12" s="45"/>
-      <c r="AP12" s="45"/>
-      <c r="AQ12" s="45"/>
-      <c r="AR12" s="45"/>
-      <c r="AS12" s="45"/>
-      <c r="AT12" s="45"/>
-      <c r="AU12" s="45"/>
-      <c r="AV12" s="45"/>
-      <c r="AW12" s="45"/>
-      <c r="AX12" s="45"/>
-      <c r="AY12" s="45"/>
-      <c r="AZ12" s="45"/>
-      <c r="BA12" s="45"/>
-      <c r="BB12" s="45"/>
-      <c r="BC12" s="45"/>
-      <c r="BD12" s="45"/>
-      <c r="BE12" s="45"/>
-      <c r="BF12" s="45"/>
-      <c r="BG12" s="45"/>
-      <c r="BH12" s="45"/>
-      <c r="BI12" s="45"/>
-      <c r="BJ12" s="45"/>
-      <c r="BK12" s="45"/>
-      <c r="BL12" s="45"/>
-      <c r="BM12" s="45"/>
-      <c r="BN12" s="46"/>
-      <c r="BO12" s="25"/>
-      <c r="BP12" s="25"/>
-      <c r="BQ12" s="25"/>
-      <c r="BR12" s="25"/>
-      <c r="BS12" s="25"/>
-      <c r="BT12" s="25"/>
-      <c r="BU12" s="25"/>
-      <c r="BV12" s="25"/>
-      <c r="BW12" s="25"/>
-      <c r="BX12" s="25"/>
-      <c r="BY12" s="25"/>
-      <c r="BZ12" s="25"/>
-      <c r="CA12" s="25"/>
-      <c r="CB12" s="25"/>
-      <c r="CC12" s="25"/>
-      <c r="CD12" s="25"/>
-      <c r="CE12" s="25"/>
-      <c r="CF12" s="25"/>
-      <c r="CG12" s="25"/>
-      <c r="CH12" s="25"/>
-      <c r="CI12" s="25"/>
-      <c r="CJ12" s="25"/>
-      <c r="CK12" s="25"/>
-      <c r="CL12" s="25"/>
-      <c r="CM12" s="25"/>
-      <c r="CN12" s="25"/>
-      <c r="CO12" s="25"/>
-      <c r="CP12" s="25"/>
-      <c r="CQ12" s="25"/>
-      <c r="CR12" s="25"/>
-      <c r="CS12" s="25"/>
-      <c r="CT12" s="25"/>
-      <c r="CU12" s="25"/>
-      <c r="CV12" s="25"/>
-      <c r="CW12" s="25"/>
-      <c r="CX12" s="25"/>
-      <c r="CY12" s="25"/>
-      <c r="CZ12" s="25"/>
-      <c r="DA12" s="30"/>
-      <c r="DB12" s="30"/>
-      <c r="DC12" s="30"/>
-      <c r="DD12" s="30"/>
-      <c r="DE12" s="30"/>
-      <c r="DF12" s="30"/>
-      <c r="DG12" s="30"/>
-      <c r="DH12" s="30"/>
-      <c r="DI12" s="30"/>
-      <c r="DJ12" s="30"/>
-    </row>
-    <row r="13" spans="4:114" x14ac:dyDescent="0.25">
+      <c r="AD12" s="27"/>
+      <c r="AE12" s="31"/>
+      <c r="AF12" s="31"/>
+      <c r="AG12" s="31"/>
+      <c r="AH12" s="31"/>
+      <c r="AI12" s="31"/>
+      <c r="AJ12" s="31"/>
+      <c r="AK12" s="31"/>
+      <c r="AL12" s="31"/>
+      <c r="AM12" s="31"/>
+      <c r="AN12" s="31"/>
+      <c r="AO12" s="31"/>
+      <c r="AP12" s="31"/>
+      <c r="AQ12" s="31"/>
+      <c r="AR12" s="31"/>
+      <c r="AS12" s="31"/>
+      <c r="AT12" s="31"/>
+      <c r="AU12" s="31"/>
+      <c r="AV12" s="31"/>
+      <c r="AW12" s="31"/>
+      <c r="AX12" s="31"/>
+      <c r="AY12" s="31"/>
+      <c r="AZ12" s="31"/>
+      <c r="BA12" s="31"/>
+      <c r="BB12" s="31"/>
+      <c r="BC12" s="31"/>
+      <c r="BD12" s="31"/>
+      <c r="BE12" s="31"/>
+      <c r="BF12" s="31"/>
+      <c r="BG12" s="31"/>
+      <c r="BH12" s="31"/>
+      <c r="BI12" s="31"/>
+      <c r="BJ12" s="31"/>
+      <c r="BK12" s="31"/>
+      <c r="BL12" s="31"/>
+      <c r="BM12" s="31"/>
+      <c r="BN12" s="32"/>
+      <c r="BO12" s="16"/>
+      <c r="BP12" s="16"/>
+      <c r="BQ12" s="16"/>
+      <c r="BR12" s="16"/>
+      <c r="BS12" s="16"/>
+      <c r="BT12" s="16"/>
+      <c r="BU12" s="16"/>
+      <c r="BV12" s="16"/>
+      <c r="BW12" s="16"/>
+      <c r="BX12" s="16"/>
+      <c r="BY12" s="16"/>
+      <c r="BZ12" s="16"/>
+      <c r="CA12" s="16"/>
+      <c r="CB12" s="16"/>
+      <c r="CC12" s="16"/>
+      <c r="CD12" s="16"/>
+      <c r="CE12" s="16"/>
+      <c r="CF12" s="16"/>
+      <c r="CG12" s="16"/>
+      <c r="CH12" s="16"/>
+      <c r="CI12" s="16"/>
+      <c r="CJ12" s="16"/>
+      <c r="CK12" s="16"/>
+      <c r="CL12" s="16"/>
+      <c r="CM12" s="16"/>
+      <c r="CN12" s="16"/>
+      <c r="CO12" s="16"/>
+      <c r="CP12" s="16"/>
+      <c r="CQ12" s="16"/>
+      <c r="CR12" s="16"/>
+      <c r="CS12" s="16"/>
+      <c r="CT12" s="16"/>
+      <c r="CU12" s="16"/>
+      <c r="CV12" s="16"/>
+      <c r="CW12" s="16"/>
+      <c r="CX12" s="16"/>
+      <c r="CY12" s="16"/>
+      <c r="CZ12" s="16"/>
+      <c r="DA12" s="21"/>
+      <c r="DB12" s="21"/>
+      <c r="DC12" s="21"/>
+      <c r="DD12" s="21"/>
+      <c r="DE12" s="21"/>
+      <c r="DF12" s="21"/>
+      <c r="DG12" s="21"/>
+      <c r="DH12" s="21"/>
+      <c r="DI12" s="21"/>
+      <c r="DJ12" s="21"/>
+    </row>
+    <row r="13" spans="4:114" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D13" s="5"/>
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
@@ -4919,538 +5066,677 @@
       <c r="AB13" s="6"/>
       <c r="AC13" s="6"/>
       <c r="AD13" s="6"/>
-      <c r="AH13" s="26"/>
-      <c r="BN13" s="28"/>
-    </row>
-    <row r="14" spans="4:114" x14ac:dyDescent="0.25">
+      <c r="AH13" s="17"/>
+      <c r="AI13" s="47" t="s">
+        <v>35</v>
+      </c>
+      <c r="AJ13" s="48"/>
+      <c r="AK13" s="48"/>
+      <c r="AL13" s="48"/>
+      <c r="AM13" s="56"/>
+      <c r="AN13" s="56"/>
+      <c r="BN13" s="19"/>
+    </row>
+    <row r="14" spans="4:114" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D14" s="8"/>
-      <c r="E14" s="24" t="s">
+      <c r="E14" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="F14" s="24"/>
-      <c r="G14" s="24"/>
-      <c r="H14" s="24"/>
-      <c r="I14" s="24"/>
+      <c r="F14" s="45"/>
+      <c r="G14" s="45"/>
+      <c r="H14" s="45"/>
+      <c r="I14" s="45"/>
       <c r="V14" s="9"/>
-      <c r="AD14" s="25"/>
-      <c r="AH14" s="28"/>
-      <c r="BN14" s="28"/>
-    </row>
-    <row r="15" spans="4:114" x14ac:dyDescent="0.25">
+      <c r="AD14" s="16"/>
+      <c r="AH14" s="19"/>
+      <c r="AI14" s="49"/>
+      <c r="AJ14" s="55"/>
+      <c r="AK14" s="55"/>
+      <c r="AL14" s="55"/>
+      <c r="AM14" s="57"/>
+      <c r="AN14" s="57"/>
+      <c r="BN14" s="19"/>
+    </row>
+    <row r="15" spans="4:114" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D15" s="8"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="24"/>
-      <c r="I15" s="24"/>
-      <c r="V15" s="28"/>
-      <c r="W15" s="25"/>
-      <c r="X15" s="25"/>
-      <c r="Y15" s="25"/>
-      <c r="Z15" s="25"/>
-      <c r="AA15" s="25"/>
-      <c r="AB15" s="25"/>
-      <c r="AC15" s="25"/>
-      <c r="AD15" s="25"/>
-      <c r="AE15" s="25"/>
-      <c r="AH15" s="28"/>
-      <c r="BN15" s="28"/>
+      <c r="E15" s="45"/>
+      <c r="F15" s="45"/>
+      <c r="G15" s="45"/>
+      <c r="H15" s="45"/>
+      <c r="I15" s="45"/>
+      <c r="V15" s="19"/>
+      <c r="W15" s="60" t="s">
+        <v>50</v>
+      </c>
+      <c r="X15" s="61"/>
+      <c r="Y15" s="61"/>
+      <c r="Z15" s="61"/>
+      <c r="AA15" s="61"/>
+      <c r="AB15" s="16"/>
+      <c r="AC15" s="16"/>
+      <c r="AD15" s="16"/>
+      <c r="AE15" s="16"/>
+      <c r="AH15" s="19"/>
+      <c r="AI15" s="49"/>
+      <c r="AJ15" s="55"/>
+      <c r="AK15" s="55"/>
+      <c r="AL15" s="55"/>
+      <c r="AM15" s="57"/>
+      <c r="AN15" s="57"/>
+      <c r="BN15" s="19"/>
     </row>
     <row r="16" spans="4:114" x14ac:dyDescent="0.25">
       <c r="D16" s="8"/>
-      <c r="V16" s="28"/>
-      <c r="W16" s="25"/>
-      <c r="X16" s="25"/>
-      <c r="Y16" s="25"/>
-      <c r="Z16" s="25"/>
-      <c r="AA16" s="25"/>
-      <c r="AB16" s="25"/>
-      <c r="AC16" s="25"/>
-      <c r="AD16" s="25"/>
-      <c r="AE16" s="25"/>
-      <c r="AH16" s="28"/>
-      <c r="BN16" s="28"/>
-    </row>
-    <row r="17" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="V16" s="19"/>
+      <c r="W16" s="16"/>
+      <c r="X16" s="16"/>
+      <c r="Y16" s="16"/>
+      <c r="Z16" s="16"/>
+      <c r="AA16" s="16"/>
+      <c r="AB16" s="16"/>
+      <c r="AC16" s="16"/>
+      <c r="AD16" s="16"/>
+      <c r="AE16" s="16"/>
+      <c r="AH16" s="19"/>
+      <c r="BN16" s="19"/>
+    </row>
+    <row r="17" spans="4:66" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D17" s="8"/>
-      <c r="V17" s="28"/>
-      <c r="W17" s="22" t="s">
-        <v>28</v>
+      <c r="V17" s="19"/>
+      <c r="W17" s="46" t="s">
+        <v>47</v>
       </c>
-      <c r="X17" s="22"/>
-      <c r="Y17" s="22"/>
-      <c r="Z17" s="22"/>
-      <c r="AA17" s="22"/>
-      <c r="AB17" s="22"/>
-      <c r="AC17" s="22"/>
-      <c r="AD17" s="22"/>
-      <c r="AE17" s="25"/>
-      <c r="AH17" s="28"/>
-      <c r="BN17" s="28"/>
+      <c r="X17" s="46"/>
+      <c r="Y17" s="46"/>
+      <c r="Z17" s="46"/>
+      <c r="AA17" s="46"/>
+      <c r="AB17" s="46"/>
+      <c r="AC17" s="46"/>
+      <c r="AD17" s="46"/>
+      <c r="AE17" s="16"/>
+      <c r="AH17" s="19"/>
+      <c r="AJ17" s="51" t="s">
+        <v>36</v>
+      </c>
+      <c r="AK17" s="51"/>
+      <c r="AL17" s="51"/>
+      <c r="AM17" s="51"/>
+      <c r="AN17" s="51"/>
+      <c r="AO17" s="51"/>
+      <c r="AP17" s="51"/>
+      <c r="AQ17" s="51"/>
+      <c r="AR17" s="51"/>
+      <c r="AS17" s="51"/>
+      <c r="AT17" s="51"/>
+      <c r="AU17" s="51"/>
+      <c r="AV17" s="51"/>
+      <c r="AW17" s="51"/>
+      <c r="AX17" s="51"/>
+      <c r="BN17" s="19"/>
     </row>
     <row r="18" spans="4:66" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D18" s="8"/>
-      <c r="V18" s="28"/>
-      <c r="W18" s="22"/>
-      <c r="X18" s="22"/>
-      <c r="Y18" s="22"/>
-      <c r="Z18" s="22"/>
-      <c r="AA18" s="22"/>
-      <c r="AB18" s="22"/>
-      <c r="AC18" s="22"/>
-      <c r="AD18" s="22"/>
-      <c r="AE18" s="25"/>
-      <c r="AH18" s="28"/>
-      <c r="BN18" s="28"/>
-    </row>
-    <row r="19" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="V18" s="19"/>
+      <c r="W18" s="46"/>
+      <c r="X18" s="46"/>
+      <c r="Y18" s="46"/>
+      <c r="Z18" s="46"/>
+      <c r="AA18" s="46"/>
+      <c r="AB18" s="46"/>
+      <c r="AC18" s="46"/>
+      <c r="AD18" s="46"/>
+      <c r="AE18" s="16"/>
+      <c r="AH18" s="19"/>
+      <c r="AJ18" s="51"/>
+      <c r="AK18" s="51"/>
+      <c r="AL18" s="51"/>
+      <c r="AM18" s="51"/>
+      <c r="AN18" s="51"/>
+      <c r="AO18" s="51"/>
+      <c r="AP18" s="51"/>
+      <c r="AQ18" s="51"/>
+      <c r="AR18" s="51"/>
+      <c r="AS18" s="51"/>
+      <c r="AT18" s="51"/>
+      <c r="AU18" s="51"/>
+      <c r="AV18" s="51"/>
+      <c r="AW18" s="51"/>
+      <c r="AX18" s="51"/>
+      <c r="BN18" s="19"/>
+    </row>
+    <row r="19" spans="4:66" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D19" s="8"/>
-      <c r="V19" s="28"/>
-      <c r="W19" s="25"/>
-      <c r="X19" s="25"/>
-      <c r="Y19" s="25"/>
-      <c r="Z19" s="25"/>
-      <c r="AA19" s="25"/>
-      <c r="AB19" s="25"/>
-      <c r="AC19" s="25"/>
-      <c r="AD19" s="25"/>
-      <c r="AE19" s="25"/>
-      <c r="AH19" s="28"/>
-      <c r="BN19" s="28"/>
-    </row>
-    <row r="20" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="V19" s="19"/>
+      <c r="W19" s="16"/>
+      <c r="X19" s="16"/>
+      <c r="Y19" s="16"/>
+      <c r="Z19" s="16"/>
+      <c r="AA19" s="16"/>
+      <c r="AB19" s="16"/>
+      <c r="AC19" s="16"/>
+      <c r="AD19" s="16"/>
+      <c r="AE19" s="16"/>
+      <c r="AH19" s="19"/>
+      <c r="AJ19" s="51"/>
+      <c r="AK19" s="51"/>
+      <c r="AL19" s="51"/>
+      <c r="AM19" s="51"/>
+      <c r="AN19" s="51"/>
+      <c r="AO19" s="51"/>
+      <c r="AP19" s="51"/>
+      <c r="AQ19" s="51"/>
+      <c r="AR19" s="51"/>
+      <c r="AS19" s="51"/>
+      <c r="AT19" s="51"/>
+      <c r="AU19" s="51"/>
+      <c r="AV19" s="51"/>
+      <c r="AW19" s="51"/>
+      <c r="AX19" s="51"/>
+      <c r="BN19" s="19"/>
+    </row>
+    <row r="20" spans="4:66" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D20" s="8"/>
-      <c r="V20" s="28"/>
-      <c r="W20" s="23" t="s">
-        <v>27</v>
+      <c r="V20" s="19"/>
+      <c r="W20" s="41" t="s">
+        <v>48</v>
       </c>
-      <c r="X20" s="23"/>
-      <c r="Y20" s="23"/>
-      <c r="Z20" s="23"/>
-      <c r="AA20" s="23"/>
-      <c r="AB20" s="23"/>
-      <c r="AC20" s="23"/>
-      <c r="AD20" s="23"/>
-      <c r="AE20" s="25"/>
-      <c r="AH20" s="28"/>
-      <c r="BN20" s="28"/>
-    </row>
-    <row r="21" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="X20" s="41"/>
+      <c r="Y20" s="41"/>
+      <c r="Z20" s="41"/>
+      <c r="AA20" s="41"/>
+      <c r="AB20" s="41"/>
+      <c r="AC20" s="41"/>
+      <c r="AD20" s="41"/>
+      <c r="AE20" s="16"/>
+      <c r="AH20" s="19"/>
+      <c r="AJ20" s="51"/>
+      <c r="AK20" s="51"/>
+      <c r="AL20" s="51"/>
+      <c r="AM20" s="51"/>
+      <c r="AN20" s="51"/>
+      <c r="AO20" s="51"/>
+      <c r="AP20" s="51"/>
+      <c r="AQ20" s="51"/>
+      <c r="AR20" s="51"/>
+      <c r="AS20" s="51"/>
+      <c r="AT20" s="51"/>
+      <c r="AU20" s="51"/>
+      <c r="AV20" s="51"/>
+      <c r="AW20" s="51"/>
+      <c r="AX20" s="51"/>
+      <c r="BN20" s="19"/>
+    </row>
+    <row r="21" spans="4:66" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D21" s="8"/>
-      <c r="V21" s="28"/>
-      <c r="W21" s="23"/>
-      <c r="X21" s="23"/>
-      <c r="Y21" s="23"/>
-      <c r="Z21" s="23"/>
-      <c r="AA21" s="23"/>
-      <c r="AB21" s="23"/>
-      <c r="AC21" s="23"/>
-      <c r="AD21" s="23"/>
-      <c r="AE21" s="25"/>
-      <c r="AH21" s="28"/>
-      <c r="BN21" s="28"/>
+      <c r="V21" s="19"/>
+      <c r="W21" s="41"/>
+      <c r="X21" s="41"/>
+      <c r="Y21" s="41"/>
+      <c r="Z21" s="41"/>
+      <c r="AA21" s="41"/>
+      <c r="AB21" s="41"/>
+      <c r="AC21" s="41"/>
+      <c r="AD21" s="41"/>
+      <c r="AE21" s="16"/>
+      <c r="AH21" s="19"/>
+      <c r="AJ21" s="51"/>
+      <c r="AK21" s="51"/>
+      <c r="AL21" s="51"/>
+      <c r="AM21" s="51"/>
+      <c r="AN21" s="51"/>
+      <c r="AO21" s="51"/>
+      <c r="AP21" s="51"/>
+      <c r="AQ21" s="51"/>
+      <c r="AR21" s="51"/>
+      <c r="AS21" s="51"/>
+      <c r="AT21" s="51"/>
+      <c r="AU21" s="51"/>
+      <c r="AV21" s="51"/>
+      <c r="AW21" s="51"/>
+      <c r="AX21" s="51"/>
+      <c r="BN21" s="19"/>
     </row>
     <row r="22" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D22" s="8"/>
-      <c r="V22" s="28"/>
-      <c r="W22" s="25"/>
-      <c r="X22" s="25"/>
-      <c r="Y22" s="25"/>
-      <c r="Z22" s="25"/>
-      <c r="AA22" s="25"/>
-      <c r="AB22" s="25"/>
-      <c r="AC22" s="25"/>
-      <c r="AD22" s="25"/>
-      <c r="AE22" s="25"/>
-      <c r="AH22" s="28"/>
-      <c r="BN22" s="28"/>
+      <c r="V22" s="19"/>
+      <c r="W22" s="16"/>
+      <c r="X22" s="16"/>
+      <c r="Y22" s="16"/>
+      <c r="Z22" s="16"/>
+      <c r="AA22" s="16"/>
+      <c r="AB22" s="16"/>
+      <c r="AC22" s="16"/>
+      <c r="AD22" s="16"/>
+      <c r="AE22" s="16"/>
+      <c r="AH22" s="19"/>
+      <c r="AJ22" s="50"/>
+      <c r="AK22" s="50"/>
+      <c r="AL22" s="50"/>
+      <c r="AM22" s="50"/>
+      <c r="AN22" s="50"/>
+      <c r="AO22" s="50"/>
+      <c r="AP22" s="50"/>
+      <c r="AQ22" s="50"/>
+      <c r="AR22" s="50"/>
+      <c r="AS22" s="50"/>
+      <c r="AT22" s="50"/>
+      <c r="AU22" s="50"/>
+      <c r="BN22" s="19"/>
     </row>
     <row r="23" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D23" s="8"/>
-      <c r="V23" s="28"/>
-      <c r="W23" s="22" t="s">
-        <v>29</v>
+      <c r="V23" s="19"/>
+      <c r="W23" s="46" t="s">
+        <v>49</v>
       </c>
-      <c r="X23" s="22"/>
-      <c r="Y23" s="22"/>
-      <c r="Z23" s="22"/>
-      <c r="AA23" s="22"/>
-      <c r="AB23" s="22"/>
-      <c r="AC23" s="22"/>
-      <c r="AD23" s="22"/>
-      <c r="AE23" s="25"/>
-      <c r="AH23" s="28"/>
-      <c r="BN23" s="28"/>
+      <c r="X23" s="46"/>
+      <c r="Y23" s="46"/>
+      <c r="Z23" s="46"/>
+      <c r="AA23" s="46"/>
+      <c r="AB23" s="46"/>
+      <c r="AC23" s="46"/>
+      <c r="AD23" s="46"/>
+      <c r="AE23" s="16"/>
+      <c r="AH23" s="19"/>
+      <c r="AJ23" s="50"/>
+      <c r="AK23" s="50"/>
+      <c r="AL23" s="50"/>
+      <c r="AM23" s="50"/>
+      <c r="AN23" s="50"/>
+      <c r="AO23" s="50"/>
+      <c r="AP23" s="50"/>
+      <c r="AQ23" s="50"/>
+      <c r="AR23" s="50"/>
+      <c r="AS23" s="50"/>
+      <c r="AT23" s="50"/>
+      <c r="AU23" s="50"/>
+      <c r="BN23" s="19"/>
     </row>
     <row r="24" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D24" s="8"/>
-      <c r="V24" s="28"/>
-      <c r="W24" s="22"/>
-      <c r="X24" s="22"/>
-      <c r="Y24" s="22"/>
-      <c r="Z24" s="22"/>
-      <c r="AA24" s="22"/>
-      <c r="AB24" s="22"/>
-      <c r="AC24" s="22"/>
-      <c r="AD24" s="22"/>
-      <c r="AE24" s="25"/>
-      <c r="AH24" s="28"/>
-      <c r="BN24" s="28"/>
+      <c r="V24" s="19"/>
+      <c r="W24" s="46"/>
+      <c r="X24" s="46"/>
+      <c r="Y24" s="46"/>
+      <c r="Z24" s="46"/>
+      <c r="AA24" s="46"/>
+      <c r="AB24" s="46"/>
+      <c r="AC24" s="46"/>
+      <c r="AD24" s="46"/>
+      <c r="AE24" s="16"/>
+      <c r="AH24" s="19"/>
+      <c r="AJ24" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="BN24" s="19"/>
     </row>
     <row r="25" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D25" s="8"/>
-      <c r="V25" s="28"/>
-      <c r="W25" s="25"/>
-      <c r="X25" s="25"/>
-      <c r="Y25" s="25"/>
-      <c r="Z25" s="25"/>
-      <c r="AA25" s="25"/>
-      <c r="AB25" s="25"/>
-      <c r="AC25" s="25"/>
-      <c r="AD25" s="25"/>
-      <c r="AE25" s="25"/>
-      <c r="AH25" s="28"/>
-      <c r="BN25" s="28"/>
+      <c r="V25" s="19"/>
+      <c r="W25" s="16"/>
+      <c r="X25" s="16"/>
+      <c r="Y25" s="16"/>
+      <c r="Z25" s="16"/>
+      <c r="AA25" s="16"/>
+      <c r="AB25" s="16"/>
+      <c r="AC25" s="16"/>
+      <c r="AD25" s="16"/>
+      <c r="AE25" s="16"/>
+      <c r="AH25" s="19"/>
+      <c r="AK25" t="s">
+        <v>38</v>
+      </c>
+      <c r="BN25" s="19"/>
     </row>
     <row r="26" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D26" s="8"/>
-      <c r="V26" s="28"/>
-      <c r="W26" s="23" t="s">
-        <v>7</v>
+      <c r="V26" s="19"/>
+      <c r="W26" s="40" t="s">
+        <v>51</v>
       </c>
-      <c r="X26" s="23"/>
-      <c r="Y26" s="23"/>
-      <c r="Z26" s="23"/>
-      <c r="AA26" s="23"/>
-      <c r="AB26" s="23"/>
-      <c r="AC26" s="23"/>
-      <c r="AD26" s="23"/>
-      <c r="AE26" s="25"/>
-      <c r="AH26" s="28"/>
-      <c r="BN26" s="28"/>
+      <c r="X26" s="40"/>
+      <c r="Y26" s="40"/>
+      <c r="Z26" s="40"/>
+      <c r="AA26" s="40"/>
+      <c r="AB26" s="40"/>
+      <c r="AC26" s="40"/>
+      <c r="AD26" s="40"/>
+      <c r="AE26" s="16"/>
+      <c r="AH26" s="19"/>
+      <c r="AK26" t="s">
+        <v>39</v>
+      </c>
+      <c r="BN26" s="19"/>
     </row>
     <row r="27" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D27" s="8"/>
-      <c r="V27" s="28"/>
-      <c r="W27" s="23"/>
-      <c r="X27" s="23"/>
-      <c r="Y27" s="23"/>
-      <c r="Z27" s="23"/>
-      <c r="AA27" s="23"/>
-      <c r="AB27" s="23"/>
-      <c r="AC27" s="23"/>
-      <c r="AD27" s="23"/>
-      <c r="AE27" s="25"/>
-      <c r="AH27" s="28"/>
-      <c r="BN27" s="28"/>
+      <c r="V27" s="19"/>
+      <c r="W27" s="40"/>
+      <c r="X27" s="40"/>
+      <c r="Y27" s="40"/>
+      <c r="Z27" s="40"/>
+      <c r="AA27" s="40"/>
+      <c r="AB27" s="40"/>
+      <c r="AC27" s="40"/>
+      <c r="AD27" s="40"/>
+      <c r="AE27" s="16"/>
+      <c r="AH27" s="19"/>
+      <c r="AK27" t="s">
+        <v>40</v>
+      </c>
+      <c r="BN27" s="19"/>
     </row>
     <row r="28" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D28" s="8"/>
-      <c r="V28" s="28"/>
-      <c r="W28" s="25"/>
-      <c r="X28" s="25"/>
-      <c r="Y28" s="25"/>
-      <c r="Z28" s="25"/>
-      <c r="AA28" s="25"/>
-      <c r="AB28" s="25"/>
-      <c r="AC28" s="25"/>
-      <c r="AD28" s="25"/>
-      <c r="AE28" s="25"/>
-      <c r="AH28" s="28"/>
-      <c r="BN28" s="28"/>
+      <c r="V28" s="19"/>
+      <c r="W28" s="16"/>
+      <c r="X28" s="16"/>
+      <c r="Y28" s="16"/>
+      <c r="Z28" s="16"/>
+      <c r="AA28" s="16"/>
+      <c r="AB28" s="16"/>
+      <c r="AC28" s="16"/>
+      <c r="AD28" s="16"/>
+      <c r="AE28" s="16"/>
+      <c r="AH28" s="19"/>
+      <c r="AK28" t="s">
+        <v>41</v>
+      </c>
+      <c r="BN28" s="19"/>
     </row>
     <row r="29" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D29" s="8"/>
-      <c r="V29" s="28"/>
-      <c r="W29" s="23" t="s">
-        <v>8</v>
+      <c r="V29" s="19"/>
+      <c r="W29" s="40" t="s">
+        <v>52</v>
       </c>
-      <c r="X29" s="23"/>
-      <c r="Y29" s="23"/>
-      <c r="Z29" s="23"/>
-      <c r="AA29" s="23"/>
-      <c r="AB29" s="23"/>
-      <c r="AC29" s="23"/>
-      <c r="AD29" s="23"/>
-      <c r="AE29" s="25"/>
-      <c r="AH29" s="28"/>
-      <c r="BN29" s="28"/>
+      <c r="X29" s="40"/>
+      <c r="Y29" s="40"/>
+      <c r="Z29" s="40"/>
+      <c r="AA29" s="40"/>
+      <c r="AB29" s="40"/>
+      <c r="AC29" s="40"/>
+      <c r="AD29" s="40"/>
+      <c r="AE29" s="16"/>
+      <c r="AH29" s="19"/>
+      <c r="AK29" t="s">
+        <v>42</v>
+      </c>
+      <c r="BN29" s="19"/>
     </row>
     <row r="30" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D30" s="8"/>
-      <c r="V30" s="28"/>
-      <c r="W30" s="23"/>
-      <c r="X30" s="23"/>
-      <c r="Y30" s="23"/>
-      <c r="Z30" s="23"/>
-      <c r="AA30" s="23"/>
-      <c r="AB30" s="23"/>
-      <c r="AC30" s="23"/>
-      <c r="AD30" s="23"/>
-      <c r="AE30" s="25"/>
-      <c r="AH30" s="28"/>
-      <c r="BN30" s="28"/>
+      <c r="V30" s="19"/>
+      <c r="W30" s="40"/>
+      <c r="X30" s="40"/>
+      <c r="Y30" s="40"/>
+      <c r="Z30" s="40"/>
+      <c r="AA30" s="40"/>
+      <c r="AB30" s="40"/>
+      <c r="AC30" s="40"/>
+      <c r="AD30" s="40"/>
+      <c r="AE30" s="16"/>
+      <c r="AH30" s="19"/>
+      <c r="BN30" s="19"/>
     </row>
     <row r="31" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D31" s="8"/>
-      <c r="V31" s="28"/>
-      <c r="W31" s="25"/>
-      <c r="X31" s="25"/>
-      <c r="Y31" s="25"/>
-      <c r="Z31" s="25"/>
-      <c r="AA31" s="25"/>
-      <c r="AB31" s="25"/>
-      <c r="AC31" s="25"/>
-      <c r="AD31" s="25"/>
-      <c r="AE31" s="25"/>
-      <c r="AH31" s="28"/>
-      <c r="BN31" s="28"/>
+      <c r="V31" s="19"/>
+      <c r="W31" s="16"/>
+      <c r="X31" s="16"/>
+      <c r="Y31" s="16"/>
+      <c r="Z31" s="16"/>
+      <c r="AA31" s="16"/>
+      <c r="AB31" s="16"/>
+      <c r="AC31" s="16"/>
+      <c r="AD31" s="16"/>
+      <c r="AE31" s="16"/>
+      <c r="AH31" s="19"/>
+      <c r="BN31" s="19"/>
     </row>
     <row r="32" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D32" s="8"/>
-      <c r="V32" s="28"/>
-      <c r="W32" s="38" t="s">
-        <v>30</v>
+      <c r="V32" s="19"/>
+      <c r="W32" s="41" t="s">
+        <v>53</v>
       </c>
-      <c r="X32" s="38"/>
-      <c r="Y32" s="38"/>
-      <c r="Z32" s="38"/>
-      <c r="AA32" s="38"/>
-      <c r="AB32" s="38"/>
-      <c r="AC32" s="38"/>
-      <c r="AD32" s="38"/>
-      <c r="AE32" s="25"/>
-      <c r="AH32" s="28"/>
-      <c r="BN32" s="28"/>
+      <c r="X32" s="41"/>
+      <c r="Y32" s="41"/>
+      <c r="Z32" s="41"/>
+      <c r="AA32" s="41"/>
+      <c r="AB32" s="41"/>
+      <c r="AC32" s="41"/>
+      <c r="AD32" s="41"/>
+      <c r="AE32" s="16"/>
+      <c r="AH32" s="19"/>
+      <c r="BN32" s="19"/>
     </row>
     <row r="33" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D33" s="8"/>
-      <c r="V33" s="28"/>
-      <c r="W33" s="38"/>
-      <c r="X33" s="38"/>
-      <c r="Y33" s="38"/>
-      <c r="Z33" s="38"/>
-      <c r="AA33" s="38"/>
-      <c r="AB33" s="38"/>
-      <c r="AC33" s="38"/>
-      <c r="AD33" s="38"/>
-      <c r="AE33" s="25"/>
-      <c r="AH33" s="28"/>
-      <c r="BN33" s="28"/>
+      <c r="V33" s="19"/>
+      <c r="W33" s="41"/>
+      <c r="X33" s="41"/>
+      <c r="Y33" s="41"/>
+      <c r="Z33" s="41"/>
+      <c r="AA33" s="41"/>
+      <c r="AB33" s="41"/>
+      <c r="AC33" s="41"/>
+      <c r="AD33" s="41"/>
+      <c r="AE33" s="16"/>
+      <c r="AH33" s="19"/>
+      <c r="BN33" s="19"/>
     </row>
     <row r="34" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D34" s="8"/>
-      <c r="V34" s="28"/>
-      <c r="W34" s="25"/>
-      <c r="X34" s="25"/>
-      <c r="Y34" s="25"/>
-      <c r="Z34" s="25"/>
-      <c r="AA34" s="25"/>
-      <c r="AB34" s="25"/>
-      <c r="AC34" s="25"/>
-      <c r="AD34" s="25"/>
-      <c r="AE34" s="25"/>
-      <c r="AH34" s="28"/>
-      <c r="BN34" s="28"/>
+      <c r="V34" s="19"/>
+      <c r="W34" s="16"/>
+      <c r="X34" s="16"/>
+      <c r="Y34" s="16"/>
+      <c r="Z34" s="16"/>
+      <c r="AA34" s="16"/>
+      <c r="AB34" s="16"/>
+      <c r="AC34" s="16"/>
+      <c r="AD34" s="16"/>
+      <c r="AE34" s="16"/>
+      <c r="AH34" s="19"/>
+      <c r="BN34" s="19"/>
     </row>
     <row r="35" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D35" s="8"/>
-      <c r="V35" s="28"/>
-      <c r="W35" s="38" t="s">
-        <v>31</v>
+      <c r="V35" s="19"/>
+      <c r="W35" s="41" t="s">
+        <v>54</v>
       </c>
-      <c r="X35" s="38"/>
-      <c r="Y35" s="38"/>
-      <c r="Z35" s="38"/>
-      <c r="AA35" s="38"/>
-      <c r="AB35" s="38"/>
-      <c r="AC35" s="38"/>
-      <c r="AD35" s="38"/>
-      <c r="AE35" s="25"/>
-      <c r="AH35" s="28"/>
-      <c r="BN35" s="28"/>
+      <c r="X35" s="41"/>
+      <c r="Y35" s="41"/>
+      <c r="Z35" s="41"/>
+      <c r="AA35" s="41"/>
+      <c r="AB35" s="41"/>
+      <c r="AC35" s="41"/>
+      <c r="AD35" s="41"/>
+      <c r="AE35" s="16"/>
+      <c r="AH35" s="19"/>
+      <c r="BN35" s="19"/>
     </row>
     <row r="36" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D36" s="8"/>
-      <c r="V36" s="28"/>
-      <c r="W36" s="38"/>
-      <c r="X36" s="38"/>
-      <c r="Y36" s="38"/>
-      <c r="Z36" s="38"/>
-      <c r="AA36" s="38"/>
-      <c r="AB36" s="38"/>
-      <c r="AC36" s="38"/>
-      <c r="AD36" s="38"/>
-      <c r="AE36" s="25"/>
-      <c r="AH36" s="28"/>
-      <c r="BN36" s="28"/>
+      <c r="V36" s="19"/>
+      <c r="W36" s="41"/>
+      <c r="X36" s="41"/>
+      <c r="Y36" s="41"/>
+      <c r="Z36" s="41"/>
+      <c r="AA36" s="41"/>
+      <c r="AB36" s="41"/>
+      <c r="AC36" s="41"/>
+      <c r="AD36" s="41"/>
+      <c r="AE36" s="16"/>
+      <c r="AH36" s="19"/>
+      <c r="BN36" s="19"/>
     </row>
     <row r="37" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D37" s="8"/>
-      <c r="V37" s="28"/>
-      <c r="W37" s="25"/>
-      <c r="X37" s="25"/>
-      <c r="Y37" s="25"/>
-      <c r="Z37" s="25"/>
-      <c r="AA37" s="25"/>
-      <c r="AB37" s="25"/>
-      <c r="AC37" s="25"/>
-      <c r="AD37" s="25"/>
-      <c r="AE37" s="25"/>
-      <c r="AH37" s="28"/>
-      <c r="BN37" s="28"/>
+      <c r="V37" s="19"/>
+      <c r="W37" s="16"/>
+      <c r="X37" s="16"/>
+      <c r="Y37" s="16"/>
+      <c r="Z37" s="16"/>
+      <c r="AA37" s="16"/>
+      <c r="AB37" s="16"/>
+      <c r="AC37" s="16"/>
+      <c r="AD37" s="16"/>
+      <c r="AE37" s="16"/>
+      <c r="AH37" s="19"/>
+      <c r="BN37" s="19"/>
     </row>
     <row r="38" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D38" s="8"/>
-      <c r="V38" s="28"/>
-      <c r="W38" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="X38" s="38"/>
-      <c r="Y38" s="38"/>
-      <c r="Z38" s="38"/>
-      <c r="AA38" s="38"/>
-      <c r="AB38" s="38"/>
-      <c r="AC38" s="38"/>
-      <c r="AD38" s="38"/>
-      <c r="AE38" s="25"/>
-      <c r="AH38" s="28"/>
-      <c r="BN38" s="28"/>
+      <c r="V38" s="19"/>
+      <c r="W38" s="62"/>
+      <c r="X38" s="62"/>
+      <c r="Y38" s="62"/>
+      <c r="Z38" s="62"/>
+      <c r="AA38" s="62"/>
+      <c r="AB38" s="62"/>
+      <c r="AC38" s="62"/>
+      <c r="AD38" s="62"/>
+      <c r="AE38" s="16"/>
+      <c r="AH38" s="19"/>
+      <c r="BN38" s="19"/>
     </row>
     <row r="39" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D39" s="8"/>
-      <c r="V39" s="28"/>
-      <c r="W39" s="38"/>
-      <c r="X39" s="38"/>
-      <c r="Y39" s="38"/>
-      <c r="Z39" s="38"/>
-      <c r="AA39" s="38"/>
-      <c r="AB39" s="38"/>
-      <c r="AC39" s="38"/>
-      <c r="AD39" s="38"/>
-      <c r="AE39" s="25"/>
-      <c r="AH39" s="28"/>
-      <c r="BN39" s="28"/>
+      <c r="V39" s="19"/>
+      <c r="W39" s="62"/>
+      <c r="X39" s="62"/>
+      <c r="Y39" s="62"/>
+      <c r="Z39" s="62"/>
+      <c r="AA39" s="62"/>
+      <c r="AB39" s="62"/>
+      <c r="AC39" s="62"/>
+      <c r="AD39" s="62"/>
+      <c r="AE39" s="16"/>
+      <c r="AH39" s="19"/>
+      <c r="BN39" s="19"/>
     </row>
     <row r="40" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D40" s="8"/>
-      <c r="V40" s="28"/>
-      <c r="W40" s="25"/>
-      <c r="X40" s="25"/>
-      <c r="Y40" s="25"/>
-      <c r="Z40" s="25"/>
-      <c r="AA40" s="25"/>
-      <c r="AB40" s="25"/>
-      <c r="AC40" s="25"/>
-      <c r="AD40" s="25"/>
-      <c r="AE40" s="25"/>
-      <c r="AH40" s="28"/>
-      <c r="BN40" s="28"/>
+      <c r="V40" s="19"/>
+      <c r="W40" s="16"/>
+      <c r="X40" s="16"/>
+      <c r="Y40" s="16"/>
+      <c r="Z40" s="16"/>
+      <c r="AA40" s="16"/>
+      <c r="AB40" s="16"/>
+      <c r="AC40" s="16"/>
+      <c r="AD40" s="16"/>
+      <c r="AE40" s="16"/>
+      <c r="AH40" s="19"/>
+      <c r="BN40" s="19"/>
     </row>
     <row r="41" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D41" s="8"/>
-      <c r="V41" s="28"/>
-      <c r="W41" s="25"/>
-      <c r="X41" s="25"/>
-      <c r="Y41" s="25"/>
-      <c r="Z41" s="25"/>
-      <c r="AA41" s="25"/>
-      <c r="AB41" s="25"/>
-      <c r="AC41" s="25"/>
-      <c r="AD41" s="25"/>
-      <c r="AE41" s="25"/>
-      <c r="AH41" s="28"/>
-      <c r="BN41" s="28"/>
+      <c r="V41" s="19"/>
+      <c r="W41" s="16"/>
+      <c r="X41" s="16"/>
+      <c r="Y41" s="16"/>
+      <c r="Z41" s="16"/>
+      <c r="AA41" s="16"/>
+      <c r="AB41" s="16"/>
+      <c r="AC41" s="16"/>
+      <c r="AD41" s="16"/>
+      <c r="AE41" s="16"/>
+      <c r="AH41" s="19"/>
+      <c r="BN41" s="19"/>
     </row>
     <row r="42" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D42" s="8"/>
-      <c r="V42" s="28"/>
-      <c r="W42" s="25"/>
-      <c r="X42" s="25"/>
-      <c r="Y42" s="25"/>
-      <c r="Z42" s="25"/>
-      <c r="AA42" s="25"/>
-      <c r="AB42" s="25"/>
-      <c r="AC42" s="25"/>
-      <c r="AD42" s="25"/>
-      <c r="AE42" s="25"/>
-      <c r="AH42" s="28"/>
-      <c r="BN42" s="28"/>
+      <c r="V42" s="19"/>
+      <c r="W42" s="16"/>
+      <c r="X42" s="16"/>
+      <c r="Y42" s="16"/>
+      <c r="Z42" s="16"/>
+      <c r="AA42" s="16"/>
+      <c r="AB42" s="16"/>
+      <c r="AC42" s="16"/>
+      <c r="AD42" s="16"/>
+      <c r="AE42" s="16"/>
+      <c r="AH42" s="19"/>
+      <c r="BN42" s="19"/>
     </row>
     <row r="43" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D43" s="8"/>
-      <c r="V43" s="28"/>
-      <c r="W43" s="25"/>
-      <c r="X43" s="25"/>
-      <c r="Y43" s="25"/>
-      <c r="Z43" s="25"/>
-      <c r="AA43" s="25"/>
-      <c r="AB43" s="25"/>
-      <c r="AC43" s="25"/>
-      <c r="AD43" s="25"/>
-      <c r="AE43" s="25"/>
-      <c r="AH43" s="28"/>
-      <c r="BN43" s="28"/>
+      <c r="V43" s="19"/>
+      <c r="W43" s="16"/>
+      <c r="X43" s="16"/>
+      <c r="Y43" s="16"/>
+      <c r="Z43" s="16"/>
+      <c r="AA43" s="16"/>
+      <c r="AB43" s="16"/>
+      <c r="AC43" s="16"/>
+      <c r="AD43" s="16"/>
+      <c r="AE43" s="16"/>
+      <c r="AH43" s="19"/>
+      <c r="BN43" s="19"/>
     </row>
     <row r="44" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D44" s="8"/>
-      <c r="V44" s="28"/>
-      <c r="W44" s="25"/>
-      <c r="X44" s="25"/>
-      <c r="Y44" s="25"/>
-      <c r="Z44" s="25"/>
-      <c r="AA44" s="25"/>
-      <c r="AB44" s="25"/>
-      <c r="AC44" s="25"/>
-      <c r="AD44" s="25"/>
-      <c r="AE44" s="25"/>
-      <c r="AH44" s="28"/>
-      <c r="BN44" s="28"/>
+      <c r="V44" s="19"/>
+      <c r="W44" s="16"/>
+      <c r="X44" s="16"/>
+      <c r="Y44" s="16"/>
+      <c r="Z44" s="16"/>
+      <c r="AA44" s="16"/>
+      <c r="AB44" s="16"/>
+      <c r="AC44" s="16"/>
+      <c r="AD44" s="16"/>
+      <c r="AE44" s="16"/>
+      <c r="AH44" s="19"/>
+      <c r="BN44" s="19"/>
     </row>
     <row r="45" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D45" s="8"/>
-      <c r="V45" s="28"/>
-      <c r="W45" s="25"/>
-      <c r="X45" s="25"/>
-      <c r="Y45" s="25"/>
-      <c r="Z45" s="25"/>
-      <c r="AA45" s="25"/>
-      <c r="AB45" s="25"/>
-      <c r="AC45" s="25"/>
-      <c r="AD45" s="25"/>
-      <c r="AE45" s="25"/>
-      <c r="AH45" s="28"/>
-      <c r="BN45" s="28"/>
+      <c r="V45" s="19"/>
+      <c r="W45" s="16"/>
+      <c r="X45" s="16"/>
+      <c r="Y45" s="16"/>
+      <c r="Z45" s="16"/>
+      <c r="AA45" s="16"/>
+      <c r="AB45" s="16"/>
+      <c r="AC45" s="16"/>
+      <c r="AD45" s="16"/>
+      <c r="AE45" s="16"/>
+      <c r="AH45" s="19"/>
+      <c r="BN45" s="19"/>
     </row>
     <row r="46" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D46" s="8"/>
-      <c r="V46" s="28"/>
-      <c r="W46" s="25"/>
-      <c r="X46" s="25"/>
-      <c r="Y46" s="25"/>
-      <c r="Z46" s="25"/>
-      <c r="AA46" s="25"/>
-      <c r="AB46" s="25"/>
-      <c r="AC46" s="25"/>
-      <c r="AD46" s="25"/>
-      <c r="AE46" s="25"/>
-      <c r="AH46" s="28"/>
-      <c r="BN46" s="28"/>
+      <c r="V46" s="19"/>
+      <c r="W46" s="16"/>
+      <c r="X46" s="16"/>
+      <c r="Y46" s="16"/>
+      <c r="Z46" s="16"/>
+      <c r="AA46" s="16"/>
+      <c r="AB46" s="16"/>
+      <c r="AC46" s="16"/>
+      <c r="AD46" s="16"/>
+      <c r="AE46" s="16"/>
+      <c r="AH46" s="19"/>
+      <c r="BN46" s="19"/>
     </row>
     <row r="47" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D47" s="8"/>
-      <c r="V47" s="28"/>
-      <c r="W47" s="25"/>
-      <c r="X47" s="25"/>
-      <c r="Y47" s="25"/>
-      <c r="Z47" s="25"/>
-      <c r="AA47" s="25"/>
-      <c r="AB47" s="25"/>
-      <c r="AC47" s="25"/>
-      <c r="AD47" s="25"/>
-      <c r="AE47" s="25"/>
-      <c r="AH47" s="28"/>
-      <c r="BN47" s="28"/>
+      <c r="V47" s="19"/>
+      <c r="W47" s="16"/>
+      <c r="X47" s="16"/>
+      <c r="Y47" s="16"/>
+      <c r="Z47" s="16"/>
+      <c r="AA47" s="16"/>
+      <c r="AB47" s="16"/>
+      <c r="AC47" s="16"/>
+      <c r="AD47" s="16"/>
+      <c r="AE47" s="16"/>
+      <c r="AH47" s="19"/>
+      <c r="BN47" s="19"/>
     </row>
     <row r="48" spans="4:66" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D48" s="10"/>
@@ -5471,3146 +5757,2959 @@
       <c r="S48" s="11"/>
       <c r="T48" s="11"/>
       <c r="U48" s="11"/>
-      <c r="V48" s="39"/>
-      <c r="W48" s="30"/>
-      <c r="X48" s="30"/>
-      <c r="Y48" s="30"/>
-      <c r="Z48" s="30"/>
-      <c r="AA48" s="30"/>
-      <c r="AB48" s="30"/>
-      <c r="AC48" s="30"/>
-      <c r="AD48" s="30"/>
-      <c r="AE48" s="30"/>
-      <c r="AF48" s="30"/>
-      <c r="AG48" s="30"/>
-      <c r="AH48" s="31"/>
-      <c r="AI48" s="30"/>
-      <c r="AJ48" s="30"/>
-      <c r="AK48" s="30"/>
-      <c r="AL48" s="30"/>
-      <c r="AM48" s="30"/>
-      <c r="AN48" s="30"/>
-      <c r="AO48" s="30"/>
-      <c r="AP48" s="30"/>
-      <c r="AQ48" s="30"/>
-      <c r="AR48" s="30"/>
-      <c r="AS48" s="30"/>
-      <c r="AT48" s="30"/>
-      <c r="AU48" s="30"/>
-      <c r="AV48" s="30"/>
-      <c r="AW48" s="30"/>
-      <c r="AX48" s="30"/>
-      <c r="AY48" s="30"/>
-      <c r="AZ48" s="30"/>
-      <c r="BA48" s="30"/>
-      <c r="BB48" s="30"/>
-      <c r="BC48" s="30"/>
-      <c r="BD48" s="30"/>
-      <c r="BE48" s="30"/>
-      <c r="BF48" s="30"/>
-      <c r="BG48" s="30"/>
-      <c r="BH48" s="30"/>
-      <c r="BI48" s="30"/>
-      <c r="BJ48" s="30"/>
-      <c r="BK48" s="30"/>
-      <c r="BL48" s="30"/>
-      <c r="BM48" s="30"/>
-      <c r="BN48" s="31"/>
-    </row>
-    <row r="49" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="V48" s="26"/>
+      <c r="W48" s="21"/>
+      <c r="X48" s="21"/>
+      <c r="Y48" s="21"/>
+      <c r="Z48" s="21"/>
+      <c r="AA48" s="21"/>
+      <c r="AB48" s="21"/>
+      <c r="AC48" s="21"/>
+      <c r="AD48" s="21"/>
+      <c r="AE48" s="21"/>
+      <c r="AF48" s="21"/>
+      <c r="AG48" s="21"/>
+      <c r="AH48" s="22"/>
+      <c r="AI48" s="21"/>
+      <c r="AJ48" s="21"/>
+      <c r="AK48" s="21"/>
+      <c r="AL48" s="21"/>
+      <c r="AM48" s="21"/>
+      <c r="AN48" s="21"/>
+      <c r="AO48" s="21"/>
+      <c r="AP48" s="21"/>
+      <c r="AQ48" s="21"/>
+      <c r="AR48" s="21"/>
+      <c r="AS48" s="21"/>
+      <c r="AT48" s="21"/>
+      <c r="AU48" s="21"/>
+      <c r="AV48" s="21"/>
+      <c r="AW48" s="21"/>
+      <c r="AX48" s="21"/>
+      <c r="AY48" s="21"/>
+      <c r="AZ48" s="21"/>
+      <c r="BA48" s="21"/>
+      <c r="BB48" s="21"/>
+      <c r="BC48" s="21"/>
+      <c r="BD48" s="21"/>
+      <c r="BE48" s="21"/>
+      <c r="BF48" s="21"/>
+      <c r="BG48" s="21"/>
+      <c r="BH48" s="21"/>
+      <c r="BI48" s="21"/>
+      <c r="BJ48" s="21"/>
+      <c r="BK48" s="21"/>
+      <c r="BL48" s="21"/>
+      <c r="BM48" s="21"/>
+      <c r="BN48" s="22"/>
+    </row>
+    <row r="49" spans="3:66" x14ac:dyDescent="0.25">
       <c r="D49" s="8"/>
-      <c r="W49" s="25"/>
-      <c r="X49" s="25"/>
-      <c r="Y49" s="25"/>
-      <c r="Z49" s="25"/>
-      <c r="AA49" s="25"/>
-      <c r="AB49" s="25"/>
-      <c r="AC49" s="25"/>
-      <c r="AD49" s="25"/>
-      <c r="AE49" s="25"/>
-      <c r="BN49" s="28"/>
-    </row>
-    <row r="50" spans="4:66" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="D50" s="33" t="s">
+      <c r="W49" s="16"/>
+      <c r="X49" s="16"/>
+      <c r="Y49" s="16"/>
+      <c r="Z49" s="16"/>
+      <c r="AA49" s="16"/>
+      <c r="AB49" s="16"/>
+      <c r="AC49" s="16"/>
+      <c r="AD49" s="16"/>
+      <c r="AE49" s="16"/>
+      <c r="BN49" s="19"/>
+    </row>
+    <row r="50" spans="3:66" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="D50" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="E50" s="43"/>
+      <c r="F50" s="43"/>
+      <c r="G50" s="43"/>
+      <c r="W50" s="16"/>
+      <c r="X50" s="16"/>
+      <c r="Y50" s="16"/>
+      <c r="Z50" s="16"/>
+      <c r="AA50" s="16"/>
+      <c r="AB50" s="16"/>
+      <c r="AC50" s="16"/>
+      <c r="AD50" s="16"/>
+      <c r="AE50" s="16"/>
+      <c r="BN50" s="19"/>
+    </row>
+    <row r="51" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="D51" s="8"/>
+      <c r="W51" s="16"/>
+      <c r="X51" s="16"/>
+      <c r="Y51" s="16"/>
+      <c r="Z51" s="16"/>
+      <c r="AA51" s="16"/>
+      <c r="AB51" s="16"/>
+      <c r="AC51" s="16"/>
+      <c r="AD51" s="16"/>
+      <c r="AE51" s="16"/>
+      <c r="BN51" s="19"/>
+    </row>
+    <row r="52" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="D52" s="8"/>
+      <c r="W52" s="16"/>
+      <c r="X52" s="16"/>
+      <c r="Y52" s="16"/>
+      <c r="Z52" s="16"/>
+      <c r="AA52" s="16"/>
+      <c r="AB52" s="16"/>
+      <c r="AC52" s="16"/>
+      <c r="AD52" s="16"/>
+      <c r="AE52" s="16"/>
+      <c r="BN52" s="19"/>
+    </row>
+    <row r="53" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="D53" s="8"/>
+      <c r="W53" s="16"/>
+      <c r="X53" s="16"/>
+      <c r="Y53" s="16"/>
+      <c r="Z53" s="16"/>
+      <c r="AA53" s="16"/>
+      <c r="AB53" s="16"/>
+      <c r="AC53" s="16"/>
+      <c r="AD53" s="16"/>
+      <c r="AE53" s="16"/>
+      <c r="BN53" s="19"/>
+    </row>
+    <row r="54" spans="3:66" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="D54" s="8"/>
+      <c r="E54" s="59" t="s">
+        <v>14</v>
+      </c>
+      <c r="F54" s="24"/>
+      <c r="G54" s="24"/>
+      <c r="H54" s="24"/>
+      <c r="I54" s="24"/>
+      <c r="L54" s="52" t="s">
+        <v>43</v>
+      </c>
+      <c r="BN54" s="19"/>
+    </row>
+    <row r="55" spans="3:66" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="D55" s="8"/>
+      <c r="E55" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="F55" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="G55" s="24"/>
+      <c r="H55" s="24"/>
+      <c r="I55" s="24"/>
+      <c r="M55" s="53" t="s">
+        <v>45</v>
+      </c>
+      <c r="N55" s="53"/>
+      <c r="O55" s="53"/>
+      <c r="P55" s="53"/>
+      <c r="Q55" s="53"/>
+      <c r="R55" s="53"/>
+      <c r="S55" s="53"/>
+      <c r="T55" s="53"/>
+      <c r="U55" s="53"/>
+      <c r="V55" s="53"/>
+      <c r="BN55" s="19"/>
+    </row>
+    <row r="56" spans="3:66" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="D56" s="8"/>
+      <c r="E56" s="24"/>
+      <c r="F56" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="G56" s="24"/>
+      <c r="H56" s="24"/>
+      <c r="I56" s="24"/>
+      <c r="M56" s="53"/>
+      <c r="N56" s="53"/>
+      <c r="O56" s="53"/>
+      <c r="P56" s="53"/>
+      <c r="Q56" s="53"/>
+      <c r="R56" s="53"/>
+      <c r="S56" s="53"/>
+      <c r="T56" s="53"/>
+      <c r="U56" s="53"/>
+      <c r="V56" s="53"/>
+      <c r="BN56" s="19"/>
+    </row>
+    <row r="57" spans="3:66" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="D57" s="8"/>
+      <c r="E57" s="24"/>
+      <c r="F57" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="G57" s="24"/>
+      <c r="H57" s="24"/>
+      <c r="I57" s="24"/>
+      <c r="M57" s="53"/>
+      <c r="N57" s="53"/>
+      <c r="O57" s="53"/>
+      <c r="P57" s="53"/>
+      <c r="Q57" s="53"/>
+      <c r="R57" s="53"/>
+      <c r="S57" s="53"/>
+      <c r="T57" s="53"/>
+      <c r="U57" s="53"/>
+      <c r="V57" s="53"/>
+      <c r="BN57" s="19"/>
+    </row>
+    <row r="58" spans="3:66" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="D58" s="8"/>
+      <c r="E58" s="24"/>
+      <c r="F58" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="G58" s="24"/>
+      <c r="H58" s="24"/>
+      <c r="I58" s="24"/>
+      <c r="BN58" s="19"/>
+    </row>
+    <row r="59" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="D59" s="8"/>
+      <c r="E59" s="16"/>
+      <c r="F59" s="16"/>
+      <c r="G59" s="16"/>
+      <c r="H59" s="16"/>
+      <c r="I59" s="16"/>
+      <c r="J59" s="16"/>
+      <c r="K59" s="16"/>
+      <c r="M59" s="53" t="s">
+        <v>44</v>
+      </c>
+      <c r="N59" s="54"/>
+      <c r="O59" s="54"/>
+      <c r="P59" s="54"/>
+      <c r="Q59" s="54"/>
+      <c r="R59" s="54"/>
+      <c r="S59" s="54"/>
+      <c r="T59" s="54"/>
+      <c r="U59" s="54"/>
+      <c r="V59" s="54"/>
+      <c r="W59" s="16"/>
+      <c r="AI59" s="16"/>
+      <c r="AJ59" s="16"/>
+      <c r="AK59" s="16"/>
+      <c r="AL59" s="16"/>
+      <c r="AM59" s="16"/>
+      <c r="AN59" s="16"/>
+      <c r="AO59" s="16"/>
+      <c r="AP59" s="16"/>
+      <c r="AQ59" s="16"/>
+      <c r="AR59" s="16"/>
+      <c r="AS59" s="16"/>
+      <c r="AT59" s="16"/>
+      <c r="AU59" s="16"/>
+      <c r="AV59" s="16"/>
+      <c r="AW59" s="16"/>
+      <c r="AX59" s="16"/>
+      <c r="AY59" s="16"/>
+      <c r="AZ59" s="16"/>
+      <c r="BA59" s="16"/>
+      <c r="BB59" s="16"/>
+      <c r="BC59" s="16"/>
+      <c r="BD59" s="16"/>
+      <c r="BE59" s="16"/>
+      <c r="BF59" s="16"/>
+      <c r="BG59" s="16"/>
+      <c r="BH59" s="16"/>
+      <c r="BI59" s="16"/>
+      <c r="BJ59" s="16"/>
+      <c r="BK59" s="16"/>
+      <c r="BL59" s="16"/>
+      <c r="BM59" s="16"/>
+      <c r="BN59" s="19"/>
+    </row>
+    <row r="60" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="D60" s="8"/>
+      <c r="M60" s="54"/>
+      <c r="N60" s="54"/>
+      <c r="O60" s="54"/>
+      <c r="P60" s="54"/>
+      <c r="Q60" s="54"/>
+      <c r="R60" s="54"/>
+      <c r="S60" s="54"/>
+      <c r="T60" s="54"/>
+      <c r="U60" s="54"/>
+      <c r="V60" s="54"/>
+      <c r="BN60" s="19"/>
+    </row>
+    <row r="61" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C61" s="19"/>
+      <c r="D61" s="16"/>
+      <c r="BN61" s="19"/>
+    </row>
+    <row r="62" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C62" s="19"/>
+      <c r="M62" s="46" t="s">
+        <v>46</v>
+      </c>
+      <c r="N62" s="58"/>
+      <c r="O62" s="58"/>
+      <c r="P62" s="58"/>
+      <c r="Q62" s="58"/>
+      <c r="R62" s="58"/>
+      <c r="S62" s="58"/>
+      <c r="T62" s="58"/>
+      <c r="U62" s="58"/>
+      <c r="V62" s="58"/>
+      <c r="BN62" s="19"/>
+    </row>
+    <row r="63" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C63" s="19"/>
+      <c r="D63" s="16"/>
+      <c r="L63" s="16"/>
+      <c r="M63" s="58"/>
+      <c r="N63" s="58"/>
+      <c r="O63" s="58"/>
+      <c r="P63" s="58"/>
+      <c r="Q63" s="58"/>
+      <c r="R63" s="58"/>
+      <c r="S63" s="58"/>
+      <c r="T63" s="58"/>
+      <c r="U63" s="58"/>
+      <c r="V63" s="58"/>
+      <c r="BN63" s="19"/>
+    </row>
+    <row r="64" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="D64" s="8"/>
+      <c r="BN64" s="19"/>
+    </row>
+    <row r="65" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="D65" s="8"/>
+      <c r="BN65" s="19"/>
+    </row>
+    <row r="66" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="D66" s="8"/>
+      <c r="BN66" s="19"/>
+    </row>
+    <row r="67" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="D67" s="8"/>
+      <c r="BN67" s="19"/>
+    </row>
+    <row r="68" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="D68" s="8"/>
+      <c r="BN68" s="19"/>
+    </row>
+    <row r="69" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="D69" s="8"/>
+      <c r="BN69" s="19"/>
+    </row>
+    <row r="70" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="D70" s="18"/>
+      <c r="BN70" s="19"/>
+    </row>
+    <row r="71" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="D71" s="18"/>
+      <c r="BN71" s="19"/>
+    </row>
+    <row r="72" spans="3:66" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="C72" s="19"/>
+      <c r="D72" s="44" t="s">
+        <v>28</v>
+      </c>
+      <c r="E72" s="44"/>
+      <c r="F72" s="44"/>
+      <c r="G72" s="44"/>
+      <c r="BN72" s="19"/>
+    </row>
+    <row r="73" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C73" s="19"/>
+      <c r="D73" s="16"/>
+      <c r="BN73" s="19"/>
+    </row>
+    <row r="74" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="D74" s="18"/>
+      <c r="BN74" s="19"/>
+    </row>
+    <row r="75" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="D75" s="18"/>
+      <c r="BN75" s="19"/>
+    </row>
+    <row r="76" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="D76" s="18"/>
+      <c r="W76" s="16"/>
+      <c r="X76" s="16"/>
+      <c r="Y76" s="16"/>
+      <c r="Z76" s="16"/>
+      <c r="AA76" s="16"/>
+      <c r="AB76" s="16"/>
+      <c r="AC76" s="16"/>
+      <c r="AD76" s="16"/>
+      <c r="AE76" s="16"/>
+      <c r="BN76" s="19"/>
+    </row>
+    <row r="77" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="D77" s="18"/>
+      <c r="W77" s="16"/>
+      <c r="X77" s="16"/>
+      <c r="Y77" s="16"/>
+      <c r="Z77" s="16"/>
+      <c r="AA77" s="16"/>
+      <c r="AB77" s="16"/>
+      <c r="AC77" s="16"/>
+      <c r="AD77" s="16"/>
+      <c r="AE77" s="16"/>
+      <c r="AO77" s="16"/>
+      <c r="AP77" s="16"/>
+      <c r="AQ77" s="16"/>
+      <c r="AR77" s="16"/>
+      <c r="AS77" s="16"/>
+      <c r="BN77" s="19"/>
+    </row>
+    <row r="78" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="D78" s="18"/>
+      <c r="F78" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>31</v>
+      </c>
+      <c r="W78" s="16"/>
+      <c r="X78" s="16"/>
+      <c r="Y78" s="16"/>
+      <c r="Z78" s="16"/>
+      <c r="AA78" s="16"/>
+      <c r="AB78" s="16"/>
+      <c r="AC78" s="16"/>
+      <c r="AD78" s="16"/>
+      <c r="AE78" s="16"/>
+      <c r="AH78" t="s">
+        <v>32</v>
+      </c>
+      <c r="AO78" s="16"/>
+      <c r="AP78" s="16"/>
+      <c r="AQ78" s="16"/>
+      <c r="AR78" s="16"/>
+      <c r="AS78" s="16"/>
+      <c r="AV78" t="s">
+        <v>34</v>
+      </c>
+      <c r="BN78" s="19"/>
+    </row>
+    <row r="79" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="D79" s="18"/>
+      <c r="W79" s="16"/>
+      <c r="X79" s="16"/>
+      <c r="Y79" s="16"/>
+      <c r="Z79" s="16"/>
+      <c r="AA79" s="16"/>
+      <c r="AB79" s="16"/>
+      <c r="AC79" s="16"/>
+      <c r="AD79" s="16"/>
+      <c r="AE79" s="16"/>
+      <c r="AO79" s="16"/>
+      <c r="AP79" s="16"/>
+      <c r="AQ79" s="16"/>
+      <c r="AR79" s="16"/>
+      <c r="AS79" s="16"/>
+      <c r="BG79" t="s">
+        <v>30</v>
+      </c>
+      <c r="BN79" s="19"/>
+    </row>
+    <row r="80" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="D80" s="18"/>
+      <c r="W80" s="16"/>
+      <c r="X80" s="16"/>
+      <c r="Y80" s="16"/>
+      <c r="Z80" s="16"/>
+      <c r="AA80" s="16"/>
+      <c r="AB80" s="16"/>
+      <c r="AC80" s="16"/>
+      <c r="AD80" s="16"/>
+      <c r="AE80" s="16"/>
+      <c r="AO80" s="16"/>
+      <c r="AP80" s="16"/>
+      <c r="AQ80" s="16"/>
+      <c r="AR80" s="16"/>
+      <c r="AS80" s="16"/>
+      <c r="BN80" s="19"/>
+    </row>
+    <row r="81" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="D81" s="18"/>
+      <c r="W81" s="16"/>
+      <c r="X81" s="16"/>
+      <c r="Y81" s="16"/>
+      <c r="Z81" s="16"/>
+      <c r="AA81" s="16"/>
+      <c r="AB81" s="16"/>
+      <c r="AC81" s="16"/>
+      <c r="AD81" s="16"/>
+      <c r="AE81" s="16"/>
+      <c r="AO81" s="16"/>
+      <c r="AP81" s="16"/>
+      <c r="AQ81" s="16"/>
+      <c r="AR81" s="16"/>
+      <c r="AS81" s="16"/>
+      <c r="BN81" s="19"/>
+    </row>
+    <row r="82" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="D82" s="18"/>
+      <c r="W82" s="16"/>
+      <c r="X82" s="16"/>
+      <c r="Y82" s="16"/>
+      <c r="Z82" s="16"/>
+      <c r="AA82" s="16"/>
+      <c r="AB82" s="16"/>
+      <c r="AC82" s="16"/>
+      <c r="AD82" s="16"/>
+      <c r="AE82" s="16"/>
+      <c r="AO82" s="16"/>
+      <c r="AP82" s="16"/>
+      <c r="AQ82" s="16"/>
+      <c r="AR82" s="16"/>
+      <c r="AS82" s="16"/>
+      <c r="BN82" s="19"/>
+    </row>
+    <row r="83" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="D83" s="18"/>
+      <c r="W83" s="16"/>
+      <c r="X83" s="16"/>
+      <c r="Y83" s="16"/>
+      <c r="Z83" s="16"/>
+      <c r="AA83" s="16"/>
+      <c r="AB83" s="16"/>
+      <c r="AC83" s="16"/>
+      <c r="AD83" s="16"/>
+      <c r="AE83" s="16"/>
+      <c r="AO83" s="16"/>
+      <c r="AP83" s="16"/>
+      <c r="AQ83" s="16"/>
+      <c r="AR83" s="16"/>
+      <c r="AS83" s="16"/>
+      <c r="BN83" s="19"/>
+    </row>
+    <row r="84" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="D84" s="18"/>
+      <c r="W84" s="16"/>
+      <c r="X84" s="16"/>
+      <c r="Y84" s="16"/>
+      <c r="Z84" s="16"/>
+      <c r="AA84" s="16"/>
+      <c r="AB84" s="16"/>
+      <c r="AC84" s="16"/>
+      <c r="AD84" s="16"/>
+      <c r="AE84" s="16"/>
+      <c r="AO84" s="16"/>
+      <c r="AP84" s="16"/>
+      <c r="AQ84" s="16"/>
+      <c r="AR84" s="16"/>
+      <c r="AS84" s="16"/>
+      <c r="BN84" s="19"/>
+    </row>
+    <row r="85" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="D85" s="18"/>
+      <c r="W85" s="16"/>
+      <c r="X85" s="16"/>
+      <c r="Y85" s="16"/>
+      <c r="Z85" s="16"/>
+      <c r="AA85" s="16"/>
+      <c r="AB85" s="16"/>
+      <c r="AC85" s="16"/>
+      <c r="AD85" s="16"/>
+      <c r="AE85" s="16"/>
+      <c r="AO85" s="16"/>
+      <c r="AP85" s="16"/>
+      <c r="AQ85" s="16"/>
+      <c r="AR85" s="16"/>
+      <c r="AS85" s="16"/>
+      <c r="BN85" s="19"/>
+    </row>
+    <row r="86" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="D86" s="18"/>
+      <c r="W86" s="16"/>
+      <c r="X86" s="16"/>
+      <c r="Y86" s="16"/>
+      <c r="Z86" s="16"/>
+      <c r="AA86" s="16"/>
+      <c r="AB86" s="16"/>
+      <c r="AC86" s="16"/>
+      <c r="AD86" s="16"/>
+      <c r="AE86" s="16"/>
+      <c r="AO86" s="16"/>
+      <c r="AP86" s="16"/>
+      <c r="AQ86" s="16"/>
+      <c r="AR86" s="16"/>
+      <c r="AS86" s="16"/>
+      <c r="BN86" s="19"/>
+    </row>
+    <row r="87" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="D87" s="18"/>
+      <c r="W87" s="16"/>
+      <c r="X87" s="16"/>
+      <c r="Y87" s="16"/>
+      <c r="Z87" s="16"/>
+      <c r="AA87" s="16"/>
+      <c r="AB87" s="16"/>
+      <c r="AC87" s="16"/>
+      <c r="AD87" s="16"/>
+      <c r="AE87" s="16"/>
+      <c r="AO87" s="16"/>
+      <c r="AP87" s="16"/>
+      <c r="AQ87" s="16"/>
+      <c r="AR87" s="16"/>
+      <c r="AS87" s="16"/>
+      <c r="BN87" s="19"/>
+    </row>
+    <row r="88" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="D88" s="18"/>
+      <c r="W88" s="16"/>
+      <c r="X88" s="16"/>
+      <c r="Y88" s="16"/>
+      <c r="Z88" s="16"/>
+      <c r="AA88" s="16"/>
+      <c r="AB88" s="16"/>
+      <c r="AC88" s="16"/>
+      <c r="AD88" s="16"/>
+      <c r="AE88" s="16"/>
+      <c r="AO88" s="16"/>
+      <c r="AP88" s="16"/>
+      <c r="AQ88" s="16"/>
+      <c r="AR88" s="16"/>
+      <c r="AS88" s="16"/>
+      <c r="BN88" s="19"/>
+    </row>
+    <row r="89" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="D89" s="18"/>
+      <c r="W89" s="16"/>
+      <c r="X89" s="16"/>
+      <c r="Y89" s="16"/>
+      <c r="Z89" s="16"/>
+      <c r="AA89" s="16"/>
+      <c r="AB89" s="16"/>
+      <c r="AC89" s="16"/>
+      <c r="AD89" s="16"/>
+      <c r="AE89" s="16"/>
+      <c r="AG89" s="16"/>
+      <c r="AH89" s="16"/>
+      <c r="AO89" s="16"/>
+      <c r="AP89" s="16"/>
+      <c r="AQ89" s="16"/>
+      <c r="AR89" s="16"/>
+      <c r="AS89" s="16"/>
+      <c r="BN89" s="19"/>
+    </row>
+    <row r="90" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="D90" s="18"/>
+      <c r="W90" s="16"/>
+      <c r="X90" s="16"/>
+      <c r="Y90" s="16"/>
+      <c r="Z90" s="16"/>
+      <c r="AA90" s="16"/>
+      <c r="AB90" s="16"/>
+      <c r="AC90" s="16"/>
+      <c r="AD90" s="16"/>
+      <c r="AE90" s="16"/>
+      <c r="AG90" s="16"/>
+      <c r="AH90" s="16"/>
+      <c r="AO90" s="16"/>
+      <c r="AP90" s="16"/>
+      <c r="AQ90" s="16"/>
+      <c r="AR90" s="16"/>
+      <c r="AS90" s="16"/>
+      <c r="BN90" s="19"/>
+    </row>
+    <row r="91" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="D91" s="18"/>
+      <c r="W91" s="16"/>
+      <c r="X91" s="16"/>
+      <c r="Y91" s="16"/>
+      <c r="Z91" s="16"/>
+      <c r="AA91" s="16"/>
+      <c r="AB91" s="16"/>
+      <c r="AC91" s="16"/>
+      <c r="AD91" s="16"/>
+      <c r="AE91" s="16"/>
+      <c r="AG91" s="16"/>
+      <c r="AH91" s="16"/>
+      <c r="AO91" s="16"/>
+      <c r="AP91" s="16"/>
+      <c r="AQ91" s="16"/>
+      <c r="AR91" s="16"/>
+      <c r="AS91" s="16"/>
+      <c r="BN91" s="19"/>
+    </row>
+    <row r="92" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="D92" s="18"/>
+      <c r="W92" s="16"/>
+      <c r="X92" s="16"/>
+      <c r="Y92" s="16"/>
+      <c r="Z92" s="16"/>
+      <c r="AA92" s="16"/>
+      <c r="AB92" s="16"/>
+      <c r="AC92" s="16"/>
+      <c r="AD92" s="16"/>
+      <c r="AE92" s="16"/>
+      <c r="AG92" s="16"/>
+      <c r="AH92" s="16"/>
+      <c r="AO92" s="16"/>
+      <c r="AP92" s="16"/>
+      <c r="AQ92" s="16"/>
+      <c r="AR92" s="16"/>
+      <c r="AS92" s="16"/>
+      <c r="BN92" s="19"/>
+    </row>
+    <row r="93" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="D93" s="18"/>
+      <c r="W93" s="16"/>
+      <c r="X93" s="16"/>
+      <c r="Y93" s="16"/>
+      <c r="Z93" s="16"/>
+      <c r="AA93" s="16"/>
+      <c r="AB93" s="16"/>
+      <c r="AC93" s="16"/>
+      <c r="AD93" s="16"/>
+      <c r="AE93" s="16"/>
+      <c r="AG93" s="16"/>
+      <c r="AH93" s="16"/>
+      <c r="AO93" s="16"/>
+      <c r="AP93" s="16"/>
+      <c r="AQ93" s="16"/>
+      <c r="AR93" s="16"/>
+      <c r="AS93" s="16"/>
+      <c r="BN93" s="19"/>
+    </row>
+    <row r="94" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="D94" s="18"/>
+      <c r="W94" s="16"/>
+      <c r="X94" s="16"/>
+      <c r="Y94" s="16"/>
+      <c r="Z94" s="16"/>
+      <c r="AA94" s="16"/>
+      <c r="AB94" s="16"/>
+      <c r="AC94" s="16"/>
+      <c r="AD94" s="16"/>
+      <c r="AE94" s="16"/>
+      <c r="AG94" s="16"/>
+      <c r="AH94" s="16"/>
+      <c r="AO94" s="16"/>
+      <c r="AP94" s="16"/>
+      <c r="AQ94" s="16"/>
+      <c r="AR94" s="16"/>
+      <c r="AS94" s="16"/>
+      <c r="BN94" s="19"/>
+    </row>
+    <row r="95" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="D95" s="18"/>
+      <c r="W95" s="16"/>
+      <c r="X95" s="16"/>
+      <c r="Y95" s="16"/>
+      <c r="Z95" s="16"/>
+      <c r="AA95" s="16"/>
+      <c r="AB95" s="16"/>
+      <c r="AC95" s="16"/>
+      <c r="AD95" s="16"/>
+      <c r="AE95" s="16"/>
+      <c r="AG95" s="16"/>
+      <c r="AH95" s="16"/>
+      <c r="AO95" s="16"/>
+      <c r="AP95" s="16"/>
+      <c r="AQ95" s="16"/>
+      <c r="AR95" s="16"/>
+      <c r="AS95" s="16"/>
+      <c r="BN95" s="19"/>
+    </row>
+    <row r="96" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="D96" s="18"/>
+      <c r="W96" s="16"/>
+      <c r="X96" s="16"/>
+      <c r="Y96" s="16"/>
+      <c r="Z96" s="16"/>
+      <c r="AA96" s="16"/>
+      <c r="AB96" s="16"/>
+      <c r="AC96" s="16"/>
+      <c r="AD96" s="16"/>
+      <c r="AE96" s="16"/>
+      <c r="AG96" s="16"/>
+      <c r="AH96" s="16"/>
+      <c r="AO96" s="16"/>
+      <c r="AP96" s="16"/>
+      <c r="AQ96" s="16"/>
+      <c r="AR96" s="16"/>
+      <c r="AS96" s="16"/>
+      <c r="BN96" s="19"/>
+    </row>
+    <row r="97" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="D97" s="18"/>
+      <c r="W97" s="16"/>
+      <c r="X97" s="16"/>
+      <c r="Y97" s="16"/>
+      <c r="Z97" s="16"/>
+      <c r="AA97" s="16"/>
+      <c r="AB97" s="16"/>
+      <c r="AC97" s="16"/>
+      <c r="AD97" s="16"/>
+      <c r="AE97" s="16"/>
+      <c r="AG97" s="16"/>
+      <c r="AH97" s="16"/>
+      <c r="AO97" s="16"/>
+      <c r="AP97" s="16"/>
+      <c r="AQ97" s="16"/>
+      <c r="AR97" s="16"/>
+      <c r="AS97" s="16"/>
+      <c r="BN97" s="19"/>
+    </row>
+    <row r="98" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="D98" s="18"/>
+      <c r="W98" s="16"/>
+      <c r="X98" s="16"/>
+      <c r="Y98" s="16"/>
+      <c r="Z98" s="16"/>
+      <c r="AA98" s="16"/>
+      <c r="AB98" s="16"/>
+      <c r="AC98" s="16"/>
+      <c r="AD98" s="16"/>
+      <c r="AE98" s="16"/>
+      <c r="AG98" s="16"/>
+      <c r="AH98" s="16"/>
+      <c r="AO98" s="16"/>
+      <c r="AP98" s="16"/>
+      <c r="AQ98" s="16"/>
+      <c r="AR98" s="16"/>
+      <c r="AS98" s="16"/>
+      <c r="BN98" s="19"/>
+    </row>
+    <row r="99" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="D99" s="18"/>
+      <c r="W99" s="16"/>
+      <c r="X99" s="16"/>
+      <c r="Y99" s="16"/>
+      <c r="Z99" s="16"/>
+      <c r="AA99" s="16"/>
+      <c r="AB99" s="16"/>
+      <c r="AC99" s="16"/>
+      <c r="AD99" s="16"/>
+      <c r="AE99" s="16"/>
+      <c r="AG99" s="16"/>
+      <c r="AH99" s="16"/>
+      <c r="AO99" s="16"/>
+      <c r="AP99" s="16"/>
+      <c r="AQ99" s="16"/>
+      <c r="AR99" s="16"/>
+      <c r="AS99" s="16"/>
+      <c r="BN99" s="19"/>
+    </row>
+    <row r="100" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="D100" s="18"/>
+      <c r="W100" s="16"/>
+      <c r="X100" s="16"/>
+      <c r="Y100" s="16"/>
+      <c r="Z100" s="16"/>
+      <c r="AA100" s="16"/>
+      <c r="AB100" s="16"/>
+      <c r="AC100" s="16"/>
+      <c r="AD100" s="16"/>
+      <c r="AE100" s="16"/>
+      <c r="AO100" s="16"/>
+      <c r="AP100" s="16"/>
+      <c r="AQ100" s="16"/>
+      <c r="AR100" s="16"/>
+      <c r="AS100" s="16"/>
+      <c r="BN100" s="19"/>
+    </row>
+    <row r="101" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="D101" s="18"/>
+      <c r="F101" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q101" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="W101" s="16"/>
+      <c r="X101" s="16"/>
+      <c r="Y101" s="16"/>
+      <c r="Z101" s="16"/>
+      <c r="AA101" s="16"/>
+      <c r="AB101" s="16"/>
+      <c r="AC101" s="16"/>
+      <c r="AD101" s="16"/>
+      <c r="AE101" s="16"/>
+      <c r="AO101" s="16"/>
+      <c r="AP101" s="16"/>
+      <c r="AQ101" s="16"/>
+      <c r="AR101" s="16"/>
+      <c r="AS101" s="16"/>
+      <c r="BN101" s="19"/>
+    </row>
+    <row r="102" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="D102" s="18"/>
+      <c r="W102" s="16"/>
+      <c r="X102" s="16"/>
+      <c r="Y102" s="16"/>
+      <c r="Z102" s="16"/>
+      <c r="AA102" s="16"/>
+      <c r="AB102" s="16"/>
+      <c r="AC102" s="16"/>
+      <c r="AD102" s="16"/>
+      <c r="AE102" s="16"/>
+      <c r="AO102" s="16"/>
+      <c r="AP102" s="16"/>
+      <c r="AQ102" s="16"/>
+      <c r="AR102" s="16"/>
+      <c r="AS102" s="16"/>
+      <c r="BN102" s="19"/>
+    </row>
+    <row r="103" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="D103" s="18"/>
+      <c r="W103" s="16"/>
+      <c r="X103" s="16"/>
+      <c r="Y103" s="16"/>
+      <c r="Z103" s="16"/>
+      <c r="AA103" s="16"/>
+      <c r="AB103" s="16"/>
+      <c r="AC103" s="16"/>
+      <c r="AD103" s="16"/>
+      <c r="AE103" s="16"/>
+      <c r="AH103" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO103" s="16"/>
+      <c r="AP103" s="16"/>
+      <c r="AQ103" s="16"/>
+      <c r="AR103" s="16"/>
+      <c r="AS103" s="16"/>
+      <c r="BN103" s="19"/>
+    </row>
+    <row r="104" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="D104" s="18"/>
+      <c r="AB104" s="16"/>
+      <c r="AC104" s="16"/>
+      <c r="AD104" s="16"/>
+      <c r="AE104" s="16"/>
+      <c r="AO104" s="16"/>
+      <c r="AP104" s="16"/>
+      <c r="AQ104" s="16"/>
+      <c r="AR104" s="16"/>
+      <c r="AS104" s="16"/>
+      <c r="BN104" s="19"/>
+    </row>
+    <row r="105" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="D105" s="18"/>
+      <c r="AB105" s="16"/>
+      <c r="AC105" s="16"/>
+      <c r="AD105" s="16"/>
+      <c r="AE105" s="16"/>
+      <c r="AO105" s="16"/>
+      <c r="AP105" s="16"/>
+      <c r="AQ105" s="16"/>
+      <c r="AR105" s="16"/>
+      <c r="AS105" s="16"/>
+      <c r="BN105" s="19"/>
+    </row>
+    <row r="106" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="D106" s="18"/>
+      <c r="AB106" s="16"/>
+      <c r="AC106" s="16"/>
+      <c r="AD106" s="16"/>
+      <c r="AE106" s="16"/>
+      <c r="AO106" s="16"/>
+      <c r="AP106" s="16"/>
+      <c r="AQ106" s="16"/>
+      <c r="AR106" s="16"/>
+      <c r="AS106" s="16"/>
+      <c r="BN106" s="19"/>
+    </row>
+    <row r="107" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="D107" s="18"/>
+      <c r="AB107" s="16"/>
+      <c r="AC107" s="16"/>
+      <c r="AD107" s="16"/>
+      <c r="AE107" s="16"/>
+      <c r="AO107" s="16"/>
+      <c r="AP107" s="16"/>
+      <c r="AQ107" s="16"/>
+      <c r="AR107" s="16"/>
+      <c r="AS107" s="16"/>
+      <c r="BN107" s="19"/>
+    </row>
+    <row r="108" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="D108" s="18"/>
+      <c r="AB108" s="16"/>
+      <c r="AC108" s="16"/>
+      <c r="AD108" s="16"/>
+      <c r="AE108" s="16"/>
+      <c r="AO108" s="16"/>
+      <c r="AP108" s="16"/>
+      <c r="AQ108" s="16"/>
+      <c r="AR108" s="16"/>
+      <c r="AS108" s="16"/>
+      <c r="BN108" s="19"/>
+    </row>
+    <row r="109" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="D109" s="18"/>
+      <c r="E109" s="16"/>
+      <c r="F109" s="16"/>
+      <c r="G109" s="16"/>
+      <c r="H109" s="16"/>
+      <c r="I109" s="16"/>
+      <c r="J109" s="16"/>
+      <c r="K109" s="16"/>
+      <c r="AB109" s="16"/>
+      <c r="AC109" s="16"/>
+      <c r="AD109" s="16"/>
+      <c r="AE109" s="16"/>
+      <c r="AO109" s="16"/>
+      <c r="AP109" s="16"/>
+      <c r="AQ109" s="16"/>
+      <c r="AR109" s="16"/>
+      <c r="AS109" s="16"/>
+      <c r="BN109" s="19"/>
+    </row>
+    <row r="110" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="D110" s="18"/>
+      <c r="E110" s="16"/>
+      <c r="F110" s="16"/>
+      <c r="G110" s="16"/>
+      <c r="H110" s="16"/>
+      <c r="I110" s="16"/>
+      <c r="J110" s="16"/>
+      <c r="K110" s="16"/>
+      <c r="AB110" s="16"/>
+      <c r="AC110" s="16"/>
+      <c r="AD110" s="16"/>
+      <c r="AE110" s="16"/>
+      <c r="AO110" s="16"/>
+      <c r="AP110" s="16"/>
+      <c r="AQ110" s="16"/>
+      <c r="AR110" s="16"/>
+      <c r="AS110" s="16"/>
+      <c r="BN110" s="19"/>
+    </row>
+    <row r="111" spans="3:66" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D111" s="20"/>
+      <c r="E111" s="21"/>
+      <c r="F111" s="21"/>
+      <c r="G111" s="21"/>
+      <c r="H111" s="21"/>
+      <c r="I111" s="21"/>
+      <c r="J111" s="21"/>
+      <c r="K111" s="21"/>
+      <c r="L111" s="21"/>
+      <c r="M111" s="21"/>
+      <c r="N111" s="21"/>
+      <c r="O111" s="21"/>
+      <c r="P111" s="21"/>
+      <c r="Q111" s="21"/>
+      <c r="R111" s="21"/>
+      <c r="S111" s="21"/>
+      <c r="T111" s="21"/>
+      <c r="U111" s="21"/>
+      <c r="V111" s="21"/>
+      <c r="W111" s="21"/>
+      <c r="X111" s="21"/>
+      <c r="Y111" s="21"/>
+      <c r="Z111" s="21"/>
+      <c r="AA111" s="21"/>
+      <c r="AB111" s="21"/>
+      <c r="AC111" s="21"/>
+      <c r="AD111" s="21"/>
+      <c r="AE111" s="21"/>
+      <c r="AF111" s="21"/>
+      <c r="AG111" s="21"/>
+      <c r="AH111" s="21"/>
+      <c r="AI111" s="21"/>
+      <c r="AJ111" s="21"/>
+      <c r="AK111" s="21"/>
+      <c r="AL111" s="21"/>
+      <c r="AM111" s="21"/>
+      <c r="AN111" s="21"/>
+      <c r="AO111" s="21"/>
+      <c r="AP111" s="21"/>
+      <c r="AQ111" s="21"/>
+      <c r="AR111" s="21"/>
+      <c r="AS111" s="21"/>
+      <c r="AT111" s="21"/>
+      <c r="AU111" s="21"/>
+      <c r="AV111" s="21"/>
+      <c r="AW111" s="21"/>
+      <c r="AX111" s="21"/>
+      <c r="AY111" s="21"/>
+      <c r="AZ111" s="21"/>
+      <c r="BA111" s="21"/>
+      <c r="BB111" s="21"/>
+      <c r="BC111" s="21"/>
+      <c r="BD111" s="21"/>
+      <c r="BE111" s="21"/>
+      <c r="BF111" s="21"/>
+      <c r="BG111" s="21"/>
+      <c r="BH111" s="21"/>
+      <c r="BI111" s="21"/>
+      <c r="BJ111" s="21"/>
+      <c r="BK111" s="21"/>
+      <c r="BL111" s="21"/>
+      <c r="BM111" s="21"/>
+      <c r="BN111" s="22"/>
+    </row>
+    <row r="112" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C112" s="19"/>
+      <c r="D112" s="16"/>
+      <c r="E112" s="16"/>
+      <c r="F112" s="16"/>
+      <c r="G112" s="16"/>
+      <c r="H112" s="16"/>
+      <c r="I112" s="16"/>
+      <c r="J112" s="16"/>
+      <c r="K112" s="16"/>
+      <c r="L112" s="16"/>
+      <c r="M112" s="16"/>
+      <c r="N112" s="16"/>
+      <c r="AB112" s="16"/>
+      <c r="AC112" s="16"/>
+      <c r="AD112" s="16"/>
+      <c r="AE112" s="16"/>
+      <c r="BN112" s="19"/>
+    </row>
+    <row r="113" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C113" s="19"/>
+      <c r="E113" s="16"/>
+      <c r="F113" s="16"/>
+      <c r="G113" s="16"/>
+      <c r="H113" s="16"/>
+      <c r="I113" s="16"/>
+      <c r="J113" s="16"/>
+      <c r="K113" s="16"/>
+      <c r="L113" s="16"/>
+      <c r="M113" s="16"/>
+      <c r="N113" s="16"/>
+      <c r="AB113" s="16"/>
+      <c r="AC113" s="16"/>
+      <c r="AD113" s="16"/>
+      <c r="AE113" s="16"/>
+      <c r="BN113" s="19"/>
+    </row>
+    <row r="114" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C114" s="19"/>
+      <c r="E114" s="16"/>
+      <c r="F114" s="16"/>
+      <c r="G114" s="16"/>
+      <c r="H114" s="16"/>
+      <c r="I114" s="16"/>
+      <c r="J114" s="16"/>
+      <c r="K114" s="16"/>
+      <c r="L114" s="16"/>
+      <c r="M114" s="16"/>
+      <c r="N114" s="16"/>
+      <c r="AB114" s="16"/>
+      <c r="AC114" s="16"/>
+      <c r="AD114" s="16"/>
+      <c r="AE114" s="16"/>
+      <c r="BN114" s="19"/>
+    </row>
+    <row r="115" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C115" s="19"/>
+      <c r="E115" s="16"/>
+      <c r="F115" s="16"/>
+      <c r="G115" s="16"/>
+      <c r="H115" s="16"/>
+      <c r="I115" s="16"/>
+      <c r="J115" s="16"/>
+      <c r="K115" s="16"/>
+      <c r="L115" s="16"/>
+      <c r="M115" s="16"/>
+      <c r="N115" s="16"/>
+      <c r="AB115" s="16"/>
+      <c r="AC115" s="16"/>
+      <c r="AD115" s="16"/>
+      <c r="AE115" s="16"/>
+      <c r="BN115" s="19"/>
+    </row>
+    <row r="116" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="C116" s="19"/>
+      <c r="D116" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="E50" s="34"/>
-      <c r="F50" s="34"/>
-      <c r="G50" s="34"/>
-      <c r="W50" s="25"/>
-      <c r="X50" s="25"/>
-      <c r="Y50" s="25"/>
-      <c r="Z50" s="25"/>
-      <c r="AA50" s="25"/>
-      <c r="AB50" s="25"/>
-      <c r="AC50" s="25"/>
-      <c r="AD50" s="25"/>
-      <c r="AE50" s="25"/>
-      <c r="BN50" s="28"/>
-    </row>
-    <row r="51" spans="4:66" x14ac:dyDescent="0.25">
-      <c r="D51" s="8"/>
-      <c r="W51" s="25"/>
-      <c r="X51" s="25"/>
-      <c r="Y51" s="25"/>
-      <c r="Z51" s="25"/>
-      <c r="AA51" s="25"/>
-      <c r="AB51" s="25"/>
-      <c r="AC51" s="25"/>
-      <c r="AD51" s="25"/>
-      <c r="AE51" s="25"/>
-      <c r="BN51" s="28"/>
-    </row>
-    <row r="52" spans="4:66" x14ac:dyDescent="0.25">
-      <c r="D52" s="8"/>
-      <c r="W52" s="25"/>
-      <c r="X52" s="25"/>
-      <c r="Y52" s="25"/>
-      <c r="Z52" s="25"/>
-      <c r="AA52" s="25"/>
-      <c r="AB52" s="25"/>
-      <c r="AC52" s="25"/>
-      <c r="AD52" s="25"/>
-      <c r="AE52" s="25"/>
-      <c r="BN52" s="28"/>
-    </row>
-    <row r="53" spans="4:66" x14ac:dyDescent="0.25">
-      <c r="D53" s="8"/>
-      <c r="W53" s="25"/>
-      <c r="X53" s="25"/>
-      <c r="Y53" s="25"/>
-      <c r="Z53" s="25"/>
-      <c r="AA53" s="25"/>
-      <c r="AB53" s="25"/>
-      <c r="AC53" s="25"/>
-      <c r="AD53" s="25"/>
-      <c r="AE53" s="25"/>
-      <c r="BN53" s="28"/>
-    </row>
-    <row r="54" spans="4:66" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="D54" s="8"/>
-      <c r="E54" s="35" t="s">
-        <v>14</v>
-      </c>
-      <c r="F54" s="35"/>
-      <c r="G54" s="35"/>
-      <c r="H54" s="35"/>
-      <c r="I54" s="35"/>
-      <c r="W54" s="25"/>
-      <c r="X54" s="25"/>
-      <c r="Y54" s="25"/>
-      <c r="Z54" s="25"/>
-      <c r="AA54" s="25"/>
-      <c r="AB54" s="25"/>
-      <c r="AC54" s="25"/>
-      <c r="AD54" s="25"/>
-      <c r="AE54" s="25"/>
-      <c r="BN54" s="28"/>
-    </row>
-    <row r="55" spans="4:66" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="D55" s="8"/>
-      <c r="E55" s="35" t="s">
-        <v>15</v>
-      </c>
-      <c r="F55" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="G55" s="35"/>
-      <c r="H55" s="35"/>
-      <c r="I55" s="35"/>
-      <c r="W55" s="25"/>
-      <c r="X55" s="25"/>
-      <c r="Y55" s="25"/>
-      <c r="Z55" s="25"/>
-      <c r="AA55" s="25"/>
-      <c r="AB55" s="25"/>
-      <c r="AC55" s="25"/>
-      <c r="AD55" s="25"/>
-      <c r="AE55" s="25"/>
-      <c r="BN55" s="28"/>
-    </row>
-    <row r="56" spans="4:66" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="D56" s="8"/>
-      <c r="E56" s="35"/>
-      <c r="F56" s="35" t="s">
-        <v>17</v>
-      </c>
-      <c r="G56" s="35"/>
-      <c r="H56" s="35"/>
-      <c r="I56" s="35"/>
-      <c r="W56" s="25"/>
-      <c r="X56" s="25"/>
-      <c r="Y56" s="25"/>
-      <c r="Z56" s="25"/>
-      <c r="AA56" s="25"/>
-      <c r="AB56" s="25"/>
-      <c r="AC56" s="25"/>
-      <c r="AD56" s="25"/>
-      <c r="AE56" s="25"/>
-      <c r="BN56" s="28"/>
-    </row>
-    <row r="57" spans="4:66" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="D57" s="8"/>
-      <c r="E57" s="35"/>
-      <c r="F57" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="G57" s="35"/>
-      <c r="H57" s="35"/>
-      <c r="I57" s="35"/>
-      <c r="W57" s="25"/>
-      <c r="X57" s="25"/>
-      <c r="Y57" s="25"/>
-      <c r="Z57" s="25"/>
-      <c r="AA57" s="25"/>
-      <c r="AB57" s="25"/>
-      <c r="AC57" s="25"/>
-      <c r="AD57" s="25"/>
-      <c r="AE57" s="25"/>
-      <c r="BN57" s="28"/>
-    </row>
-    <row r="58" spans="4:66" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="D58" s="8"/>
-      <c r="E58" s="35"/>
-      <c r="F58" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="G58" s="35"/>
-      <c r="H58" s="35"/>
-      <c r="I58" s="35"/>
-      <c r="W58" s="25"/>
-      <c r="X58" s="25"/>
-      <c r="Y58" s="25"/>
-      <c r="Z58" s="25"/>
-      <c r="AA58" s="25"/>
-      <c r="AB58" s="25"/>
-      <c r="AC58" s="25"/>
-      <c r="AD58" s="25"/>
-      <c r="AE58" s="25"/>
-      <c r="BN58" s="28"/>
-    </row>
-    <row r="59" spans="4:66" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D59" s="40"/>
-      <c r="E59" s="30"/>
-      <c r="F59" s="30"/>
-      <c r="G59" s="30"/>
-      <c r="H59" s="30"/>
-      <c r="I59" s="30"/>
-      <c r="J59" s="30"/>
-      <c r="K59" s="30"/>
-      <c r="L59" s="30"/>
-      <c r="M59" s="30"/>
-      <c r="N59" s="30"/>
-      <c r="O59" s="30"/>
-      <c r="P59" s="30"/>
-      <c r="Q59" s="30"/>
-      <c r="R59" s="30"/>
-      <c r="S59" s="30"/>
-      <c r="T59" s="30"/>
-      <c r="U59" s="30"/>
-      <c r="V59" s="30"/>
-      <c r="W59" s="30"/>
-      <c r="X59" s="30"/>
-      <c r="Y59" s="30"/>
-      <c r="Z59" s="30"/>
-      <c r="AA59" s="30"/>
-      <c r="AB59" s="30"/>
-      <c r="AC59" s="30"/>
-      <c r="AD59" s="30"/>
-      <c r="AE59" s="30"/>
-      <c r="AF59" s="30"/>
-      <c r="AG59" s="30"/>
-      <c r="AH59" s="30"/>
-      <c r="AI59" s="30"/>
-      <c r="AJ59" s="30"/>
-      <c r="AK59" s="30"/>
-      <c r="AL59" s="30"/>
-      <c r="AM59" s="30"/>
-      <c r="AN59" s="30"/>
-      <c r="AO59" s="30"/>
-      <c r="AP59" s="30"/>
-      <c r="AQ59" s="30"/>
-      <c r="AR59" s="30"/>
-      <c r="AS59" s="30"/>
-      <c r="AT59" s="30"/>
-      <c r="AU59" s="30"/>
-      <c r="AV59" s="30"/>
-      <c r="AW59" s="30"/>
-      <c r="AX59" s="30"/>
-      <c r="AY59" s="30"/>
-      <c r="AZ59" s="30"/>
-      <c r="BA59" s="30"/>
-      <c r="BB59" s="30"/>
-      <c r="BC59" s="30"/>
-      <c r="BD59" s="30"/>
-      <c r="BE59" s="30"/>
-      <c r="BF59" s="30"/>
-      <c r="BG59" s="30"/>
-      <c r="BH59" s="30"/>
-      <c r="BI59" s="30"/>
-      <c r="BJ59" s="30"/>
-      <c r="BK59" s="30"/>
-      <c r="BL59" s="30"/>
-      <c r="BM59" s="30"/>
-      <c r="BN59" s="31"/>
-    </row>
-    <row r="60" spans="4:66" x14ac:dyDescent="0.25">
-      <c r="D60" s="8"/>
-      <c r="W60" s="25"/>
-      <c r="X60" s="25"/>
-      <c r="Y60" s="25"/>
-      <c r="Z60" s="25"/>
-      <c r="AA60" s="25"/>
-      <c r="AB60" s="25"/>
-      <c r="AC60" s="25"/>
-      <c r="AD60" s="25"/>
-      <c r="AE60" s="25"/>
-      <c r="BN60" s="28"/>
-    </row>
-    <row r="61" spans="4:66" x14ac:dyDescent="0.25">
-      <c r="D61" s="8"/>
-      <c r="W61" s="25"/>
-      <c r="X61" s="25"/>
-      <c r="Y61" s="25"/>
-      <c r="Z61" s="25"/>
-      <c r="AA61" s="25"/>
-      <c r="AB61" s="25"/>
-      <c r="AC61" s="25"/>
-      <c r="AD61" s="25"/>
-      <c r="AE61" s="25"/>
-      <c r="BN61" s="28"/>
-    </row>
-    <row r="62" spans="4:66" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="D62" s="47" t="s">
-        <v>34</v>
-      </c>
-      <c r="E62" s="47"/>
-      <c r="F62" s="47"/>
-      <c r="G62" s="47"/>
-      <c r="W62" s="25"/>
-      <c r="X62" s="25"/>
-      <c r="Y62" s="25"/>
-      <c r="Z62" s="25"/>
-      <c r="AA62" s="25"/>
-      <c r="AB62" s="25"/>
-      <c r="AC62" s="25"/>
-      <c r="AD62" s="25"/>
-      <c r="AE62" s="25"/>
-      <c r="BN62" s="28"/>
-    </row>
-    <row r="63" spans="4:66" x14ac:dyDescent="0.25">
-      <c r="D63" s="8"/>
-      <c r="W63" s="25"/>
-      <c r="X63" s="25"/>
-      <c r="Y63" s="25"/>
-      <c r="Z63" s="25"/>
-      <c r="AA63" s="25"/>
-      <c r="AB63" s="25"/>
-      <c r="AC63" s="25"/>
-      <c r="AD63" s="25"/>
-      <c r="AE63" s="25"/>
-      <c r="BN63" s="28"/>
-    </row>
-    <row r="64" spans="4:66" x14ac:dyDescent="0.25">
-      <c r="D64" s="8"/>
-      <c r="W64" s="25"/>
-      <c r="X64" s="25"/>
-      <c r="Y64" s="25"/>
-      <c r="Z64" s="25"/>
-      <c r="AA64" s="25"/>
-      <c r="AB64" s="25"/>
-      <c r="AC64" s="25"/>
-      <c r="AD64" s="25"/>
-      <c r="AE64" s="25"/>
-      <c r="BN64" s="28"/>
-    </row>
-    <row r="65" spans="4:66" x14ac:dyDescent="0.25">
-      <c r="D65" s="8"/>
-      <c r="W65" s="25"/>
-      <c r="X65" s="25"/>
-      <c r="Y65" s="25"/>
-      <c r="Z65" s="25"/>
-      <c r="AA65" s="25"/>
-      <c r="AB65" s="25"/>
-      <c r="AC65" s="25"/>
-      <c r="AD65" s="25"/>
-      <c r="AE65" s="25"/>
-      <c r="BN65" s="28"/>
-    </row>
-    <row r="66" spans="4:66" x14ac:dyDescent="0.25">
-      <c r="D66" s="8"/>
-      <c r="W66" s="25"/>
-      <c r="X66" s="25"/>
-      <c r="Y66" s="25"/>
-      <c r="Z66" s="25"/>
-      <c r="AA66" s="25"/>
-      <c r="AB66" s="25"/>
-      <c r="AC66" s="25"/>
-      <c r="AD66" s="25"/>
-      <c r="AE66" s="25"/>
-      <c r="AO66" s="25"/>
-      <c r="AP66" s="25"/>
-      <c r="AQ66" s="25"/>
-      <c r="AR66" s="25"/>
-      <c r="AS66" s="25"/>
-      <c r="BN66" s="28"/>
-    </row>
-    <row r="67" spans="4:66" x14ac:dyDescent="0.25">
-      <c r="D67" s="8"/>
-      <c r="F67" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q67" t="s">
-        <v>38</v>
-      </c>
-      <c r="W67" s="25"/>
-      <c r="X67" s="25"/>
-      <c r="Y67" s="25"/>
-      <c r="Z67" s="25"/>
-      <c r="AA67" s="25"/>
-      <c r="AB67" s="25"/>
-      <c r="AC67" s="25"/>
-      <c r="AD67" s="25"/>
-      <c r="AE67" s="25"/>
-      <c r="AH67" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO67" s="25"/>
-      <c r="AP67" s="25"/>
-      <c r="AQ67" s="25"/>
-      <c r="AR67" s="25"/>
-      <c r="AS67" s="25"/>
-      <c r="AV67" t="s">
-        <v>36</v>
-      </c>
-      <c r="BN67" s="28"/>
-    </row>
-    <row r="68" spans="4:66" x14ac:dyDescent="0.25">
-      <c r="D68" s="8"/>
-      <c r="W68" s="25"/>
-      <c r="X68" s="25"/>
-      <c r="Y68" s="25"/>
-      <c r="Z68" s="25"/>
-      <c r="AA68" s="25"/>
-      <c r="AB68" s="25"/>
-      <c r="AC68" s="25"/>
-      <c r="AD68" s="25"/>
-      <c r="AE68" s="25"/>
-      <c r="AO68" s="25"/>
-      <c r="AP68" s="25"/>
-      <c r="AQ68" s="25"/>
-      <c r="AR68" s="25"/>
-      <c r="AS68" s="25"/>
-      <c r="BG68" t="s">
-        <v>37</v>
-      </c>
-      <c r="BN68" s="28"/>
-    </row>
-    <row r="69" spans="4:66" x14ac:dyDescent="0.25">
-      <c r="D69" s="8"/>
-      <c r="W69" s="25"/>
-      <c r="X69" s="25"/>
-      <c r="Y69" s="25"/>
-      <c r="Z69" s="25"/>
-      <c r="AA69" s="25"/>
-      <c r="AB69" s="25"/>
-      <c r="AC69" s="25"/>
-      <c r="AD69" s="25"/>
-      <c r="AE69" s="25"/>
-      <c r="AO69" s="25"/>
-      <c r="AP69" s="25"/>
-      <c r="AQ69" s="25"/>
-      <c r="AR69" s="25"/>
-      <c r="AS69" s="25"/>
-      <c r="BN69" s="28"/>
-    </row>
-    <row r="70" spans="4:66" x14ac:dyDescent="0.25">
-      <c r="D70" s="27"/>
-      <c r="W70" s="25"/>
-      <c r="X70" s="25"/>
-      <c r="Y70" s="25"/>
-      <c r="Z70" s="25"/>
-      <c r="AA70" s="25"/>
-      <c r="AB70" s="25"/>
-      <c r="AC70" s="25"/>
-      <c r="AD70" s="25"/>
-      <c r="AE70" s="25"/>
-      <c r="AO70" s="25"/>
-      <c r="AP70" s="25"/>
-      <c r="AQ70" s="25"/>
-      <c r="AR70" s="25"/>
-      <c r="AS70" s="25"/>
-      <c r="BN70" s="28"/>
-    </row>
-    <row r="71" spans="4:66" x14ac:dyDescent="0.25">
-      <c r="D71" s="27"/>
-      <c r="W71" s="25"/>
-      <c r="X71" s="25"/>
-      <c r="Y71" s="25"/>
-      <c r="Z71" s="25"/>
-      <c r="AA71" s="25"/>
-      <c r="AB71" s="25"/>
-      <c r="AC71" s="25"/>
-      <c r="AD71" s="25"/>
-      <c r="AE71" s="25"/>
-      <c r="AO71" s="25"/>
-      <c r="AP71" s="25"/>
-      <c r="AQ71" s="25"/>
-      <c r="AR71" s="25"/>
-      <c r="AS71" s="25"/>
-      <c r="BN71" s="28"/>
-    </row>
-    <row r="72" spans="4:66" x14ac:dyDescent="0.25">
-      <c r="D72" s="27"/>
-      <c r="W72" s="25"/>
-      <c r="X72" s="25"/>
-      <c r="Y72" s="25"/>
-      <c r="Z72" s="25"/>
-      <c r="AA72" s="25"/>
-      <c r="AB72" s="25"/>
-      <c r="AC72" s="25"/>
-      <c r="AD72" s="25"/>
-      <c r="AE72" s="25"/>
-      <c r="AO72" s="25"/>
-      <c r="AP72" s="25"/>
-      <c r="AQ72" s="25"/>
-      <c r="AR72" s="25"/>
-      <c r="AS72" s="25"/>
-      <c r="BN72" s="28"/>
-    </row>
-    <row r="73" spans="4:66" x14ac:dyDescent="0.25">
-      <c r="D73" s="27"/>
-      <c r="W73" s="25"/>
-      <c r="X73" s="25"/>
-      <c r="Y73" s="25"/>
-      <c r="Z73" s="25"/>
-      <c r="AA73" s="25"/>
-      <c r="AB73" s="25"/>
-      <c r="AC73" s="25"/>
-      <c r="AD73" s="25"/>
-      <c r="AE73" s="25"/>
-      <c r="AO73" s="25"/>
-      <c r="AP73" s="25"/>
-      <c r="AQ73" s="25"/>
-      <c r="AR73" s="25"/>
-      <c r="AS73" s="25"/>
-      <c r="BN73" s="28"/>
-    </row>
-    <row r="74" spans="4:66" x14ac:dyDescent="0.25">
-      <c r="D74" s="27"/>
-      <c r="W74" s="25"/>
-      <c r="X74" s="25"/>
-      <c r="Y74" s="25"/>
-      <c r="Z74" s="25"/>
-      <c r="AA74" s="25"/>
-      <c r="AB74" s="25"/>
-      <c r="AC74" s="25"/>
-      <c r="AD74" s="25"/>
-      <c r="AE74" s="25"/>
-      <c r="AO74" s="25"/>
-      <c r="AP74" s="25"/>
-      <c r="AQ74" s="25"/>
-      <c r="AR74" s="25"/>
-      <c r="AS74" s="25"/>
-      <c r="BN74" s="28"/>
-    </row>
-    <row r="75" spans="4:66" x14ac:dyDescent="0.25">
-      <c r="D75" s="27"/>
-      <c r="W75" s="25"/>
-      <c r="X75" s="25"/>
-      <c r="Y75" s="25"/>
-      <c r="Z75" s="25"/>
-      <c r="AA75" s="25"/>
-      <c r="AB75" s="25"/>
-      <c r="AC75" s="25"/>
-      <c r="AD75" s="25"/>
-      <c r="AE75" s="25"/>
-      <c r="AO75" s="25"/>
-      <c r="AP75" s="25"/>
-      <c r="AQ75" s="25"/>
-      <c r="AR75" s="25"/>
-      <c r="AS75" s="25"/>
-      <c r="BN75" s="28"/>
-    </row>
-    <row r="76" spans="4:66" x14ac:dyDescent="0.25">
-      <c r="D76" s="27"/>
-      <c r="W76" s="25"/>
-      <c r="X76" s="25"/>
-      <c r="Y76" s="25"/>
-      <c r="Z76" s="25"/>
-      <c r="AA76" s="25"/>
-      <c r="AB76" s="25"/>
-      <c r="AC76" s="25"/>
-      <c r="AD76" s="25"/>
-      <c r="AE76" s="25"/>
-      <c r="AO76" s="25"/>
-      <c r="AP76" s="25"/>
-      <c r="AQ76" s="25"/>
-      <c r="AR76" s="25"/>
-      <c r="AS76" s="25"/>
-      <c r="BN76" s="28"/>
-    </row>
-    <row r="77" spans="4:66" x14ac:dyDescent="0.25">
-      <c r="D77" s="27"/>
-      <c r="W77" s="25"/>
-      <c r="X77" s="25"/>
-      <c r="Y77" s="25"/>
-      <c r="Z77" s="25"/>
-      <c r="AA77" s="25"/>
-      <c r="AB77" s="25"/>
-      <c r="AC77" s="25"/>
-      <c r="AD77" s="25"/>
-      <c r="AE77" s="25"/>
-      <c r="AO77" s="25"/>
-      <c r="AP77" s="25"/>
-      <c r="AQ77" s="25"/>
-      <c r="AR77" s="25"/>
-      <c r="AS77" s="25"/>
-      <c r="BN77" s="28"/>
-    </row>
-    <row r="78" spans="4:66" x14ac:dyDescent="0.25">
-      <c r="D78" s="27"/>
-      <c r="W78" s="25"/>
-      <c r="X78" s="25"/>
-      <c r="Y78" s="25"/>
-      <c r="Z78" s="25"/>
-      <c r="AA78" s="25"/>
-      <c r="AB78" s="25"/>
-      <c r="AC78" s="25"/>
-      <c r="AD78" s="25"/>
-      <c r="AE78" s="25"/>
-      <c r="AG78" s="25"/>
-      <c r="AH78" s="25"/>
-      <c r="AO78" s="25"/>
-      <c r="AP78" s="25"/>
-      <c r="AQ78" s="25"/>
-      <c r="AR78" s="25"/>
-      <c r="AS78" s="25"/>
-      <c r="BN78" s="28"/>
-    </row>
-    <row r="79" spans="4:66" x14ac:dyDescent="0.25">
-      <c r="D79" s="27"/>
-      <c r="W79" s="25"/>
-      <c r="X79" s="25"/>
-      <c r="Y79" s="25"/>
-      <c r="Z79" s="25"/>
-      <c r="AA79" s="25"/>
-      <c r="AB79" s="25"/>
-      <c r="AC79" s="25"/>
-      <c r="AD79" s="25"/>
-      <c r="AE79" s="25"/>
-      <c r="AG79" s="25"/>
-      <c r="AH79" s="25"/>
-      <c r="AO79" s="25"/>
-      <c r="AP79" s="25"/>
-      <c r="AQ79" s="25"/>
-      <c r="AR79" s="25"/>
-      <c r="AS79" s="25"/>
-      <c r="BN79" s="28"/>
-    </row>
-    <row r="80" spans="4:66" x14ac:dyDescent="0.25">
-      <c r="D80" s="27"/>
-      <c r="W80" s="25"/>
-      <c r="X80" s="25"/>
-      <c r="Y80" s="25"/>
-      <c r="Z80" s="25"/>
-      <c r="AA80" s="25"/>
-      <c r="AB80" s="25"/>
-      <c r="AC80" s="25"/>
-      <c r="AD80" s="25"/>
-      <c r="AE80" s="25"/>
-      <c r="AG80" s="25"/>
-      <c r="AH80" s="25"/>
-      <c r="AO80" s="25"/>
-      <c r="AP80" s="25"/>
-      <c r="AQ80" s="25"/>
-      <c r="AR80" s="25"/>
-      <c r="AS80" s="25"/>
-      <c r="BN80" s="28"/>
-    </row>
-    <row r="81" spans="4:66" x14ac:dyDescent="0.25">
-      <c r="D81" s="27"/>
-      <c r="W81" s="25"/>
-      <c r="X81" s="25"/>
-      <c r="Y81" s="25"/>
-      <c r="Z81" s="25"/>
-      <c r="AA81" s="25"/>
-      <c r="AB81" s="25"/>
-      <c r="AC81" s="25"/>
-      <c r="AD81" s="25"/>
-      <c r="AE81" s="25"/>
-      <c r="AG81" s="25"/>
-      <c r="AH81" s="25"/>
-      <c r="AO81" s="25"/>
-      <c r="AP81" s="25"/>
-      <c r="AQ81" s="25"/>
-      <c r="AR81" s="25"/>
-      <c r="AS81" s="25"/>
-      <c r="BN81" s="28"/>
-    </row>
-    <row r="82" spans="4:66" x14ac:dyDescent="0.25">
-      <c r="D82" s="27"/>
-      <c r="W82" s="25"/>
-      <c r="X82" s="25"/>
-      <c r="Y82" s="25"/>
-      <c r="Z82" s="25"/>
-      <c r="AA82" s="25"/>
-      <c r="AB82" s="25"/>
-      <c r="AC82" s="25"/>
-      <c r="AD82" s="25"/>
-      <c r="AE82" s="25"/>
-      <c r="AG82" s="25"/>
-      <c r="AH82" s="25"/>
-      <c r="AO82" s="25"/>
-      <c r="AP82" s="25"/>
-      <c r="AQ82" s="25"/>
-      <c r="AR82" s="25"/>
-      <c r="AS82" s="25"/>
-      <c r="BN82" s="28"/>
-    </row>
-    <row r="83" spans="4:66" x14ac:dyDescent="0.25">
-      <c r="D83" s="27"/>
-      <c r="W83" s="25"/>
-      <c r="X83" s="25"/>
-      <c r="Y83" s="25"/>
-      <c r="Z83" s="25"/>
-      <c r="AA83" s="25"/>
-      <c r="AB83" s="25"/>
-      <c r="AC83" s="25"/>
-      <c r="AD83" s="25"/>
-      <c r="AE83" s="25"/>
-      <c r="AG83" s="25"/>
-      <c r="AH83" s="25"/>
-      <c r="AO83" s="25"/>
-      <c r="AP83" s="25"/>
-      <c r="AQ83" s="25"/>
-      <c r="AR83" s="25"/>
-      <c r="AS83" s="25"/>
-      <c r="BN83" s="28"/>
-    </row>
-    <row r="84" spans="4:66" x14ac:dyDescent="0.25">
-      <c r="D84" s="27"/>
-      <c r="W84" s="25"/>
-      <c r="X84" s="25"/>
-      <c r="Y84" s="25"/>
-      <c r="Z84" s="25"/>
-      <c r="AA84" s="25"/>
-      <c r="AB84" s="25"/>
-      <c r="AC84" s="25"/>
-      <c r="AD84" s="25"/>
-      <c r="AE84" s="25"/>
-      <c r="AG84" s="25"/>
-      <c r="AH84" s="25"/>
-      <c r="AO84" s="25"/>
-      <c r="AP84" s="25"/>
-      <c r="AQ84" s="25"/>
-      <c r="AR84" s="25"/>
-      <c r="AS84" s="25"/>
-      <c r="BN84" s="28"/>
-    </row>
-    <row r="85" spans="4:66" x14ac:dyDescent="0.25">
-      <c r="D85" s="27"/>
-      <c r="W85" s="25"/>
-      <c r="X85" s="25"/>
-      <c r="Y85" s="25"/>
-      <c r="Z85" s="25"/>
-      <c r="AA85" s="25"/>
-      <c r="AB85" s="25"/>
-      <c r="AC85" s="25"/>
-      <c r="AD85" s="25"/>
-      <c r="AE85" s="25"/>
-      <c r="AG85" s="25"/>
-      <c r="AH85" s="25"/>
-      <c r="AO85" s="25"/>
-      <c r="AP85" s="25"/>
-      <c r="AQ85" s="25"/>
-      <c r="AR85" s="25"/>
-      <c r="AS85" s="25"/>
-      <c r="BN85" s="28"/>
-    </row>
-    <row r="86" spans="4:66" x14ac:dyDescent="0.25">
-      <c r="D86" s="27"/>
-      <c r="W86" s="25"/>
-      <c r="X86" s="25"/>
-      <c r="Y86" s="25"/>
-      <c r="Z86" s="25"/>
-      <c r="AA86" s="25"/>
-      <c r="AB86" s="25"/>
-      <c r="AC86" s="25"/>
-      <c r="AD86" s="25"/>
-      <c r="AE86" s="25"/>
-      <c r="AG86" s="25"/>
-      <c r="AH86" s="25"/>
-      <c r="AO86" s="25"/>
-      <c r="AP86" s="25"/>
-      <c r="AQ86" s="25"/>
-      <c r="AR86" s="25"/>
-      <c r="AS86" s="25"/>
-      <c r="BN86" s="28"/>
-    </row>
-    <row r="87" spans="4:66" x14ac:dyDescent="0.25">
-      <c r="D87" s="27"/>
-      <c r="W87" s="25"/>
-      <c r="X87" s="25"/>
-      <c r="Y87" s="25"/>
-      <c r="Z87" s="25"/>
-      <c r="AA87" s="25"/>
-      <c r="AB87" s="25"/>
-      <c r="AC87" s="25"/>
-      <c r="AD87" s="25"/>
-      <c r="AE87" s="25"/>
-      <c r="AG87" s="25"/>
-      <c r="AH87" s="25"/>
-      <c r="AO87" s="25"/>
-      <c r="AP87" s="25"/>
-      <c r="AQ87" s="25"/>
-      <c r="AR87" s="25"/>
-      <c r="AS87" s="25"/>
-      <c r="BN87" s="28"/>
-    </row>
-    <row r="88" spans="4:66" x14ac:dyDescent="0.25">
-      <c r="D88" s="27"/>
-      <c r="W88" s="25"/>
-      <c r="X88" s="25"/>
-      <c r="Y88" s="25"/>
-      <c r="Z88" s="25"/>
-      <c r="AA88" s="25"/>
-      <c r="AB88" s="25"/>
-      <c r="AC88" s="25"/>
-      <c r="AD88" s="25"/>
-      <c r="AE88" s="25"/>
-      <c r="AG88" s="25"/>
-      <c r="AH88" s="25"/>
-      <c r="AO88" s="25"/>
-      <c r="AP88" s="25"/>
-      <c r="AQ88" s="25"/>
-      <c r="AR88" s="25"/>
-      <c r="AS88" s="25"/>
-      <c r="BN88" s="28"/>
-    </row>
-    <row r="89" spans="4:66" x14ac:dyDescent="0.25">
-      <c r="D89" s="27"/>
-      <c r="W89" s="25"/>
-      <c r="X89" s="25"/>
-      <c r="Y89" s="25"/>
-      <c r="Z89" s="25"/>
-      <c r="AA89" s="25"/>
-      <c r="AB89" s="25"/>
-      <c r="AC89" s="25"/>
-      <c r="AD89" s="25"/>
-      <c r="AE89" s="25"/>
-      <c r="AO89" s="25"/>
-      <c r="AP89" s="25"/>
-      <c r="AQ89" s="25"/>
-      <c r="AR89" s="25"/>
-      <c r="AS89" s="25"/>
-      <c r="BN89" s="28"/>
-    </row>
-    <row r="90" spans="4:66" x14ac:dyDescent="0.25">
-      <c r="D90" s="27"/>
-      <c r="F90" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q90" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="W90" s="25"/>
-      <c r="X90" s="25"/>
-      <c r="Y90" s="25"/>
-      <c r="Z90" s="25"/>
-      <c r="AA90" s="25"/>
-      <c r="AB90" s="25"/>
-      <c r="AC90" s="25"/>
-      <c r="AD90" s="25"/>
-      <c r="AE90" s="25"/>
-      <c r="AO90" s="25"/>
-      <c r="AP90" s="25"/>
-      <c r="AQ90" s="25"/>
-      <c r="AR90" s="25"/>
-      <c r="AS90" s="25"/>
-      <c r="BN90" s="28"/>
-    </row>
-    <row r="91" spans="4:66" x14ac:dyDescent="0.25">
-      <c r="D91" s="27"/>
-      <c r="W91" s="25"/>
-      <c r="X91" s="25"/>
-      <c r="Y91" s="25"/>
-      <c r="Z91" s="25"/>
-      <c r="AA91" s="25"/>
-      <c r="AB91" s="25"/>
-      <c r="AC91" s="25"/>
-      <c r="AD91" s="25"/>
-      <c r="AE91" s="25"/>
-      <c r="AO91" s="25"/>
-      <c r="AP91" s="25"/>
-      <c r="AQ91" s="25"/>
-      <c r="AR91" s="25"/>
-      <c r="AS91" s="25"/>
-      <c r="BN91" s="28"/>
-    </row>
-    <row r="92" spans="4:66" x14ac:dyDescent="0.25">
-      <c r="D92" s="27"/>
-      <c r="W92" s="25"/>
-      <c r="X92" s="25"/>
-      <c r="Y92" s="25"/>
-      <c r="Z92" s="25"/>
-      <c r="AA92" s="25"/>
-      <c r="AB92" s="25"/>
-      <c r="AC92" s="25"/>
-      <c r="AD92" s="25"/>
-      <c r="AE92" s="25"/>
-      <c r="AH92" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="AO92" s="25"/>
-      <c r="AP92" s="25"/>
-      <c r="AQ92" s="25"/>
-      <c r="AR92" s="25"/>
-      <c r="AS92" s="25"/>
-      <c r="BN92" s="28"/>
-    </row>
-    <row r="93" spans="4:66" x14ac:dyDescent="0.25">
-      <c r="D93" s="27"/>
-      <c r="AB93" s="25"/>
-      <c r="AC93" s="25"/>
-      <c r="AD93" s="25"/>
-      <c r="AE93" s="25"/>
-      <c r="AO93" s="25"/>
-      <c r="AP93" s="25"/>
-      <c r="AQ93" s="25"/>
-      <c r="AR93" s="25"/>
-      <c r="AS93" s="25"/>
-      <c r="BN93" s="28"/>
-    </row>
-    <row r="94" spans="4:66" x14ac:dyDescent="0.25">
-      <c r="D94" s="27"/>
-      <c r="AB94" s="25"/>
-      <c r="AC94" s="25"/>
-      <c r="AD94" s="25"/>
-      <c r="AE94" s="25"/>
-      <c r="AO94" s="25"/>
-      <c r="AP94" s="25"/>
-      <c r="AQ94" s="25"/>
-      <c r="AR94" s="25"/>
-      <c r="AS94" s="25"/>
-      <c r="BN94" s="28"/>
-    </row>
-    <row r="95" spans="4:66" x14ac:dyDescent="0.25">
-      <c r="D95" s="27"/>
-      <c r="AB95" s="25"/>
-      <c r="AC95" s="25"/>
-      <c r="AD95" s="25"/>
-      <c r="AE95" s="25"/>
-      <c r="AO95" s="25"/>
-      <c r="AP95" s="25"/>
-      <c r="AQ95" s="25"/>
-      <c r="AR95" s="25"/>
-      <c r="AS95" s="25"/>
-      <c r="BN95" s="28"/>
-    </row>
-    <row r="96" spans="4:66" x14ac:dyDescent="0.25">
-      <c r="D96" s="27"/>
-      <c r="AB96" s="25"/>
-      <c r="AC96" s="25"/>
-      <c r="AD96" s="25"/>
-      <c r="AE96" s="25"/>
-      <c r="AO96" s="25"/>
-      <c r="AP96" s="25"/>
-      <c r="AQ96" s="25"/>
-      <c r="AR96" s="25"/>
-      <c r="AS96" s="25"/>
-      <c r="BN96" s="28"/>
-    </row>
-    <row r="97" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="D97" s="27"/>
-      <c r="AB97" s="25"/>
-      <c r="AC97" s="25"/>
-      <c r="AD97" s="25"/>
-      <c r="AE97" s="25"/>
-      <c r="AO97" s="25"/>
-      <c r="AP97" s="25"/>
-      <c r="AQ97" s="25"/>
-      <c r="AR97" s="25"/>
-      <c r="AS97" s="25"/>
-      <c r="BN97" s="28"/>
-    </row>
-    <row r="98" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="D98" s="27"/>
-      <c r="E98" s="25"/>
-      <c r="F98" s="25"/>
-      <c r="G98" s="25"/>
-      <c r="H98" s="25"/>
-      <c r="I98" s="25"/>
-      <c r="J98" s="25"/>
-      <c r="K98" s="25"/>
-      <c r="AB98" s="25"/>
-      <c r="AC98" s="25"/>
-      <c r="AD98" s="25"/>
-      <c r="AE98" s="25"/>
-      <c r="AO98" s="25"/>
-      <c r="AP98" s="25"/>
-      <c r="AQ98" s="25"/>
-      <c r="AR98" s="25"/>
-      <c r="AS98" s="25"/>
-      <c r="BN98" s="28"/>
-    </row>
-    <row r="99" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="D99" s="27"/>
-      <c r="E99" s="25"/>
-      <c r="F99" s="25"/>
-      <c r="G99" s="25"/>
-      <c r="H99" s="25"/>
-      <c r="I99" s="25"/>
-      <c r="J99" s="25"/>
-      <c r="K99" s="25"/>
-      <c r="AB99" s="25"/>
-      <c r="AC99" s="25"/>
-      <c r="AD99" s="25"/>
-      <c r="AE99" s="25"/>
-      <c r="AO99" s="25"/>
-      <c r="AP99" s="25"/>
-      <c r="AQ99" s="25"/>
-      <c r="AR99" s="25"/>
-      <c r="AS99" s="25"/>
-      <c r="BN99" s="28"/>
-    </row>
-    <row r="100" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="D100" s="27"/>
-      <c r="E100" s="25"/>
-      <c r="F100" s="25"/>
-      <c r="G100" s="25"/>
-      <c r="H100" s="25"/>
-      <c r="I100" s="25"/>
-      <c r="J100" s="25"/>
-      <c r="K100" s="25"/>
-      <c r="AB100" s="25"/>
-      <c r="AC100" s="25"/>
-      <c r="AD100" s="25"/>
-      <c r="AE100" s="25"/>
-      <c r="AO100" s="25"/>
-      <c r="AP100" s="25"/>
-      <c r="AQ100" s="25"/>
-      <c r="AR100" s="25"/>
-      <c r="AS100" s="25"/>
-      <c r="BN100" s="28"/>
-    </row>
-    <row r="101" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="D101" s="27"/>
-      <c r="E101" s="25"/>
-      <c r="F101" s="25"/>
-      <c r="G101" s="25"/>
-      <c r="H101" s="25"/>
-      <c r="I101" s="25"/>
-      <c r="J101" s="25"/>
-      <c r="K101" s="25"/>
-      <c r="AB101" s="25"/>
-      <c r="AC101" s="25"/>
-      <c r="AD101" s="25"/>
-      <c r="AE101" s="25"/>
-      <c r="AO101" s="25"/>
-      <c r="AP101" s="25"/>
-      <c r="AQ101" s="25"/>
-      <c r="AR101" s="25"/>
-      <c r="AS101" s="25"/>
-      <c r="BN101" s="28"/>
-    </row>
-    <row r="102" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="D102" s="27"/>
-      <c r="E102" s="25"/>
-      <c r="F102" s="25"/>
-      <c r="G102" s="25"/>
-      <c r="H102" s="25"/>
-      <c r="I102" s="25"/>
-      <c r="J102" s="25"/>
-      <c r="K102" s="25"/>
-      <c r="AB102" s="25"/>
-      <c r="AC102" s="25"/>
-      <c r="AD102" s="25"/>
-      <c r="AE102" s="25"/>
-      <c r="AO102" s="25"/>
-      <c r="AP102" s="25"/>
-      <c r="AQ102" s="25"/>
-      <c r="AR102" s="25"/>
-      <c r="AS102" s="25"/>
-      <c r="BN102" s="28"/>
-    </row>
-    <row r="103" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="D103" s="27"/>
-      <c r="E103" s="25"/>
-      <c r="F103" s="25"/>
-      <c r="G103" s="25"/>
-      <c r="H103" s="25"/>
-      <c r="I103" s="25"/>
-      <c r="J103" s="25"/>
-      <c r="K103" s="25"/>
-      <c r="AB103" s="25"/>
-      <c r="AC103" s="25"/>
-      <c r="AD103" s="25"/>
-      <c r="AE103" s="25"/>
-      <c r="BN103" s="28"/>
-    </row>
-    <row r="104" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="D104" s="27"/>
-      <c r="E104" s="25"/>
-      <c r="F104" s="25"/>
-      <c r="G104" s="25"/>
-      <c r="H104" s="25"/>
-      <c r="I104" s="25"/>
-      <c r="J104" s="25"/>
-      <c r="K104" s="25"/>
-      <c r="AB104" s="25"/>
-      <c r="AC104" s="25"/>
-      <c r="AD104" s="25"/>
-      <c r="AE104" s="25"/>
-      <c r="AO104" s="25"/>
-      <c r="AP104" s="25"/>
-      <c r="AQ104" s="25"/>
-      <c r="AR104" s="25"/>
-      <c r="AS104" s="25"/>
-      <c r="BN104" s="28"/>
-    </row>
-    <row r="105" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="D105" s="27"/>
-      <c r="E105" s="25"/>
-      <c r="F105" s="25"/>
-      <c r="G105" s="25"/>
-      <c r="H105" s="25"/>
-      <c r="I105" s="25"/>
-      <c r="J105" s="25"/>
-      <c r="K105" s="25"/>
-      <c r="L105" s="25"/>
-      <c r="M105" s="25"/>
-      <c r="N105" s="25"/>
-      <c r="AB105" s="25"/>
-      <c r="AC105" s="25"/>
-      <c r="AD105" s="25"/>
-      <c r="AE105" s="25"/>
-      <c r="AO105" s="25"/>
-      <c r="AP105" s="25"/>
-      <c r="AQ105" s="25"/>
-      <c r="AR105" s="25"/>
-      <c r="AS105" s="25"/>
-      <c r="BN105" s="28"/>
-    </row>
-    <row r="106" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="D106" s="27"/>
-      <c r="E106" s="25"/>
-      <c r="F106" s="25"/>
-      <c r="G106" s="25"/>
-      <c r="H106" s="25"/>
-      <c r="I106" s="25"/>
-      <c r="J106" s="25"/>
-      <c r="K106" s="25"/>
-      <c r="L106" s="25"/>
-      <c r="M106" s="25"/>
-      <c r="N106" s="25"/>
-      <c r="AB106" s="25"/>
-      <c r="AC106" s="25"/>
-      <c r="AD106" s="25"/>
-      <c r="AE106" s="25"/>
-      <c r="BN106" s="28"/>
-    </row>
-    <row r="107" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="D107" s="27"/>
-      <c r="E107" s="25"/>
-      <c r="F107" s="25"/>
-      <c r="G107" s="25"/>
-      <c r="H107" s="25"/>
-      <c r="I107" s="25"/>
-      <c r="J107" s="25"/>
-      <c r="K107" s="25"/>
-      <c r="L107" s="25"/>
-      <c r="M107" s="25"/>
-      <c r="N107" s="25"/>
-      <c r="AB107" s="25"/>
-      <c r="AC107" s="25"/>
-      <c r="AD107" s="25"/>
-      <c r="AE107" s="25"/>
-      <c r="BN107" s="28"/>
-    </row>
-    <row r="108" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="D108" s="27"/>
-      <c r="E108" s="25"/>
-      <c r="F108" s="25"/>
-      <c r="G108" s="25"/>
-      <c r="H108" s="25"/>
-      <c r="I108" s="25"/>
-      <c r="J108" s="25"/>
-      <c r="K108" s="25"/>
-      <c r="L108" s="25"/>
-      <c r="M108" s="25"/>
-      <c r="N108" s="25"/>
-      <c r="AB108" s="25"/>
-      <c r="AC108" s="25"/>
-      <c r="AD108" s="25"/>
-      <c r="AE108" s="25"/>
-      <c r="BN108" s="28"/>
-    </row>
-    <row r="109" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="D109" s="27"/>
-      <c r="E109" s="25"/>
-      <c r="F109" s="25"/>
-      <c r="G109" s="25"/>
-      <c r="H109" s="25"/>
-      <c r="I109" s="25"/>
-      <c r="J109" s="25"/>
-      <c r="K109" s="25"/>
-      <c r="L109" s="25"/>
-      <c r="M109" s="25"/>
-      <c r="N109" s="25"/>
-      <c r="AB109" s="25"/>
-      <c r="AC109" s="25"/>
-      <c r="AD109" s="25"/>
-      <c r="AE109" s="25"/>
-      <c r="BN109" s="28"/>
-    </row>
-    <row r="110" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="D110" s="27"/>
-      <c r="E110" s="25"/>
-      <c r="F110" s="25"/>
-      <c r="G110" s="25"/>
-      <c r="H110" s="25"/>
-      <c r="I110" s="25"/>
-      <c r="J110" s="25"/>
-      <c r="K110" s="25"/>
-      <c r="L110" s="25"/>
-      <c r="M110" s="25"/>
-      <c r="N110" s="25"/>
-      <c r="AB110" s="25"/>
-      <c r="AC110" s="25"/>
-      <c r="AD110" s="25"/>
-      <c r="AE110" s="25"/>
-      <c r="BN110" s="28"/>
-    </row>
-    <row r="111" spans="3:66" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D111" s="29"/>
-      <c r="E111" s="30"/>
-      <c r="F111" s="30"/>
-      <c r="G111" s="30"/>
-      <c r="H111" s="30"/>
-      <c r="I111" s="30"/>
-      <c r="J111" s="30"/>
-      <c r="K111" s="30"/>
-      <c r="L111" s="30"/>
-      <c r="M111" s="30"/>
-      <c r="N111" s="30"/>
-      <c r="O111" s="30"/>
-      <c r="P111" s="30"/>
-      <c r="Q111" s="30"/>
-      <c r="R111" s="30"/>
-      <c r="S111" s="30"/>
-      <c r="T111" s="30"/>
-      <c r="U111" s="30"/>
-      <c r="V111" s="30"/>
-      <c r="W111" s="30"/>
-      <c r="X111" s="30"/>
-      <c r="Y111" s="30"/>
-      <c r="Z111" s="30"/>
-      <c r="AA111" s="30"/>
-      <c r="AB111" s="30"/>
-      <c r="AC111" s="30"/>
-      <c r="AD111" s="30"/>
-      <c r="AE111" s="30"/>
-      <c r="AF111" s="30"/>
-      <c r="AG111" s="30"/>
-      <c r="AH111" s="30"/>
-      <c r="AI111" s="30"/>
-      <c r="AJ111" s="30"/>
-      <c r="AK111" s="30"/>
-      <c r="AL111" s="30"/>
-      <c r="AM111" s="30"/>
-      <c r="AN111" s="30"/>
-      <c r="AO111" s="30"/>
-      <c r="AP111" s="30"/>
-      <c r="AQ111" s="30"/>
-      <c r="AR111" s="30"/>
-      <c r="AS111" s="30"/>
-      <c r="AT111" s="30"/>
-      <c r="AU111" s="30"/>
-      <c r="AV111" s="30"/>
-      <c r="AW111" s="30"/>
-      <c r="AX111" s="30"/>
-      <c r="AY111" s="30"/>
-      <c r="AZ111" s="30"/>
-      <c r="BA111" s="30"/>
-      <c r="BB111" s="30"/>
-      <c r="BC111" s="30"/>
-      <c r="BD111" s="30"/>
-      <c r="BE111" s="30"/>
-      <c r="BF111" s="30"/>
-      <c r="BG111" s="30"/>
-      <c r="BH111" s="30"/>
-      <c r="BI111" s="30"/>
-      <c r="BJ111" s="30"/>
-      <c r="BK111" s="30"/>
-      <c r="BL111" s="30"/>
-      <c r="BM111" s="30"/>
-      <c r="BN111" s="31"/>
-    </row>
-    <row r="112" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C112" s="28"/>
-      <c r="D112" s="25"/>
-      <c r="E112" s="25"/>
-      <c r="F112" s="25"/>
-      <c r="G112" s="25"/>
-      <c r="H112" s="25"/>
-      <c r="I112" s="25"/>
-      <c r="J112" s="25"/>
-      <c r="K112" s="25"/>
-      <c r="L112" s="25"/>
-      <c r="M112" s="25"/>
-      <c r="N112" s="25"/>
-      <c r="AB112" s="25"/>
-      <c r="AC112" s="25"/>
-      <c r="AD112" s="25"/>
-      <c r="AE112" s="25"/>
-      <c r="BN112" s="28"/>
-    </row>
-    <row r="113" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C113" s="28"/>
-      <c r="E113" s="25"/>
-      <c r="F113" s="25"/>
-      <c r="G113" s="25"/>
-      <c r="H113" s="25"/>
-      <c r="I113" s="25"/>
-      <c r="J113" s="25"/>
-      <c r="K113" s="25"/>
-      <c r="L113" s="25"/>
-      <c r="M113" s="25"/>
-      <c r="N113" s="25"/>
-      <c r="AB113" s="25"/>
-      <c r="AC113" s="25"/>
-      <c r="AD113" s="25"/>
-      <c r="AE113" s="25"/>
-      <c r="BN113" s="28"/>
-    </row>
-    <row r="114" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C114" s="28"/>
-      <c r="E114" s="25"/>
-      <c r="F114" s="25"/>
-      <c r="G114" s="25"/>
-      <c r="H114" s="25"/>
-      <c r="I114" s="25"/>
-      <c r="J114" s="25"/>
-      <c r="K114" s="25"/>
-      <c r="L114" s="25"/>
-      <c r="M114" s="25"/>
-      <c r="N114" s="25"/>
-      <c r="AB114" s="25"/>
-      <c r="AC114" s="25"/>
-      <c r="AD114" s="25"/>
-      <c r="AE114" s="25"/>
-      <c r="BN114" s="28"/>
-    </row>
-    <row r="115" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C115" s="28"/>
-      <c r="E115" s="25"/>
-      <c r="F115" s="25"/>
-      <c r="G115" s="25"/>
-      <c r="H115" s="25"/>
-      <c r="I115" s="25"/>
-      <c r="J115" s="25"/>
-      <c r="K115" s="25"/>
-      <c r="L115" s="25"/>
-      <c r="M115" s="25"/>
-      <c r="N115" s="25"/>
-      <c r="AB115" s="25"/>
-      <c r="AC115" s="25"/>
-      <c r="AD115" s="25"/>
-      <c r="AE115" s="25"/>
-      <c r="BN115" s="28"/>
-    </row>
-    <row r="116" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C116" s="28"/>
-      <c r="D116" s="37" t="s">
-        <v>40</v>
-      </c>
-      <c r="E116" s="37"/>
-      <c r="F116" s="37"/>
-      <c r="G116" s="37"/>
-      <c r="AB116" s="25"/>
-      <c r="AC116" s="25"/>
-      <c r="AD116" s="25"/>
-      <c r="AE116" s="25"/>
-      <c r="BN116" s="28"/>
+      <c r="E116" s="39"/>
+      <c r="F116" s="39"/>
+      <c r="G116" s="39"/>
+      <c r="AB116" s="16"/>
+      <c r="AC116" s="16"/>
+      <c r="AD116" s="16"/>
+      <c r="AE116" s="16"/>
+      <c r="BN116" s="19"/>
     </row>
     <row r="117" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C117" s="28"/>
-      <c r="AB117" s="25"/>
-      <c r="AC117" s="25"/>
-      <c r="AD117" s="25"/>
-      <c r="AE117" s="25"/>
-      <c r="BN117" s="28"/>
+      <c r="C117" s="19"/>
+      <c r="AB117" s="16"/>
+      <c r="AC117" s="16"/>
+      <c r="AD117" s="16"/>
+      <c r="AE117" s="16"/>
+      <c r="BN117" s="19"/>
     </row>
     <row r="118" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C118" s="28"/>
-      <c r="AB118" s="25"/>
-      <c r="AC118" s="25"/>
-      <c r="AD118" s="25"/>
-      <c r="AE118" s="25"/>
-      <c r="BN118" s="28"/>
+      <c r="C118" s="19"/>
+      <c r="AB118" s="16"/>
+      <c r="AC118" s="16"/>
+      <c r="AD118" s="16"/>
+      <c r="AE118" s="16"/>
+      <c r="BN118" s="19"/>
     </row>
     <row r="119" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C119" s="28"/>
-      <c r="AB119" s="25"/>
-      <c r="AC119" s="25"/>
-      <c r="AD119" s="25"/>
-      <c r="AE119" s="25"/>
-      <c r="BN119" s="28"/>
+      <c r="C119" s="19"/>
+      <c r="AB119" s="16"/>
+      <c r="AC119" s="16"/>
+      <c r="AD119" s="16"/>
+      <c r="AE119" s="16"/>
+      <c r="BN119" s="19"/>
     </row>
     <row r="120" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C120" s="28"/>
-      <c r="AB120" s="25"/>
-      <c r="AC120" s="25"/>
-      <c r="AD120" s="25"/>
-      <c r="AE120" s="25"/>
-      <c r="BN120" s="28"/>
+      <c r="C120" s="19"/>
+      <c r="AB120" s="16"/>
+      <c r="AC120" s="16"/>
+      <c r="AD120" s="16"/>
+      <c r="AE120" s="16"/>
+      <c r="BN120" s="19"/>
     </row>
     <row r="121" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C121" s="28"/>
-      <c r="AB121" s="25"/>
-      <c r="AC121" s="25"/>
-      <c r="AD121" s="25"/>
-      <c r="AE121" s="25"/>
-      <c r="BN121" s="28"/>
+      <c r="C121" s="19"/>
+      <c r="AB121" s="16"/>
+      <c r="AC121" s="16"/>
+      <c r="AD121" s="16"/>
+      <c r="AE121" s="16"/>
+      <c r="BN121" s="19"/>
     </row>
     <row r="122" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C122" s="28"/>
-      <c r="AB122" s="25"/>
-      <c r="AC122" s="25"/>
-      <c r="AD122" s="25"/>
-      <c r="AE122" s="25"/>
-      <c r="BN122" s="28"/>
+      <c r="C122" s="19"/>
+      <c r="AB122" s="16"/>
+      <c r="AC122" s="16"/>
+      <c r="AD122" s="16"/>
+      <c r="AE122" s="16"/>
+      <c r="BN122" s="19"/>
     </row>
     <row r="123" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C123" s="28"/>
-      <c r="AB123" s="25"/>
-      <c r="AC123" s="25"/>
-      <c r="AD123" s="25"/>
-      <c r="AE123" s="25"/>
-      <c r="BN123" s="28"/>
+      <c r="C123" s="19"/>
+      <c r="AB123" s="16"/>
+      <c r="AC123" s="16"/>
+      <c r="AD123" s="16"/>
+      <c r="AE123" s="16"/>
+      <c r="BN123" s="19"/>
     </row>
     <row r="124" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C124" s="28"/>
-      <c r="AB124" s="25"/>
-      <c r="AC124" s="25"/>
-      <c r="AD124" s="25"/>
-      <c r="AE124" s="25"/>
-      <c r="BN124" s="28"/>
+      <c r="C124" s="19"/>
+      <c r="AB124" s="16"/>
+      <c r="AC124" s="16"/>
+      <c r="AD124" s="16"/>
+      <c r="AE124" s="16"/>
+      <c r="BN124" s="19"/>
     </row>
     <row r="125" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C125" s="28"/>
-      <c r="AB125" s="25"/>
-      <c r="AC125" s="25"/>
-      <c r="AD125" s="25"/>
-      <c r="AE125" s="25"/>
-      <c r="BN125" s="28"/>
+      <c r="C125" s="19"/>
+      <c r="AB125" s="16"/>
+      <c r="AC125" s="16"/>
+      <c r="AD125" s="16"/>
+      <c r="AE125" s="16"/>
+      <c r="BN125" s="19"/>
     </row>
     <row r="126" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C126" s="28"/>
-      <c r="AB126" s="25"/>
-      <c r="AC126" s="25"/>
-      <c r="AD126" s="25"/>
-      <c r="AE126" s="25"/>
-      <c r="BN126" s="28"/>
+      <c r="C126" s="19"/>
+      <c r="AB126" s="16"/>
+      <c r="AC126" s="16"/>
+      <c r="AD126" s="16"/>
+      <c r="AE126" s="16"/>
+      <c r="BN126" s="19"/>
     </row>
     <row r="127" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C127" s="28"/>
-      <c r="AB127" s="25"/>
-      <c r="AC127" s="25"/>
-      <c r="AD127" s="25"/>
-      <c r="AE127" s="25"/>
-      <c r="BN127" s="28"/>
+      <c r="C127" s="19"/>
+      <c r="AB127" s="16"/>
+      <c r="AC127" s="16"/>
+      <c r="AD127" s="16"/>
+      <c r="AE127" s="16"/>
+      <c r="BN127" s="19"/>
     </row>
     <row r="128" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C128" s="28"/>
-      <c r="AB128" s="25"/>
-      <c r="AC128" s="25"/>
-      <c r="AD128" s="25"/>
-      <c r="AE128" s="25"/>
-      <c r="BN128" s="28"/>
+      <c r="C128" s="19"/>
+      <c r="AB128" s="16"/>
+      <c r="AC128" s="16"/>
+      <c r="AD128" s="16"/>
+      <c r="AE128" s="16"/>
+      <c r="BN128" s="19"/>
     </row>
     <row r="129" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C129" s="28"/>
-      <c r="AB129" s="25"/>
-      <c r="AC129" s="25"/>
-      <c r="AD129" s="25"/>
-      <c r="AE129" s="25"/>
-      <c r="BN129" s="28"/>
+      <c r="C129" s="19"/>
+      <c r="AB129" s="16"/>
+      <c r="AC129" s="16"/>
+      <c r="AD129" s="16"/>
+      <c r="AE129" s="16"/>
+      <c r="BN129" s="19"/>
     </row>
     <row r="130" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C130" s="28"/>
-      <c r="AB130" s="25"/>
-      <c r="AC130" s="25"/>
-      <c r="AD130" s="25"/>
-      <c r="AE130" s="25"/>
-      <c r="BN130" s="28"/>
+      <c r="C130" s="19"/>
+      <c r="AB130" s="16"/>
+      <c r="AC130" s="16"/>
+      <c r="AD130" s="16"/>
+      <c r="AE130" s="16"/>
+      <c r="BN130" s="19"/>
     </row>
     <row r="131" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C131" s="28"/>
-      <c r="AB131" s="25"/>
-      <c r="AC131" s="25"/>
-      <c r="AD131" s="25"/>
-      <c r="AE131" s="25"/>
-      <c r="BN131" s="28"/>
+      <c r="C131" s="19"/>
+      <c r="AB131" s="16"/>
+      <c r="AC131" s="16"/>
+      <c r="AD131" s="16"/>
+      <c r="AE131" s="16"/>
+      <c r="BN131" s="19"/>
     </row>
     <row r="132" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C132" s="28"/>
-      <c r="W132" s="25"/>
-      <c r="X132" s="25"/>
-      <c r="Y132" s="25"/>
-      <c r="Z132" s="25"/>
-      <c r="AA132" s="25"/>
-      <c r="AB132" s="25"/>
-      <c r="AC132" s="25"/>
-      <c r="AD132" s="25"/>
-      <c r="AE132" s="25"/>
-      <c r="BN132" s="28"/>
+      <c r="C132" s="19"/>
+      <c r="W132" s="16"/>
+      <c r="X132" s="16"/>
+      <c r="Y132" s="16"/>
+      <c r="Z132" s="16"/>
+      <c r="AA132" s="16"/>
+      <c r="AB132" s="16"/>
+      <c r="AC132" s="16"/>
+      <c r="AD132" s="16"/>
+      <c r="AE132" s="16"/>
+      <c r="BN132" s="19"/>
     </row>
     <row r="133" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C133" s="28"/>
-      <c r="W133" s="25"/>
-      <c r="X133" s="25"/>
-      <c r="Y133" s="25"/>
-      <c r="Z133" s="25"/>
-      <c r="AA133" s="25"/>
-      <c r="AB133" s="25"/>
-      <c r="AC133" s="25"/>
-      <c r="AD133" s="25"/>
-      <c r="AE133" s="25"/>
-      <c r="BN133" s="28"/>
+      <c r="C133" s="19"/>
+      <c r="W133" s="16"/>
+      <c r="X133" s="16"/>
+      <c r="Y133" s="16"/>
+      <c r="Z133" s="16"/>
+      <c r="AA133" s="16"/>
+      <c r="AB133" s="16"/>
+      <c r="AC133" s="16"/>
+      <c r="AD133" s="16"/>
+      <c r="AE133" s="16"/>
+      <c r="BN133" s="19"/>
     </row>
     <row r="134" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C134" s="28"/>
-      <c r="W134" s="25"/>
-      <c r="X134" s="25"/>
-      <c r="Y134" s="25"/>
-      <c r="Z134" s="25"/>
-      <c r="AA134" s="25"/>
-      <c r="AB134" s="25"/>
-      <c r="AC134" s="25"/>
-      <c r="AD134" s="25"/>
-      <c r="AE134" s="25"/>
-      <c r="BN134" s="28"/>
+      <c r="C134" s="19"/>
+      <c r="W134" s="16"/>
+      <c r="X134" s="16"/>
+      <c r="Y134" s="16"/>
+      <c r="Z134" s="16"/>
+      <c r="AA134" s="16"/>
+      <c r="AB134" s="16"/>
+      <c r="AC134" s="16"/>
+      <c r="AD134" s="16"/>
+      <c r="AE134" s="16"/>
+      <c r="BN134" s="19"/>
     </row>
     <row r="135" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C135" s="28"/>
-      <c r="W135" s="25"/>
-      <c r="X135" s="25"/>
-      <c r="Y135" s="25"/>
-      <c r="Z135" s="25"/>
-      <c r="AA135" s="25"/>
-      <c r="AB135" s="25"/>
-      <c r="AC135" s="25"/>
-      <c r="AD135" s="25"/>
-      <c r="AE135" s="25"/>
-      <c r="BN135" s="28"/>
+      <c r="C135" s="19"/>
+      <c r="W135" s="16"/>
+      <c r="X135" s="16"/>
+      <c r="Y135" s="16"/>
+      <c r="Z135" s="16"/>
+      <c r="AA135" s="16"/>
+      <c r="AB135" s="16"/>
+      <c r="AC135" s="16"/>
+      <c r="AD135" s="16"/>
+      <c r="AE135" s="16"/>
+      <c r="BN135" s="19"/>
     </row>
     <row r="136" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C136" s="28"/>
-      <c r="W136" s="25"/>
-      <c r="X136" s="25"/>
-      <c r="Y136" s="25"/>
-      <c r="Z136" s="25"/>
-      <c r="AA136" s="25"/>
-      <c r="AB136" s="25"/>
-      <c r="AC136" s="25"/>
-      <c r="AD136" s="25"/>
-      <c r="AE136" s="25"/>
-      <c r="BN136" s="28"/>
+      <c r="C136" s="19"/>
+      <c r="W136" s="16"/>
+      <c r="X136" s="16"/>
+      <c r="Y136" s="16"/>
+      <c r="Z136" s="16"/>
+      <c r="AA136" s="16"/>
+      <c r="AB136" s="16"/>
+      <c r="AC136" s="16"/>
+      <c r="AD136" s="16"/>
+      <c r="AE136" s="16"/>
+      <c r="BN136" s="19"/>
     </row>
     <row r="137" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C137" s="28"/>
-      <c r="W137" s="25"/>
-      <c r="X137" s="25"/>
-      <c r="Y137" s="25"/>
-      <c r="Z137" s="25"/>
-      <c r="AA137" s="25"/>
-      <c r="AB137" s="25"/>
-      <c r="AC137" s="25"/>
-      <c r="AD137" s="25"/>
-      <c r="AE137" s="25"/>
-      <c r="BN137" s="28"/>
+      <c r="C137" s="19"/>
+      <c r="W137" s="16"/>
+      <c r="X137" s="16"/>
+      <c r="Y137" s="16"/>
+      <c r="Z137" s="16"/>
+      <c r="AA137" s="16"/>
+      <c r="AB137" s="16"/>
+      <c r="AC137" s="16"/>
+      <c r="AD137" s="16"/>
+      <c r="AE137" s="16"/>
+      <c r="BN137" s="19"/>
     </row>
     <row r="138" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C138" s="28"/>
-      <c r="W138" s="25"/>
-      <c r="X138" s="25"/>
-      <c r="Y138" s="25"/>
-      <c r="Z138" s="25"/>
-      <c r="AA138" s="25"/>
-      <c r="AB138" s="25"/>
-      <c r="AC138" s="25"/>
-      <c r="AD138" s="25"/>
-      <c r="AE138" s="25"/>
-      <c r="BN138" s="28"/>
+      <c r="C138" s="19"/>
+      <c r="W138" s="16"/>
+      <c r="X138" s="16"/>
+      <c r="Y138" s="16"/>
+      <c r="Z138" s="16"/>
+      <c r="AA138" s="16"/>
+      <c r="AB138" s="16"/>
+      <c r="AC138" s="16"/>
+      <c r="AD138" s="16"/>
+      <c r="AE138" s="16"/>
+      <c r="BN138" s="19"/>
     </row>
     <row r="139" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C139" s="28"/>
-      <c r="W139" s="25"/>
-      <c r="X139" s="25"/>
-      <c r="Y139" s="25"/>
-      <c r="Z139" s="25"/>
-      <c r="AA139" s="25"/>
-      <c r="AB139" s="25"/>
-      <c r="AC139" s="25"/>
-      <c r="AD139" s="25"/>
-      <c r="AE139" s="25"/>
-      <c r="BN139" s="28"/>
+      <c r="C139" s="19"/>
+      <c r="W139" s="16"/>
+      <c r="X139" s="16"/>
+      <c r="Y139" s="16"/>
+      <c r="Z139" s="16"/>
+      <c r="AA139" s="16"/>
+      <c r="AB139" s="16"/>
+      <c r="AC139" s="16"/>
+      <c r="AD139" s="16"/>
+      <c r="AE139" s="16"/>
+      <c r="BN139" s="19"/>
     </row>
     <row r="140" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C140" s="28"/>
-      <c r="W140" s="25"/>
-      <c r="X140" s="25"/>
-      <c r="Y140" s="25"/>
-      <c r="Z140" s="25"/>
-      <c r="AA140" s="25"/>
-      <c r="AB140" s="25"/>
-      <c r="AC140" s="25"/>
-      <c r="AD140" s="25"/>
-      <c r="AE140" s="25"/>
-      <c r="BN140" s="28"/>
+      <c r="C140" s="19"/>
+      <c r="W140" s="16"/>
+      <c r="X140" s="16"/>
+      <c r="Y140" s="16"/>
+      <c r="Z140" s="16"/>
+      <c r="AA140" s="16"/>
+      <c r="AB140" s="16"/>
+      <c r="AC140" s="16"/>
+      <c r="AD140" s="16"/>
+      <c r="AE140" s="16"/>
+      <c r="BN140" s="19"/>
     </row>
     <row r="141" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C141" s="28"/>
-      <c r="W141" s="25"/>
-      <c r="X141" s="25"/>
-      <c r="Y141" s="25"/>
-      <c r="Z141" s="25"/>
-      <c r="AA141" s="25"/>
-      <c r="AB141" s="25"/>
-      <c r="AC141" s="25"/>
-      <c r="AD141" s="25"/>
-      <c r="AE141" s="25"/>
-      <c r="BN141" s="28"/>
+      <c r="C141" s="19"/>
+      <c r="W141" s="16"/>
+      <c r="X141" s="16"/>
+      <c r="Y141" s="16"/>
+      <c r="Z141" s="16"/>
+      <c r="AA141" s="16"/>
+      <c r="AB141" s="16"/>
+      <c r="AC141" s="16"/>
+      <c r="AD141" s="16"/>
+      <c r="AE141" s="16"/>
+      <c r="BN141" s="19"/>
     </row>
     <row r="142" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C142" s="28"/>
-      <c r="W142" s="25"/>
-      <c r="X142" s="25"/>
-      <c r="Y142" s="25"/>
-      <c r="Z142" s="25"/>
-      <c r="AA142" s="25"/>
-      <c r="AB142" s="25"/>
-      <c r="AC142" s="25"/>
-      <c r="AD142" s="25"/>
-      <c r="AE142" s="25"/>
-      <c r="BN142" s="28"/>
+      <c r="C142" s="19"/>
+      <c r="W142" s="16"/>
+      <c r="X142" s="16"/>
+      <c r="Y142" s="16"/>
+      <c r="Z142" s="16"/>
+      <c r="AA142" s="16"/>
+      <c r="AB142" s="16"/>
+      <c r="AC142" s="16"/>
+      <c r="AD142" s="16"/>
+      <c r="AE142" s="16"/>
+      <c r="BN142" s="19"/>
     </row>
     <row r="143" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C143" s="28"/>
-      <c r="W143" s="25"/>
-      <c r="X143" s="25"/>
-      <c r="Y143" s="25"/>
-      <c r="Z143" s="25"/>
-      <c r="AA143" s="25"/>
-      <c r="AB143" s="25"/>
-      <c r="AC143" s="25"/>
-      <c r="AD143" s="25"/>
-      <c r="AE143" s="25"/>
-      <c r="BN143" s="28"/>
+      <c r="C143" s="19"/>
+      <c r="W143" s="16"/>
+      <c r="X143" s="16"/>
+      <c r="Y143" s="16"/>
+      <c r="Z143" s="16"/>
+      <c r="AA143" s="16"/>
+      <c r="AB143" s="16"/>
+      <c r="AC143" s="16"/>
+      <c r="AD143" s="16"/>
+      <c r="AE143" s="16"/>
+      <c r="BN143" s="19"/>
     </row>
     <row r="144" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C144" s="28"/>
-      <c r="W144" s="25"/>
-      <c r="X144" s="25"/>
-      <c r="Y144" s="25"/>
-      <c r="Z144" s="25"/>
-      <c r="AA144" s="25"/>
-      <c r="AB144" s="25"/>
-      <c r="AC144" s="25"/>
-      <c r="AD144" s="25"/>
-      <c r="AE144" s="25"/>
-      <c r="BN144" s="28"/>
+      <c r="C144" s="19"/>
+      <c r="W144" s="16"/>
+      <c r="X144" s="16"/>
+      <c r="Y144" s="16"/>
+      <c r="Z144" s="16"/>
+      <c r="AA144" s="16"/>
+      <c r="AB144" s="16"/>
+      <c r="AC144" s="16"/>
+      <c r="AD144" s="16"/>
+      <c r="AE144" s="16"/>
+      <c r="BN144" s="19"/>
     </row>
     <row r="145" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C145" s="28"/>
-      <c r="W145" s="25"/>
-      <c r="X145" s="25"/>
-      <c r="Y145" s="25"/>
-      <c r="Z145" s="25"/>
-      <c r="AA145" s="25"/>
-      <c r="AB145" s="25"/>
-      <c r="AC145" s="25"/>
-      <c r="AD145" s="25"/>
-      <c r="AE145" s="25"/>
-      <c r="BN145" s="28"/>
+      <c r="C145" s="19"/>
+      <c r="W145" s="16"/>
+      <c r="X145" s="16"/>
+      <c r="Y145" s="16"/>
+      <c r="Z145" s="16"/>
+      <c r="AA145" s="16"/>
+      <c r="AB145" s="16"/>
+      <c r="AC145" s="16"/>
+      <c r="AD145" s="16"/>
+      <c r="AE145" s="16"/>
+      <c r="BN145" s="19"/>
     </row>
     <row r="146" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C146" s="28"/>
-      <c r="W146" s="25"/>
-      <c r="X146" s="25"/>
-      <c r="Y146" s="25"/>
-      <c r="Z146" s="25"/>
-      <c r="AA146" s="25"/>
-      <c r="AB146" s="25"/>
-      <c r="AC146" s="25"/>
-      <c r="AD146" s="25"/>
-      <c r="AE146" s="25"/>
-      <c r="BN146" s="28"/>
+      <c r="C146" s="19"/>
+      <c r="W146" s="16"/>
+      <c r="X146" s="16"/>
+      <c r="Y146" s="16"/>
+      <c r="Z146" s="16"/>
+      <c r="AA146" s="16"/>
+      <c r="AB146" s="16"/>
+      <c r="AC146" s="16"/>
+      <c r="AD146" s="16"/>
+      <c r="AE146" s="16"/>
+      <c r="BN146" s="19"/>
     </row>
     <row r="147" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C147" s="28"/>
-      <c r="W147" s="25"/>
-      <c r="X147" s="25"/>
-      <c r="Y147" s="25"/>
-      <c r="Z147" s="25"/>
-      <c r="AA147" s="25"/>
-      <c r="AB147" s="25"/>
-      <c r="AC147" s="25"/>
-      <c r="AD147" s="25"/>
-      <c r="AE147" s="25"/>
-      <c r="BN147" s="28"/>
+      <c r="C147" s="19"/>
+      <c r="W147" s="16"/>
+      <c r="X147" s="16"/>
+      <c r="Y147" s="16"/>
+      <c r="Z147" s="16"/>
+      <c r="AA147" s="16"/>
+      <c r="AB147" s="16"/>
+      <c r="AC147" s="16"/>
+      <c r="AD147" s="16"/>
+      <c r="AE147" s="16"/>
+      <c r="BN147" s="19"/>
     </row>
     <row r="148" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C148" s="28"/>
-      <c r="W148" s="25"/>
-      <c r="X148" s="25"/>
-      <c r="Y148" s="25"/>
-      <c r="Z148" s="25"/>
-      <c r="AA148" s="25"/>
-      <c r="AB148" s="25"/>
-      <c r="AC148" s="25"/>
-      <c r="AD148" s="25"/>
-      <c r="AE148" s="25"/>
-      <c r="BN148" s="28"/>
+      <c r="C148" s="19"/>
+      <c r="W148" s="16"/>
+      <c r="X148" s="16"/>
+      <c r="Y148" s="16"/>
+      <c r="Z148" s="16"/>
+      <c r="AA148" s="16"/>
+      <c r="AB148" s="16"/>
+      <c r="AC148" s="16"/>
+      <c r="AD148" s="16"/>
+      <c r="AE148" s="16"/>
+      <c r="BN148" s="19"/>
     </row>
     <row r="149" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C149" s="28"/>
-      <c r="W149" s="25"/>
-      <c r="X149" s="25"/>
-      <c r="Y149" s="25"/>
-      <c r="Z149" s="25"/>
-      <c r="AA149" s="25"/>
-      <c r="AB149" s="25"/>
-      <c r="AC149" s="25"/>
-      <c r="AD149" s="25"/>
-      <c r="AE149" s="25"/>
-      <c r="BN149" s="28"/>
+      <c r="C149" s="19"/>
+      <c r="W149" s="16"/>
+      <c r="X149" s="16"/>
+      <c r="Y149" s="16"/>
+      <c r="Z149" s="16"/>
+      <c r="AA149" s="16"/>
+      <c r="AB149" s="16"/>
+      <c r="AC149" s="16"/>
+      <c r="AD149" s="16"/>
+      <c r="AE149" s="16"/>
+      <c r="BN149" s="19"/>
     </row>
     <row r="150" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C150" s="28"/>
-      <c r="W150" s="25"/>
-      <c r="X150" s="25"/>
-      <c r="Y150" s="25"/>
-      <c r="Z150" s="25"/>
-      <c r="AA150" s="25"/>
-      <c r="AB150" s="25"/>
-      <c r="AC150" s="25"/>
-      <c r="AD150" s="25"/>
-      <c r="AE150" s="25"/>
-      <c r="BN150" s="28"/>
+      <c r="C150" s="19"/>
+      <c r="W150" s="16"/>
+      <c r="X150" s="16"/>
+      <c r="Y150" s="16"/>
+      <c r="Z150" s="16"/>
+      <c r="AA150" s="16"/>
+      <c r="AB150" s="16"/>
+      <c r="AC150" s="16"/>
+      <c r="AD150" s="16"/>
+      <c r="AE150" s="16"/>
+      <c r="BN150" s="19"/>
     </row>
     <row r="151" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C151" s="28"/>
-      <c r="W151" s="25"/>
-      <c r="X151" s="25"/>
-      <c r="Y151" s="25"/>
-      <c r="Z151" s="25"/>
-      <c r="AA151" s="25"/>
-      <c r="AB151" s="25"/>
-      <c r="AC151" s="25"/>
-      <c r="AD151" s="25"/>
-      <c r="AE151" s="25"/>
-      <c r="BN151" s="28"/>
+      <c r="C151" s="19"/>
+      <c r="W151" s="16"/>
+      <c r="X151" s="16"/>
+      <c r="Y151" s="16"/>
+      <c r="Z151" s="16"/>
+      <c r="AA151" s="16"/>
+      <c r="AB151" s="16"/>
+      <c r="AC151" s="16"/>
+      <c r="AD151" s="16"/>
+      <c r="AE151" s="16"/>
+      <c r="BN151" s="19"/>
     </row>
     <row r="152" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C152" s="28"/>
-      <c r="W152" s="25"/>
-      <c r="X152" s="25"/>
-      <c r="Y152" s="25"/>
-      <c r="Z152" s="25"/>
-      <c r="AA152" s="25"/>
-      <c r="AB152" s="25"/>
-      <c r="AC152" s="25"/>
-      <c r="AD152" s="25"/>
-      <c r="AE152" s="25"/>
-      <c r="BN152" s="28"/>
+      <c r="C152" s="19"/>
+      <c r="W152" s="16"/>
+      <c r="X152" s="16"/>
+      <c r="Y152" s="16"/>
+      <c r="Z152" s="16"/>
+      <c r="AA152" s="16"/>
+      <c r="AB152" s="16"/>
+      <c r="AC152" s="16"/>
+      <c r="AD152" s="16"/>
+      <c r="AE152" s="16"/>
+      <c r="BN152" s="19"/>
     </row>
     <row r="153" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C153" s="28"/>
-      <c r="W153" s="25"/>
-      <c r="X153" s="25"/>
-      <c r="Y153" s="25"/>
-      <c r="Z153" s="25"/>
-      <c r="AA153" s="25"/>
-      <c r="AB153" s="25"/>
-      <c r="AC153" s="25"/>
-      <c r="AD153" s="25"/>
-      <c r="AE153" s="25"/>
-      <c r="BN153" s="28"/>
+      <c r="C153" s="19"/>
+      <c r="W153" s="16"/>
+      <c r="X153" s="16"/>
+      <c r="Y153" s="16"/>
+      <c r="Z153" s="16"/>
+      <c r="AA153" s="16"/>
+      <c r="AB153" s="16"/>
+      <c r="AC153" s="16"/>
+      <c r="AD153" s="16"/>
+      <c r="AE153" s="16"/>
+      <c r="BN153" s="19"/>
     </row>
     <row r="154" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C154" s="28"/>
-      <c r="W154" s="25"/>
-      <c r="X154" s="25"/>
-      <c r="Y154" s="25"/>
-      <c r="Z154" s="25"/>
-      <c r="AA154" s="25"/>
-      <c r="AB154" s="25"/>
-      <c r="AC154" s="25"/>
-      <c r="AD154" s="25"/>
-      <c r="AE154" s="25"/>
-      <c r="BN154" s="28"/>
+      <c r="C154" s="19"/>
+      <c r="W154" s="16"/>
+      <c r="X154" s="16"/>
+      <c r="Y154" s="16"/>
+      <c r="Z154" s="16"/>
+      <c r="AA154" s="16"/>
+      <c r="AB154" s="16"/>
+      <c r="AC154" s="16"/>
+      <c r="AD154" s="16"/>
+      <c r="AE154" s="16"/>
+      <c r="BN154" s="19"/>
     </row>
     <row r="155" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C155" s="28"/>
-      <c r="W155" s="25"/>
-      <c r="X155" s="25"/>
-      <c r="Y155" s="25"/>
-      <c r="Z155" s="25"/>
-      <c r="AA155" s="25"/>
-      <c r="AB155" s="25"/>
-      <c r="AC155" s="25"/>
-      <c r="AD155" s="25"/>
-      <c r="AE155" s="25"/>
-      <c r="BN155" s="28"/>
+      <c r="C155" s="19"/>
+      <c r="W155" s="16"/>
+      <c r="X155" s="16"/>
+      <c r="Y155" s="16"/>
+      <c r="Z155" s="16"/>
+      <c r="AA155" s="16"/>
+      <c r="AB155" s="16"/>
+      <c r="AC155" s="16"/>
+      <c r="AD155" s="16"/>
+      <c r="AE155" s="16"/>
+      <c r="BN155" s="19"/>
     </row>
     <row r="156" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C156" s="28"/>
-      <c r="W156" s="25"/>
-      <c r="X156" s="25"/>
-      <c r="Y156" s="25"/>
-      <c r="Z156" s="25"/>
-      <c r="AA156" s="25"/>
-      <c r="AB156" s="25"/>
-      <c r="AC156" s="25"/>
-      <c r="AD156" s="25"/>
-      <c r="AE156" s="25"/>
-      <c r="BN156" s="28"/>
+      <c r="C156" s="19"/>
+      <c r="W156" s="16"/>
+      <c r="X156" s="16"/>
+      <c r="Y156" s="16"/>
+      <c r="Z156" s="16"/>
+      <c r="AA156" s="16"/>
+      <c r="AB156" s="16"/>
+      <c r="AC156" s="16"/>
+      <c r="AD156" s="16"/>
+      <c r="AE156" s="16"/>
+      <c r="BN156" s="19"/>
     </row>
     <row r="157" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C157" s="28"/>
-      <c r="W157" s="25"/>
-      <c r="X157" s="25"/>
-      <c r="Y157" s="25"/>
-      <c r="Z157" s="25"/>
-      <c r="AA157" s="25"/>
-      <c r="AB157" s="25"/>
-      <c r="AC157" s="25"/>
-      <c r="AD157" s="25"/>
-      <c r="AE157" s="25"/>
-      <c r="BN157" s="28"/>
+      <c r="C157" s="19"/>
+      <c r="W157" s="16"/>
+      <c r="X157" s="16"/>
+      <c r="Y157" s="16"/>
+      <c r="Z157" s="16"/>
+      <c r="AA157" s="16"/>
+      <c r="AB157" s="16"/>
+      <c r="AC157" s="16"/>
+      <c r="AD157" s="16"/>
+      <c r="AE157" s="16"/>
+      <c r="BN157" s="19"/>
     </row>
     <row r="158" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C158" s="28"/>
-      <c r="W158" s="25"/>
-      <c r="X158" s="25"/>
-      <c r="Y158" s="25"/>
-      <c r="Z158" s="25"/>
-      <c r="AA158" s="25"/>
-      <c r="AB158" s="25"/>
-      <c r="AC158" s="25"/>
-      <c r="AD158" s="25"/>
-      <c r="AE158" s="25"/>
-      <c r="BN158" s="28"/>
+      <c r="C158" s="19"/>
+      <c r="W158" s="16"/>
+      <c r="X158" s="16"/>
+      <c r="Y158" s="16"/>
+      <c r="Z158" s="16"/>
+      <c r="AA158" s="16"/>
+      <c r="AB158" s="16"/>
+      <c r="AC158" s="16"/>
+      <c r="AD158" s="16"/>
+      <c r="AE158" s="16"/>
+      <c r="BN158" s="19"/>
     </row>
     <row r="159" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C159" s="28"/>
-      <c r="W159" s="25"/>
-      <c r="X159" s="25"/>
-      <c r="Y159" s="25"/>
-      <c r="Z159" s="25"/>
-      <c r="AA159" s="25"/>
-      <c r="AB159" s="25"/>
-      <c r="AC159" s="25"/>
-      <c r="AD159" s="25"/>
-      <c r="AE159" s="25"/>
-      <c r="BN159" s="28"/>
+      <c r="C159" s="19"/>
+      <c r="W159" s="16"/>
+      <c r="X159" s="16"/>
+      <c r="Y159" s="16"/>
+      <c r="Z159" s="16"/>
+      <c r="AA159" s="16"/>
+      <c r="AB159" s="16"/>
+      <c r="AC159" s="16"/>
+      <c r="AD159" s="16"/>
+      <c r="AE159" s="16"/>
+      <c r="BN159" s="19"/>
     </row>
     <row r="160" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C160" s="28"/>
-      <c r="W160" s="25"/>
-      <c r="X160" s="25"/>
-      <c r="Y160" s="25"/>
-      <c r="Z160" s="25"/>
-      <c r="AA160" s="25"/>
-      <c r="AB160" s="25"/>
-      <c r="AC160" s="25"/>
-      <c r="AD160" s="25"/>
-      <c r="AE160" s="25"/>
-      <c r="BN160" s="28"/>
+      <c r="C160" s="19"/>
+      <c r="W160" s="16"/>
+      <c r="X160" s="16"/>
+      <c r="Y160" s="16"/>
+      <c r="Z160" s="16"/>
+      <c r="AA160" s="16"/>
+      <c r="AB160" s="16"/>
+      <c r="AC160" s="16"/>
+      <c r="AD160" s="16"/>
+      <c r="AE160" s="16"/>
+      <c r="BN160" s="19"/>
     </row>
     <row r="161" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C161" s="28"/>
-      <c r="W161" s="25"/>
-      <c r="X161" s="25"/>
-      <c r="Y161" s="25"/>
-      <c r="Z161" s="25"/>
-      <c r="AA161" s="25"/>
-      <c r="AB161" s="25"/>
-      <c r="AC161" s="25"/>
-      <c r="AD161" s="25"/>
-      <c r="AE161" s="25"/>
-      <c r="BN161" s="28"/>
+      <c r="C161" s="19"/>
+      <c r="W161" s="16"/>
+      <c r="X161" s="16"/>
+      <c r="Y161" s="16"/>
+      <c r="Z161" s="16"/>
+      <c r="AA161" s="16"/>
+      <c r="AB161" s="16"/>
+      <c r="AC161" s="16"/>
+      <c r="AD161" s="16"/>
+      <c r="AE161" s="16"/>
+      <c r="BN161" s="19"/>
     </row>
     <row r="162" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C162" s="28"/>
-      <c r="W162" s="25"/>
-      <c r="X162" s="25"/>
-      <c r="Y162" s="25"/>
-      <c r="Z162" s="25"/>
-      <c r="AA162" s="25"/>
-      <c r="AB162" s="25"/>
-      <c r="AC162" s="25"/>
-      <c r="AD162" s="25"/>
-      <c r="AE162" s="25"/>
-      <c r="BN162" s="28"/>
+      <c r="C162" s="19"/>
+      <c r="W162" s="16"/>
+      <c r="X162" s="16"/>
+      <c r="Y162" s="16"/>
+      <c r="Z162" s="16"/>
+      <c r="AA162" s="16"/>
+      <c r="AB162" s="16"/>
+      <c r="AC162" s="16"/>
+      <c r="AD162" s="16"/>
+      <c r="AE162" s="16"/>
+      <c r="BN162" s="19"/>
     </row>
     <row r="163" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C163" s="28"/>
-      <c r="W163" s="25"/>
-      <c r="X163" s="25"/>
-      <c r="Y163" s="25"/>
-      <c r="Z163" s="25"/>
-      <c r="AA163" s="25"/>
-      <c r="AB163" s="25"/>
-      <c r="AC163" s="25"/>
-      <c r="AD163" s="25"/>
-      <c r="AE163" s="25"/>
-      <c r="BN163" s="28"/>
+      <c r="C163" s="19"/>
+      <c r="W163" s="16"/>
+      <c r="X163" s="16"/>
+      <c r="Y163" s="16"/>
+      <c r="Z163" s="16"/>
+      <c r="AA163" s="16"/>
+      <c r="AB163" s="16"/>
+      <c r="AC163" s="16"/>
+      <c r="AD163" s="16"/>
+      <c r="AE163" s="16"/>
+      <c r="BN163" s="19"/>
     </row>
     <row r="164" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C164" s="28"/>
-      <c r="W164" s="25"/>
-      <c r="X164" s="25"/>
-      <c r="Y164" s="25"/>
-      <c r="Z164" s="25"/>
-      <c r="AA164" s="25"/>
-      <c r="AB164" s="25"/>
-      <c r="AC164" s="25"/>
-      <c r="AD164" s="25"/>
-      <c r="AE164" s="25"/>
-      <c r="BN164" s="28"/>
+      <c r="C164" s="19"/>
+      <c r="W164" s="16"/>
+      <c r="X164" s="16"/>
+      <c r="Y164" s="16"/>
+      <c r="Z164" s="16"/>
+      <c r="AA164" s="16"/>
+      <c r="AB164" s="16"/>
+      <c r="AC164" s="16"/>
+      <c r="AD164" s="16"/>
+      <c r="AE164" s="16"/>
+      <c r="BN164" s="19"/>
     </row>
     <row r="165" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C165" s="28"/>
-      <c r="W165" s="25"/>
-      <c r="X165" s="25"/>
-      <c r="Y165" s="25"/>
-      <c r="Z165" s="25"/>
-      <c r="AA165" s="25"/>
-      <c r="AB165" s="25"/>
-      <c r="AC165" s="25"/>
-      <c r="AD165" s="25"/>
-      <c r="AE165" s="25"/>
-      <c r="BN165" s="28"/>
+      <c r="C165" s="19"/>
+      <c r="W165" s="16"/>
+      <c r="X165" s="16"/>
+      <c r="Y165" s="16"/>
+      <c r="Z165" s="16"/>
+      <c r="AA165" s="16"/>
+      <c r="AB165" s="16"/>
+      <c r="AC165" s="16"/>
+      <c r="AD165" s="16"/>
+      <c r="AE165" s="16"/>
+      <c r="BN165" s="19"/>
     </row>
     <row r="166" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C166" s="28"/>
-      <c r="W166" s="25"/>
-      <c r="X166" s="25"/>
-      <c r="Y166" s="25"/>
-      <c r="Z166" s="25"/>
-      <c r="AA166" s="25"/>
-      <c r="AB166" s="25"/>
-      <c r="AC166" s="25"/>
-      <c r="AD166" s="25"/>
-      <c r="AE166" s="25"/>
-      <c r="BN166" s="28"/>
+      <c r="C166" s="19"/>
+      <c r="W166" s="16"/>
+      <c r="X166" s="16"/>
+      <c r="Y166" s="16"/>
+      <c r="Z166" s="16"/>
+      <c r="AA166" s="16"/>
+      <c r="AB166" s="16"/>
+      <c r="AC166" s="16"/>
+      <c r="AD166" s="16"/>
+      <c r="AE166" s="16"/>
+      <c r="BN166" s="19"/>
     </row>
     <row r="167" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C167" s="28"/>
-      <c r="W167" s="25"/>
-      <c r="X167" s="25"/>
-      <c r="Y167" s="25"/>
-      <c r="Z167" s="25"/>
-      <c r="AA167" s="25"/>
-      <c r="AB167" s="25"/>
-      <c r="AC167" s="25"/>
-      <c r="AD167" s="25"/>
-      <c r="AE167" s="25"/>
-      <c r="BN167" s="28"/>
+      <c r="C167" s="19"/>
+      <c r="W167" s="16"/>
+      <c r="X167" s="16"/>
+      <c r="Y167" s="16"/>
+      <c r="Z167" s="16"/>
+      <c r="AA167" s="16"/>
+      <c r="AB167" s="16"/>
+      <c r="AC167" s="16"/>
+      <c r="AD167" s="16"/>
+      <c r="AE167" s="16"/>
+      <c r="BN167" s="19"/>
     </row>
     <row r="168" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C168" s="28"/>
-      <c r="W168" s="25"/>
-      <c r="X168" s="25"/>
-      <c r="Y168" s="25"/>
-      <c r="Z168" s="25"/>
-      <c r="AA168" s="25"/>
-      <c r="AB168" s="25"/>
-      <c r="AC168" s="25"/>
-      <c r="AD168" s="25"/>
-      <c r="AE168" s="25"/>
-      <c r="BN168" s="28"/>
+      <c r="C168" s="19"/>
+      <c r="W168" s="16"/>
+      <c r="X168" s="16"/>
+      <c r="Y168" s="16"/>
+      <c r="Z168" s="16"/>
+      <c r="AA168" s="16"/>
+      <c r="AB168" s="16"/>
+      <c r="AC168" s="16"/>
+      <c r="AD168" s="16"/>
+      <c r="AE168" s="16"/>
+      <c r="BN168" s="19"/>
     </row>
     <row r="169" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C169" s="28"/>
-      <c r="W169" s="25"/>
-      <c r="X169" s="25"/>
-      <c r="Y169" s="25"/>
-      <c r="Z169" s="25"/>
-      <c r="AA169" s="25"/>
-      <c r="AB169" s="25"/>
-      <c r="AC169" s="25"/>
-      <c r="AD169" s="25"/>
-      <c r="AE169" s="25"/>
-      <c r="BN169" s="28"/>
+      <c r="C169" s="19"/>
+      <c r="W169" s="16"/>
+      <c r="X169" s="16"/>
+      <c r="Y169" s="16"/>
+      <c r="Z169" s="16"/>
+      <c r="AA169" s="16"/>
+      <c r="AB169" s="16"/>
+      <c r="AC169" s="16"/>
+      <c r="AD169" s="16"/>
+      <c r="AE169" s="16"/>
+      <c r="BN169" s="19"/>
     </row>
     <row r="170" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C170" s="28"/>
-      <c r="W170" s="25"/>
-      <c r="X170" s="25"/>
-      <c r="Y170" s="25"/>
-      <c r="Z170" s="25"/>
-      <c r="AA170" s="25"/>
-      <c r="AB170" s="25"/>
-      <c r="AC170" s="25"/>
-      <c r="AD170" s="25"/>
-      <c r="AE170" s="25"/>
-      <c r="BN170" s="28"/>
+      <c r="C170" s="19"/>
+      <c r="W170" s="16"/>
+      <c r="X170" s="16"/>
+      <c r="Y170" s="16"/>
+      <c r="Z170" s="16"/>
+      <c r="AA170" s="16"/>
+      <c r="AB170" s="16"/>
+      <c r="AC170" s="16"/>
+      <c r="AD170" s="16"/>
+      <c r="AE170" s="16"/>
+      <c r="BN170" s="19"/>
     </row>
     <row r="171" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C171" s="28"/>
-      <c r="W171" s="25"/>
-      <c r="X171" s="25"/>
-      <c r="Y171" s="25"/>
-      <c r="Z171" s="25"/>
-      <c r="AA171" s="25"/>
-      <c r="AB171" s="25"/>
-      <c r="AC171" s="25"/>
-      <c r="AD171" s="25"/>
-      <c r="AE171" s="25"/>
-      <c r="BN171" s="28"/>
+      <c r="C171" s="19"/>
+      <c r="W171" s="16"/>
+      <c r="X171" s="16"/>
+      <c r="Y171" s="16"/>
+      <c r="Z171" s="16"/>
+      <c r="AA171" s="16"/>
+      <c r="AB171" s="16"/>
+      <c r="AC171" s="16"/>
+      <c r="AD171" s="16"/>
+      <c r="AE171" s="16"/>
+      <c r="BN171" s="19"/>
     </row>
     <row r="172" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C172" s="28"/>
-      <c r="W172" s="25"/>
-      <c r="X172" s="25"/>
-      <c r="Y172" s="25"/>
-      <c r="Z172" s="25"/>
-      <c r="AA172" s="25"/>
-      <c r="AB172" s="25"/>
-      <c r="AC172" s="25"/>
-      <c r="AD172" s="25"/>
-      <c r="AE172" s="25"/>
-      <c r="BN172" s="28"/>
+      <c r="C172" s="19"/>
+      <c r="W172" s="16"/>
+      <c r="X172" s="16"/>
+      <c r="Y172" s="16"/>
+      <c r="Z172" s="16"/>
+      <c r="AA172" s="16"/>
+      <c r="AB172" s="16"/>
+      <c r="AC172" s="16"/>
+      <c r="AD172" s="16"/>
+      <c r="AE172" s="16"/>
+      <c r="BN172" s="19"/>
     </row>
     <row r="173" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C173" s="28"/>
-      <c r="W173" s="25"/>
-      <c r="X173" s="25"/>
-      <c r="Y173" s="25"/>
-      <c r="Z173" s="25"/>
-      <c r="AA173" s="25"/>
-      <c r="AB173" s="25"/>
-      <c r="AC173" s="25"/>
-      <c r="AD173" s="25"/>
-      <c r="AE173" s="25"/>
-      <c r="BN173" s="28"/>
+      <c r="C173" s="19"/>
+      <c r="W173" s="16"/>
+      <c r="X173" s="16"/>
+      <c r="Y173" s="16"/>
+      <c r="Z173" s="16"/>
+      <c r="AA173" s="16"/>
+      <c r="AB173" s="16"/>
+      <c r="AC173" s="16"/>
+      <c r="AD173" s="16"/>
+      <c r="AE173" s="16"/>
+      <c r="BN173" s="19"/>
     </row>
     <row r="174" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C174" s="28"/>
-      <c r="W174" s="25"/>
-      <c r="X174" s="25"/>
-      <c r="Y174" s="25"/>
-      <c r="Z174" s="25"/>
-      <c r="AA174" s="25"/>
-      <c r="AB174" s="25"/>
-      <c r="AC174" s="25"/>
-      <c r="AD174" s="25"/>
-      <c r="AE174" s="25"/>
-      <c r="BN174" s="28"/>
+      <c r="C174" s="19"/>
+      <c r="W174" s="16"/>
+      <c r="X174" s="16"/>
+      <c r="Y174" s="16"/>
+      <c r="Z174" s="16"/>
+      <c r="AA174" s="16"/>
+      <c r="AB174" s="16"/>
+      <c r="AC174" s="16"/>
+      <c r="AD174" s="16"/>
+      <c r="AE174" s="16"/>
+      <c r="BN174" s="19"/>
     </row>
     <row r="175" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C175" s="28"/>
-      <c r="W175" s="25"/>
-      <c r="X175" s="25"/>
-      <c r="Y175" s="25"/>
-      <c r="Z175" s="25"/>
-      <c r="AA175" s="25"/>
-      <c r="AB175" s="25"/>
-      <c r="AC175" s="25"/>
-      <c r="AD175" s="25"/>
-      <c r="AE175" s="25"/>
-      <c r="BN175" s="28"/>
+      <c r="C175" s="19"/>
+      <c r="W175" s="16"/>
+      <c r="X175" s="16"/>
+      <c r="Y175" s="16"/>
+      <c r="Z175" s="16"/>
+      <c r="AA175" s="16"/>
+      <c r="AB175" s="16"/>
+      <c r="AC175" s="16"/>
+      <c r="AD175" s="16"/>
+      <c r="AE175" s="16"/>
+      <c r="BN175" s="19"/>
     </row>
     <row r="176" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C176" s="28"/>
-      <c r="W176" s="25"/>
-      <c r="X176" s="25"/>
-      <c r="Y176" s="25"/>
-      <c r="Z176" s="25"/>
-      <c r="AA176" s="25"/>
-      <c r="AB176" s="25"/>
-      <c r="AC176" s="25"/>
-      <c r="AD176" s="25"/>
-      <c r="AE176" s="25"/>
-      <c r="BN176" s="28"/>
+      <c r="C176" s="19"/>
+      <c r="W176" s="16"/>
+      <c r="X176" s="16"/>
+      <c r="Y176" s="16"/>
+      <c r="Z176" s="16"/>
+      <c r="AA176" s="16"/>
+      <c r="AB176" s="16"/>
+      <c r="AC176" s="16"/>
+      <c r="AD176" s="16"/>
+      <c r="AE176" s="16"/>
+      <c r="BN176" s="19"/>
     </row>
     <row r="177" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C177" s="28"/>
-      <c r="W177" s="25"/>
-      <c r="X177" s="25"/>
-      <c r="Y177" s="25"/>
-      <c r="Z177" s="25"/>
-      <c r="AA177" s="25"/>
-      <c r="AB177" s="25"/>
-      <c r="AC177" s="25"/>
-      <c r="AD177" s="25"/>
-      <c r="AE177" s="25"/>
-      <c r="BN177" s="28"/>
+      <c r="C177" s="19"/>
+      <c r="W177" s="16"/>
+      <c r="X177" s="16"/>
+      <c r="Y177" s="16"/>
+      <c r="Z177" s="16"/>
+      <c r="AA177" s="16"/>
+      <c r="AB177" s="16"/>
+      <c r="AC177" s="16"/>
+      <c r="AD177" s="16"/>
+      <c r="AE177" s="16"/>
+      <c r="BN177" s="19"/>
     </row>
     <row r="178" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C178" s="28"/>
-      <c r="W178" s="25"/>
-      <c r="X178" s="25"/>
-      <c r="Y178" s="25"/>
-      <c r="Z178" s="25"/>
-      <c r="AA178" s="25"/>
-      <c r="AB178" s="25"/>
-      <c r="AC178" s="25"/>
-      <c r="AD178" s="25"/>
-      <c r="AE178" s="25"/>
-      <c r="BN178" s="28"/>
+      <c r="C178" s="19"/>
+      <c r="W178" s="16"/>
+      <c r="X178" s="16"/>
+      <c r="Y178" s="16"/>
+      <c r="Z178" s="16"/>
+      <c r="AA178" s="16"/>
+      <c r="AB178" s="16"/>
+      <c r="AC178" s="16"/>
+      <c r="AD178" s="16"/>
+      <c r="AE178" s="16"/>
+      <c r="BN178" s="19"/>
     </row>
     <row r="179" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C179" s="28"/>
-      <c r="W179" s="25"/>
-      <c r="X179" s="25"/>
-      <c r="Y179" s="25"/>
-      <c r="Z179" s="25"/>
-      <c r="AA179" s="25"/>
-      <c r="AB179" s="25"/>
-      <c r="AC179" s="25"/>
-      <c r="AD179" s="25"/>
-      <c r="AE179" s="25"/>
-      <c r="BN179" s="28"/>
+      <c r="C179" s="19"/>
+      <c r="W179" s="16"/>
+      <c r="X179" s="16"/>
+      <c r="Y179" s="16"/>
+      <c r="Z179" s="16"/>
+      <c r="AA179" s="16"/>
+      <c r="AB179" s="16"/>
+      <c r="AC179" s="16"/>
+      <c r="AD179" s="16"/>
+      <c r="AE179" s="16"/>
+      <c r="BN179" s="19"/>
     </row>
     <row r="180" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C180" s="28"/>
-      <c r="W180" s="25"/>
-      <c r="X180" s="25"/>
-      <c r="Y180" s="25"/>
-      <c r="Z180" s="25"/>
-      <c r="AA180" s="25"/>
-      <c r="AB180" s="25"/>
-      <c r="AC180" s="25"/>
-      <c r="AD180" s="25"/>
-      <c r="AE180" s="25"/>
-      <c r="BN180" s="28"/>
+      <c r="C180" s="19"/>
+      <c r="W180" s="16"/>
+      <c r="X180" s="16"/>
+      <c r="Y180" s="16"/>
+      <c r="Z180" s="16"/>
+      <c r="AA180" s="16"/>
+      <c r="AB180" s="16"/>
+      <c r="AC180" s="16"/>
+      <c r="AD180" s="16"/>
+      <c r="AE180" s="16"/>
+      <c r="BN180" s="19"/>
     </row>
     <row r="181" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C181" s="28"/>
-      <c r="W181" s="25"/>
-      <c r="X181" s="25"/>
-      <c r="Y181" s="25"/>
-      <c r="Z181" s="25"/>
-      <c r="AA181" s="25"/>
-      <c r="AB181" s="25"/>
-      <c r="AC181" s="25"/>
-      <c r="AD181" s="25"/>
-      <c r="AE181" s="25"/>
-      <c r="BN181" s="28"/>
+      <c r="C181" s="19"/>
+      <c r="W181" s="16"/>
+      <c r="X181" s="16"/>
+      <c r="Y181" s="16"/>
+      <c r="Z181" s="16"/>
+      <c r="AA181" s="16"/>
+      <c r="AB181" s="16"/>
+      <c r="AC181" s="16"/>
+      <c r="AD181" s="16"/>
+      <c r="AE181" s="16"/>
+      <c r="BN181" s="19"/>
     </row>
     <row r="182" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C182" s="28"/>
-      <c r="W182" s="25"/>
-      <c r="X182" s="25"/>
-      <c r="Y182" s="25"/>
-      <c r="Z182" s="25"/>
-      <c r="AA182" s="25"/>
-      <c r="AB182" s="25"/>
-      <c r="AC182" s="25"/>
-      <c r="AD182" s="25"/>
-      <c r="AE182" s="25"/>
-      <c r="BN182" s="28"/>
+      <c r="C182" s="19"/>
+      <c r="W182" s="16"/>
+      <c r="X182" s="16"/>
+      <c r="Y182" s="16"/>
+      <c r="Z182" s="16"/>
+      <c r="AA182" s="16"/>
+      <c r="AB182" s="16"/>
+      <c r="AC182" s="16"/>
+      <c r="AD182" s="16"/>
+      <c r="AE182" s="16"/>
+      <c r="BN182" s="19"/>
     </row>
     <row r="183" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C183" s="28"/>
-      <c r="W183" s="25"/>
-      <c r="X183" s="25"/>
-      <c r="Y183" s="25"/>
-      <c r="Z183" s="25"/>
-      <c r="AA183" s="25"/>
-      <c r="AB183" s="25"/>
-      <c r="AC183" s="25"/>
-      <c r="AD183" s="25"/>
-      <c r="AE183" s="25"/>
-      <c r="BN183" s="28"/>
+      <c r="C183" s="19"/>
+      <c r="W183" s="16"/>
+      <c r="X183" s="16"/>
+      <c r="Y183" s="16"/>
+      <c r="Z183" s="16"/>
+      <c r="AA183" s="16"/>
+      <c r="AB183" s="16"/>
+      <c r="AC183" s="16"/>
+      <c r="AD183" s="16"/>
+      <c r="AE183" s="16"/>
+      <c r="BN183" s="19"/>
     </row>
     <row r="184" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C184" s="28"/>
-      <c r="W184" s="25"/>
-      <c r="X184" s="25"/>
-      <c r="Y184" s="25"/>
-      <c r="Z184" s="25"/>
-      <c r="AA184" s="25"/>
-      <c r="AB184" s="25"/>
-      <c r="AC184" s="25"/>
-      <c r="AD184" s="25"/>
-      <c r="AE184" s="25"/>
-      <c r="BN184" s="28"/>
+      <c r="C184" s="19"/>
+      <c r="W184" s="16"/>
+      <c r="X184" s="16"/>
+      <c r="Y184" s="16"/>
+      <c r="Z184" s="16"/>
+      <c r="AA184" s="16"/>
+      <c r="AB184" s="16"/>
+      <c r="AC184" s="16"/>
+      <c r="AD184" s="16"/>
+      <c r="AE184" s="16"/>
+      <c r="BN184" s="19"/>
     </row>
     <row r="185" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C185" s="28"/>
-      <c r="W185" s="25"/>
-      <c r="X185" s="25"/>
-      <c r="Y185" s="25"/>
-      <c r="Z185" s="25"/>
-      <c r="AA185" s="25"/>
-      <c r="AB185" s="25"/>
-      <c r="AC185" s="25"/>
-      <c r="AD185" s="25"/>
-      <c r="AE185" s="25"/>
-      <c r="BN185" s="28"/>
+      <c r="C185" s="19"/>
+      <c r="W185" s="16"/>
+      <c r="X185" s="16"/>
+      <c r="Y185" s="16"/>
+      <c r="Z185" s="16"/>
+      <c r="AA185" s="16"/>
+      <c r="AB185" s="16"/>
+      <c r="AC185" s="16"/>
+      <c r="AD185" s="16"/>
+      <c r="AE185" s="16"/>
+      <c r="BN185" s="19"/>
     </row>
     <row r="186" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C186" s="28"/>
-      <c r="W186" s="25"/>
-      <c r="X186" s="25"/>
-      <c r="Y186" s="25"/>
-      <c r="Z186" s="25"/>
-      <c r="AA186" s="25"/>
-      <c r="AB186" s="25"/>
-      <c r="AC186" s="25"/>
-      <c r="AD186" s="25"/>
-      <c r="AE186" s="25"/>
-      <c r="BN186" s="28"/>
+      <c r="C186" s="19"/>
+      <c r="W186" s="16"/>
+      <c r="X186" s="16"/>
+      <c r="Y186" s="16"/>
+      <c r="Z186" s="16"/>
+      <c r="AA186" s="16"/>
+      <c r="AB186" s="16"/>
+      <c r="AC186" s="16"/>
+      <c r="AD186" s="16"/>
+      <c r="AE186" s="16"/>
+      <c r="BN186" s="19"/>
     </row>
     <row r="187" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C187" s="28"/>
-      <c r="W187" s="25"/>
-      <c r="X187" s="25"/>
-      <c r="Y187" s="25"/>
-      <c r="Z187" s="25"/>
-      <c r="AA187" s="25"/>
-      <c r="AB187" s="25"/>
-      <c r="AC187" s="25"/>
-      <c r="AD187" s="25"/>
-      <c r="AE187" s="25"/>
-      <c r="BN187" s="28"/>
+      <c r="C187" s="19"/>
+      <c r="W187" s="16"/>
+      <c r="X187" s="16"/>
+      <c r="Y187" s="16"/>
+      <c r="Z187" s="16"/>
+      <c r="AA187" s="16"/>
+      <c r="AB187" s="16"/>
+      <c r="AC187" s="16"/>
+      <c r="AD187" s="16"/>
+      <c r="AE187" s="16"/>
+      <c r="BN187" s="19"/>
     </row>
     <row r="188" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C188" s="28"/>
-      <c r="W188" s="25"/>
-      <c r="X188" s="25"/>
-      <c r="Y188" s="25"/>
-      <c r="Z188" s="25"/>
-      <c r="AA188" s="25"/>
-      <c r="AB188" s="25"/>
-      <c r="AC188" s="25"/>
-      <c r="AD188" s="25"/>
-      <c r="AE188" s="25"/>
-      <c r="BN188" s="28"/>
+      <c r="C188" s="19"/>
+      <c r="W188" s="16"/>
+      <c r="X188" s="16"/>
+      <c r="Y188" s="16"/>
+      <c r="Z188" s="16"/>
+      <c r="AA188" s="16"/>
+      <c r="AB188" s="16"/>
+      <c r="AC188" s="16"/>
+      <c r="AD188" s="16"/>
+      <c r="AE188" s="16"/>
+      <c r="BN188" s="19"/>
     </row>
     <row r="189" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C189" s="28"/>
-      <c r="W189" s="25"/>
-      <c r="X189" s="25"/>
-      <c r="Y189" s="25"/>
-      <c r="Z189" s="25"/>
-      <c r="AA189" s="25"/>
-      <c r="AB189" s="25"/>
-      <c r="AC189" s="25"/>
-      <c r="AD189" s="25"/>
-      <c r="AE189" s="25"/>
-      <c r="BN189" s="28"/>
+      <c r="C189" s="19"/>
+      <c r="W189" s="16"/>
+      <c r="X189" s="16"/>
+      <c r="Y189" s="16"/>
+      <c r="Z189" s="16"/>
+      <c r="AA189" s="16"/>
+      <c r="AB189" s="16"/>
+      <c r="AC189" s="16"/>
+      <c r="AD189" s="16"/>
+      <c r="AE189" s="16"/>
+      <c r="BN189" s="19"/>
     </row>
     <row r="190" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C190" s="28"/>
-      <c r="W190" s="25"/>
-      <c r="X190" s="25"/>
-      <c r="Y190" s="25"/>
-      <c r="Z190" s="25"/>
-      <c r="AA190" s="25"/>
-      <c r="AB190" s="25"/>
-      <c r="AC190" s="25"/>
-      <c r="AD190" s="25"/>
-      <c r="AE190" s="25"/>
-      <c r="BN190" s="28"/>
+      <c r="C190" s="19"/>
+      <c r="W190" s="16"/>
+      <c r="X190" s="16"/>
+      <c r="Y190" s="16"/>
+      <c r="Z190" s="16"/>
+      <c r="AA190" s="16"/>
+      <c r="AB190" s="16"/>
+      <c r="AC190" s="16"/>
+      <c r="AD190" s="16"/>
+      <c r="AE190" s="16"/>
+      <c r="BN190" s="19"/>
     </row>
     <row r="191" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C191" s="28"/>
-      <c r="W191" s="25"/>
-      <c r="X191" s="25"/>
-      <c r="Y191" s="25"/>
-      <c r="Z191" s="25"/>
-      <c r="AA191" s="25"/>
-      <c r="AB191" s="25"/>
-      <c r="AC191" s="25"/>
-      <c r="AD191" s="25"/>
-      <c r="AE191" s="25"/>
-      <c r="BN191" s="28"/>
+      <c r="C191" s="19"/>
+      <c r="W191" s="16"/>
+      <c r="X191" s="16"/>
+      <c r="Y191" s="16"/>
+      <c r="Z191" s="16"/>
+      <c r="AA191" s="16"/>
+      <c r="AB191" s="16"/>
+      <c r="AC191" s="16"/>
+      <c r="AD191" s="16"/>
+      <c r="AE191" s="16"/>
+      <c r="BN191" s="19"/>
     </row>
     <row r="192" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C192" s="28"/>
-      <c r="W192" s="25"/>
-      <c r="X192" s="25"/>
-      <c r="Y192" s="25"/>
-      <c r="Z192" s="25"/>
-      <c r="AA192" s="25"/>
-      <c r="AB192" s="25"/>
-      <c r="AC192" s="25"/>
-      <c r="AD192" s="25"/>
-      <c r="AE192" s="25"/>
-      <c r="BN192" s="28"/>
+      <c r="C192" s="19"/>
+      <c r="W192" s="16"/>
+      <c r="X192" s="16"/>
+      <c r="Y192" s="16"/>
+      <c r="Z192" s="16"/>
+      <c r="AA192" s="16"/>
+      <c r="AB192" s="16"/>
+      <c r="AC192" s="16"/>
+      <c r="AD192" s="16"/>
+      <c r="AE192" s="16"/>
+      <c r="BN192" s="19"/>
     </row>
     <row r="193" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C193" s="28"/>
-      <c r="W193" s="25"/>
-      <c r="X193" s="25"/>
-      <c r="Y193" s="25"/>
-      <c r="Z193" s="25"/>
-      <c r="AA193" s="25"/>
-      <c r="AB193" s="25"/>
-      <c r="AC193" s="25"/>
-      <c r="AD193" s="25"/>
-      <c r="AE193" s="25"/>
-      <c r="BN193" s="28"/>
+      <c r="C193" s="19"/>
+      <c r="W193" s="16"/>
+      <c r="X193" s="16"/>
+      <c r="Y193" s="16"/>
+      <c r="Z193" s="16"/>
+      <c r="AA193" s="16"/>
+      <c r="AB193" s="16"/>
+      <c r="AC193" s="16"/>
+      <c r="AD193" s="16"/>
+      <c r="AE193" s="16"/>
+      <c r="BN193" s="19"/>
     </row>
     <row r="194" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C194" s="28"/>
-      <c r="W194" s="25"/>
-      <c r="X194" s="25"/>
-      <c r="Y194" s="25"/>
-      <c r="Z194" s="25"/>
-      <c r="AA194" s="25"/>
-      <c r="AB194" s="25"/>
-      <c r="AC194" s="25"/>
-      <c r="AD194" s="25"/>
-      <c r="AE194" s="25"/>
-      <c r="BN194" s="28"/>
+      <c r="C194" s="19"/>
+      <c r="W194" s="16"/>
+      <c r="X194" s="16"/>
+      <c r="Y194" s="16"/>
+      <c r="Z194" s="16"/>
+      <c r="AA194" s="16"/>
+      <c r="AB194" s="16"/>
+      <c r="AC194" s="16"/>
+      <c r="AD194" s="16"/>
+      <c r="AE194" s="16"/>
+      <c r="BN194" s="19"/>
     </row>
     <row r="195" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C195" s="28"/>
-      <c r="W195" s="25"/>
-      <c r="X195" s="25"/>
-      <c r="Y195" s="25"/>
-      <c r="Z195" s="25"/>
-      <c r="AA195" s="25"/>
-      <c r="AB195" s="25"/>
-      <c r="AC195" s="25"/>
-      <c r="AD195" s="25"/>
-      <c r="AE195" s="25"/>
-      <c r="BN195" s="28"/>
+      <c r="C195" s="19"/>
+      <c r="W195" s="16"/>
+      <c r="X195" s="16"/>
+      <c r="Y195" s="16"/>
+      <c r="Z195" s="16"/>
+      <c r="AA195" s="16"/>
+      <c r="AB195" s="16"/>
+      <c r="AC195" s="16"/>
+      <c r="AD195" s="16"/>
+      <c r="AE195" s="16"/>
+      <c r="BN195" s="19"/>
     </row>
     <row r="196" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C196" s="28"/>
-      <c r="W196" s="25"/>
-      <c r="X196" s="25"/>
-      <c r="Y196" s="25"/>
-      <c r="Z196" s="25"/>
-      <c r="AA196" s="25"/>
-      <c r="AB196" s="25"/>
-      <c r="AC196" s="25"/>
-      <c r="AD196" s="25"/>
-      <c r="AE196" s="25"/>
-      <c r="BN196" s="28"/>
+      <c r="C196" s="19"/>
+      <c r="W196" s="16"/>
+      <c r="X196" s="16"/>
+      <c r="Y196" s="16"/>
+      <c r="Z196" s="16"/>
+      <c r="AA196" s="16"/>
+      <c r="AB196" s="16"/>
+      <c r="AC196" s="16"/>
+      <c r="AD196" s="16"/>
+      <c r="AE196" s="16"/>
+      <c r="BN196" s="19"/>
     </row>
     <row r="197" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="W197" s="25"/>
-      <c r="X197" s="25"/>
-      <c r="Y197" s="25"/>
-      <c r="Z197" s="25"/>
-      <c r="AA197" s="25"/>
-      <c r="AB197" s="25"/>
-      <c r="AC197" s="25"/>
-      <c r="AD197" s="25"/>
-      <c r="AE197" s="25"/>
-      <c r="BN197" s="28"/>
+      <c r="W197" s="16"/>
+      <c r="X197" s="16"/>
+      <c r="Y197" s="16"/>
+      <c r="Z197" s="16"/>
+      <c r="AA197" s="16"/>
+      <c r="AB197" s="16"/>
+      <c r="AC197" s="16"/>
+      <c r="AD197" s="16"/>
+      <c r="AE197" s="16"/>
+      <c r="BN197" s="19"/>
     </row>
     <row r="198" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="W198" s="25"/>
-      <c r="X198" s="25"/>
-      <c r="Y198" s="25"/>
-      <c r="Z198" s="25"/>
-      <c r="AA198" s="25"/>
-      <c r="AB198" s="25"/>
-      <c r="AC198" s="25"/>
-      <c r="AD198" s="25"/>
-      <c r="AE198" s="25"/>
-      <c r="BN198" s="28"/>
+      <c r="W198" s="16"/>
+      <c r="X198" s="16"/>
+      <c r="Y198" s="16"/>
+      <c r="Z198" s="16"/>
+      <c r="AA198" s="16"/>
+      <c r="AB198" s="16"/>
+      <c r="AC198" s="16"/>
+      <c r="AD198" s="16"/>
+      <c r="AE198" s="16"/>
+      <c r="BN198" s="19"/>
     </row>
     <row r="199" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="W199" s="25"/>
-      <c r="X199" s="25"/>
-      <c r="Y199" s="25"/>
-      <c r="Z199" s="25"/>
-      <c r="AA199" s="25"/>
-      <c r="AB199" s="25"/>
-      <c r="AC199" s="25"/>
-      <c r="AD199" s="25"/>
-      <c r="AE199" s="25"/>
-      <c r="BN199" s="28"/>
+      <c r="W199" s="16"/>
+      <c r="X199" s="16"/>
+      <c r="Y199" s="16"/>
+      <c r="Z199" s="16"/>
+      <c r="AA199" s="16"/>
+      <c r="AB199" s="16"/>
+      <c r="AC199" s="16"/>
+      <c r="AD199" s="16"/>
+      <c r="AE199" s="16"/>
+      <c r="BN199" s="19"/>
     </row>
     <row r="200" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="W200" s="25"/>
-      <c r="X200" s="25"/>
-      <c r="Y200" s="25"/>
-      <c r="Z200" s="25"/>
-      <c r="AA200" s="25"/>
-      <c r="AB200" s="25"/>
-      <c r="AC200" s="25"/>
-      <c r="AD200" s="25"/>
-      <c r="AE200" s="25"/>
-      <c r="BN200" s="28"/>
+      <c r="W200" s="16"/>
+      <c r="X200" s="16"/>
+      <c r="Y200" s="16"/>
+      <c r="Z200" s="16"/>
+      <c r="AA200" s="16"/>
+      <c r="AB200" s="16"/>
+      <c r="AC200" s="16"/>
+      <c r="AD200" s="16"/>
+      <c r="AE200" s="16"/>
+      <c r="BN200" s="19"/>
     </row>
     <row r="201" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="W201" s="25"/>
-      <c r="X201" s="25"/>
-      <c r="Y201" s="25"/>
-      <c r="Z201" s="25"/>
-      <c r="AA201" s="25"/>
-      <c r="AB201" s="25"/>
-      <c r="AC201" s="25"/>
-      <c r="AD201" s="25"/>
-      <c r="AE201" s="25"/>
-      <c r="BN201" s="28"/>
+      <c r="W201" s="16"/>
+      <c r="X201" s="16"/>
+      <c r="Y201" s="16"/>
+      <c r="Z201" s="16"/>
+      <c r="AA201" s="16"/>
+      <c r="AB201" s="16"/>
+      <c r="AC201" s="16"/>
+      <c r="AD201" s="16"/>
+      <c r="AE201" s="16"/>
+      <c r="BN201" s="19"/>
     </row>
     <row r="202" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="W202" s="25"/>
-      <c r="X202" s="25"/>
-      <c r="Y202" s="25"/>
-      <c r="Z202" s="25"/>
-      <c r="AA202" s="25"/>
-      <c r="AB202" s="25"/>
-      <c r="AC202" s="25"/>
-      <c r="AD202" s="25"/>
-      <c r="AE202" s="25"/>
-      <c r="BN202" s="28"/>
+      <c r="W202" s="16"/>
+      <c r="X202" s="16"/>
+      <c r="Y202" s="16"/>
+      <c r="Z202" s="16"/>
+      <c r="AA202" s="16"/>
+      <c r="AB202" s="16"/>
+      <c r="AC202" s="16"/>
+      <c r="AD202" s="16"/>
+      <c r="AE202" s="16"/>
+      <c r="BN202" s="19"/>
     </row>
     <row r="203" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="W203" s="25"/>
-      <c r="X203" s="25"/>
-      <c r="Y203" s="25"/>
-      <c r="Z203" s="25"/>
-      <c r="AA203" s="25"/>
-      <c r="AB203" s="25"/>
-      <c r="AC203" s="25"/>
-      <c r="AD203" s="25"/>
-      <c r="AE203" s="25"/>
-      <c r="BN203" s="28"/>
+      <c r="W203" s="16"/>
+      <c r="X203" s="16"/>
+      <c r="Y203" s="16"/>
+      <c r="Z203" s="16"/>
+      <c r="AA203" s="16"/>
+      <c r="AB203" s="16"/>
+      <c r="AC203" s="16"/>
+      <c r="AD203" s="16"/>
+      <c r="AE203" s="16"/>
+      <c r="BN203" s="19"/>
     </row>
     <row r="204" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="W204" s="25"/>
-      <c r="X204" s="25"/>
-      <c r="Y204" s="25"/>
-      <c r="Z204" s="25"/>
-      <c r="AA204" s="25"/>
-      <c r="AB204" s="25"/>
-      <c r="AC204" s="25"/>
-      <c r="AD204" s="25"/>
-      <c r="AE204" s="25"/>
-      <c r="BN204" s="28"/>
+      <c r="W204" s="16"/>
+      <c r="X204" s="16"/>
+      <c r="Y204" s="16"/>
+      <c r="Z204" s="16"/>
+      <c r="AA204" s="16"/>
+      <c r="AB204" s="16"/>
+      <c r="AC204" s="16"/>
+      <c r="AD204" s="16"/>
+      <c r="AE204" s="16"/>
+      <c r="BN204" s="19"/>
     </row>
     <row r="205" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="W205" s="25"/>
-      <c r="X205" s="25"/>
-      <c r="Y205" s="25"/>
-      <c r="Z205" s="25"/>
-      <c r="AA205" s="25"/>
-      <c r="AB205" s="25"/>
-      <c r="AC205" s="25"/>
-      <c r="AD205" s="25"/>
-      <c r="AE205" s="25"/>
-      <c r="BN205" s="28"/>
+      <c r="W205" s="16"/>
+      <c r="X205" s="16"/>
+      <c r="Y205" s="16"/>
+      <c r="Z205" s="16"/>
+      <c r="AA205" s="16"/>
+      <c r="AB205" s="16"/>
+      <c r="AC205" s="16"/>
+      <c r="AD205" s="16"/>
+      <c r="AE205" s="16"/>
+      <c r="BN205" s="19"/>
     </row>
     <row r="206" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="W206" s="25"/>
-      <c r="X206" s="25"/>
-      <c r="Y206" s="25"/>
-      <c r="Z206" s="25"/>
-      <c r="AA206" s="25"/>
-      <c r="AB206" s="25"/>
-      <c r="AC206" s="25"/>
-      <c r="AD206" s="25"/>
-      <c r="AE206" s="25"/>
-      <c r="BN206" s="28"/>
+      <c r="W206" s="16"/>
+      <c r="X206" s="16"/>
+      <c r="Y206" s="16"/>
+      <c r="Z206" s="16"/>
+      <c r="AA206" s="16"/>
+      <c r="AB206" s="16"/>
+      <c r="AC206" s="16"/>
+      <c r="AD206" s="16"/>
+      <c r="AE206" s="16"/>
+      <c r="BN206" s="19"/>
     </row>
     <row r="207" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="W207" s="25"/>
-      <c r="X207" s="25"/>
-      <c r="Y207" s="25"/>
-      <c r="Z207" s="25"/>
-      <c r="AA207" s="25"/>
-      <c r="AB207" s="25"/>
-      <c r="AC207" s="25"/>
-      <c r="AD207" s="25"/>
-      <c r="AE207" s="25"/>
-      <c r="BN207" s="28"/>
+      <c r="W207" s="16"/>
+      <c r="X207" s="16"/>
+      <c r="Y207" s="16"/>
+      <c r="Z207" s="16"/>
+      <c r="AA207" s="16"/>
+      <c r="AB207" s="16"/>
+      <c r="AC207" s="16"/>
+      <c r="AD207" s="16"/>
+      <c r="AE207" s="16"/>
+      <c r="BN207" s="19"/>
     </row>
     <row r="208" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="W208" s="25"/>
-      <c r="X208" s="25"/>
-      <c r="Y208" s="25"/>
-      <c r="Z208" s="25"/>
-      <c r="AA208" s="25"/>
-      <c r="AB208" s="25"/>
-      <c r="AC208" s="25"/>
-      <c r="AD208" s="25"/>
-      <c r="AE208" s="25"/>
-      <c r="BN208" s="28"/>
+      <c r="W208" s="16"/>
+      <c r="X208" s="16"/>
+      <c r="Y208" s="16"/>
+      <c r="Z208" s="16"/>
+      <c r="AA208" s="16"/>
+      <c r="AB208" s="16"/>
+      <c r="AC208" s="16"/>
+      <c r="AD208" s="16"/>
+      <c r="AE208" s="16"/>
+      <c r="BN208" s="19"/>
     </row>
     <row r="209" spans="23:66" x14ac:dyDescent="0.25">
-      <c r="W209" s="25"/>
-      <c r="X209" s="25"/>
-      <c r="Y209" s="25"/>
-      <c r="Z209" s="25"/>
-      <c r="AA209" s="25"/>
-      <c r="AB209" s="25"/>
-      <c r="AC209" s="25"/>
-      <c r="AD209" s="25"/>
-      <c r="AE209" s="25"/>
-      <c r="BN209" s="28"/>
+      <c r="W209" s="16"/>
+      <c r="X209" s="16"/>
+      <c r="Y209" s="16"/>
+      <c r="Z209" s="16"/>
+      <c r="AA209" s="16"/>
+      <c r="AB209" s="16"/>
+      <c r="AC209" s="16"/>
+      <c r="AD209" s="16"/>
+      <c r="AE209" s="16"/>
+      <c r="BN209" s="19"/>
     </row>
     <row r="210" spans="23:66" x14ac:dyDescent="0.25">
-      <c r="W210" s="25"/>
-      <c r="X210" s="25"/>
-      <c r="Y210" s="25"/>
-      <c r="Z210" s="25"/>
-      <c r="AA210" s="25"/>
-      <c r="AB210" s="25"/>
-      <c r="AC210" s="25"/>
-      <c r="AD210" s="25"/>
-      <c r="AE210" s="25"/>
-      <c r="BN210" s="28"/>
+      <c r="W210" s="16"/>
+      <c r="X210" s="16"/>
+      <c r="Y210" s="16"/>
+      <c r="Z210" s="16"/>
+      <c r="AA210" s="16"/>
+      <c r="AB210" s="16"/>
+      <c r="AC210" s="16"/>
+      <c r="AD210" s="16"/>
+      <c r="AE210" s="16"/>
+      <c r="BN210" s="19"/>
     </row>
     <row r="211" spans="23:66" x14ac:dyDescent="0.25">
-      <c r="W211" s="25"/>
-      <c r="X211" s="25"/>
-      <c r="Y211" s="25"/>
-      <c r="Z211" s="25"/>
-      <c r="AA211" s="25"/>
-      <c r="AB211" s="25"/>
-      <c r="AC211" s="25"/>
-      <c r="AD211" s="25"/>
-      <c r="AE211" s="25"/>
-      <c r="BN211" s="28"/>
+      <c r="W211" s="16"/>
+      <c r="X211" s="16"/>
+      <c r="Y211" s="16"/>
+      <c r="Z211" s="16"/>
+      <c r="AA211" s="16"/>
+      <c r="AB211" s="16"/>
+      <c r="AC211" s="16"/>
+      <c r="AD211" s="16"/>
+      <c r="AE211" s="16"/>
+      <c r="BN211" s="19"/>
     </row>
     <row r="212" spans="23:66" x14ac:dyDescent="0.25">
-      <c r="W212" s="25"/>
-      <c r="X212" s="25"/>
-      <c r="Y212" s="25"/>
-      <c r="Z212" s="25"/>
-      <c r="AA212" s="25"/>
-      <c r="AB212" s="25"/>
-      <c r="AC212" s="25"/>
-      <c r="AD212" s="25"/>
-      <c r="AE212" s="25"/>
-      <c r="BN212" s="28"/>
+      <c r="W212" s="16"/>
+      <c r="X212" s="16"/>
+      <c r="Y212" s="16"/>
+      <c r="Z212" s="16"/>
+      <c r="AA212" s="16"/>
+      <c r="AB212" s="16"/>
+      <c r="AC212" s="16"/>
+      <c r="AD212" s="16"/>
+      <c r="AE212" s="16"/>
+      <c r="BN212" s="19"/>
     </row>
     <row r="213" spans="23:66" x14ac:dyDescent="0.25">
-      <c r="W213" s="25"/>
-      <c r="X213" s="25"/>
-      <c r="Y213" s="25"/>
-      <c r="Z213" s="25"/>
-      <c r="AA213" s="25"/>
-      <c r="AB213" s="25"/>
-      <c r="AC213" s="25"/>
-      <c r="AD213" s="25"/>
-      <c r="AE213" s="25"/>
-      <c r="BN213" s="28"/>
+      <c r="W213" s="16"/>
+      <c r="X213" s="16"/>
+      <c r="Y213" s="16"/>
+      <c r="Z213" s="16"/>
+      <c r="AA213" s="16"/>
+      <c r="AB213" s="16"/>
+      <c r="AC213" s="16"/>
+      <c r="AD213" s="16"/>
+      <c r="AE213" s="16"/>
+      <c r="BN213" s="19"/>
     </row>
     <row r="214" spans="23:66" x14ac:dyDescent="0.25">
-      <c r="W214" s="25"/>
-      <c r="X214" s="25"/>
-      <c r="Y214" s="25"/>
-      <c r="Z214" s="25"/>
-      <c r="AA214" s="25"/>
-      <c r="AB214" s="25"/>
-      <c r="AC214" s="25"/>
-      <c r="AD214" s="25"/>
-      <c r="AE214" s="25"/>
-      <c r="BN214" s="28"/>
+      <c r="W214" s="16"/>
+      <c r="X214" s="16"/>
+      <c r="Y214" s="16"/>
+      <c r="Z214" s="16"/>
+      <c r="AA214" s="16"/>
+      <c r="AB214" s="16"/>
+      <c r="AC214" s="16"/>
+      <c r="AD214" s="16"/>
+      <c r="AE214" s="16"/>
+      <c r="BN214" s="19"/>
     </row>
     <row r="215" spans="23:66" x14ac:dyDescent="0.25">
-      <c r="W215" s="25"/>
-      <c r="X215" s="25"/>
-      <c r="Y215" s="25"/>
-      <c r="Z215" s="25"/>
-      <c r="AA215" s="25"/>
-      <c r="AB215" s="25"/>
-      <c r="AC215" s="25"/>
-      <c r="AD215" s="25"/>
-      <c r="AE215" s="25"/>
-      <c r="BN215" s="28"/>
+      <c r="W215" s="16"/>
+      <c r="X215" s="16"/>
+      <c r="Y215" s="16"/>
+      <c r="Z215" s="16"/>
+      <c r="AA215" s="16"/>
+      <c r="AB215" s="16"/>
+      <c r="AC215" s="16"/>
+      <c r="AD215" s="16"/>
+      <c r="AE215" s="16"/>
+      <c r="BN215" s="19"/>
     </row>
     <row r="216" spans="23:66" x14ac:dyDescent="0.25">
-      <c r="W216" s="25"/>
-      <c r="X216" s="25"/>
-      <c r="Y216" s="25"/>
-      <c r="Z216" s="25"/>
-      <c r="AA216" s="25"/>
-      <c r="AB216" s="25"/>
-      <c r="AC216" s="25"/>
-      <c r="AD216" s="25"/>
-      <c r="AE216" s="25"/>
-      <c r="BN216" s="28"/>
+      <c r="W216" s="16"/>
+      <c r="X216" s="16"/>
+      <c r="Y216" s="16"/>
+      <c r="Z216" s="16"/>
+      <c r="AA216" s="16"/>
+      <c r="AB216" s="16"/>
+      <c r="AC216" s="16"/>
+      <c r="AD216" s="16"/>
+      <c r="AE216" s="16"/>
+      <c r="BN216" s="19"/>
     </row>
     <row r="217" spans="23:66" x14ac:dyDescent="0.25">
-      <c r="W217" s="25"/>
-      <c r="X217" s="25"/>
-      <c r="Y217" s="25"/>
-      <c r="Z217" s="25"/>
-      <c r="AA217" s="25"/>
-      <c r="AB217" s="25"/>
-      <c r="AC217" s="25"/>
-      <c r="AD217" s="25"/>
-      <c r="AE217" s="25"/>
-      <c r="BN217" s="28"/>
+      <c r="W217" s="16"/>
+      <c r="X217" s="16"/>
+      <c r="Y217" s="16"/>
+      <c r="Z217" s="16"/>
+      <c r="AA217" s="16"/>
+      <c r="AB217" s="16"/>
+      <c r="AC217" s="16"/>
+      <c r="AD217" s="16"/>
+      <c r="AE217" s="16"/>
+      <c r="BN217" s="19"/>
     </row>
     <row r="218" spans="23:66" x14ac:dyDescent="0.25">
-      <c r="W218" s="25"/>
-      <c r="X218" s="25"/>
-      <c r="Y218" s="25"/>
-      <c r="Z218" s="25"/>
-      <c r="AA218" s="25"/>
-      <c r="AB218" s="25"/>
-      <c r="AC218" s="25"/>
-      <c r="AD218" s="25"/>
-      <c r="AE218" s="25"/>
-      <c r="BN218" s="28"/>
+      <c r="W218" s="16"/>
+      <c r="X218" s="16"/>
+      <c r="Y218" s="16"/>
+      <c r="Z218" s="16"/>
+      <c r="AA218" s="16"/>
+      <c r="AB218" s="16"/>
+      <c r="AC218" s="16"/>
+      <c r="AD218" s="16"/>
+      <c r="AE218" s="16"/>
+      <c r="BN218" s="19"/>
     </row>
     <row r="219" spans="23:66" x14ac:dyDescent="0.25">
-      <c r="W219" s="25"/>
-      <c r="X219" s="25"/>
-      <c r="Y219" s="25"/>
-      <c r="Z219" s="25"/>
-      <c r="AA219" s="25"/>
-      <c r="AB219" s="25"/>
-      <c r="AC219" s="25"/>
-      <c r="AD219" s="25"/>
-      <c r="AE219" s="25"/>
-      <c r="BN219" s="28"/>
+      <c r="W219" s="16"/>
+      <c r="X219" s="16"/>
+      <c r="Y219" s="16"/>
+      <c r="Z219" s="16"/>
+      <c r="AA219" s="16"/>
+      <c r="AB219" s="16"/>
+      <c r="AC219" s="16"/>
+      <c r="AD219" s="16"/>
+      <c r="AE219" s="16"/>
+      <c r="BN219" s="19"/>
     </row>
     <row r="220" spans="23:66" x14ac:dyDescent="0.25">
-      <c r="W220" s="25"/>
-      <c r="X220" s="25"/>
-      <c r="Y220" s="25"/>
-      <c r="Z220" s="25"/>
-      <c r="AA220" s="25"/>
-      <c r="AB220" s="25"/>
-      <c r="AC220" s="25"/>
-      <c r="AD220" s="25"/>
-      <c r="AE220" s="25"/>
-      <c r="BN220" s="28"/>
+      <c r="W220" s="16"/>
+      <c r="X220" s="16"/>
+      <c r="Y220" s="16"/>
+      <c r="Z220" s="16"/>
+      <c r="AA220" s="16"/>
+      <c r="AB220" s="16"/>
+      <c r="AC220" s="16"/>
+      <c r="AD220" s="16"/>
+      <c r="AE220" s="16"/>
+      <c r="BN220" s="19"/>
     </row>
     <row r="221" spans="23:66" x14ac:dyDescent="0.25">
-      <c r="W221" s="25"/>
-      <c r="X221" s="25"/>
-      <c r="Y221" s="25"/>
-      <c r="Z221" s="25"/>
-      <c r="AA221" s="25"/>
-      <c r="AB221" s="25"/>
-      <c r="AC221" s="25"/>
-      <c r="AD221" s="25"/>
-      <c r="AE221" s="25"/>
-      <c r="BN221" s="28"/>
+      <c r="W221" s="16"/>
+      <c r="X221" s="16"/>
+      <c r="Y221" s="16"/>
+      <c r="Z221" s="16"/>
+      <c r="AA221" s="16"/>
+      <c r="AB221" s="16"/>
+      <c r="AC221" s="16"/>
+      <c r="AD221" s="16"/>
+      <c r="AE221" s="16"/>
+      <c r="BN221" s="19"/>
     </row>
     <row r="222" spans="23:66" x14ac:dyDescent="0.25">
-      <c r="W222" s="25"/>
-      <c r="X222" s="25"/>
-      <c r="Y222" s="25"/>
-      <c r="Z222" s="25"/>
-      <c r="AA222" s="25"/>
-      <c r="AB222" s="25"/>
-      <c r="AC222" s="25"/>
-      <c r="AD222" s="25"/>
-      <c r="AE222" s="25"/>
-      <c r="BN222" s="28"/>
+      <c r="W222" s="16"/>
+      <c r="X222" s="16"/>
+      <c r="Y222" s="16"/>
+      <c r="Z222" s="16"/>
+      <c r="AA222" s="16"/>
+      <c r="AB222" s="16"/>
+      <c r="AC222" s="16"/>
+      <c r="AD222" s="16"/>
+      <c r="AE222" s="16"/>
+      <c r="BN222" s="19"/>
     </row>
     <row r="223" spans="23:66" x14ac:dyDescent="0.25">
-      <c r="W223" s="25"/>
-      <c r="X223" s="25"/>
-      <c r="Y223" s="25"/>
-      <c r="Z223" s="25"/>
-      <c r="AA223" s="25"/>
-      <c r="AB223" s="25"/>
-      <c r="AC223" s="25"/>
-      <c r="AD223" s="25"/>
-      <c r="AE223" s="25"/>
-      <c r="BN223" s="28"/>
+      <c r="W223" s="16"/>
+      <c r="X223" s="16"/>
+      <c r="Y223" s="16"/>
+      <c r="Z223" s="16"/>
+      <c r="AA223" s="16"/>
+      <c r="AB223" s="16"/>
+      <c r="AC223" s="16"/>
+      <c r="AD223" s="16"/>
+      <c r="AE223" s="16"/>
+      <c r="BN223" s="19"/>
     </row>
     <row r="224" spans="23:66" x14ac:dyDescent="0.25">
-      <c r="W224" s="25"/>
-      <c r="X224" s="25"/>
-      <c r="Y224" s="25"/>
-      <c r="Z224" s="25"/>
-      <c r="AA224" s="25"/>
-      <c r="AB224" s="25"/>
-      <c r="AC224" s="25"/>
-      <c r="AD224" s="25"/>
-      <c r="AE224" s="25"/>
-      <c r="BN224" s="28"/>
+      <c r="W224" s="16"/>
+      <c r="X224" s="16"/>
+      <c r="Y224" s="16"/>
+      <c r="Z224" s="16"/>
+      <c r="AA224" s="16"/>
+      <c r="AB224" s="16"/>
+      <c r="AC224" s="16"/>
+      <c r="AD224" s="16"/>
+      <c r="AE224" s="16"/>
+      <c r="BN224" s="19"/>
     </row>
     <row r="225" spans="23:66" x14ac:dyDescent="0.25">
-      <c r="W225" s="25"/>
-      <c r="X225" s="25"/>
-      <c r="Y225" s="25"/>
-      <c r="Z225" s="25"/>
-      <c r="AA225" s="25"/>
-      <c r="AB225" s="25"/>
-      <c r="AC225" s="25"/>
-      <c r="AD225" s="25"/>
-      <c r="AE225" s="25"/>
-      <c r="BN225" s="28"/>
+      <c r="W225" s="16"/>
+      <c r="X225" s="16"/>
+      <c r="Y225" s="16"/>
+      <c r="Z225" s="16"/>
+      <c r="AA225" s="16"/>
+      <c r="AB225" s="16"/>
+      <c r="AC225" s="16"/>
+      <c r="AD225" s="16"/>
+      <c r="AE225" s="16"/>
+      <c r="BN225" s="19"/>
     </row>
     <row r="226" spans="23:66" x14ac:dyDescent="0.25">
-      <c r="W226" s="25"/>
-      <c r="X226" s="25"/>
-      <c r="Y226" s="25"/>
-      <c r="Z226" s="25"/>
-      <c r="AA226" s="25"/>
-      <c r="AB226" s="25"/>
-      <c r="AC226" s="25"/>
-      <c r="AD226" s="25"/>
-      <c r="AE226" s="25"/>
-      <c r="BN226" s="28"/>
+      <c r="W226" s="16"/>
+      <c r="X226" s="16"/>
+      <c r="Y226" s="16"/>
+      <c r="Z226" s="16"/>
+      <c r="AA226" s="16"/>
+      <c r="AB226" s="16"/>
+      <c r="AC226" s="16"/>
+      <c r="AD226" s="16"/>
+      <c r="AE226" s="16"/>
+      <c r="BN226" s="19"/>
     </row>
     <row r="227" spans="23:66" x14ac:dyDescent="0.25">
-      <c r="W227" s="25"/>
-      <c r="X227" s="25"/>
-      <c r="Y227" s="25"/>
-      <c r="Z227" s="25"/>
-      <c r="AA227" s="25"/>
-      <c r="AB227" s="25"/>
-      <c r="AC227" s="25"/>
-      <c r="AD227" s="25"/>
-      <c r="AE227" s="25"/>
-      <c r="BN227" s="28"/>
+      <c r="W227" s="16"/>
+      <c r="X227" s="16"/>
+      <c r="Y227" s="16"/>
+      <c r="Z227" s="16"/>
+      <c r="AA227" s="16"/>
+      <c r="AB227" s="16"/>
+      <c r="AC227" s="16"/>
+      <c r="AD227" s="16"/>
+      <c r="AE227" s="16"/>
+      <c r="BN227" s="19"/>
     </row>
     <row r="228" spans="23:66" x14ac:dyDescent="0.25">
-      <c r="W228" s="25"/>
-      <c r="X228" s="25"/>
-      <c r="Y228" s="25"/>
-      <c r="Z228" s="25"/>
-      <c r="AA228" s="25"/>
-      <c r="AB228" s="25"/>
-      <c r="AC228" s="25"/>
-      <c r="AD228" s="25"/>
-      <c r="AE228" s="25"/>
-      <c r="BN228" s="28"/>
+      <c r="W228" s="16"/>
+      <c r="X228" s="16"/>
+      <c r="Y228" s="16"/>
+      <c r="Z228" s="16"/>
+      <c r="AA228" s="16"/>
+      <c r="AB228" s="16"/>
+      <c r="AC228" s="16"/>
+      <c r="AD228" s="16"/>
+      <c r="AE228" s="16"/>
+      <c r="BN228" s="19"/>
     </row>
     <row r="229" spans="23:66" x14ac:dyDescent="0.25">
-      <c r="W229" s="25"/>
-      <c r="X229" s="25"/>
-      <c r="Y229" s="25"/>
-      <c r="Z229" s="25"/>
-      <c r="AA229" s="25"/>
-      <c r="AB229" s="25"/>
-      <c r="AC229" s="25"/>
-      <c r="AD229" s="25"/>
-      <c r="AE229" s="25"/>
-      <c r="BN229" s="28"/>
+      <c r="W229" s="16"/>
+      <c r="X229" s="16"/>
+      <c r="Y229" s="16"/>
+      <c r="Z229" s="16"/>
+      <c r="AA229" s="16"/>
+      <c r="AB229" s="16"/>
+      <c r="AC229" s="16"/>
+      <c r="AD229" s="16"/>
+      <c r="AE229" s="16"/>
+      <c r="BN229" s="19"/>
     </row>
     <row r="230" spans="23:66" x14ac:dyDescent="0.25">
-      <c r="W230" s="25"/>
-      <c r="X230" s="25"/>
-      <c r="Y230" s="25"/>
-      <c r="Z230" s="25"/>
-      <c r="AA230" s="25"/>
-      <c r="AB230" s="25"/>
-      <c r="AC230" s="25"/>
-      <c r="AD230" s="25"/>
-      <c r="AE230" s="25"/>
-      <c r="BN230" s="28"/>
+      <c r="W230" s="16"/>
+      <c r="X230" s="16"/>
+      <c r="Y230" s="16"/>
+      <c r="Z230" s="16"/>
+      <c r="AA230" s="16"/>
+      <c r="AB230" s="16"/>
+      <c r="AC230" s="16"/>
+      <c r="AD230" s="16"/>
+      <c r="AE230" s="16"/>
+      <c r="BN230" s="19"/>
     </row>
     <row r="231" spans="23:66" x14ac:dyDescent="0.25">
-      <c r="W231" s="25"/>
-      <c r="X231" s="25"/>
-      <c r="Y231" s="25"/>
-      <c r="Z231" s="25"/>
-      <c r="AA231" s="25"/>
-      <c r="AB231" s="25"/>
-      <c r="AC231" s="25"/>
-      <c r="AD231" s="25"/>
-      <c r="AE231" s="25"/>
-      <c r="BN231" s="28"/>
+      <c r="W231" s="16"/>
+      <c r="X231" s="16"/>
+      <c r="Y231" s="16"/>
+      <c r="Z231" s="16"/>
+      <c r="AA231" s="16"/>
+      <c r="AB231" s="16"/>
+      <c r="AC231" s="16"/>
+      <c r="AD231" s="16"/>
+      <c r="AE231" s="16"/>
+      <c r="BN231" s="19"/>
     </row>
     <row r="232" spans="23:66" x14ac:dyDescent="0.25">
-      <c r="W232" s="25"/>
-      <c r="X232" s="25"/>
-      <c r="Y232" s="25"/>
-      <c r="Z232" s="25"/>
-      <c r="AA232" s="25"/>
-      <c r="AB232" s="25"/>
-      <c r="AC232" s="25"/>
-      <c r="AD232" s="25"/>
-      <c r="AE232" s="25"/>
-      <c r="BN232" s="28"/>
+      <c r="W232" s="16"/>
+      <c r="X232" s="16"/>
+      <c r="Y232" s="16"/>
+      <c r="Z232" s="16"/>
+      <c r="AA232" s="16"/>
+      <c r="AB232" s="16"/>
+      <c r="AC232" s="16"/>
+      <c r="AD232" s="16"/>
+      <c r="AE232" s="16"/>
+      <c r="BN232" s="19"/>
     </row>
     <row r="233" spans="23:66" x14ac:dyDescent="0.25">
-      <c r="W233" s="25"/>
-      <c r="X233" s="25"/>
-      <c r="Y233" s="25"/>
-      <c r="Z233" s="25"/>
-      <c r="AA233" s="25"/>
-      <c r="AB233" s="25"/>
-      <c r="AC233" s="25"/>
-      <c r="AD233" s="25"/>
-      <c r="AE233" s="25"/>
-      <c r="BN233" s="28"/>
+      <c r="W233" s="16"/>
+      <c r="X233" s="16"/>
+      <c r="Y233" s="16"/>
+      <c r="Z233" s="16"/>
+      <c r="AA233" s="16"/>
+      <c r="AB233" s="16"/>
+      <c r="AC233" s="16"/>
+      <c r="AD233" s="16"/>
+      <c r="AE233" s="16"/>
+      <c r="BN233" s="19"/>
     </row>
     <row r="234" spans="23:66" x14ac:dyDescent="0.25">
-      <c r="BN234" s="28"/>
+      <c r="BN234" s="19"/>
     </row>
     <row r="235" spans="23:66" x14ac:dyDescent="0.25">
-      <c r="BN235" s="28"/>
+      <c r="BN235" s="19"/>
     </row>
     <row r="236" spans="23:66" x14ac:dyDescent="0.25">
-      <c r="BN236" s="28"/>
+      <c r="BN236" s="19"/>
     </row>
     <row r="237" spans="23:66" x14ac:dyDescent="0.25">
-      <c r="BN237" s="28"/>
+      <c r="BN237" s="19"/>
     </row>
     <row r="238" spans="23:66" x14ac:dyDescent="0.25">
-      <c r="BN238" s="28"/>
+      <c r="BN238" s="19"/>
     </row>
     <row r="239" spans="23:66" x14ac:dyDescent="0.25">
-      <c r="BN239" s="28"/>
+      <c r="BN239" s="19"/>
     </row>
     <row r="240" spans="23:66" x14ac:dyDescent="0.25">
-      <c r="BN240" s="28"/>
+      <c r="BN240" s="19"/>
     </row>
     <row r="241" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN241" s="28"/>
+      <c r="BN241" s="19"/>
     </row>
     <row r="242" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN242" s="28"/>
+      <c r="BN242" s="19"/>
     </row>
     <row r="243" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN243" s="28"/>
+      <c r="BN243" s="19"/>
     </row>
     <row r="244" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN244" s="28"/>
+      <c r="BN244" s="19"/>
     </row>
     <row r="245" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN245" s="28"/>
+      <c r="BN245" s="19"/>
     </row>
     <row r="246" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN246" s="28"/>
+      <c r="BN246" s="19"/>
     </row>
     <row r="247" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN247" s="28"/>
+      <c r="BN247" s="19"/>
     </row>
     <row r="248" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN248" s="28"/>
+      <c r="BN248" s="19"/>
     </row>
     <row r="249" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN249" s="28"/>
+      <c r="BN249" s="19"/>
     </row>
     <row r="250" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN250" s="28"/>
+      <c r="BN250" s="19"/>
     </row>
     <row r="251" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN251" s="28"/>
+      <c r="BN251" s="19"/>
     </row>
     <row r="252" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN252" s="28"/>
+      <c r="BN252" s="19"/>
     </row>
     <row r="253" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN253" s="28"/>
+      <c r="BN253" s="19"/>
     </row>
     <row r="254" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN254" s="28"/>
+      <c r="BN254" s="19"/>
     </row>
     <row r="255" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN255" s="28"/>
+      <c r="BN255" s="19"/>
     </row>
     <row r="256" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN256" s="28"/>
+      <c r="BN256" s="19"/>
     </row>
     <row r="257" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN257" s="28"/>
+      <c r="BN257" s="19"/>
     </row>
     <row r="258" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN258" s="28"/>
+      <c r="BN258" s="19"/>
     </row>
     <row r="259" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN259" s="28"/>
+      <c r="BN259" s="19"/>
     </row>
     <row r="260" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN260" s="28"/>
+      <c r="BN260" s="19"/>
     </row>
     <row r="261" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN261" s="28"/>
+      <c r="BN261" s="19"/>
     </row>
     <row r="262" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN262" s="28"/>
+      <c r="BN262" s="19"/>
     </row>
     <row r="263" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN263" s="28"/>
+      <c r="BN263" s="19"/>
     </row>
     <row r="264" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN264" s="28"/>
+      <c r="BN264" s="19"/>
     </row>
     <row r="265" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN265" s="28"/>
+      <c r="BN265" s="19"/>
     </row>
     <row r="266" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN266" s="28"/>
+      <c r="BN266" s="19"/>
     </row>
     <row r="267" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN267" s="28"/>
+      <c r="BN267" s="19"/>
     </row>
     <row r="268" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN268" s="28"/>
+      <c r="BN268" s="19"/>
     </row>
     <row r="269" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN269" s="28"/>
+      <c r="BN269" s="19"/>
     </row>
     <row r="270" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN270" s="28"/>
+      <c r="BN270" s="19"/>
     </row>
     <row r="271" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN271" s="28"/>
+      <c r="BN271" s="19"/>
     </row>
     <row r="272" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN272" s="28"/>
+      <c r="BN272" s="19"/>
     </row>
     <row r="273" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN273" s="28"/>
+      <c r="BN273" s="19"/>
     </row>
     <row r="274" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN274" s="28"/>
+      <c r="BN274" s="19"/>
     </row>
     <row r="275" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN275" s="28"/>
+      <c r="BN275" s="19"/>
     </row>
     <row r="276" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN276" s="28"/>
+      <c r="BN276" s="19"/>
     </row>
     <row r="277" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN277" s="28"/>
+      <c r="BN277" s="19"/>
     </row>
     <row r="278" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN278" s="28"/>
+      <c r="BN278" s="19"/>
     </row>
     <row r="279" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN279" s="28"/>
+      <c r="BN279" s="19"/>
     </row>
     <row r="280" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN280" s="28"/>
+      <c r="BN280" s="19"/>
     </row>
     <row r="281" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN281" s="28"/>
+      <c r="BN281" s="19"/>
     </row>
     <row r="282" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN282" s="28"/>
+      <c r="BN282" s="19"/>
     </row>
     <row r="283" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN283" s="28"/>
+      <c r="BN283" s="19"/>
     </row>
     <row r="284" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN284" s="28"/>
+      <c r="BN284" s="19"/>
     </row>
     <row r="285" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN285" s="28"/>
+      <c r="BN285" s="19"/>
     </row>
     <row r="286" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN286" s="28"/>
+      <c r="BN286" s="19"/>
     </row>
     <row r="287" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN287" s="28"/>
+      <c r="BN287" s="19"/>
     </row>
     <row r="288" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN288" s="28"/>
+      <c r="BN288" s="19"/>
     </row>
     <row r="289" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN289" s="28"/>
+      <c r="BN289" s="19"/>
     </row>
     <row r="290" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN290" s="28"/>
+      <c r="BN290" s="19"/>
     </row>
     <row r="291" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN291" s="28"/>
+      <c r="BN291" s="19"/>
     </row>
     <row r="292" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN292" s="28"/>
+      <c r="BN292" s="19"/>
     </row>
     <row r="293" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN293" s="28"/>
+      <c r="BN293" s="19"/>
     </row>
     <row r="294" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN294" s="28"/>
+      <c r="BN294" s="19"/>
     </row>
     <row r="295" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN295" s="28"/>
+      <c r="BN295" s="19"/>
     </row>
     <row r="296" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN296" s="28"/>
+      <c r="BN296" s="19"/>
     </row>
     <row r="297" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN297" s="28"/>
+      <c r="BN297" s="19"/>
     </row>
     <row r="298" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN298" s="28"/>
+      <c r="BN298" s="19"/>
     </row>
     <row r="299" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN299" s="28"/>
+      <c r="BN299" s="19"/>
     </row>
     <row r="300" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN300" s="28"/>
+      <c r="BN300" s="19"/>
     </row>
     <row r="301" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN301" s="28"/>
+      <c r="BN301" s="19"/>
     </row>
     <row r="302" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN302" s="28"/>
+      <c r="BN302" s="19"/>
     </row>
     <row r="303" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN303" s="28"/>
+      <c r="BN303" s="19"/>
     </row>
     <row r="304" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN304" s="28"/>
+      <c r="BN304" s="19"/>
     </row>
     <row r="305" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN305" s="28"/>
+      <c r="BN305" s="19"/>
     </row>
     <row r="306" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN306" s="28"/>
+      <c r="BN306" s="19"/>
     </row>
     <row r="307" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN307" s="28"/>
+      <c r="BN307" s="19"/>
     </row>
     <row r="308" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN308" s="28"/>
+      <c r="BN308" s="19"/>
     </row>
     <row r="309" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN309" s="28"/>
+      <c r="BN309" s="19"/>
     </row>
     <row r="310" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN310" s="28"/>
+      <c r="BN310" s="19"/>
     </row>
     <row r="311" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN311" s="28"/>
+      <c r="BN311" s="19"/>
     </row>
     <row r="312" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN312" s="28"/>
+      <c r="BN312" s="19"/>
     </row>
     <row r="313" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN313" s="28"/>
+      <c r="BN313" s="19"/>
     </row>
     <row r="314" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN314" s="28"/>
+      <c r="BN314" s="19"/>
     </row>
     <row r="315" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN315" s="28"/>
+      <c r="BN315" s="19"/>
     </row>
     <row r="316" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN316" s="28"/>
+      <c r="BN316" s="19"/>
     </row>
     <row r="317" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN317" s="28"/>
+      <c r="BN317" s="19"/>
     </row>
     <row r="318" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN318" s="28"/>
+      <c r="BN318" s="19"/>
     </row>
     <row r="319" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN319" s="28"/>
+      <c r="BN319" s="19"/>
     </row>
     <row r="320" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN320" s="28"/>
+      <c r="BN320" s="19"/>
     </row>
     <row r="321" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN321" s="28"/>
+      <c r="BN321" s="19"/>
     </row>
     <row r="322" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN322" s="28"/>
+      <c r="BN322" s="19"/>
     </row>
     <row r="323" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN323" s="28"/>
+      <c r="BN323" s="19"/>
     </row>
     <row r="324" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN324" s="28"/>
+      <c r="BN324" s="19"/>
     </row>
     <row r="325" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN325" s="28"/>
+      <c r="BN325" s="19"/>
     </row>
     <row r="326" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN326" s="28"/>
+      <c r="BN326" s="19"/>
     </row>
     <row r="327" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN327" s="28"/>
+      <c r="BN327" s="19"/>
     </row>
     <row r="328" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN328" s="28"/>
+      <c r="BN328" s="19"/>
     </row>
     <row r="329" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN329" s="28"/>
+      <c r="BN329" s="19"/>
     </row>
     <row r="330" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN330" s="28"/>
+      <c r="BN330" s="19"/>
     </row>
     <row r="331" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN331" s="28"/>
+      <c r="BN331" s="19"/>
     </row>
     <row r="332" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN332" s="28"/>
+      <c r="BN332" s="19"/>
     </row>
     <row r="333" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN333" s="28"/>
+      <c r="BN333" s="19"/>
     </row>
     <row r="334" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN334" s="28"/>
+      <c r="BN334" s="19"/>
     </row>
     <row r="335" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN335" s="28"/>
+      <c r="BN335" s="19"/>
     </row>
     <row r="336" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN336" s="28"/>
+      <c r="BN336" s="19"/>
     </row>
     <row r="337" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN337" s="28"/>
+      <c r="BN337" s="19"/>
     </row>
     <row r="338" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN338" s="28"/>
+      <c r="BN338" s="19"/>
     </row>
     <row r="339" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN339" s="28"/>
+      <c r="BN339" s="19"/>
     </row>
     <row r="340" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN340" s="28"/>
+      <c r="BN340" s="19"/>
     </row>
     <row r="341" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN341" s="28"/>
+      <c r="BN341" s="19"/>
     </row>
     <row r="342" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN342" s="28"/>
+      <c r="BN342" s="19"/>
     </row>
     <row r="343" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN343" s="28"/>
+      <c r="BN343" s="19"/>
     </row>
     <row r="344" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN344" s="28"/>
+      <c r="BN344" s="19"/>
     </row>
     <row r="345" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN345" s="28"/>
+      <c r="BN345" s="19"/>
     </row>
     <row r="346" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN346" s="28"/>
+      <c r="BN346" s="19"/>
     </row>
     <row r="347" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN347" s="28"/>
+      <c r="BN347" s="19"/>
     </row>
     <row r="348" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN348" s="28"/>
+      <c r="BN348" s="19"/>
     </row>
     <row r="349" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN349" s="28"/>
+      <c r="BN349" s="19"/>
     </row>
     <row r="350" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN350" s="28"/>
+      <c r="BN350" s="19"/>
     </row>
     <row r="351" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN351" s="28"/>
+      <c r="BN351" s="19"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="D116:G116"/>
-    <mergeCell ref="W29:AD30"/>
-    <mergeCell ref="W32:AD33"/>
-    <mergeCell ref="W35:AD36"/>
-    <mergeCell ref="W38:AD39"/>
-    <mergeCell ref="D50:G50"/>
-    <mergeCell ref="D62:G62"/>
+  <mergeCells count="17">
+    <mergeCell ref="M59:V60"/>
+    <mergeCell ref="M62:V63"/>
+    <mergeCell ref="AI13:AL15"/>
+    <mergeCell ref="W15:AA15"/>
+    <mergeCell ref="AJ17:AX21"/>
+    <mergeCell ref="M55:V57"/>
     <mergeCell ref="E14:I15"/>
     <mergeCell ref="W17:AD18"/>
     <mergeCell ref="W20:AD21"/>
     <mergeCell ref="W23:AD24"/>
     <mergeCell ref="W26:AD27"/>
+    <mergeCell ref="D116:G116"/>
+    <mergeCell ref="W29:AD30"/>
+    <mergeCell ref="W32:AD33"/>
+    <mergeCell ref="W35:AD36"/>
+    <mergeCell ref="D50:G50"/>
+    <mergeCell ref="D72:G72"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="F55" location="'AUTOMATION CONTROL'!D62" display="1. Automate Webpages " xr:uid="{D0968135-C58E-46C6-9C10-12729229DAC1}"/>

--- a/DOCUMENTATION/WEB_SCRAPE_AUTOMATIOn.xlsx
+++ b/DOCUMENTATION/WEB_SCRAPE_AUTOMATIOn.xlsx
@@ -5,16 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UNIFIED_SYSTEM_AUTOMATION\DOCUMENTATION\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://globaldenso-my.sharepoint.com/personal/vincent_joe_narvaez_a3n_ap_denso_com/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DFB2F0C-A621-485A-AAB9-CACF82B7AC2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="406" documentId="8_{806AF5CC-A047-4755-93E4-4C776A16F281}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B521E11-D60C-4673-9B6E-19497975A241}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{AF954AEF-E990-4149-A50E-313C2C1CB0ED}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="AUTOMATION CONTROL" sheetId="2" r:id="rId2"/>
+    <sheet name="CREATE CONFIGURATION" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="73">
   <si>
     <t xml:space="preserve">WEB_SCRAPE Automation User's Manual </t>
   </si>
@@ -124,28 +125,13 @@
     <t>1.Automate Webpages</t>
   </si>
   <si>
-    <t>1.To begin in automating webpages, click 'START AUTOMATION'.</t>
-  </si>
-  <si>
     <t>`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. The folder validated first if there are existing MHTML files, then skipped it the existing one and proceed on the next categories not yet executed. </t>
-  </si>
-  <si>
-    <t>3. When a pop-up notification showed in your screen, you need to go on the browser itself to manually solve it.</t>
   </si>
   <si>
     <t>1.Scrape MHTML Files</t>
   </si>
   <si>
-    <t>4. When finished a dialog appeared containing a no. of successful and failed during automation along with the location of folder that have MHTML and excel files.</t>
-  </si>
-  <si>
     <t>Overview</t>
-  </si>
-  <si>
-    <t>The Automation Control tab is the main operational screen. It automatically visits multiple app store intelligence platforms across 22 countries, captures each page as an MHTML snapshot, and extracts the top app rankings into an Excel file — all without manual intervention.</t>
   </si>
   <si>
     <t>What it does:</t>
@@ -220,10 +206,6 @@
     </r>
   </si>
   <si>
-    <t>📝 Make sure Google Chrome is installed.
-ChromeDriver is downloaded automatically — no manual installation needed.</t>
-  </si>
-  <si>
     <t>START AUTOMATION: Launches the full automation loop in a background thread. The GUI stays responsive while it runs.</t>
   </si>
   <si>
@@ -247,12 +229,302 @@
   <si>
     <t>CLEAR FILTER: Removes all filters and restores the full log view.</t>
   </si>
+  <si>
+    <t>📝 Make sure Google Chrome is installed.</t>
+  </si>
+  <si>
+    <t>Note: Buttons will disables right after clicking , the status will change to green showing its running.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> switch to the Chrome window and solve the verification manually.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> failed captures, and the output folder location.</t>
+  </si>
+  <si>
+    <t>you will find the dated sub-folder with all MHTML files and All_platforms.xlsx.</t>
+  </si>
+  <si>
+    <t>It automatically visits multiple app store intelligence platforms across 22 countries, captures each page as an MHTML snapshot, and extracts the top app rankings into an Excel file — all without manual intervention.</t>
+  </si>
+  <si>
+    <t>The Scrape Files feature allows you to extract app ranking data from a folder of existing MHTML files without launching a browser or re-running the full automation. It reads each saved page file, pulls out the app rankings, and writes the results into an Excel workbook — all without visiting any website</t>
+  </si>
+  <si>
+    <t>What It does:</t>
+  </si>
+  <si>
+    <t>Reads each .mhtml file in the selected folder one by one — no browser is opened.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Automatically detects the platform, country, and category from the filename.</t>
+    </r>
+  </si>
+  <si>
+    <t>Parses the saved HTML inside the MHTML file.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Extracts the app rankings (rank, publisher, app name, store link, app icon) using the configurations in config.json.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Appends all extracted rows to the correct category sheet in the output Excel file.</t>
+    </r>
+  </si>
+  <si>
+    <t>📝  NOTE
+Make sure your MHTML files follow the correct naming convention.
+The application detects platform, country, and category from the filename automatically.
+Files with unrecognized names will be skipped and logged as failed.
+Expected format:
+{country_number}{sequence}_{country_code}_{platform}_{app_platform}_{category}_{date}.mhtml
+Example: 0101_US_AppFollow_android_Music_and_Audio_20260322.mhtml</t>
+  </si>
+  <si>
+    <t>✅  TIP
+The MHTML files from the automation session are already named correctly.
+If you are using files from a previous run, just point Scrape Files
+to the AUTOMATION_YYYY-MM-DD folder inside AUTOMATION FILE.</t>
+  </si>
+  <si>
+    <t>⚠️  WARNING
+Do not rename or move MHTML files before running Scrape Files.
+The platform, country, and category detection depends entirely on the filename.
+Renamed files will be skipped or assigned to the wrong category.</t>
+  </si>
+  <si>
+    <r>
+      <t>3.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Monitor the Log Output </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>The right panel shows live activity. Green = successful. Orange = errors or skipped pages.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">2. To start click </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ▶ START AUTOMATION </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>the button and Chrome opens automatically.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Open the application </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>click the WEB_SCRAPE_AUTOMATION.exe</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>4.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Handle CAPTCHA if prompted </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>If a pop-up notification appears,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>5.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Wait for completion </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>when finished, a dialog appears showing successful captures,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Retrieve your files</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Go to the Output Directory shown in the left panel. Inside AUTOMATION FILE/ </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>What happens in the background for each page:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+1. Checks if already captured — if yes, skips it
+2. Opens the target URL in Chrome
+3. Waits for the page to fully load
+4. Checks if the page is valid (not 404, blocked, or empty)
+5. Captures the full page as an MHTML snapshot
+6. Reads the MHTML and extracts app ranking data into Excel
+7. Moves on to the next category, country, or platform</t>
+    </r>
+  </si>
+  <si>
+    <t>3. Create and Update  Configuration</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -343,9 +615,49 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="14"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -542,13 +854,13 @@
     </border>
     <border>
       <left style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right/>
-      <top style="medium">
+      <top/>
+      <bottom style="medium">
         <color indexed="64"/>
-      </top>
-      <bottom/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -556,7 +868,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -596,6 +908,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -622,15 +935,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="6"/>
     </xf>
@@ -643,17 +947,8 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -665,22 +960,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -689,6 +975,60 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2704,8 +3044,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="2291711" y="3214331"/>
-          <a:ext cx="8831120" cy="5997740"/>
+          <a:off x="2302102" y="3172767"/>
+          <a:ext cx="8883074" cy="6150140"/>
           <a:chOff x="2469366" y="5346324"/>
           <a:chExt cx="8923895" cy="5997740"/>
         </a:xfrm>
@@ -3830,10 +4170,10 @@
   </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>600076</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>327773</xdr:colOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>28015</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="5355262" cy="3836355"/>
     <xdr:pic>
@@ -3863,7 +4203,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7313814" y="15417646"/>
+          <a:off x="7642973" y="18277915"/>
           <a:ext cx="5355262" cy="3836355"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3875,16 +4215,16 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>145677</xdr:colOff>
-      <xdr:row>86</xdr:row>
-      <xdr:rowOff>11206</xdr:rowOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>128359</xdr:colOff>
+      <xdr:row>101</xdr:row>
+      <xdr:rowOff>132433</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>518967</xdr:colOff>
-      <xdr:row>88</xdr:row>
-      <xdr:rowOff>114838</xdr:rowOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>501649</xdr:colOff>
+      <xdr:row>104</xdr:row>
+      <xdr:rowOff>45565</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3899,8 +4239,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6241677" y="10107706"/>
-          <a:ext cx="982890" cy="484632"/>
+          <a:off x="13463359" y="19979069"/>
+          <a:ext cx="979426" cy="484632"/>
         </a:xfrm>
         <a:prstGeom prst="rightArrow">
           <a:avLst/>
@@ -3938,16 +4278,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>34217</xdr:colOff>
-      <xdr:row>78</xdr:row>
-      <xdr:rowOff>80945</xdr:rowOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>553762</xdr:colOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>98263</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>293760</xdr:colOff>
-      <xdr:row>98</xdr:row>
-      <xdr:rowOff>175287</xdr:rowOff>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>207169</xdr:colOff>
+      <xdr:row>114</xdr:row>
+      <xdr:rowOff>2105</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3970,8 +4310,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9793164" y="13374169"/>
-          <a:ext cx="7509006" cy="4081981"/>
+          <a:off x="14494898" y="18420899"/>
+          <a:ext cx="7533180" cy="3904342"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3982,16 +4322,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>32</xdr:col>
-      <xdr:colOff>492638</xdr:colOff>
-      <xdr:row>78</xdr:row>
-      <xdr:rowOff>48727</xdr:rowOff>
+      <xdr:col>41</xdr:col>
+      <xdr:colOff>315127</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>101548</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>38</xdr:col>
-      <xdr:colOff>544894</xdr:colOff>
-      <xdr:row>87</xdr:row>
-      <xdr:rowOff>1753</xdr:rowOff>
+      <xdr:col>47</xdr:col>
+      <xdr:colOff>367383</xdr:colOff>
+      <xdr:row>100</xdr:row>
+      <xdr:rowOff>6952</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4015,8 +4355,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8962165" y="18635349"/>
-          <a:ext cx="3682054" cy="1682435"/>
+          <a:off x="25166718" y="18043184"/>
+          <a:ext cx="3689074" cy="1667526"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4027,16 +4367,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>35</xdr:col>
-      <xdr:colOff>241964</xdr:colOff>
-      <xdr:row>89</xdr:row>
-      <xdr:rowOff>47369</xdr:rowOff>
+      <xdr:col>40</xdr:col>
+      <xdr:colOff>394364</xdr:colOff>
+      <xdr:row>100</xdr:row>
+      <xdr:rowOff>150412</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>42</xdr:col>
-      <xdr:colOff>484500</xdr:colOff>
-      <xdr:row>102</xdr:row>
-      <xdr:rowOff>5344</xdr:rowOff>
+      <xdr:col>48</xdr:col>
+      <xdr:colOff>30765</xdr:colOff>
+      <xdr:row>113</xdr:row>
+      <xdr:rowOff>108387</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4059,8 +4399,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="21500660" y="15480630"/>
-          <a:ext cx="4494275" cy="2455700"/>
+          <a:off x="24639819" y="19806548"/>
+          <a:ext cx="4485491" cy="2434475"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4071,16 +4411,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>331304</xdr:colOff>
-      <xdr:row>86</xdr:row>
-      <xdr:rowOff>96631</xdr:rowOff>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>435213</xdr:colOff>
+      <xdr:row>101</xdr:row>
+      <xdr:rowOff>131267</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>31</xdr:col>
-      <xdr:colOff>97204</xdr:colOff>
-      <xdr:row>89</xdr:row>
-      <xdr:rowOff>7002</xdr:rowOff>
+      <xdr:col>38</xdr:col>
+      <xdr:colOff>201113</xdr:colOff>
+      <xdr:row>104</xdr:row>
+      <xdr:rowOff>41638</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4095,8 +4435,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="17945652" y="14950109"/>
-          <a:ext cx="980682" cy="490154"/>
+          <a:off x="22256122" y="19977903"/>
+          <a:ext cx="978173" cy="481871"/>
         </a:xfrm>
         <a:prstGeom prst="rightArrow">
           <a:avLst/>
@@ -4134,16 +4474,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>45</xdr:col>
-      <xdr:colOff>241904</xdr:colOff>
-      <xdr:row>87</xdr:row>
-      <xdr:rowOff>166310</xdr:rowOff>
+      <xdr:col>48</xdr:col>
+      <xdr:colOff>359058</xdr:colOff>
+      <xdr:row>101</xdr:row>
+      <xdr:rowOff>65457</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>47</xdr:col>
-      <xdr:colOff>7804</xdr:colOff>
-      <xdr:row>90</xdr:row>
-      <xdr:rowOff>76680</xdr:rowOff>
+      <xdr:col>50</xdr:col>
+      <xdr:colOff>118771</xdr:colOff>
+      <xdr:row>103</xdr:row>
+      <xdr:rowOff>166327</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4158,8 +4498,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="27456190" y="15481905"/>
-          <a:ext cx="975424" cy="500013"/>
+          <a:off x="29404705" y="19821428"/>
+          <a:ext cx="969948" cy="481870"/>
         </a:xfrm>
         <a:prstGeom prst="rightArrow">
           <a:avLst/>
@@ -4197,16 +4537,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>47</xdr:col>
-      <xdr:colOff>78992</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>6431</xdr:rowOff>
+      <xdr:col>50</xdr:col>
+      <xdr:colOff>181446</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>108957</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>57</xdr:col>
-      <xdr:colOff>419017</xdr:colOff>
-      <xdr:row>104</xdr:row>
-      <xdr:rowOff>480</xdr:rowOff>
+      <xdr:col>60</xdr:col>
+      <xdr:colOff>514266</xdr:colOff>
+      <xdr:row>114</xdr:row>
+      <xdr:rowOff>954</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4229,14 +4569,999 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="28680450" y="13606014"/>
-          <a:ext cx="6425442" cy="4838331"/>
+          <a:off x="30437328" y="17578928"/>
+          <a:ext cx="6383997" cy="4756549"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>458561</xdr:colOff>
+      <xdr:row>102</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>219529</xdr:colOff>
+      <xdr:row>105</xdr:row>
+      <xdr:rowOff>36957</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="32" name="Arrow: Right 31">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{65E64FC8-A57E-4DDF-BDD1-EB200649E9BE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6581775" y="20153539"/>
+          <a:ext cx="985611" cy="484632"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100" kern="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>560974</xdr:colOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>82284</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>603836</xdr:colOff>
+      <xdr:row>108</xdr:row>
+      <xdr:rowOff>77920</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="46" name="Group 45">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B8E5F571-5830-9ECE-B4AA-C079FA41FBFF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="2389774" y="19284684"/>
+          <a:ext cx="3700462" cy="2853136"/>
+          <a:chOff x="2449966" y="18756086"/>
+          <a:chExt cx="3716791" cy="2853136"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="31" name="Picture 30">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2D4B5788-C714-C032-EA71-E3416E1454A9}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill rotWithShape="1">
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
+          <a:srcRect t="166" r="57686" b="1"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="2449966" y="18756086"/>
+            <a:ext cx="3716791" cy="2853136"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="33" name="Rectangle 32">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9ABCDFE4-F272-67EB-62C7-AB031464D67B}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="3870937" y="21241341"/>
+            <a:ext cx="2068877" cy="273326"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="28575">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr lang="en-US" sz="1100" kern="1200"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>61</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>102</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>62</xdr:col>
+      <xdr:colOff>562534</xdr:colOff>
+      <xdr:row>104</xdr:row>
+      <xdr:rowOff>100870</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="34" name="Arrow: Right 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{41543A1A-6CD2-49A1-9867-69DA0E0CFCC7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="37542107" y="20029714"/>
+          <a:ext cx="984356" cy="481870"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100" kern="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>63</xdr:col>
+      <xdr:colOff>160564</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>103414</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>75</xdr:col>
+      <xdr:colOff>582386</xdr:colOff>
+      <xdr:row>102</xdr:row>
+      <xdr:rowOff>69101</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="39" name="Picture 38">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1FE55DF7-CA77-1B5A-CFBE-980F58907503}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="38565364" y="17667514"/>
+          <a:ext cx="7737022" cy="2299309"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>353213</xdr:colOff>
+      <xdr:row>148</xdr:row>
+      <xdr:rowOff>101541</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>70568</xdr:colOff>
+      <xdr:row>174</xdr:row>
+      <xdr:rowOff>24245</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="40" name="Picture 39">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FFB3ACE4-E696-0A3B-8047-5B40C3FB72E8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2791613" y="29171841"/>
+          <a:ext cx="7032555" cy="4875704"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>72942</xdr:colOff>
+      <xdr:row>151</xdr:row>
+      <xdr:rowOff>97466</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>415637</xdr:colOff>
+      <xdr:row>170</xdr:row>
+      <xdr:rowOff>88445</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="43" name="Picture 42">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{21697CF4-E19A-C81B-3856-17A218BFAD72}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17"/>
+        <a:srcRect r="38860"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11655342" y="29739266"/>
+          <a:ext cx="6438695" cy="3610479"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>481198</xdr:colOff>
+      <xdr:row>158</xdr:row>
+      <xdr:rowOff>150916</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>247333</xdr:colOff>
+      <xdr:row>161</xdr:row>
+      <xdr:rowOff>64048</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="44" name="Arrow: Right 43">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{70D817A2-D49B-9CB5-4822-04DE02561F58}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10278341" y="31311273"/>
+          <a:ext cx="990778" cy="484632"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100" kern="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>474210</xdr:colOff>
+      <xdr:row>151</xdr:row>
+      <xdr:rowOff>150360</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>44</xdr:col>
+      <xdr:colOff>93209</xdr:colOff>
+      <xdr:row>172</xdr:row>
+      <xdr:rowOff>18688</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="53" name="Picture 52">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CB7D5AE9-9144-680C-6C21-2818DB1E19AF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="20068496" y="29977217"/>
+          <a:ext cx="6966856" cy="3868828"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>446006</xdr:colOff>
+      <xdr:row>148</xdr:row>
+      <xdr:rowOff>164894</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>60</xdr:col>
+      <xdr:colOff>592066</xdr:colOff>
+      <xdr:row>174</xdr:row>
+      <xdr:rowOff>96548</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="54" name="Picture 53">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7D1FDA52-8E9D-BC9C-3C85-468FA46B0C25}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId19"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="28328279" y="29484576"/>
+          <a:ext cx="8631969" cy="4884654"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>63</xdr:col>
+      <xdr:colOff>61356</xdr:colOff>
+      <xdr:row>151</xdr:row>
+      <xdr:rowOff>62903</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>70</xdr:col>
+      <xdr:colOff>531473</xdr:colOff>
+      <xdr:row>170</xdr:row>
+      <xdr:rowOff>72935</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="55" name="Picture 54">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{60EBE141-FF90-247E-F274-3B589C44BF2D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="38637606" y="29889760"/>
+          <a:ext cx="4756367" cy="3629532"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>72</xdr:col>
+      <xdr:colOff>594254</xdr:colOff>
+      <xdr:row>149</xdr:row>
+      <xdr:rowOff>160564</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>86</xdr:col>
+      <xdr:colOff>213311</xdr:colOff>
+      <xdr:row>174</xdr:row>
+      <xdr:rowOff>15688</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="57" name="Picture 56">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{95825F24-B42D-9F4E-6917-D68DB0E88ECB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId21"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="45171254" y="29521377"/>
+          <a:ext cx="8286807" cy="4617624"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>88</xdr:col>
+      <xdr:colOff>353786</xdr:colOff>
+      <xdr:row>154</xdr:row>
+      <xdr:rowOff>157843</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>101</xdr:col>
+      <xdr:colOff>166008</xdr:colOff>
+      <xdr:row>166</xdr:row>
+      <xdr:rowOff>171152</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="58" name="Picture 57">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE30FC16-098D-4AFF-B063-9DAB2B962D39}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="54238072" y="30556200"/>
+          <a:ext cx="7772400" cy="2299309"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>350960</xdr:colOff>
+      <xdr:row>159</xdr:row>
+      <xdr:rowOff>190134</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>118560</xdr:colOff>
+      <xdr:row>162</xdr:row>
+      <xdr:rowOff>103266</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="59" name="Arrow: Right 58">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BF630081-121F-472F-8D18-05E5B277145F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18594998" y="31520057"/>
+          <a:ext cx="983870" cy="484632"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100" kern="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>44</xdr:col>
+      <xdr:colOff>341634</xdr:colOff>
+      <xdr:row>159</xdr:row>
+      <xdr:rowOff>156830</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>109234</xdr:colOff>
+      <xdr:row>162</xdr:row>
+      <xdr:rowOff>69962</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="60" name="Arrow: Right 59">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ADF96A81-207E-44BE-8435-62390239154D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="27011634" y="31572012"/>
+          <a:ext cx="979873" cy="484632"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100" kern="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>61</xdr:col>
+      <xdr:colOff>136072</xdr:colOff>
+      <xdr:row>159</xdr:row>
+      <xdr:rowOff>163285</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>62</xdr:col>
+      <xdr:colOff>515993</xdr:colOff>
+      <xdr:row>162</xdr:row>
+      <xdr:rowOff>76417</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="61" name="Arrow: Right 60">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1BF10585-92B3-471B-A373-DFEB6F54FF13}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="37487679" y="31514142"/>
+          <a:ext cx="992243" cy="484632"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100" kern="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>71</xdr:col>
+      <xdr:colOff>149679</xdr:colOff>
+      <xdr:row>159</xdr:row>
+      <xdr:rowOff>68036</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>72</xdr:col>
+      <xdr:colOff>529600</xdr:colOff>
+      <xdr:row>161</xdr:row>
+      <xdr:rowOff>171668</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="62" name="Arrow: Right 61">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AB126009-5667-4986-B76D-70DA3B8B96FC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="43624500" y="31418893"/>
+          <a:ext cx="992243" cy="484632"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100" kern="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>86</xdr:col>
+      <xdr:colOff>449035</xdr:colOff>
+      <xdr:row>160</xdr:row>
+      <xdr:rowOff>149678</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>88</xdr:col>
+      <xdr:colOff>213914</xdr:colOff>
+      <xdr:row>163</xdr:row>
+      <xdr:rowOff>62810</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="63" name="Arrow: Right 62">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B2014A9A-802B-4347-99A9-66C5BBA7C91B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="53108678" y="31691035"/>
+          <a:ext cx="989522" cy="484632"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100" kern="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -4563,49 +5888,49 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
     </row>
     <row r="2" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A2" s="37"/>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
+      <c r="A2" s="38"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
     </row>
     <row r="3" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A3" s="38" t="s">
+      <c r="A3" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
     </row>
     <row r="5" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A5" s="35" t="s">
+      <c r="A5" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="35"/>
-      <c r="C5" s="35"/>
-      <c r="D5" s="35"/>
+      <c r="B5" s="36"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
     </row>
     <row r="7" spans="1:42" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
@@ -4648,12 +5973,12 @@
       </c>
     </row>
     <row r="16" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A16" s="34" t="s">
+      <c r="A16" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="B16" s="34"/>
-      <c r="C16" s="34"/>
-      <c r="D16" s="34"/>
+      <c r="B16" s="35"/>
+      <c r="C16" s="35"/>
+      <c r="D16" s="35"/>
       <c r="AN16" t="s">
         <v>12</v>
       </c>
@@ -4690,12 +6015,12 @@
       </c>
     </row>
     <row r="41" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A41" s="33" t="s">
+      <c r="A41" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="B41" s="33"/>
-      <c r="C41" s="33"/>
-      <c r="D41" s="33"/>
+      <c r="B41" s="34"/>
+      <c r="C41" s="34"/>
+      <c r="D41" s="34"/>
     </row>
     <row r="45" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
@@ -4740,7 +6065,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40098BD2-3A0C-4DBD-8904-60C96FC01DEF}">
-  <dimension ref="C10:DJ351"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="C10:HJ446"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="10" spans="4:114" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -4781,30 +6109,30 @@
       <c r="BL10" s="21"/>
       <c r="BM10" s="21"/>
       <c r="BN10" s="21"/>
-      <c r="BO10" s="16"/>
-      <c r="BP10" s="16"/>
-      <c r="BQ10" s="16"/>
-      <c r="BR10" s="16"/>
-      <c r="BS10" s="16"/>
-      <c r="BT10" s="16"/>
-      <c r="BU10" s="16"/>
-      <c r="BV10" s="16"/>
-      <c r="BW10" s="16"/>
-      <c r="BX10" s="16"/>
-      <c r="BY10" s="16"/>
-      <c r="BZ10" s="16"/>
-      <c r="CA10" s="16"/>
-      <c r="CB10" s="16"/>
-      <c r="CC10" s="16"/>
-      <c r="CD10" s="16"/>
-      <c r="CE10" s="16"/>
-      <c r="CF10" s="16"/>
-      <c r="CG10" s="16"/>
-      <c r="CH10" s="16"/>
-      <c r="CI10" s="16"/>
-      <c r="CJ10" s="16"/>
-      <c r="CK10" s="16"/>
-      <c r="CL10" s="16"/>
+      <c r="BO10" s="21"/>
+      <c r="BP10" s="21"/>
+      <c r="BQ10" s="21"/>
+      <c r="BR10" s="21"/>
+      <c r="BS10" s="21"/>
+      <c r="BT10" s="21"/>
+      <c r="BU10" s="21"/>
+      <c r="BV10" s="21"/>
+      <c r="BW10" s="21"/>
+      <c r="BX10" s="21"/>
+      <c r="BY10" s="21"/>
+      <c r="BZ10" s="21"/>
+      <c r="CA10" s="21"/>
+      <c r="CB10" s="21"/>
+      <c r="CC10" s="21"/>
+      <c r="CD10" s="21"/>
+      <c r="CE10" s="21"/>
+      <c r="CF10" s="21"/>
+      <c r="CG10" s="21"/>
+      <c r="CH10" s="21"/>
+      <c r="CI10" s="21"/>
+      <c r="CJ10" s="21"/>
+      <c r="CK10" s="21"/>
+      <c r="CL10" s="22"/>
       <c r="CM10" s="16"/>
       <c r="CN10" s="16"/>
       <c r="CO10" s="16"/>
@@ -4819,7 +6147,7 @@
       <c r="CX10" s="16"/>
       <c r="CY10" s="16"/>
       <c r="CZ10" s="16"/>
-      <c r="DA10" s="21"/>
+      <c r="DA10" s="16"/>
     </row>
     <row r="11" spans="4:114" ht="24" x14ac:dyDescent="0.25">
       <c r="D11" s="15" t="s">
@@ -4850,43 +6178,43 @@
       <c r="AA11" s="12"/>
       <c r="AB11" s="12"/>
       <c r="AC11" s="12"/>
-      <c r="AD11" s="27"/>
-      <c r="AE11" s="28"/>
-      <c r="AF11" s="29"/>
-      <c r="AG11" s="29"/>
-      <c r="AH11" s="29"/>
-      <c r="AI11" s="29"/>
-      <c r="AJ11" s="29"/>
-      <c r="AK11" s="29"/>
-      <c r="AL11" s="29"/>
-      <c r="AM11" s="29"/>
-      <c r="AN11" s="29"/>
-      <c r="AO11" s="29"/>
-      <c r="AP11" s="29"/>
-      <c r="AQ11" s="29"/>
-      <c r="AR11" s="29"/>
-      <c r="AS11" s="29"/>
-      <c r="AT11" s="29"/>
-      <c r="AU11" s="29"/>
-      <c r="AV11" s="29"/>
-      <c r="AW11" s="29"/>
-      <c r="AX11" s="29"/>
-      <c r="AY11" s="29"/>
-      <c r="AZ11" s="29"/>
-      <c r="BA11" s="29"/>
-      <c r="BB11" s="29"/>
-      <c r="BC11" s="29"/>
-      <c r="BD11" s="29"/>
-      <c r="BE11" s="29"/>
-      <c r="BF11" s="29"/>
-      <c r="BG11" s="29"/>
-      <c r="BH11" s="29"/>
-      <c r="BI11" s="29"/>
-      <c r="BJ11" s="29"/>
-      <c r="BK11" s="29"/>
-      <c r="BL11" s="29"/>
-      <c r="BM11" s="29"/>
-      <c r="BN11" s="30"/>
+      <c r="AD11" s="28"/>
+      <c r="AE11" s="29"/>
+      <c r="AF11" s="30"/>
+      <c r="AG11" s="30"/>
+      <c r="AH11" s="30"/>
+      <c r="AI11" s="30"/>
+      <c r="AJ11" s="30"/>
+      <c r="AK11" s="30"/>
+      <c r="AL11" s="30"/>
+      <c r="AM11" s="30"/>
+      <c r="AN11" s="30"/>
+      <c r="AO11" s="30"/>
+      <c r="AP11" s="30"/>
+      <c r="AQ11" s="30"/>
+      <c r="AR11" s="30"/>
+      <c r="AS11" s="30"/>
+      <c r="AT11" s="30"/>
+      <c r="AU11" s="30"/>
+      <c r="AV11" s="30"/>
+      <c r="AW11" s="30"/>
+      <c r="AX11" s="30"/>
+      <c r="AY11" s="30"/>
+      <c r="AZ11" s="30"/>
+      <c r="BA11" s="30"/>
+      <c r="BB11" s="30"/>
+      <c r="BC11" s="30"/>
+      <c r="BD11" s="30"/>
+      <c r="BE11" s="30"/>
+      <c r="BF11" s="30"/>
+      <c r="BG11" s="30"/>
+      <c r="BH11" s="30"/>
+      <c r="BI11" s="30"/>
+      <c r="BJ11" s="30"/>
+      <c r="BK11" s="30"/>
+      <c r="BL11" s="30"/>
+      <c r="BM11" s="30"/>
+      <c r="BN11" s="31"/>
       <c r="BO11" s="16"/>
       <c r="BP11" s="16"/>
       <c r="BQ11" s="16"/>
@@ -4910,7 +6238,7 @@
       <c r="CI11" s="16"/>
       <c r="CJ11" s="16"/>
       <c r="CK11" s="16"/>
-      <c r="CL11" s="16"/>
+      <c r="CL11" s="19"/>
       <c r="CM11" s="16"/>
       <c r="CN11" s="16"/>
       <c r="CO11" s="16"/>
@@ -4925,6 +6253,15 @@
       <c r="CX11" s="16"/>
       <c r="CY11" s="16"/>
       <c r="CZ11" s="16"/>
+      <c r="DA11" s="16"/>
+      <c r="DB11" s="16"/>
+      <c r="DC11" s="16"/>
+      <c r="DD11" s="16"/>
+      <c r="DE11" s="16"/>
+      <c r="DF11" s="16"/>
+      <c r="DG11" s="16"/>
+      <c r="DH11" s="16"/>
+      <c r="DI11" s="16"/>
     </row>
     <row r="12" spans="4:114" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D12" s="14"/>
@@ -4953,67 +6290,67 @@
       <c r="AA12" s="4"/>
       <c r="AB12" s="4"/>
       <c r="AC12" s="4"/>
-      <c r="AD12" s="27"/>
-      <c r="AE12" s="31"/>
-      <c r="AF12" s="31"/>
-      <c r="AG12" s="31"/>
-      <c r="AH12" s="31"/>
-      <c r="AI12" s="31"/>
-      <c r="AJ12" s="31"/>
-      <c r="AK12" s="31"/>
-      <c r="AL12" s="31"/>
-      <c r="AM12" s="31"/>
-      <c r="AN12" s="31"/>
-      <c r="AO12" s="31"/>
-      <c r="AP12" s="31"/>
-      <c r="AQ12" s="31"/>
-      <c r="AR12" s="31"/>
-      <c r="AS12" s="31"/>
-      <c r="AT12" s="31"/>
-      <c r="AU12" s="31"/>
-      <c r="AV12" s="31"/>
-      <c r="AW12" s="31"/>
-      <c r="AX12" s="31"/>
-      <c r="AY12" s="31"/>
-      <c r="AZ12" s="31"/>
-      <c r="BA12" s="31"/>
-      <c r="BB12" s="31"/>
-      <c r="BC12" s="31"/>
-      <c r="BD12" s="31"/>
-      <c r="BE12" s="31"/>
-      <c r="BF12" s="31"/>
-      <c r="BG12" s="31"/>
-      <c r="BH12" s="31"/>
-      <c r="BI12" s="31"/>
-      <c r="BJ12" s="31"/>
-      <c r="BK12" s="31"/>
-      <c r="BL12" s="31"/>
-      <c r="BM12" s="31"/>
-      <c r="BN12" s="32"/>
-      <c r="BO12" s="16"/>
-      <c r="BP12" s="16"/>
-      <c r="BQ12" s="16"/>
-      <c r="BR12" s="16"/>
-      <c r="BS12" s="16"/>
-      <c r="BT12" s="16"/>
-      <c r="BU12" s="16"/>
-      <c r="BV12" s="16"/>
-      <c r="BW12" s="16"/>
-      <c r="BX12" s="16"/>
-      <c r="BY12" s="16"/>
-      <c r="BZ12" s="16"/>
-      <c r="CA12" s="16"/>
-      <c r="CB12" s="16"/>
-      <c r="CC12" s="16"/>
-      <c r="CD12" s="16"/>
-      <c r="CE12" s="16"/>
-      <c r="CF12" s="16"/>
-      <c r="CG12" s="16"/>
-      <c r="CH12" s="16"/>
-      <c r="CI12" s="16"/>
-      <c r="CJ12" s="16"/>
-      <c r="CK12" s="16"/>
-      <c r="CL12" s="16"/>
+      <c r="AD12" s="28"/>
+      <c r="AE12" s="32"/>
+      <c r="AF12" s="32"/>
+      <c r="AG12" s="32"/>
+      <c r="AH12" s="32"/>
+      <c r="AI12" s="32"/>
+      <c r="AJ12" s="32"/>
+      <c r="AK12" s="32"/>
+      <c r="AL12" s="32"/>
+      <c r="AM12" s="32"/>
+      <c r="AN12" s="32"/>
+      <c r="AO12" s="32"/>
+      <c r="AP12" s="32"/>
+      <c r="AQ12" s="32"/>
+      <c r="AR12" s="32"/>
+      <c r="AS12" s="32"/>
+      <c r="AT12" s="32"/>
+      <c r="AU12" s="32"/>
+      <c r="AV12" s="32"/>
+      <c r="AW12" s="32"/>
+      <c r="AX12" s="32"/>
+      <c r="AY12" s="32"/>
+      <c r="AZ12" s="32"/>
+      <c r="BA12" s="32"/>
+      <c r="BB12" s="32"/>
+      <c r="BC12" s="32"/>
+      <c r="BD12" s="32"/>
+      <c r="BE12" s="32"/>
+      <c r="BF12" s="32"/>
+      <c r="BG12" s="32"/>
+      <c r="BH12" s="32"/>
+      <c r="BI12" s="32"/>
+      <c r="BJ12" s="32"/>
+      <c r="BK12" s="32"/>
+      <c r="BL12" s="32"/>
+      <c r="BM12" s="32"/>
+      <c r="BN12" s="33"/>
+      <c r="BO12" s="21"/>
+      <c r="BP12" s="21"/>
+      <c r="BQ12" s="21"/>
+      <c r="BR12" s="21"/>
+      <c r="BS12" s="21"/>
+      <c r="BT12" s="21"/>
+      <c r="BU12" s="21"/>
+      <c r="BV12" s="21"/>
+      <c r="BW12" s="21"/>
+      <c r="BX12" s="21"/>
+      <c r="BY12" s="21"/>
+      <c r="BZ12" s="21"/>
+      <c r="CA12" s="21"/>
+      <c r="CB12" s="21"/>
+      <c r="CC12" s="21"/>
+      <c r="CD12" s="21"/>
+      <c r="CE12" s="21"/>
+      <c r="CF12" s="21"/>
+      <c r="CG12" s="21"/>
+      <c r="CH12" s="21"/>
+      <c r="CI12" s="21"/>
+      <c r="CJ12" s="21"/>
+      <c r="CK12" s="21"/>
+      <c r="CL12" s="22"/>
       <c r="CM12" s="16"/>
       <c r="CN12" s="16"/>
       <c r="CO12" s="16"/>
@@ -5028,15 +6365,15 @@
       <c r="CX12" s="16"/>
       <c r="CY12" s="16"/>
       <c r="CZ12" s="16"/>
-      <c r="DA12" s="21"/>
-      <c r="DB12" s="21"/>
-      <c r="DC12" s="21"/>
-      <c r="DD12" s="21"/>
-      <c r="DE12" s="21"/>
-      <c r="DF12" s="21"/>
-      <c r="DG12" s="21"/>
-      <c r="DH12" s="21"/>
-      <c r="DI12" s="21"/>
+      <c r="DA12" s="16"/>
+      <c r="DB12" s="16"/>
+      <c r="DC12" s="16"/>
+      <c r="DD12" s="16"/>
+      <c r="DE12" s="16"/>
+      <c r="DF12" s="16"/>
+      <c r="DG12" s="16"/>
+      <c r="DH12" s="16"/>
+      <c r="DI12" s="16"/>
       <c r="DJ12" s="21"/>
     </row>
     <row r="13" spans="4:114" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5067,63 +6404,56 @@
       <c r="AC13" s="6"/>
       <c r="AD13" s="6"/>
       <c r="AH13" s="17"/>
-      <c r="AI13" s="47" t="s">
-        <v>35</v>
-      </c>
-      <c r="AJ13" s="48"/>
-      <c r="AK13" s="48"/>
-      <c r="AL13" s="48"/>
-      <c r="AM13" s="56"/>
-      <c r="AN13" s="56"/>
-      <c r="BN13" s="19"/>
+      <c r="BN13" s="57"/>
+      <c r="CL13" s="19"/>
+      <c r="CZ13" s="16"/>
+      <c r="DA13" s="16"/>
+      <c r="DB13" s="16"/>
+      <c r="DC13" s="16"/>
+      <c r="DD13" s="16"/>
+      <c r="DE13" s="16"/>
+      <c r="DF13" s="16"/>
+      <c r="DG13" s="16"/>
+      <c r="DH13" s="16"/>
+      <c r="DI13" s="16"/>
     </row>
     <row r="14" spans="4:114" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D14" s="8"/>
-      <c r="E14" s="45" t="s">
+      <c r="E14" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="F14" s="45"/>
-      <c r="G14" s="45"/>
-      <c r="H14" s="45"/>
-      <c r="I14" s="45"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="43"/>
       <c r="V14" s="9"/>
       <c r="AD14" s="16"/>
       <c r="AH14" s="19"/>
-      <c r="AI14" s="49"/>
-      <c r="AJ14" s="55"/>
-      <c r="AK14" s="55"/>
-      <c r="AL14" s="55"/>
-      <c r="AM14" s="57"/>
-      <c r="AN14" s="57"/>
-      <c r="BN14" s="19"/>
+      <c r="BN14" s="16"/>
+      <c r="CL14" s="19"/>
     </row>
     <row r="15" spans="4:114" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D15" s="8"/>
-      <c r="E15" s="45"/>
-      <c r="F15" s="45"/>
-      <c r="G15" s="45"/>
-      <c r="H15" s="45"/>
-      <c r="I15" s="45"/>
+      <c r="E15" s="43"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="43"/>
+      <c r="I15" s="43"/>
       <c r="V15" s="19"/>
-      <c r="W15" s="60" t="s">
-        <v>50</v>
+      <c r="W15" s="52" t="s">
+        <v>44</v>
       </c>
-      <c r="X15" s="61"/>
-      <c r="Y15" s="61"/>
-      <c r="Z15" s="61"/>
-      <c r="AA15" s="61"/>
+      <c r="X15" s="53"/>
+      <c r="Y15" s="53"/>
+      <c r="Z15" s="53"/>
+      <c r="AA15" s="53"/>
       <c r="AB15" s="16"/>
       <c r="AC15" s="16"/>
       <c r="AD15" s="16"/>
       <c r="AE15" s="16"/>
       <c r="AH15" s="19"/>
-      <c r="AI15" s="49"/>
-      <c r="AJ15" s="55"/>
-      <c r="AK15" s="55"/>
-      <c r="AL15" s="55"/>
-      <c r="AM15" s="57"/>
-      <c r="AN15" s="57"/>
-      <c r="BN15" s="19"/>
+      <c r="BN15" s="16"/>
+      <c r="CL15" s="19"/>
     </row>
     <row r="16" spans="4:114" x14ac:dyDescent="0.25">
       <c r="D16" s="8"/>
@@ -5138,442 +6468,356 @@
       <c r="AD16" s="16"/>
       <c r="AE16" s="16"/>
       <c r="AH16" s="19"/>
-      <c r="BN16" s="19"/>
-    </row>
-    <row r="17" spans="4:66" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BN16" s="16"/>
+      <c r="CL16" s="19"/>
+    </row>
+    <row r="17" spans="4:90" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D17" s="8"/>
       <c r="V17" s="19"/>
-      <c r="W17" s="46" t="s">
+      <c r="W17" s="73" t="s">
+        <v>41</v>
+      </c>
+      <c r="X17" s="70"/>
+      <c r="Y17" s="70"/>
+      <c r="Z17" s="70"/>
+      <c r="AA17" s="70"/>
+      <c r="AB17" s="70"/>
+      <c r="AC17" s="70"/>
+      <c r="AD17" s="70"/>
+      <c r="AE17" s="70"/>
+      <c r="AF17" s="70"/>
+      <c r="AG17" s="70"/>
+      <c r="AH17" s="78"/>
+      <c r="BN17" s="16"/>
+      <c r="CL17" s="19"/>
+    </row>
+    <row r="18" spans="4:90" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D18" s="8"/>
+      <c r="V18" s="19"/>
+      <c r="W18" s="73"/>
+      <c r="X18" s="70"/>
+      <c r="Y18" s="70"/>
+      <c r="Z18" s="70"/>
+      <c r="AA18" s="70"/>
+      <c r="AB18" s="70"/>
+      <c r="AC18" s="70"/>
+      <c r="AD18" s="70"/>
+      <c r="AE18" s="70"/>
+      <c r="AF18" s="70"/>
+      <c r="AG18" s="70"/>
+      <c r="AH18" s="78"/>
+      <c r="BN18" s="16"/>
+      <c r="CL18" s="19"/>
+    </row>
+    <row r="19" spans="4:90" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D19" s="8"/>
+      <c r="V19" s="19"/>
+      <c r="W19" s="66"/>
+      <c r="X19" s="66"/>
+      <c r="Y19" s="66"/>
+      <c r="Z19" s="66"/>
+      <c r="AA19" s="66"/>
+      <c r="AB19" s="66"/>
+      <c r="AC19" s="66"/>
+      <c r="AD19" s="66"/>
+      <c r="AE19" s="16"/>
+      <c r="AH19" s="19"/>
+      <c r="BN19" s="16"/>
+      <c r="CL19" s="19"/>
+    </row>
+    <row r="20" spans="4:90" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D20" s="8"/>
+      <c r="V20" s="19"/>
+      <c r="W20" s="75" t="s">
+        <v>42</v>
+      </c>
+      <c r="X20" s="76"/>
+      <c r="Y20" s="76"/>
+      <c r="Z20" s="76"/>
+      <c r="AA20" s="76"/>
+      <c r="AB20" s="76"/>
+      <c r="AC20" s="76"/>
+      <c r="AD20" s="76"/>
+      <c r="AE20" s="76"/>
+      <c r="AF20" s="76"/>
+      <c r="AG20" s="76"/>
+      <c r="AH20" s="19"/>
+      <c r="BN20" s="16"/>
+      <c r="CL20" s="19"/>
+    </row>
+    <row r="21" spans="4:90" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D21" s="8"/>
+      <c r="V21" s="19"/>
+      <c r="W21" s="75"/>
+      <c r="X21" s="76"/>
+      <c r="Y21" s="76"/>
+      <c r="Z21" s="76"/>
+      <c r="AA21" s="76"/>
+      <c r="AB21" s="76"/>
+      <c r="AC21" s="76"/>
+      <c r="AD21" s="76"/>
+      <c r="AE21" s="76"/>
+      <c r="AF21" s="76"/>
+      <c r="AG21" s="76"/>
+      <c r="AH21" s="19"/>
+      <c r="BN21" s="16"/>
+      <c r="CL21" s="19"/>
+    </row>
+    <row r="22" spans="4:90" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D22" s="8"/>
+      <c r="V22" s="19"/>
+      <c r="W22" s="66"/>
+      <c r="X22" s="66"/>
+      <c r="Y22" s="66"/>
+      <c r="Z22" s="66"/>
+      <c r="AA22" s="66"/>
+      <c r="AB22" s="66"/>
+      <c r="AC22" s="66"/>
+      <c r="AD22" s="66"/>
+      <c r="AE22" s="16"/>
+      <c r="AH22" s="19"/>
+      <c r="BN22" s="16"/>
+      <c r="CL22" s="19"/>
+    </row>
+    <row r="23" spans="4:90" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D23" s="8"/>
+      <c r="V23" s="19"/>
+      <c r="W23" s="75" t="s">
+        <v>43</v>
+      </c>
+      <c r="X23" s="72"/>
+      <c r="Y23" s="72"/>
+      <c r="Z23" s="72"/>
+      <c r="AA23" s="72"/>
+      <c r="AB23" s="72"/>
+      <c r="AC23" s="72"/>
+      <c r="AD23" s="72"/>
+      <c r="AE23" s="72"/>
+      <c r="AF23" s="72"/>
+      <c r="AG23" s="72"/>
+      <c r="AH23" s="19"/>
+      <c r="BN23" s="16"/>
+      <c r="CL23" s="19"/>
+    </row>
+    <row r="24" spans="4:90" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D24" s="8"/>
+      <c r="V24" s="19"/>
+      <c r="W24" s="74"/>
+      <c r="X24" s="72"/>
+      <c r="Y24" s="72"/>
+      <c r="Z24" s="72"/>
+      <c r="AA24" s="72"/>
+      <c r="AB24" s="72"/>
+      <c r="AC24" s="72"/>
+      <c r="AD24" s="72"/>
+      <c r="AE24" s="72"/>
+      <c r="AF24" s="72"/>
+      <c r="AG24" s="72"/>
+      <c r="AH24" s="19"/>
+      <c r="BN24" s="16"/>
+      <c r="CL24" s="19"/>
+    </row>
+    <row r="25" spans="4:90" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="D25" s="8"/>
+      <c r="V25" s="19"/>
+      <c r="W25" s="66"/>
+      <c r="X25" s="66"/>
+      <c r="Y25" s="66"/>
+      <c r="Z25" s="66"/>
+      <c r="AA25" s="66"/>
+      <c r="AB25" s="66"/>
+      <c r="AC25" s="66"/>
+      <c r="AD25" s="66"/>
+      <c r="AE25" s="16"/>
+      <c r="AH25" s="19"/>
+      <c r="BN25" s="16"/>
+      <c r="CL25" s="19"/>
+    </row>
+    <row r="26" spans="4:90" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D26" s="8"/>
+      <c r="V26" s="19"/>
+      <c r="W26" s="77" t="s">
+        <v>45</v>
+      </c>
+      <c r="X26" s="71"/>
+      <c r="Y26" s="71"/>
+      <c r="Z26" s="71"/>
+      <c r="AA26" s="71"/>
+      <c r="AB26" s="71"/>
+      <c r="AC26" s="71"/>
+      <c r="AD26" s="71"/>
+      <c r="AE26" s="16"/>
+      <c r="AH26" s="19"/>
+      <c r="BN26" s="16"/>
+      <c r="CL26" s="19"/>
+    </row>
+    <row r="27" spans="4:90" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D27" s="8"/>
+      <c r="V27" s="19"/>
+      <c r="W27" s="77"/>
+      <c r="X27" s="71"/>
+      <c r="Y27" s="71"/>
+      <c r="Z27" s="71"/>
+      <c r="AA27" s="71"/>
+      <c r="AB27" s="71"/>
+      <c r="AC27" s="71"/>
+      <c r="AD27" s="71"/>
+      <c r="AE27" s="16"/>
+      <c r="AH27" s="19"/>
+      <c r="BN27" s="16"/>
+      <c r="CL27" s="19"/>
+    </row>
+    <row r="28" spans="4:90" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="D28" s="8"/>
+      <c r="V28" s="19"/>
+      <c r="W28" s="66"/>
+      <c r="X28" s="66"/>
+      <c r="Y28" s="66"/>
+      <c r="Z28" s="66"/>
+      <c r="AA28" s="66"/>
+      <c r="AB28" s="66"/>
+      <c r="AC28" s="66"/>
+      <c r="AD28" s="66"/>
+      <c r="AE28" s="16"/>
+      <c r="AH28" s="19"/>
+      <c r="BN28" s="16"/>
+      <c r="CL28" s="19"/>
+    </row>
+    <row r="29" spans="4:90" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D29" s="8"/>
+      <c r="V29" s="19"/>
+      <c r="W29" s="77" t="s">
+        <v>46</v>
+      </c>
+      <c r="X29" s="71"/>
+      <c r="Y29" s="71"/>
+      <c r="Z29" s="71"/>
+      <c r="AA29" s="71"/>
+      <c r="AB29" s="71"/>
+      <c r="AC29" s="71"/>
+      <c r="AD29" s="71"/>
+      <c r="AE29" s="16"/>
+      <c r="AH29" s="19"/>
+      <c r="BN29" s="16"/>
+      <c r="CL29" s="19"/>
+    </row>
+    <row r="30" spans="4:90" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D30" s="8"/>
+      <c r="V30" s="19"/>
+      <c r="W30" s="77"/>
+      <c r="X30" s="71"/>
+      <c r="Y30" s="71"/>
+      <c r="Z30" s="71"/>
+      <c r="AA30" s="71"/>
+      <c r="AB30" s="71"/>
+      <c r="AC30" s="71"/>
+      <c r="AD30" s="71"/>
+      <c r="AE30" s="16"/>
+      <c r="AH30" s="19"/>
+      <c r="BN30" s="16"/>
+      <c r="CL30" s="19"/>
+    </row>
+    <row r="31" spans="4:90" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="D31" s="8"/>
+      <c r="V31" s="19"/>
+      <c r="W31" s="66"/>
+      <c r="X31" s="66"/>
+      <c r="Y31" s="66"/>
+      <c r="Z31" s="66"/>
+      <c r="AA31" s="66"/>
+      <c r="AB31" s="66"/>
+      <c r="AC31" s="66"/>
+      <c r="AD31" s="66"/>
+      <c r="AE31" s="16"/>
+      <c r="AH31" s="19"/>
+      <c r="BN31" s="16"/>
+      <c r="CL31" s="19"/>
+    </row>
+    <row r="32" spans="4:90" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D32" s="8"/>
+      <c r="V32" s="19"/>
+      <c r="W32" s="73" t="s">
         <v>47</v>
       </c>
-      <c r="X17" s="46"/>
-      <c r="Y17" s="46"/>
-      <c r="Z17" s="46"/>
-      <c r="AA17" s="46"/>
-      <c r="AB17" s="46"/>
-      <c r="AC17" s="46"/>
-      <c r="AD17" s="46"/>
-      <c r="AE17" s="16"/>
-      <c r="AH17" s="19"/>
-      <c r="AJ17" s="51" t="s">
-        <v>36</v>
-      </c>
-      <c r="AK17" s="51"/>
-      <c r="AL17" s="51"/>
-      <c r="AM17" s="51"/>
-      <c r="AN17" s="51"/>
-      <c r="AO17" s="51"/>
-      <c r="AP17" s="51"/>
-      <c r="AQ17" s="51"/>
-      <c r="AR17" s="51"/>
-      <c r="AS17" s="51"/>
-      <c r="AT17" s="51"/>
-      <c r="AU17" s="51"/>
-      <c r="AV17" s="51"/>
-      <c r="AW17" s="51"/>
-      <c r="AX17" s="51"/>
-      <c r="BN17" s="19"/>
-    </row>
-    <row r="18" spans="4:66" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D18" s="8"/>
-      <c r="V18" s="19"/>
-      <c r="W18" s="46"/>
-      <c r="X18" s="46"/>
-      <c r="Y18" s="46"/>
-      <c r="Z18" s="46"/>
-      <c r="AA18" s="46"/>
-      <c r="AB18" s="46"/>
-      <c r="AC18" s="46"/>
-      <c r="AD18" s="46"/>
-      <c r="AE18" s="16"/>
-      <c r="AH18" s="19"/>
-      <c r="AJ18" s="51"/>
-      <c r="AK18" s="51"/>
-      <c r="AL18" s="51"/>
-      <c r="AM18" s="51"/>
-      <c r="AN18" s="51"/>
-      <c r="AO18" s="51"/>
-      <c r="AP18" s="51"/>
-      <c r="AQ18" s="51"/>
-      <c r="AR18" s="51"/>
-      <c r="AS18" s="51"/>
-      <c r="AT18" s="51"/>
-      <c r="AU18" s="51"/>
-      <c r="AV18" s="51"/>
-      <c r="AW18" s="51"/>
-      <c r="AX18" s="51"/>
-      <c r="BN18" s="19"/>
-    </row>
-    <row r="19" spans="4:66" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D19" s="8"/>
-      <c r="V19" s="19"/>
-      <c r="W19" s="16"/>
-      <c r="X19" s="16"/>
-      <c r="Y19" s="16"/>
-      <c r="Z19" s="16"/>
-      <c r="AA19" s="16"/>
-      <c r="AB19" s="16"/>
-      <c r="AC19" s="16"/>
-      <c r="AD19" s="16"/>
-      <c r="AE19" s="16"/>
-      <c r="AH19" s="19"/>
-      <c r="AJ19" s="51"/>
-      <c r="AK19" s="51"/>
-      <c r="AL19" s="51"/>
-      <c r="AM19" s="51"/>
-      <c r="AN19" s="51"/>
-      <c r="AO19" s="51"/>
-      <c r="AP19" s="51"/>
-      <c r="AQ19" s="51"/>
-      <c r="AR19" s="51"/>
-      <c r="AS19" s="51"/>
-      <c r="AT19" s="51"/>
-      <c r="AU19" s="51"/>
-      <c r="AV19" s="51"/>
-      <c r="AW19" s="51"/>
-      <c r="AX19" s="51"/>
-      <c r="BN19" s="19"/>
-    </row>
-    <row r="20" spans="4:66" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D20" s="8"/>
-      <c r="V20" s="19"/>
-      <c r="W20" s="41" t="s">
+      <c r="X32" s="70"/>
+      <c r="Y32" s="70"/>
+      <c r="Z32" s="70"/>
+      <c r="AA32" s="70"/>
+      <c r="AB32" s="70"/>
+      <c r="AC32" s="70"/>
+      <c r="AD32" s="70"/>
+      <c r="AE32" s="16"/>
+      <c r="AH32" s="19"/>
+      <c r="BN32" s="16"/>
+      <c r="CL32" s="19"/>
+    </row>
+    <row r="33" spans="4:90" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D33" s="8"/>
+      <c r="V33" s="19"/>
+      <c r="W33" s="73"/>
+      <c r="X33" s="70"/>
+      <c r="Y33" s="70"/>
+      <c r="Z33" s="70"/>
+      <c r="AA33" s="70"/>
+      <c r="AB33" s="70"/>
+      <c r="AC33" s="70"/>
+      <c r="AD33" s="70"/>
+      <c r="AE33" s="16"/>
+      <c r="AH33" s="19"/>
+      <c r="BN33" s="16"/>
+      <c r="CL33" s="19"/>
+    </row>
+    <row r="34" spans="4:90" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="D34" s="8"/>
+      <c r="V34" s="19"/>
+      <c r="W34" s="66"/>
+      <c r="X34" s="66"/>
+      <c r="Y34" s="66"/>
+      <c r="Z34" s="66"/>
+      <c r="AA34" s="66"/>
+      <c r="AB34" s="66"/>
+      <c r="AC34" s="66"/>
+      <c r="AD34" s="66"/>
+      <c r="AE34" s="16"/>
+      <c r="AH34" s="19"/>
+      <c r="BN34" s="16"/>
+      <c r="CL34" s="19"/>
+    </row>
+    <row r="35" spans="4:90" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D35" s="8"/>
+      <c r="V35" s="19"/>
+      <c r="W35" s="73" t="s">
         <v>48</v>
       </c>
-      <c r="X20" s="41"/>
-      <c r="Y20" s="41"/>
-      <c r="Z20" s="41"/>
-      <c r="AA20" s="41"/>
-      <c r="AB20" s="41"/>
-      <c r="AC20" s="41"/>
-      <c r="AD20" s="41"/>
-      <c r="AE20" s="16"/>
-      <c r="AH20" s="19"/>
-      <c r="AJ20" s="51"/>
-      <c r="AK20" s="51"/>
-      <c r="AL20" s="51"/>
-      <c r="AM20" s="51"/>
-      <c r="AN20" s="51"/>
-      <c r="AO20" s="51"/>
-      <c r="AP20" s="51"/>
-      <c r="AQ20" s="51"/>
-      <c r="AR20" s="51"/>
-      <c r="AS20" s="51"/>
-      <c r="AT20" s="51"/>
-      <c r="AU20" s="51"/>
-      <c r="AV20" s="51"/>
-      <c r="AW20" s="51"/>
-      <c r="AX20" s="51"/>
-      <c r="BN20" s="19"/>
-    </row>
-    <row r="21" spans="4:66" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D21" s="8"/>
-      <c r="V21" s="19"/>
-      <c r="W21" s="41"/>
-      <c r="X21" s="41"/>
-      <c r="Y21" s="41"/>
-      <c r="Z21" s="41"/>
-      <c r="AA21" s="41"/>
-      <c r="AB21" s="41"/>
-      <c r="AC21" s="41"/>
-      <c r="AD21" s="41"/>
-      <c r="AE21" s="16"/>
-      <c r="AH21" s="19"/>
-      <c r="AJ21" s="51"/>
-      <c r="AK21" s="51"/>
-      <c r="AL21" s="51"/>
-      <c r="AM21" s="51"/>
-      <c r="AN21" s="51"/>
-      <c r="AO21" s="51"/>
-      <c r="AP21" s="51"/>
-      <c r="AQ21" s="51"/>
-      <c r="AR21" s="51"/>
-      <c r="AS21" s="51"/>
-      <c r="AT21" s="51"/>
-      <c r="AU21" s="51"/>
-      <c r="AV21" s="51"/>
-      <c r="AW21" s="51"/>
-      <c r="AX21" s="51"/>
-      <c r="BN21" s="19"/>
-    </row>
-    <row r="22" spans="4:66" x14ac:dyDescent="0.25">
-      <c r="D22" s="8"/>
-      <c r="V22" s="19"/>
-      <c r="W22" s="16"/>
-      <c r="X22" s="16"/>
-      <c r="Y22" s="16"/>
-      <c r="Z22" s="16"/>
-      <c r="AA22" s="16"/>
-      <c r="AB22" s="16"/>
-      <c r="AC22" s="16"/>
-      <c r="AD22" s="16"/>
-      <c r="AE22" s="16"/>
-      <c r="AH22" s="19"/>
-      <c r="AJ22" s="50"/>
-      <c r="AK22" s="50"/>
-      <c r="AL22" s="50"/>
-      <c r="AM22" s="50"/>
-      <c r="AN22" s="50"/>
-      <c r="AO22" s="50"/>
-      <c r="AP22" s="50"/>
-      <c r="AQ22" s="50"/>
-      <c r="AR22" s="50"/>
-      <c r="AS22" s="50"/>
-      <c r="AT22" s="50"/>
-      <c r="AU22" s="50"/>
-      <c r="BN22" s="19"/>
-    </row>
-    <row r="23" spans="4:66" x14ac:dyDescent="0.25">
-      <c r="D23" s="8"/>
-      <c r="V23" s="19"/>
-      <c r="W23" s="46" t="s">
-        <v>49</v>
-      </c>
-      <c r="X23" s="46"/>
-      <c r="Y23" s="46"/>
-      <c r="Z23" s="46"/>
-      <c r="AA23" s="46"/>
-      <c r="AB23" s="46"/>
-      <c r="AC23" s="46"/>
-      <c r="AD23" s="46"/>
-      <c r="AE23" s="16"/>
-      <c r="AH23" s="19"/>
-      <c r="AJ23" s="50"/>
-      <c r="AK23" s="50"/>
-      <c r="AL23" s="50"/>
-      <c r="AM23" s="50"/>
-      <c r="AN23" s="50"/>
-      <c r="AO23" s="50"/>
-      <c r="AP23" s="50"/>
-      <c r="AQ23" s="50"/>
-      <c r="AR23" s="50"/>
-      <c r="AS23" s="50"/>
-      <c r="AT23" s="50"/>
-      <c r="AU23" s="50"/>
-      <c r="BN23" s="19"/>
-    </row>
-    <row r="24" spans="4:66" x14ac:dyDescent="0.25">
-      <c r="D24" s="8"/>
-      <c r="V24" s="19"/>
-      <c r="W24" s="46"/>
-      <c r="X24" s="46"/>
-      <c r="Y24" s="46"/>
-      <c r="Z24" s="46"/>
-      <c r="AA24" s="46"/>
-      <c r="AB24" s="46"/>
-      <c r="AC24" s="46"/>
-      <c r="AD24" s="46"/>
-      <c r="AE24" s="16"/>
-      <c r="AH24" s="19"/>
-      <c r="AJ24" s="52" t="s">
-        <v>37</v>
-      </c>
-      <c r="BN24" s="19"/>
-    </row>
-    <row r="25" spans="4:66" x14ac:dyDescent="0.25">
-      <c r="D25" s="8"/>
-      <c r="V25" s="19"/>
-      <c r="W25" s="16"/>
-      <c r="X25" s="16"/>
-      <c r="Y25" s="16"/>
-      <c r="Z25" s="16"/>
-      <c r="AA25" s="16"/>
-      <c r="AB25" s="16"/>
-      <c r="AC25" s="16"/>
-      <c r="AD25" s="16"/>
-      <c r="AE25" s="16"/>
-      <c r="AH25" s="19"/>
-      <c r="AK25" t="s">
-        <v>38</v>
-      </c>
-      <c r="BN25" s="19"/>
-    </row>
-    <row r="26" spans="4:66" x14ac:dyDescent="0.25">
-      <c r="D26" s="8"/>
-      <c r="V26" s="19"/>
-      <c r="W26" s="40" t="s">
-        <v>51</v>
-      </c>
-      <c r="X26" s="40"/>
-      <c r="Y26" s="40"/>
-      <c r="Z26" s="40"/>
-      <c r="AA26" s="40"/>
-      <c r="AB26" s="40"/>
-      <c r="AC26" s="40"/>
-      <c r="AD26" s="40"/>
-      <c r="AE26" s="16"/>
-      <c r="AH26" s="19"/>
-      <c r="AK26" t="s">
-        <v>39</v>
-      </c>
-      <c r="BN26" s="19"/>
-    </row>
-    <row r="27" spans="4:66" x14ac:dyDescent="0.25">
-      <c r="D27" s="8"/>
-      <c r="V27" s="19"/>
-      <c r="W27" s="40"/>
-      <c r="X27" s="40"/>
-      <c r="Y27" s="40"/>
-      <c r="Z27" s="40"/>
-      <c r="AA27" s="40"/>
-      <c r="AB27" s="40"/>
-      <c r="AC27" s="40"/>
-      <c r="AD27" s="40"/>
-      <c r="AE27" s="16"/>
-      <c r="AH27" s="19"/>
-      <c r="AK27" t="s">
-        <v>40</v>
-      </c>
-      <c r="BN27" s="19"/>
-    </row>
-    <row r="28" spans="4:66" x14ac:dyDescent="0.25">
-      <c r="D28" s="8"/>
-      <c r="V28" s="19"/>
-      <c r="W28" s="16"/>
-      <c r="X28" s="16"/>
-      <c r="Y28" s="16"/>
-      <c r="Z28" s="16"/>
-      <c r="AA28" s="16"/>
-      <c r="AB28" s="16"/>
-      <c r="AC28" s="16"/>
-      <c r="AD28" s="16"/>
-      <c r="AE28" s="16"/>
-      <c r="AH28" s="19"/>
-      <c r="AK28" t="s">
-        <v>41</v>
-      </c>
-      <c r="BN28" s="19"/>
-    </row>
-    <row r="29" spans="4:66" x14ac:dyDescent="0.25">
-      <c r="D29" s="8"/>
-      <c r="V29" s="19"/>
-      <c r="W29" s="40" t="s">
-        <v>52</v>
-      </c>
-      <c r="X29" s="40"/>
-      <c r="Y29" s="40"/>
-      <c r="Z29" s="40"/>
-      <c r="AA29" s="40"/>
-      <c r="AB29" s="40"/>
-      <c r="AC29" s="40"/>
-      <c r="AD29" s="40"/>
-      <c r="AE29" s="16"/>
-      <c r="AH29" s="19"/>
-      <c r="AK29" t="s">
-        <v>42</v>
-      </c>
-      <c r="BN29" s="19"/>
-    </row>
-    <row r="30" spans="4:66" x14ac:dyDescent="0.25">
-      <c r="D30" s="8"/>
-      <c r="V30" s="19"/>
-      <c r="W30" s="40"/>
-      <c r="X30" s="40"/>
-      <c r="Y30" s="40"/>
-      <c r="Z30" s="40"/>
-      <c r="AA30" s="40"/>
-      <c r="AB30" s="40"/>
-      <c r="AC30" s="40"/>
-      <c r="AD30" s="40"/>
-      <c r="AE30" s="16"/>
-      <c r="AH30" s="19"/>
-      <c r="BN30" s="19"/>
-    </row>
-    <row r="31" spans="4:66" x14ac:dyDescent="0.25">
-      <c r="D31" s="8"/>
-      <c r="V31" s="19"/>
-      <c r="W31" s="16"/>
-      <c r="X31" s="16"/>
-      <c r="Y31" s="16"/>
-      <c r="Z31" s="16"/>
-      <c r="AA31" s="16"/>
-      <c r="AB31" s="16"/>
-      <c r="AC31" s="16"/>
-      <c r="AD31" s="16"/>
-      <c r="AE31" s="16"/>
-      <c r="AH31" s="19"/>
-      <c r="BN31" s="19"/>
-    </row>
-    <row r="32" spans="4:66" x14ac:dyDescent="0.25">
-      <c r="D32" s="8"/>
-      <c r="V32" s="19"/>
-      <c r="W32" s="41" t="s">
-        <v>53</v>
-      </c>
-      <c r="X32" s="41"/>
-      <c r="Y32" s="41"/>
-      <c r="Z32" s="41"/>
-      <c r="AA32" s="41"/>
-      <c r="AB32" s="41"/>
-      <c r="AC32" s="41"/>
-      <c r="AD32" s="41"/>
-      <c r="AE32" s="16"/>
-      <c r="AH32" s="19"/>
-      <c r="BN32" s="19"/>
-    </row>
-    <row r="33" spans="4:66" x14ac:dyDescent="0.25">
-      <c r="D33" s="8"/>
-      <c r="V33" s="19"/>
-      <c r="W33" s="41"/>
-      <c r="X33" s="41"/>
-      <c r="Y33" s="41"/>
-      <c r="Z33" s="41"/>
-      <c r="AA33" s="41"/>
-      <c r="AB33" s="41"/>
-      <c r="AC33" s="41"/>
-      <c r="AD33" s="41"/>
-      <c r="AE33" s="16"/>
-      <c r="AH33" s="19"/>
-      <c r="BN33" s="19"/>
-    </row>
-    <row r="34" spans="4:66" x14ac:dyDescent="0.25">
-      <c r="D34" s="8"/>
-      <c r="V34" s="19"/>
-      <c r="W34" s="16"/>
-      <c r="X34" s="16"/>
-      <c r="Y34" s="16"/>
-      <c r="Z34" s="16"/>
-      <c r="AA34" s="16"/>
-      <c r="AB34" s="16"/>
-      <c r="AC34" s="16"/>
-      <c r="AD34" s="16"/>
-      <c r="AE34" s="16"/>
-      <c r="AH34" s="19"/>
-      <c r="BN34" s="19"/>
-    </row>
-    <row r="35" spans="4:66" x14ac:dyDescent="0.25">
-      <c r="D35" s="8"/>
-      <c r="V35" s="19"/>
-      <c r="W35" s="41" t="s">
-        <v>54</v>
-      </c>
-      <c r="X35" s="41"/>
-      <c r="Y35" s="41"/>
-      <c r="Z35" s="41"/>
-      <c r="AA35" s="41"/>
-      <c r="AB35" s="41"/>
-      <c r="AC35" s="41"/>
-      <c r="AD35" s="41"/>
+      <c r="X35" s="70"/>
+      <c r="Y35" s="70"/>
+      <c r="Z35" s="70"/>
+      <c r="AA35" s="70"/>
+      <c r="AB35" s="70"/>
+      <c r="AC35" s="70"/>
+      <c r="AD35" s="70"/>
       <c r="AE35" s="16"/>
       <c r="AH35" s="19"/>
-      <c r="BN35" s="19"/>
-    </row>
-    <row r="36" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="BN35" s="16"/>
+      <c r="CL35" s="19"/>
+    </row>
+    <row r="36" spans="4:90" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D36" s="8"/>
       <c r="V36" s="19"/>
-      <c r="W36" s="41"/>
-      <c r="X36" s="41"/>
-      <c r="Y36" s="41"/>
-      <c r="Z36" s="41"/>
-      <c r="AA36" s="41"/>
-      <c r="AB36" s="41"/>
-      <c r="AC36" s="41"/>
-      <c r="AD36" s="41"/>
+      <c r="W36" s="73"/>
+      <c r="X36" s="70"/>
+      <c r="Y36" s="70"/>
+      <c r="Z36" s="70"/>
+      <c r="AA36" s="70"/>
+      <c r="AB36" s="70"/>
+      <c r="AC36" s="70"/>
+      <c r="AD36" s="70"/>
       <c r="AE36" s="16"/>
       <c r="AH36" s="19"/>
-      <c r="BN36" s="19"/>
-    </row>
-    <row r="37" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="BN36" s="16"/>
+      <c r="CL36" s="19"/>
+    </row>
+    <row r="37" spans="4:90" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D37" s="8"/>
       <c r="V37" s="19"/>
       <c r="W37" s="16"/>
@@ -5586,39 +6830,42 @@
       <c r="AD37" s="16"/>
       <c r="AE37" s="16"/>
       <c r="AH37" s="19"/>
-      <c r="BN37" s="19"/>
-    </row>
-    <row r="38" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="BN37" s="16"/>
+      <c r="CL37" s="19"/>
+    </row>
+    <row r="38" spans="4:90" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D38" s="8"/>
       <c r="V38" s="19"/>
-      <c r="W38" s="62"/>
-      <c r="X38" s="62"/>
-      <c r="Y38" s="62"/>
-      <c r="Z38" s="62"/>
-      <c r="AA38" s="62"/>
-      <c r="AB38" s="62"/>
-      <c r="AC38" s="62"/>
-      <c r="AD38" s="62"/>
+      <c r="W38" s="54"/>
+      <c r="X38" s="54"/>
+      <c r="Y38" s="54"/>
+      <c r="Z38" s="54"/>
+      <c r="AA38" s="54"/>
+      <c r="AB38" s="54"/>
+      <c r="AC38" s="54"/>
+      <c r="AD38" s="54"/>
       <c r="AE38" s="16"/>
       <c r="AH38" s="19"/>
-      <c r="BN38" s="19"/>
-    </row>
-    <row r="39" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="BN38" s="16"/>
+      <c r="CL38" s="19"/>
+    </row>
+    <row r="39" spans="4:90" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D39" s="8"/>
       <c r="V39" s="19"/>
-      <c r="W39" s="62"/>
-      <c r="X39" s="62"/>
-      <c r="Y39" s="62"/>
-      <c r="Z39" s="62"/>
-      <c r="AA39" s="62"/>
-      <c r="AB39" s="62"/>
-      <c r="AC39" s="62"/>
-      <c r="AD39" s="62"/>
+      <c r="W39" s="54"/>
+      <c r="X39" s="54"/>
+      <c r="Y39" s="54"/>
+      <c r="Z39" s="54"/>
+      <c r="AA39" s="54"/>
+      <c r="AB39" s="54"/>
+      <c r="AC39" s="54"/>
+      <c r="AD39" s="54"/>
       <c r="AE39" s="16"/>
       <c r="AH39" s="19"/>
-      <c r="BN39" s="19"/>
-    </row>
-    <row r="40" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="BN39" s="16"/>
+      <c r="CL39" s="19"/>
+    </row>
+    <row r="40" spans="4:90" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D40" s="8"/>
       <c r="V40" s="19"/>
       <c r="W40" s="16"/>
@@ -5631,9 +6878,10 @@
       <c r="AD40" s="16"/>
       <c r="AE40" s="16"/>
       <c r="AH40" s="19"/>
-      <c r="BN40" s="19"/>
-    </row>
-    <row r="41" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="BN40" s="16"/>
+      <c r="CL40" s="19"/>
+    </row>
+    <row r="41" spans="4:90" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D41" s="8"/>
       <c r="V41" s="19"/>
       <c r="W41" s="16"/>
@@ -5646,9 +6894,10 @@
       <c r="AD41" s="16"/>
       <c r="AE41" s="16"/>
       <c r="AH41" s="19"/>
-      <c r="BN41" s="19"/>
-    </row>
-    <row r="42" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="BN41" s="16"/>
+      <c r="CL41" s="19"/>
+    </row>
+    <row r="42" spans="4:90" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D42" s="8"/>
       <c r="V42" s="19"/>
       <c r="W42" s="16"/>
@@ -5661,9 +6910,10 @@
       <c r="AD42" s="16"/>
       <c r="AE42" s="16"/>
       <c r="AH42" s="19"/>
-      <c r="BN42" s="19"/>
-    </row>
-    <row r="43" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="BN42" s="16"/>
+      <c r="CL42" s="19"/>
+    </row>
+    <row r="43" spans="4:90" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D43" s="8"/>
       <c r="V43" s="19"/>
       <c r="W43" s="16"/>
@@ -5676,9 +6926,10 @@
       <c r="AD43" s="16"/>
       <c r="AE43" s="16"/>
       <c r="AH43" s="19"/>
-      <c r="BN43" s="19"/>
-    </row>
-    <row r="44" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="BN43" s="16"/>
+      <c r="CL43" s="19"/>
+    </row>
+    <row r="44" spans="4:90" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D44" s="8"/>
       <c r="V44" s="19"/>
       <c r="W44" s="16"/>
@@ -5691,9 +6942,10 @@
       <c r="AD44" s="16"/>
       <c r="AE44" s="16"/>
       <c r="AH44" s="19"/>
-      <c r="BN44" s="19"/>
-    </row>
-    <row r="45" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="BN44" s="16"/>
+      <c r="CL44" s="19"/>
+    </row>
+    <row r="45" spans="4:90" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D45" s="8"/>
       <c r="V45" s="19"/>
       <c r="W45" s="16"/>
@@ -5706,9 +6958,10 @@
       <c r="AD45" s="16"/>
       <c r="AE45" s="16"/>
       <c r="AH45" s="19"/>
-      <c r="BN45" s="19"/>
-    </row>
-    <row r="46" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="BN45" s="16"/>
+      <c r="CL45" s="19"/>
+    </row>
+    <row r="46" spans="4:90" x14ac:dyDescent="0.25">
       <c r="D46" s="8"/>
       <c r="V46" s="19"/>
       <c r="W46" s="16"/>
@@ -5721,9 +6974,10 @@
       <c r="AD46" s="16"/>
       <c r="AE46" s="16"/>
       <c r="AH46" s="19"/>
-      <c r="BN46" s="19"/>
-    </row>
-    <row r="47" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="BN46" s="16"/>
+      <c r="CL46" s="19"/>
+    </row>
+    <row r="47" spans="4:90" x14ac:dyDescent="0.25">
       <c r="D47" s="8"/>
       <c r="V47" s="19"/>
       <c r="W47" s="16"/>
@@ -5736,9 +6990,10 @@
       <c r="AD47" s="16"/>
       <c r="AE47" s="16"/>
       <c r="AH47" s="19"/>
-      <c r="BN47" s="19"/>
-    </row>
-    <row r="48" spans="4:66" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BN47" s="16"/>
+      <c r="CL47" s="19"/>
+    </row>
+    <row r="48" spans="4:90" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D48" s="10"/>
       <c r="E48" s="11"/>
       <c r="F48" s="11"/>
@@ -5801,9 +7056,33 @@
       <c r="BK48" s="21"/>
       <c r="BL48" s="21"/>
       <c r="BM48" s="21"/>
-      <c r="BN48" s="22"/>
-    </row>
-    <row r="49" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="BN48" s="21"/>
+      <c r="BO48" s="21"/>
+      <c r="BP48" s="21"/>
+      <c r="BQ48" s="21"/>
+      <c r="BR48" s="21"/>
+      <c r="BS48" s="21"/>
+      <c r="BT48" s="21"/>
+      <c r="BU48" s="21"/>
+      <c r="BV48" s="21"/>
+      <c r="BW48" s="21"/>
+      <c r="BX48" s="21"/>
+      <c r="BY48" s="21"/>
+      <c r="BZ48" s="21"/>
+      <c r="CA48" s="21"/>
+      <c r="CB48" s="21"/>
+      <c r="CC48" s="21"/>
+      <c r="CD48" s="21"/>
+      <c r="CE48" s="21"/>
+      <c r="CF48" s="21"/>
+      <c r="CG48" s="21"/>
+      <c r="CH48" s="21"/>
+      <c r="CI48" s="21"/>
+      <c r="CJ48" s="21"/>
+      <c r="CK48" s="21"/>
+      <c r="CL48" s="22"/>
+    </row>
+    <row r="49" spans="3:90" x14ac:dyDescent="0.25">
       <c r="D49" s="8"/>
       <c r="W49" s="16"/>
       <c r="X49" s="16"/>
@@ -5814,15 +7093,16 @@
       <c r="AC49" s="16"/>
       <c r="AD49" s="16"/>
       <c r="AE49" s="16"/>
-      <c r="BN49" s="19"/>
-    </row>
-    <row r="50" spans="3:66" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="D50" s="42" t="s">
+      <c r="BN49" s="57"/>
+      <c r="CL49" s="19"/>
+    </row>
+    <row r="50" spans="3:90" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="D50" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="E50" s="43"/>
-      <c r="F50" s="43"/>
-      <c r="G50" s="43"/>
+      <c r="E50" s="41"/>
+      <c r="F50" s="41"/>
+      <c r="G50" s="41"/>
       <c r="W50" s="16"/>
       <c r="X50" s="16"/>
       <c r="Y50" s="16"/>
@@ -5832,9 +7112,10 @@
       <c r="AC50" s="16"/>
       <c r="AD50" s="16"/>
       <c r="AE50" s="16"/>
-      <c r="BN50" s="19"/>
-    </row>
-    <row r="51" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="BN50" s="16"/>
+      <c r="CL50" s="19"/>
+    </row>
+    <row r="51" spans="3:90" x14ac:dyDescent="0.25">
       <c r="D51" s="8"/>
       <c r="W51" s="16"/>
       <c r="X51" s="16"/>
@@ -5845,10 +7126,12 @@
       <c r="AC51" s="16"/>
       <c r="AD51" s="16"/>
       <c r="AE51" s="16"/>
-      <c r="BN51" s="19"/>
-    </row>
-    <row r="52" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="D52" s="8"/>
+      <c r="BN51" s="16"/>
+      <c r="CL51" s="19"/>
+    </row>
+    <row r="52" spans="3:90" x14ac:dyDescent="0.25">
+      <c r="C52" s="19"/>
+      <c r="D52" s="16"/>
       <c r="W52" s="16"/>
       <c r="X52" s="16"/>
       <c r="Y52" s="16"/>
@@ -5858,10 +7141,12 @@
       <c r="AC52" s="16"/>
       <c r="AD52" s="16"/>
       <c r="AE52" s="16"/>
-      <c r="BN52" s="19"/>
-    </row>
-    <row r="53" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="D53" s="8"/>
+      <c r="BN52" s="16"/>
+      <c r="BO52" s="16"/>
+      <c r="CL52" s="19"/>
+    </row>
+    <row r="53" spans="3:90" x14ac:dyDescent="0.25">
+      <c r="C53" s="19"/>
       <c r="W53" s="16"/>
       <c r="X53" s="16"/>
       <c r="Y53" s="16"/>
@@ -5871,121 +7156,42 @@
       <c r="AC53" s="16"/>
       <c r="AD53" s="16"/>
       <c r="AE53" s="16"/>
-      <c r="BN53" s="19"/>
-    </row>
-    <row r="54" spans="3:66" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="D54" s="8"/>
-      <c r="E54" s="59" t="s">
-        <v>14</v>
-      </c>
-      <c r="F54" s="24"/>
-      <c r="G54" s="24"/>
-      <c r="H54" s="24"/>
-      <c r="I54" s="24"/>
-      <c r="L54" s="52" t="s">
-        <v>43</v>
-      </c>
-      <c r="BN54" s="19"/>
-    </row>
-    <row r="55" spans="3:66" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="D55" s="8"/>
-      <c r="E55" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="F55" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="G55" s="24"/>
-      <c r="H55" s="24"/>
-      <c r="I55" s="24"/>
-      <c r="M55" s="53" t="s">
-        <v>45</v>
-      </c>
-      <c r="N55" s="53"/>
-      <c r="O55" s="53"/>
-      <c r="P55" s="53"/>
-      <c r="Q55" s="53"/>
-      <c r="R55" s="53"/>
-      <c r="S55" s="53"/>
-      <c r="T55" s="53"/>
-      <c r="U55" s="53"/>
-      <c r="V55" s="53"/>
-      <c r="BN55" s="19"/>
-    </row>
-    <row r="56" spans="3:66" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="D56" s="8"/>
-      <c r="E56" s="24"/>
-      <c r="F56" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="G56" s="24"/>
-      <c r="H56" s="24"/>
-      <c r="I56" s="24"/>
-      <c r="M56" s="53"/>
-      <c r="N56" s="53"/>
-      <c r="O56" s="53"/>
-      <c r="P56" s="53"/>
-      <c r="Q56" s="53"/>
-      <c r="R56" s="53"/>
-      <c r="S56" s="53"/>
-      <c r="T56" s="53"/>
-      <c r="U56" s="53"/>
-      <c r="V56" s="53"/>
-      <c r="BN56" s="19"/>
-    </row>
-    <row r="57" spans="3:66" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="D57" s="8"/>
-      <c r="E57" s="24"/>
-      <c r="F57" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="G57" s="24"/>
-      <c r="H57" s="24"/>
-      <c r="I57" s="24"/>
-      <c r="M57" s="53"/>
-      <c r="N57" s="53"/>
-      <c r="O57" s="53"/>
-      <c r="P57" s="53"/>
-      <c r="Q57" s="53"/>
-      <c r="R57" s="53"/>
-      <c r="S57" s="53"/>
-      <c r="T57" s="53"/>
-      <c r="U57" s="53"/>
-      <c r="V57" s="53"/>
-      <c r="BN57" s="19"/>
-    </row>
-    <row r="58" spans="3:66" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="D58" s="8"/>
-      <c r="E58" s="24"/>
-      <c r="F58" s="24" t="s">
-        <v>19</v>
-      </c>
-      <c r="G58" s="24"/>
-      <c r="H58" s="24"/>
-      <c r="I58" s="24"/>
-      <c r="BN58" s="19"/>
-    </row>
-    <row r="59" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="D59" s="8"/>
-      <c r="E59" s="16"/>
-      <c r="F59" s="16"/>
-      <c r="G59" s="16"/>
-      <c r="H59" s="16"/>
-      <c r="I59" s="16"/>
-      <c r="J59" s="16"/>
-      <c r="K59" s="16"/>
-      <c r="M59" s="53" t="s">
-        <v>44</v>
-      </c>
-      <c r="N59" s="54"/>
-      <c r="O59" s="54"/>
-      <c r="P59" s="54"/>
-      <c r="Q59" s="54"/>
-      <c r="R59" s="54"/>
-      <c r="S59" s="54"/>
-      <c r="T59" s="54"/>
-      <c r="U59" s="54"/>
-      <c r="V59" s="54"/>
+      <c r="BN53" s="16"/>
+      <c r="BO53" s="16"/>
+      <c r="CL53" s="19"/>
+    </row>
+    <row r="54" spans="3:90" x14ac:dyDescent="0.25">
+      <c r="C54" s="19"/>
+      <c r="BN54" s="16"/>
+      <c r="BO54" s="16"/>
+      <c r="CL54" s="19"/>
+    </row>
+    <row r="55" spans="3:90" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C55" s="19"/>
+      <c r="BN55" s="16"/>
+      <c r="BO55" s="16"/>
+      <c r="CL55" s="19"/>
+    </row>
+    <row r="56" spans="3:90" x14ac:dyDescent="0.25">
+      <c r="C56" s="19"/>
+      <c r="BN56" s="16"/>
+      <c r="BO56" s="16"/>
+      <c r="CL56" s="19"/>
+    </row>
+    <row r="57" spans="3:90" x14ac:dyDescent="0.25">
+      <c r="C57" s="19"/>
+      <c r="BN57" s="16"/>
+      <c r="BO57" s="16"/>
+      <c r="CL57" s="19"/>
+    </row>
+    <row r="58" spans="3:90" x14ac:dyDescent="0.25">
+      <c r="C58" s="19"/>
+      <c r="BN58" s="16"/>
+      <c r="BO58" s="16"/>
+      <c r="CL58" s="19"/>
+    </row>
+    <row r="59" spans="3:90" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C59" s="19"/>
       <c r="W59" s="16"/>
       <c r="AI59" s="16"/>
       <c r="AJ59" s="16"/>
@@ -6018,725 +7224,1125 @@
       <c r="BK59" s="16"/>
       <c r="BL59" s="16"/>
       <c r="BM59" s="16"/>
-      <c r="BN59" s="19"/>
-    </row>
-    <row r="60" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="D60" s="8"/>
-      <c r="M60" s="54"/>
-      <c r="N60" s="54"/>
-      <c r="O60" s="54"/>
-      <c r="P60" s="54"/>
-      <c r="Q60" s="54"/>
-      <c r="R60" s="54"/>
-      <c r="S60" s="54"/>
-      <c r="T60" s="54"/>
-      <c r="U60" s="54"/>
-      <c r="V60" s="54"/>
-      <c r="BN60" s="19"/>
-    </row>
-    <row r="61" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="BN59" s="16"/>
+      <c r="BO59" s="16"/>
+      <c r="CL59" s="19"/>
+    </row>
+    <row r="60" spans="3:90" x14ac:dyDescent="0.25">
+      <c r="C60" s="19"/>
+      <c r="BN60" s="16"/>
+      <c r="BO60" s="16"/>
+      <c r="CL60" s="19"/>
+    </row>
+    <row r="61" spans="3:90" x14ac:dyDescent="0.25">
       <c r="C61" s="19"/>
-      <c r="D61" s="16"/>
-      <c r="BN61" s="19"/>
-    </row>
-    <row r="62" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="BN61" s="16"/>
+      <c r="BO61" s="16"/>
+      <c r="CL61" s="19"/>
+    </row>
+    <row r="62" spans="3:90" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C62" s="19"/>
-      <c r="M62" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="N62" s="58"/>
-      <c r="O62" s="58"/>
-      <c r="P62" s="58"/>
-      <c r="Q62" s="58"/>
-      <c r="R62" s="58"/>
-      <c r="S62" s="58"/>
-      <c r="T62" s="58"/>
-      <c r="U62" s="58"/>
-      <c r="V62" s="58"/>
-      <c r="BN62" s="19"/>
-    </row>
-    <row r="63" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="BN62" s="16"/>
+      <c r="BO62" s="16"/>
+      <c r="CL62" s="19"/>
+    </row>
+    <row r="63" spans="3:90" x14ac:dyDescent="0.25">
       <c r="C63" s="19"/>
       <c r="D63" s="16"/>
-      <c r="L63" s="16"/>
-      <c r="M63" s="58"/>
-      <c r="N63" s="58"/>
-      <c r="O63" s="58"/>
-      <c r="P63" s="58"/>
-      <c r="Q63" s="58"/>
-      <c r="R63" s="58"/>
-      <c r="S63" s="58"/>
-      <c r="T63" s="58"/>
-      <c r="U63" s="58"/>
-      <c r="V63" s="58"/>
-      <c r="BN63" s="19"/>
-    </row>
-    <row r="64" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="BN63" s="16"/>
+      <c r="BO63" s="16"/>
+      <c r="CL63" s="19"/>
+    </row>
+    <row r="64" spans="3:90" ht="18.75" x14ac:dyDescent="0.3">
       <c r="D64" s="8"/>
-      <c r="BN64" s="19"/>
-    </row>
-    <row r="65" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="E64" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="F64" s="24"/>
+      <c r="G64" s="24"/>
+      <c r="H64" s="24"/>
+      <c r="I64" s="24"/>
+      <c r="BN64" s="16"/>
+      <c r="BO64" s="16"/>
+      <c r="CL64" s="19"/>
+    </row>
+    <row r="65" spans="3:90" ht="18.75" x14ac:dyDescent="0.3">
       <c r="D65" s="8"/>
-      <c r="BN65" s="19"/>
-    </row>
-    <row r="66" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="E65" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="F65" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="G65" s="24"/>
+      <c r="H65" s="24"/>
+      <c r="I65" s="24"/>
+      <c r="BN65" s="16"/>
+      <c r="BO65" s="16"/>
+      <c r="CL65" s="19"/>
+    </row>
+    <row r="66" spans="3:90" ht="18.75" x14ac:dyDescent="0.3">
       <c r="D66" s="8"/>
-      <c r="BN66" s="19"/>
-    </row>
-    <row r="67" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="E66" s="24"/>
+      <c r="F66" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="G66" s="24"/>
+      <c r="H66" s="24"/>
+      <c r="I66" s="24"/>
+      <c r="BN66" s="16"/>
+      <c r="BO66" s="16"/>
+      <c r="CL66" s="19"/>
+    </row>
+    <row r="67" spans="3:90" ht="18.75" x14ac:dyDescent="0.3">
       <c r="D67" s="8"/>
-      <c r="BN67" s="19"/>
-    </row>
-    <row r="68" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="E67" s="24"/>
+      <c r="F67" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="H67" s="24"/>
+      <c r="I67" s="24"/>
+      <c r="BN67" s="16"/>
+      <c r="BO67" s="16"/>
+      <c r="CL67" s="19"/>
+    </row>
+    <row r="68" spans="3:90" ht="18.75" x14ac:dyDescent="0.3">
       <c r="D68" s="8"/>
-      <c r="BN68" s="19"/>
-    </row>
-    <row r="69" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="D69" s="8"/>
-      <c r="BN69" s="19"/>
-    </row>
-    <row r="70" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="E68" s="24"/>
+      <c r="F68" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="G68" s="24"/>
+      <c r="H68" s="24"/>
+      <c r="I68" s="24"/>
+      <c r="BN68" s="16"/>
+      <c r="BO68" s="16"/>
+      <c r="CL68" s="19"/>
+    </row>
+    <row r="69" spans="3:90" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D69" s="27"/>
+      <c r="E69" s="21"/>
+      <c r="F69" s="21"/>
+      <c r="G69" s="21"/>
+      <c r="H69" s="21"/>
+      <c r="I69" s="21"/>
+      <c r="J69" s="21"/>
+      <c r="K69" s="21"/>
+      <c r="L69" s="21"/>
+      <c r="M69" s="21"/>
+      <c r="N69" s="21"/>
+      <c r="O69" s="21"/>
+      <c r="P69" s="21"/>
+      <c r="Q69" s="21"/>
+      <c r="R69" s="21"/>
+      <c r="S69" s="21"/>
+      <c r="T69" s="21"/>
+      <c r="U69" s="21"/>
+      <c r="V69" s="21"/>
+      <c r="W69" s="21"/>
+      <c r="X69" s="21"/>
+      <c r="Y69" s="21"/>
+      <c r="Z69" s="21"/>
+      <c r="AA69" s="21"/>
+      <c r="AB69" s="21"/>
+      <c r="AC69" s="21"/>
+      <c r="AD69" s="21"/>
+      <c r="AE69" s="21"/>
+      <c r="AF69" s="21"/>
+      <c r="AG69" s="21"/>
+      <c r="AH69" s="21"/>
+      <c r="AI69" s="21"/>
+      <c r="AJ69" s="21"/>
+      <c r="AK69" s="21"/>
+      <c r="AL69" s="21"/>
+      <c r="AM69" s="21"/>
+      <c r="AN69" s="21"/>
+      <c r="AO69" s="21"/>
+      <c r="AP69" s="21"/>
+      <c r="AQ69" s="21"/>
+      <c r="AR69" s="21"/>
+      <c r="AS69" s="21"/>
+      <c r="AT69" s="21"/>
+      <c r="AU69" s="21"/>
+      <c r="AV69" s="21"/>
+      <c r="AW69" s="21"/>
+      <c r="AX69" s="21"/>
+      <c r="AY69" s="21"/>
+      <c r="AZ69" s="21"/>
+      <c r="BA69" s="21"/>
+      <c r="BB69" s="21"/>
+      <c r="BC69" s="21"/>
+      <c r="BD69" s="21"/>
+      <c r="BE69" s="21"/>
+      <c r="BF69" s="21"/>
+      <c r="BG69" s="21"/>
+      <c r="BH69" s="21"/>
+      <c r="BI69" s="21"/>
+      <c r="BJ69" s="21"/>
+      <c r="BK69" s="21"/>
+      <c r="BL69" s="21"/>
+      <c r="BM69" s="21"/>
+      <c r="BN69" s="21"/>
+      <c r="BO69" s="21"/>
+      <c r="BP69" s="21"/>
+      <c r="BQ69" s="21"/>
+      <c r="BR69" s="21"/>
+      <c r="BS69" s="21"/>
+      <c r="BT69" s="21"/>
+      <c r="BU69" s="21"/>
+      <c r="BV69" s="21"/>
+      <c r="BW69" s="21"/>
+      <c r="BX69" s="21"/>
+      <c r="BY69" s="21"/>
+      <c r="BZ69" s="21"/>
+      <c r="CA69" s="21"/>
+      <c r="CB69" s="21"/>
+      <c r="CC69" s="21"/>
+      <c r="CD69" s="21"/>
+      <c r="CE69" s="21"/>
+      <c r="CF69" s="21"/>
+      <c r="CG69" s="21"/>
+      <c r="CH69" s="21"/>
+      <c r="CI69" s="21"/>
+      <c r="CJ69" s="21"/>
+      <c r="CK69" s="21"/>
+      <c r="CL69" s="22"/>
+    </row>
+    <row r="70" spans="3:90" x14ac:dyDescent="0.25">
       <c r="D70" s="18"/>
-      <c r="BN70" s="19"/>
-    </row>
-    <row r="71" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="BN70" s="16"/>
+      <c r="BO70" s="16"/>
+      <c r="CL70" s="17"/>
+    </row>
+    <row r="71" spans="3:90" x14ac:dyDescent="0.25">
       <c r="D71" s="18"/>
-      <c r="BN71" s="19"/>
-    </row>
-    <row r="72" spans="3:66" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="BN71" s="16"/>
+      <c r="BO71" s="16"/>
+      <c r="CL71" s="19"/>
+    </row>
+    <row r="72" spans="3:90" ht="18.75" x14ac:dyDescent="0.3">
       <c r="C72" s="19"/>
-      <c r="D72" s="44" t="s">
+      <c r="D72" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="E72" s="44"/>
-      <c r="F72" s="44"/>
-      <c r="G72" s="44"/>
-      <c r="BN72" s="19"/>
-    </row>
-    <row r="73" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="E72" s="42"/>
+      <c r="F72" s="42"/>
+      <c r="G72" s="42"/>
+      <c r="BN72" s="16"/>
+      <c r="BO72" s="16"/>
+      <c r="CL72" s="19"/>
+    </row>
+    <row r="73" spans="3:90" x14ac:dyDescent="0.25">
       <c r="C73" s="19"/>
       <c r="D73" s="16"/>
-      <c r="BN73" s="19"/>
-    </row>
-    <row r="74" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="H73" s="16"/>
+      <c r="I73" s="16"/>
+      <c r="J73" s="16"/>
+      <c r="AA73" s="16"/>
+      <c r="BN73" s="16"/>
+      <c r="BO73" s="16"/>
+      <c r="CL73" s="19"/>
+    </row>
+    <row r="74" spans="3:90" ht="24" x14ac:dyDescent="0.25">
       <c r="D74" s="18"/>
-      <c r="BN74" s="19"/>
-    </row>
-    <row r="75" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="I74" s="50"/>
+      <c r="J74" s="50"/>
+      <c r="CL74" s="19"/>
+    </row>
+    <row r="75" spans="3:90" ht="24" x14ac:dyDescent="0.25">
       <c r="D75" s="18"/>
-      <c r="BN75" s="19"/>
-    </row>
-    <row r="76" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="I75" s="50"/>
+      <c r="J75" s="50"/>
+      <c r="CL75" s="19"/>
+    </row>
+    <row r="76" spans="3:90" ht="24" x14ac:dyDescent="0.25">
       <c r="D76" s="18"/>
-      <c r="W76" s="16"/>
-      <c r="X76" s="16"/>
-      <c r="Y76" s="16"/>
-      <c r="Z76" s="16"/>
-      <c r="AA76" s="16"/>
-      <c r="AB76" s="16"/>
-      <c r="AC76" s="16"/>
-      <c r="AD76" s="16"/>
-      <c r="AE76" s="16"/>
-      <c r="BN76" s="19"/>
-    </row>
-    <row r="77" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="E76" s="49" t="s">
+        <v>31</v>
+      </c>
+      <c r="F76" s="49"/>
+      <c r="G76" s="49"/>
+      <c r="H76" s="49"/>
+      <c r="I76" s="50"/>
+      <c r="J76" s="50"/>
+      <c r="CL76" s="19"/>
+    </row>
+    <row r="77" spans="3:90" x14ac:dyDescent="0.25">
       <c r="D77" s="18"/>
-      <c r="W77" s="16"/>
-      <c r="X77" s="16"/>
-      <c r="Y77" s="16"/>
-      <c r="Z77" s="16"/>
-      <c r="AA77" s="16"/>
-      <c r="AB77" s="16"/>
-      <c r="AC77" s="16"/>
-      <c r="AD77" s="16"/>
-      <c r="AE77" s="16"/>
+      <c r="E77" s="49"/>
+      <c r="F77" s="49"/>
+      <c r="G77" s="49"/>
+      <c r="H77" s="49"/>
+      <c r="AM77" s="16"/>
+      <c r="AN77" s="16"/>
       <c r="AO77" s="16"/>
-      <c r="AP77" s="16"/>
-      <c r="AQ77" s="16"/>
-      <c r="AR77" s="16"/>
-      <c r="AS77" s="16"/>
-      <c r="BN77" s="19"/>
-    </row>
-    <row r="78" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="BM77" s="16"/>
+      <c r="BN77" s="16"/>
+      <c r="CE77" s="16"/>
+      <c r="CL77" s="19"/>
+    </row>
+    <row r="78" spans="3:90" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D78" s="18"/>
-      <c r="F78" s="16" t="s">
+      <c r="F78" s="46" t="s">
+        <v>54</v>
+      </c>
+      <c r="G78" s="46"/>
+      <c r="H78" s="46"/>
+      <c r="I78" s="46"/>
+      <c r="J78" s="46"/>
+      <c r="K78" s="46"/>
+      <c r="L78" s="46"/>
+      <c r="M78" s="46"/>
+      <c r="N78" s="46"/>
+      <c r="O78" s="46"/>
+      <c r="P78" s="46"/>
+      <c r="Q78" s="46"/>
+      <c r="R78" s="46"/>
+      <c r="S78" s="46"/>
+      <c r="T78" s="46"/>
+      <c r="V78" s="16"/>
+      <c r="W78" s="16"/>
+      <c r="X78" s="47" t="s">
+        <v>38</v>
+      </c>
+      <c r="AM78" s="16"/>
+      <c r="AN78" s="16"/>
+      <c r="AO78" s="16"/>
+      <c r="AY78" s="16"/>
+      <c r="AZ78" s="16"/>
+      <c r="BA78" s="16"/>
+      <c r="BM78" s="16"/>
+      <c r="BN78" s="16"/>
+      <c r="CL78" s="61"/>
+    </row>
+    <row r="79" spans="3:90" x14ac:dyDescent="0.25">
+      <c r="D79" s="18"/>
+      <c r="F79" s="46"/>
+      <c r="G79" s="46"/>
+      <c r="H79" s="46"/>
+      <c r="I79" s="46"/>
+      <c r="J79" s="46"/>
+      <c r="K79" s="46"/>
+      <c r="L79" s="46"/>
+      <c r="M79" s="46"/>
+      <c r="N79" s="46"/>
+      <c r="O79" s="46"/>
+      <c r="P79" s="46"/>
+      <c r="Q79" s="46"/>
+      <c r="R79" s="46"/>
+      <c r="S79" s="46"/>
+      <c r="T79" s="46"/>
+      <c r="V79" s="16"/>
+      <c r="W79" s="16"/>
+      <c r="Y79" s="48" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z79" s="48"/>
+      <c r="AA79" s="48"/>
+      <c r="AB79" s="48"/>
+      <c r="AC79" s="48"/>
+      <c r="AD79" s="48"/>
+      <c r="AE79" s="48"/>
+      <c r="AF79" s="48"/>
+      <c r="AG79" s="48"/>
+      <c r="AH79" s="48"/>
+      <c r="AM79" s="16"/>
+      <c r="AN79" s="16"/>
+      <c r="AO79" s="16"/>
+      <c r="AS79" s="56"/>
+      <c r="AY79" s="16"/>
+      <c r="AZ79" s="16"/>
+      <c r="BA79" s="16"/>
+      <c r="BM79" s="16"/>
+      <c r="BN79" s="16"/>
+      <c r="CL79" s="61"/>
+    </row>
+    <row r="80" spans="3:90" x14ac:dyDescent="0.25">
+      <c r="D80" s="18"/>
+      <c r="F80" s="46"/>
+      <c r="G80" s="46"/>
+      <c r="H80" s="46"/>
+      <c r="I80" s="46"/>
+      <c r="J80" s="46"/>
+      <c r="K80" s="46"/>
+      <c r="L80" s="46"/>
+      <c r="M80" s="46"/>
+      <c r="N80" s="46"/>
+      <c r="O80" s="46"/>
+      <c r="P80" s="46"/>
+      <c r="Q80" s="46"/>
+      <c r="R80" s="46"/>
+      <c r="S80" s="46"/>
+      <c r="T80" s="46"/>
+      <c r="V80" s="16"/>
+      <c r="W80" s="16"/>
+      <c r="Y80" s="48"/>
+      <c r="Z80" s="48"/>
+      <c r="AA80" s="48"/>
+      <c r="AB80" s="48"/>
+      <c r="AC80" s="48"/>
+      <c r="AD80" s="48"/>
+      <c r="AE80" s="48"/>
+      <c r="AF80" s="48"/>
+      <c r="AG80" s="48"/>
+      <c r="AH80" s="48"/>
+      <c r="AI80" s="16"/>
+      <c r="AJ80" s="16"/>
+      <c r="AK80" s="16"/>
+      <c r="AL80" s="16"/>
+      <c r="AM80" s="16"/>
+      <c r="AN80" s="16"/>
+      <c r="AO80" s="16"/>
+      <c r="AY80" s="16"/>
+      <c r="AZ80" s="16"/>
+      <c r="BA80" s="16"/>
+      <c r="CL80" s="61"/>
+    </row>
+    <row r="81" spans="4:91" x14ac:dyDescent="0.25">
+      <c r="D81" s="18"/>
+      <c r="F81" s="46"/>
+      <c r="G81" s="46"/>
+      <c r="H81" s="46"/>
+      <c r="I81" s="46"/>
+      <c r="J81" s="46"/>
+      <c r="K81" s="46"/>
+      <c r="L81" s="46"/>
+      <c r="M81" s="46"/>
+      <c r="N81" s="46"/>
+      <c r="O81" s="46"/>
+      <c r="P81" s="46"/>
+      <c r="Q81" s="46"/>
+      <c r="R81" s="46"/>
+      <c r="S81" s="46"/>
+      <c r="T81" s="46"/>
+      <c r="V81" s="16"/>
+      <c r="W81" s="16"/>
+      <c r="Y81" s="48"/>
+      <c r="Z81" s="48"/>
+      <c r="AA81" s="48"/>
+      <c r="AB81" s="48"/>
+      <c r="AC81" s="48"/>
+      <c r="AD81" s="48"/>
+      <c r="AE81" s="48"/>
+      <c r="AF81" s="48"/>
+      <c r="AG81" s="48"/>
+      <c r="AH81" s="48"/>
+      <c r="AI81" s="16"/>
+      <c r="AJ81" s="16"/>
+      <c r="AK81" s="16"/>
+      <c r="AL81" s="16"/>
+      <c r="AM81" s="16"/>
+      <c r="AN81" s="16"/>
+      <c r="AO81" s="16"/>
+      <c r="AY81" s="16"/>
+      <c r="AZ81" s="16"/>
+      <c r="BA81" s="16"/>
+      <c r="BB81" s="16"/>
+      <c r="CL81" s="61"/>
+    </row>
+    <row r="82" spans="4:91" x14ac:dyDescent="0.25">
+      <c r="D82" s="18"/>
+      <c r="F82" s="46"/>
+      <c r="G82" s="46"/>
+      <c r="H82" s="46"/>
+      <c r="I82" s="46"/>
+      <c r="J82" s="46"/>
+      <c r="K82" s="46"/>
+      <c r="L82" s="46"/>
+      <c r="M82" s="46"/>
+      <c r="N82" s="46"/>
+      <c r="O82" s="46"/>
+      <c r="P82" s="46"/>
+      <c r="Q82" s="46"/>
+      <c r="R82" s="46"/>
+      <c r="S82" s="46"/>
+      <c r="T82" s="46"/>
+      <c r="V82" s="16"/>
+      <c r="W82" s="16"/>
+      <c r="AI82" s="16"/>
+      <c r="AJ82" s="16"/>
+      <c r="AK82" s="16"/>
+      <c r="AL82" s="16"/>
+      <c r="AM82" s="16"/>
+      <c r="AN82" s="16"/>
+      <c r="AO82" s="16"/>
+      <c r="AY82" s="16"/>
+      <c r="AZ82" s="16"/>
+      <c r="BA82" s="16"/>
+      <c r="BB82" s="16"/>
+      <c r="CL82" s="61"/>
+    </row>
+    <row r="83" spans="4:91" ht="21" x14ac:dyDescent="0.35">
+      <c r="D83" s="18"/>
+      <c r="F83" s="68" t="s">
+        <v>32</v>
+      </c>
+      <c r="O83" s="45"/>
+      <c r="P83" s="45"/>
+      <c r="Q83" s="45"/>
+      <c r="V83" s="16"/>
+      <c r="W83" s="16"/>
+      <c r="Y83" s="48" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z83" s="48"/>
+      <c r="AA83" s="48"/>
+      <c r="AB83" s="48"/>
+      <c r="AC83" s="48"/>
+      <c r="AD83" s="48"/>
+      <c r="AE83" s="48"/>
+      <c r="AF83" s="48"/>
+      <c r="AG83" s="48"/>
+      <c r="AH83" s="48"/>
+      <c r="AI83" s="16"/>
+      <c r="AJ83" s="16"/>
+      <c r="AK83" s="16"/>
+      <c r="AL83" s="16"/>
+      <c r="AM83" s="16"/>
+      <c r="AN83" s="16"/>
+      <c r="AO83" s="16"/>
+      <c r="AY83" s="16"/>
+      <c r="AZ83" s="16"/>
+      <c r="BA83" s="16"/>
+      <c r="BB83" s="16"/>
+      <c r="BP83" t="s">
         <v>29</v>
       </c>
-      <c r="Q78" t="s">
-        <v>31</v>
+      <c r="CL83" s="61"/>
+    </row>
+    <row r="84" spans="4:91" ht="21" x14ac:dyDescent="0.35">
+      <c r="D84" s="18"/>
+      <c r="G84" s="67" t="s">
+        <v>33</v>
       </c>
-      <c r="W78" s="16"/>
-      <c r="X78" s="16"/>
-      <c r="Y78" s="16"/>
-      <c r="Z78" s="16"/>
-      <c r="AA78" s="16"/>
-      <c r="AB78" s="16"/>
-      <c r="AC78" s="16"/>
-      <c r="AD78" s="16"/>
-      <c r="AE78" s="16"/>
-      <c r="AH78" t="s">
-        <v>32</v>
-      </c>
-      <c r="AO78" s="16"/>
-      <c r="AP78" s="16"/>
-      <c r="AQ78" s="16"/>
-      <c r="AR78" s="16"/>
-      <c r="AS78" s="16"/>
-      <c r="AV78" t="s">
+      <c r="O84" s="45"/>
+      <c r="P84" s="45"/>
+      <c r="Q84" s="45"/>
+      <c r="V84" s="16"/>
+      <c r="W84" s="16"/>
+      <c r="Y84" s="48"/>
+      <c r="Z84" s="48"/>
+      <c r="AA84" s="48"/>
+      <c r="AB84" s="48"/>
+      <c r="AC84" s="48"/>
+      <c r="AD84" s="48"/>
+      <c r="AE84" s="48"/>
+      <c r="AF84" s="48"/>
+      <c r="AG84" s="48"/>
+      <c r="AH84" s="48"/>
+      <c r="AI84" s="16"/>
+      <c r="AJ84" s="16"/>
+      <c r="AK84" s="16"/>
+      <c r="AL84" s="16"/>
+      <c r="AM84" s="16"/>
+      <c r="AN84" s="16"/>
+      <c r="AO84" s="16"/>
+      <c r="AY84" s="16"/>
+      <c r="AZ84" s="16"/>
+      <c r="BA84" s="16"/>
+      <c r="BB84" s="16"/>
+      <c r="CL84" s="61"/>
+    </row>
+    <row r="85" spans="4:91" ht="21" x14ac:dyDescent="0.35">
+      <c r="D85" s="18"/>
+      <c r="G85" s="67" t="s">
         <v>34</v>
       </c>
-      <c r="BN78" s="19"/>
-    </row>
-    <row r="79" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="D79" s="18"/>
-      <c r="W79" s="16"/>
-      <c r="X79" s="16"/>
-      <c r="Y79" s="16"/>
-      <c r="Z79" s="16"/>
-      <c r="AA79" s="16"/>
-      <c r="AB79" s="16"/>
-      <c r="AC79" s="16"/>
-      <c r="AD79" s="16"/>
-      <c r="AE79" s="16"/>
-      <c r="AO79" s="16"/>
-      <c r="AP79" s="16"/>
-      <c r="AQ79" s="16"/>
-      <c r="AR79" s="16"/>
-      <c r="AS79" s="16"/>
-      <c r="BG79" t="s">
-        <v>30</v>
+      <c r="V85" s="16"/>
+      <c r="W85" s="16"/>
+      <c r="AI85" s="16"/>
+      <c r="AJ85" s="16"/>
+      <c r="AK85" s="16"/>
+      <c r="AL85" s="16"/>
+      <c r="AM85" s="16"/>
+      <c r="AN85" s="16"/>
+      <c r="AO85" s="16"/>
+      <c r="AY85" s="16"/>
+      <c r="AZ85" s="16"/>
+      <c r="BA85" s="16"/>
+      <c r="BB85" s="16"/>
+      <c r="CL85" s="61"/>
+    </row>
+    <row r="86" spans="4:91" ht="21" x14ac:dyDescent="0.35">
+      <c r="D86" s="18"/>
+      <c r="G86" s="67" t="s">
+        <v>35</v>
       </c>
-      <c r="BN79" s="19"/>
-    </row>
-    <row r="80" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="D80" s="18"/>
-      <c r="W80" s="16"/>
-      <c r="X80" s="16"/>
-      <c r="Y80" s="16"/>
-      <c r="Z80" s="16"/>
-      <c r="AA80" s="16"/>
-      <c r="AB80" s="16"/>
-      <c r="AC80" s="16"/>
-      <c r="AD80" s="16"/>
-      <c r="AE80" s="16"/>
-      <c r="AO80" s="16"/>
-      <c r="AP80" s="16"/>
-      <c r="AQ80" s="16"/>
-      <c r="AR80" s="16"/>
-      <c r="AS80" s="16"/>
-      <c r="BN80" s="19"/>
-    </row>
-    <row r="81" spans="4:66" x14ac:dyDescent="0.25">
-      <c r="D81" s="18"/>
-      <c r="W81" s="16"/>
-      <c r="X81" s="16"/>
-      <c r="Y81" s="16"/>
-      <c r="Z81" s="16"/>
-      <c r="AA81" s="16"/>
-      <c r="AB81" s="16"/>
-      <c r="AC81" s="16"/>
-      <c r="AD81" s="16"/>
-      <c r="AE81" s="16"/>
-      <c r="AO81" s="16"/>
-      <c r="AP81" s="16"/>
-      <c r="AQ81" s="16"/>
-      <c r="AR81" s="16"/>
-      <c r="AS81" s="16"/>
-      <c r="BN81" s="19"/>
-    </row>
-    <row r="82" spans="4:66" x14ac:dyDescent="0.25">
-      <c r="D82" s="18"/>
-      <c r="W82" s="16"/>
-      <c r="X82" s="16"/>
-      <c r="Y82" s="16"/>
-      <c r="Z82" s="16"/>
-      <c r="AA82" s="16"/>
-      <c r="AB82" s="16"/>
-      <c r="AC82" s="16"/>
-      <c r="AD82" s="16"/>
-      <c r="AE82" s="16"/>
-      <c r="AO82" s="16"/>
-      <c r="AP82" s="16"/>
-      <c r="AQ82" s="16"/>
-      <c r="AR82" s="16"/>
-      <c r="AS82" s="16"/>
-      <c r="BN82" s="19"/>
-    </row>
-    <row r="83" spans="4:66" x14ac:dyDescent="0.25">
-      <c r="D83" s="18"/>
-      <c r="W83" s="16"/>
-      <c r="X83" s="16"/>
-      <c r="Y83" s="16"/>
-      <c r="Z83" s="16"/>
-      <c r="AA83" s="16"/>
-      <c r="AB83" s="16"/>
-      <c r="AC83" s="16"/>
-      <c r="AD83" s="16"/>
-      <c r="AE83" s="16"/>
-      <c r="AO83" s="16"/>
-      <c r="AP83" s="16"/>
-      <c r="AQ83" s="16"/>
-      <c r="AR83" s="16"/>
-      <c r="AS83" s="16"/>
-      <c r="BN83" s="19"/>
-    </row>
-    <row r="84" spans="4:66" x14ac:dyDescent="0.25">
-      <c r="D84" s="18"/>
-      <c r="W84" s="16"/>
-      <c r="X84" s="16"/>
-      <c r="Y84" s="16"/>
-      <c r="Z84" s="16"/>
-      <c r="AA84" s="16"/>
-      <c r="AB84" s="16"/>
-      <c r="AC84" s="16"/>
-      <c r="AD84" s="16"/>
-      <c r="AE84" s="16"/>
-      <c r="AO84" s="16"/>
-      <c r="AP84" s="16"/>
-      <c r="AQ84" s="16"/>
-      <c r="AR84" s="16"/>
-      <c r="AS84" s="16"/>
-      <c r="BN84" s="19"/>
-    </row>
-    <row r="85" spans="4:66" x14ac:dyDescent="0.25">
-      <c r="D85" s="18"/>
-      <c r="W85" s="16"/>
-      <c r="X85" s="16"/>
-      <c r="Y85" s="16"/>
-      <c r="Z85" s="16"/>
-      <c r="AA85" s="16"/>
-      <c r="AB85" s="16"/>
-      <c r="AC85" s="16"/>
-      <c r="AD85" s="16"/>
-      <c r="AE85" s="16"/>
-      <c r="AO85" s="16"/>
-      <c r="AP85" s="16"/>
-      <c r="AQ85" s="16"/>
-      <c r="AR85" s="16"/>
-      <c r="AS85" s="16"/>
-      <c r="BN85" s="19"/>
-    </row>
-    <row r="86" spans="4:66" x14ac:dyDescent="0.25">
-      <c r="D86" s="18"/>
       <c r="W86" s="16"/>
-      <c r="X86" s="16"/>
-      <c r="Y86" s="16"/>
-      <c r="Z86" s="16"/>
-      <c r="AA86" s="16"/>
-      <c r="AB86" s="16"/>
-      <c r="AC86" s="16"/>
-      <c r="AD86" s="16"/>
-      <c r="AE86" s="16"/>
+      <c r="Y86" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z86" s="55"/>
+      <c r="AA86" s="55"/>
+      <c r="AB86" s="55"/>
+      <c r="AC86" s="55"/>
+      <c r="AD86" s="55"/>
+      <c r="AE86" s="55"/>
+      <c r="AF86" s="55"/>
+      <c r="AG86" s="55"/>
+      <c r="AH86" s="55"/>
+      <c r="AI86" s="16"/>
+      <c r="AJ86" s="16"/>
+      <c r="AK86" s="16"/>
+      <c r="AL86" s="16"/>
+      <c r="AM86" s="16"/>
+      <c r="AN86" s="16"/>
       <c r="AO86" s="16"/>
-      <c r="AP86" s="16"/>
-      <c r="AQ86" s="16"/>
-      <c r="AR86" s="16"/>
-      <c r="AS86" s="16"/>
-      <c r="BN86" s="19"/>
-    </row>
-    <row r="87" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="AY86" s="16"/>
+      <c r="AZ86" s="16"/>
+      <c r="BA86" s="16"/>
+      <c r="BB86" s="16"/>
+      <c r="CL86" s="61"/>
+    </row>
+    <row r="87" spans="4:91" ht="21" x14ac:dyDescent="0.35">
       <c r="D87" s="18"/>
-      <c r="W87" s="16"/>
+      <c r="G87" s="67" t="s">
+        <v>36</v>
+      </c>
       <c r="X87" s="16"/>
-      <c r="Y87" s="16"/>
-      <c r="Z87" s="16"/>
-      <c r="AA87" s="16"/>
-      <c r="AB87" s="16"/>
-      <c r="AC87" s="16"/>
-      <c r="AD87" s="16"/>
-      <c r="AE87" s="16"/>
+      <c r="Y87" s="55"/>
+      <c r="Z87" s="55"/>
+      <c r="AA87" s="55"/>
+      <c r="AB87" s="55"/>
+      <c r="AC87" s="55"/>
+      <c r="AD87" s="55"/>
+      <c r="AE87" s="55"/>
+      <c r="AF87" s="55"/>
+      <c r="AG87" s="55"/>
+      <c r="AH87" s="55"/>
+      <c r="AI87" s="16"/>
+      <c r="AJ87" s="16"/>
+      <c r="AK87" s="16"/>
+      <c r="AL87" s="16"/>
+      <c r="AM87" s="16"/>
+      <c r="AN87" s="16"/>
       <c r="AO87" s="16"/>
-      <c r="AP87" s="16"/>
-      <c r="AQ87" s="16"/>
-      <c r="AR87" s="16"/>
-      <c r="AS87" s="16"/>
-      <c r="BN87" s="19"/>
-    </row>
-    <row r="88" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="AY87" s="16"/>
+      <c r="AZ87" s="16"/>
+      <c r="BA87" s="16"/>
+      <c r="BB87" s="16"/>
+      <c r="CL87" s="61"/>
+    </row>
+    <row r="88" spans="4:91" ht="21" x14ac:dyDescent="0.35">
       <c r="D88" s="18"/>
-      <c r="W88" s="16"/>
-      <c r="X88" s="16"/>
-      <c r="Y88" s="16"/>
-      <c r="Z88" s="16"/>
-      <c r="AA88" s="16"/>
-      <c r="AB88" s="16"/>
-      <c r="AC88" s="16"/>
-      <c r="AD88" s="16"/>
-      <c r="AE88" s="16"/>
+      <c r="G88" s="67" t="s">
+        <v>37</v>
+      </c>
+      <c r="AG88" s="16"/>
+      <c r="AH88" s="16"/>
+      <c r="AI88" s="16"/>
+      <c r="AJ88" s="16"/>
+      <c r="AK88" s="16"/>
+      <c r="AL88" s="16"/>
+      <c r="AM88" s="16"/>
+      <c r="AN88" s="16"/>
       <c r="AO88" s="16"/>
-      <c r="AP88" s="16"/>
-      <c r="AQ88" s="16"/>
-      <c r="AR88" s="16"/>
-      <c r="AS88" s="16"/>
-      <c r="BN88" s="19"/>
-    </row>
-    <row r="89" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="AY88" s="16"/>
+      <c r="AZ88" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="BA88" s="16"/>
+      <c r="BB88" s="16"/>
+      <c r="BM88" s="51" t="s">
+        <v>70</v>
+      </c>
+      <c r="CL88" s="61"/>
+    </row>
+    <row r="89" spans="4:91" ht="18.75" x14ac:dyDescent="0.3">
       <c r="D89" s="18"/>
-      <c r="W89" s="16"/>
-      <c r="X89" s="16"/>
-      <c r="Y89" s="16"/>
-      <c r="Z89" s="16"/>
-      <c r="AA89" s="16"/>
-      <c r="AB89" s="16"/>
-      <c r="AC89" s="16"/>
-      <c r="AD89" s="16"/>
-      <c r="AE89" s="16"/>
       <c r="AG89" s="16"/>
       <c r="AH89" s="16"/>
-      <c r="AO89" s="16"/>
-      <c r="AP89" s="16"/>
-      <c r="AQ89" s="16"/>
-      <c r="AR89" s="16"/>
-      <c r="AS89" s="16"/>
-      <c r="BN89" s="19"/>
-    </row>
-    <row r="90" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="AI89" s="16"/>
+      <c r="AJ89" s="16"/>
+      <c r="AK89" s="16"/>
+      <c r="AL89" s="16"/>
+      <c r="AM89" s="16"/>
+      <c r="AN89" s="16"/>
+      <c r="AO89" s="65" t="s">
+        <v>68</v>
+      </c>
+      <c r="AY89" s="16"/>
+      <c r="AZ89" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="BA89" s="16"/>
+      <c r="BB89" s="16"/>
+      <c r="BM89" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="CL89" s="61"/>
+      <c r="CM89" s="60"/>
+    </row>
+    <row r="90" spans="4:91" ht="18.75" x14ac:dyDescent="0.3">
       <c r="D90" s="18"/>
-      <c r="W90" s="16"/>
-      <c r="X90" s="16"/>
-      <c r="Y90" s="16"/>
-      <c r="Z90" s="16"/>
-      <c r="AA90" s="16"/>
-      <c r="AB90" s="16"/>
-      <c r="AC90" s="16"/>
-      <c r="AD90" s="16"/>
-      <c r="AE90" s="16"/>
       <c r="AG90" s="16"/>
       <c r="AH90" s="16"/>
-      <c r="AO90" s="16"/>
-      <c r="AP90" s="16"/>
+      <c r="AI90" s="16"/>
+      <c r="AJ90" s="16"/>
+      <c r="AK90" s="16"/>
+      <c r="AL90" s="16"/>
+      <c r="AM90" s="16"/>
+      <c r="AN90" s="16"/>
+      <c r="AO90" s="24" t="s">
+        <v>51</v>
+      </c>
       <c r="AQ90" s="16"/>
       <c r="AR90" s="16"/>
-      <c r="AS90" s="16"/>
-      <c r="BN90" s="19"/>
-    </row>
-    <row r="91" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="AY90" s="16"/>
+      <c r="AZ90" s="16"/>
+      <c r="BA90" s="16"/>
+      <c r="BB90" s="16"/>
+      <c r="CE90" s="59"/>
+      <c r="CF90" s="59"/>
+      <c r="CG90" s="59"/>
+      <c r="CH90" s="59"/>
+      <c r="CI90" s="59"/>
+      <c r="CJ90" s="59"/>
+      <c r="CK90" s="59"/>
+      <c r="CL90" s="61"/>
+    </row>
+    <row r="91" spans="4:91" x14ac:dyDescent="0.25">
       <c r="D91" s="18"/>
-      <c r="W91" s="16"/>
-      <c r="X91" s="16"/>
-      <c r="Y91" s="16"/>
-      <c r="Z91" s="16"/>
-      <c r="AA91" s="16"/>
-      <c r="AB91" s="16"/>
-      <c r="AC91" s="16"/>
-      <c r="AD91" s="16"/>
-      <c r="AE91" s="16"/>
       <c r="AG91" s="16"/>
       <c r="AH91" s="16"/>
+      <c r="AI91" s="16"/>
+      <c r="AJ91" s="16"/>
+      <c r="AK91" s="16"/>
+      <c r="AL91" s="16"/>
+      <c r="AM91" s="16"/>
+      <c r="AN91" s="16"/>
       <c r="AO91" s="16"/>
-      <c r="AP91" s="16"/>
       <c r="AQ91" s="16"/>
       <c r="AR91" s="16"/>
-      <c r="AS91" s="16"/>
-      <c r="BN91" s="19"/>
-    </row>
-    <row r="92" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="AY91" s="16"/>
+      <c r="AZ91" s="16"/>
+      <c r="BA91" s="16"/>
+      <c r="BB91" s="16"/>
+      <c r="CA91" s="46" t="s">
+        <v>71</v>
+      </c>
+      <c r="CB91" s="46"/>
+      <c r="CC91" s="46"/>
+      <c r="CD91" s="46"/>
+      <c r="CE91" s="46"/>
+      <c r="CF91" s="46"/>
+      <c r="CG91" s="46"/>
+      <c r="CH91" s="59"/>
+      <c r="CI91" s="59"/>
+      <c r="CJ91" s="59"/>
+      <c r="CK91" s="59"/>
+      <c r="CL91" s="61"/>
+    </row>
+    <row r="92" spans="4:91" ht="18.75" x14ac:dyDescent="0.3">
       <c r="D92" s="18"/>
-      <c r="W92" s="16"/>
-      <c r="X92" s="16"/>
-      <c r="Y92" s="16"/>
-      <c r="Z92" s="16"/>
-      <c r="AA92" s="16"/>
-      <c r="AB92" s="16"/>
-      <c r="AC92" s="16"/>
-      <c r="AD92" s="16"/>
-      <c r="AE92" s="16"/>
-      <c r="AG92" s="16"/>
-      <c r="AH92" s="16"/>
+      <c r="E92" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="M92" s="66" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y92" s="65" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z92" s="65"/>
+      <c r="AA92" s="65"/>
+      <c r="AB92" s="65"/>
+      <c r="AC92" s="65"/>
+      <c r="AD92" s="65"/>
+      <c r="AE92" s="65"/>
+      <c r="AF92" s="65"/>
+      <c r="AG92" s="65"/>
+      <c r="AH92" s="65"/>
+      <c r="AI92" s="65"/>
+      <c r="AJ92" s="65"/>
+      <c r="AK92" s="65"/>
+      <c r="AL92" s="16"/>
+      <c r="AM92" s="16"/>
+      <c r="AN92" s="16"/>
       <c r="AO92" s="16"/>
-      <c r="AP92" s="16"/>
       <c r="AQ92" s="16"/>
       <c r="AR92" s="16"/>
-      <c r="AS92" s="16"/>
-      <c r="BN92" s="19"/>
-    </row>
-    <row r="93" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="AY92" s="16"/>
+      <c r="AZ92" s="16"/>
+      <c r="BA92" s="16"/>
+      <c r="BB92" s="16"/>
+      <c r="CA92" s="46"/>
+      <c r="CB92" s="46"/>
+      <c r="CC92" s="46"/>
+      <c r="CD92" s="46"/>
+      <c r="CE92" s="46"/>
+      <c r="CF92" s="46"/>
+      <c r="CG92" s="46"/>
+      <c r="CH92" s="59"/>
+      <c r="CI92" s="59"/>
+      <c r="CJ92" s="59"/>
+      <c r="CK92" s="59"/>
+      <c r="CL92" s="61"/>
+    </row>
+    <row r="93" spans="4:91" x14ac:dyDescent="0.25">
       <c r="D93" s="18"/>
-      <c r="W93" s="16"/>
-      <c r="X93" s="16"/>
-      <c r="Y93" s="16"/>
-      <c r="Z93" s="16"/>
-      <c r="AA93" s="16"/>
-      <c r="AB93" s="16"/>
-      <c r="AC93" s="16"/>
-      <c r="AD93" s="16"/>
-      <c r="AE93" s="16"/>
       <c r="AG93" s="16"/>
       <c r="AH93" s="16"/>
+      <c r="AI93" s="16"/>
+      <c r="AJ93" s="16"/>
+      <c r="AK93" s="16"/>
+      <c r="AL93" s="16"/>
+      <c r="AM93" s="16"/>
+      <c r="AN93" s="16"/>
       <c r="AO93" s="16"/>
-      <c r="AP93" s="16"/>
       <c r="AQ93" s="16"/>
       <c r="AR93" s="16"/>
-      <c r="AS93" s="16"/>
-      <c r="BN93" s="19"/>
-    </row>
-    <row r="94" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="AY93" s="16"/>
+      <c r="AZ93" s="16"/>
+      <c r="BA93" s="16"/>
+      <c r="BB93" s="16"/>
+      <c r="CA93" s="46"/>
+      <c r="CB93" s="46"/>
+      <c r="CC93" s="46"/>
+      <c r="CD93" s="46"/>
+      <c r="CE93" s="46"/>
+      <c r="CF93" s="46"/>
+      <c r="CG93" s="46"/>
+      <c r="CH93" s="59"/>
+      <c r="CI93" s="59"/>
+      <c r="CJ93" s="59"/>
+      <c r="CK93" s="59"/>
+      <c r="CL93" s="61"/>
+    </row>
+    <row r="94" spans="4:91" x14ac:dyDescent="0.25">
       <c r="D94" s="18"/>
-      <c r="W94" s="16"/>
-      <c r="X94" s="16"/>
-      <c r="Y94" s="16"/>
-      <c r="Z94" s="16"/>
-      <c r="AA94" s="16"/>
-      <c r="AB94" s="16"/>
-      <c r="AC94" s="16"/>
-      <c r="AD94" s="16"/>
-      <c r="AE94" s="16"/>
       <c r="AG94" s="16"/>
       <c r="AH94" s="16"/>
+      <c r="AI94" s="16"/>
+      <c r="AJ94" s="16"/>
+      <c r="AK94" s="16"/>
+      <c r="AL94" s="16"/>
+      <c r="AM94" s="16"/>
+      <c r="AN94" s="16"/>
       <c r="AO94" s="16"/>
-      <c r="AP94" s="16"/>
       <c r="AQ94" s="16"/>
       <c r="AR94" s="16"/>
-      <c r="AS94" s="16"/>
-      <c r="BN94" s="19"/>
-    </row>
-    <row r="95" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="AY94" s="16"/>
+      <c r="AZ94" s="16"/>
+      <c r="BA94" s="16"/>
+      <c r="BB94" s="16"/>
+      <c r="CA94" s="46"/>
+      <c r="CB94" s="46"/>
+      <c r="CC94" s="46"/>
+      <c r="CD94" s="46"/>
+      <c r="CE94" s="46"/>
+      <c r="CF94" s="46"/>
+      <c r="CG94" s="46"/>
+      <c r="CH94" s="59"/>
+      <c r="CI94" s="59"/>
+      <c r="CJ94" s="59"/>
+      <c r="CK94" s="59"/>
+      <c r="CL94" s="61"/>
+    </row>
+    <row r="95" spans="4:91" x14ac:dyDescent="0.25">
       <c r="D95" s="18"/>
-      <c r="W95" s="16"/>
-      <c r="X95" s="16"/>
-      <c r="Y95" s="16"/>
-      <c r="Z95" s="16"/>
-      <c r="AA95" s="16"/>
-      <c r="AB95" s="16"/>
-      <c r="AC95" s="16"/>
-      <c r="AD95" s="16"/>
-      <c r="AE95" s="16"/>
       <c r="AG95" s="16"/>
       <c r="AH95" s="16"/>
+      <c r="AI95" s="16"/>
+      <c r="AJ95" s="16"/>
+      <c r="AK95" s="16"/>
+      <c r="AL95" s="16"/>
+      <c r="AM95" s="16"/>
+      <c r="AN95" s="16"/>
       <c r="AO95" s="16"/>
-      <c r="AP95" s="16"/>
       <c r="AQ95" s="16"/>
       <c r="AR95" s="16"/>
-      <c r="AS95" s="16"/>
-      <c r="BN95" s="19"/>
-    </row>
-    <row r="96" spans="4:66" x14ac:dyDescent="0.25">
+      <c r="AY95" s="16"/>
+      <c r="AZ95" s="16"/>
+      <c r="BA95" s="16"/>
+      <c r="BB95" s="16"/>
+      <c r="CA95" s="46"/>
+      <c r="CB95" s="46"/>
+      <c r="CC95" s="46"/>
+      <c r="CD95" s="46"/>
+      <c r="CE95" s="46"/>
+      <c r="CF95" s="46"/>
+      <c r="CG95" s="46"/>
+      <c r="CH95" s="59"/>
+      <c r="CI95" s="59"/>
+      <c r="CJ95" s="59"/>
+      <c r="CK95" s="59"/>
+      <c r="CL95" s="61"/>
+    </row>
+    <row r="96" spans="4:91" x14ac:dyDescent="0.25">
       <c r="D96" s="18"/>
-      <c r="W96" s="16"/>
-      <c r="X96" s="16"/>
-      <c r="Y96" s="16"/>
-      <c r="Z96" s="16"/>
-      <c r="AA96" s="16"/>
-      <c r="AB96" s="16"/>
-      <c r="AC96" s="16"/>
-      <c r="AD96" s="16"/>
-      <c r="AE96" s="16"/>
       <c r="AG96" s="16"/>
       <c r="AH96" s="16"/>
+      <c r="AI96" s="16"/>
+      <c r="AJ96" s="16"/>
+      <c r="AK96" s="16"/>
+      <c r="AL96" s="16"/>
+      <c r="AM96" s="16"/>
+      <c r="AN96" s="16"/>
       <c r="AO96" s="16"/>
-      <c r="AP96" s="16"/>
       <c r="AQ96" s="16"/>
       <c r="AR96" s="16"/>
-      <c r="AS96" s="16"/>
-      <c r="BN96" s="19"/>
-    </row>
-    <row r="97" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="AY96" s="16"/>
+      <c r="AZ96" s="16"/>
+      <c r="BA96" s="16"/>
+      <c r="BB96" s="16"/>
+      <c r="CA96" s="46"/>
+      <c r="CB96" s="46"/>
+      <c r="CC96" s="46"/>
+      <c r="CD96" s="46"/>
+      <c r="CE96" s="46"/>
+      <c r="CF96" s="46"/>
+      <c r="CG96" s="46"/>
+      <c r="CH96" s="59"/>
+      <c r="CI96" s="59"/>
+      <c r="CJ96" s="59"/>
+      <c r="CK96" s="59"/>
+      <c r="CL96" s="61"/>
+    </row>
+    <row r="97" spans="3:218" x14ac:dyDescent="0.25">
       <c r="D97" s="18"/>
-      <c r="W97" s="16"/>
-      <c r="X97" s="16"/>
-      <c r="Y97" s="16"/>
-      <c r="Z97" s="16"/>
-      <c r="AA97" s="16"/>
-      <c r="AB97" s="16"/>
-      <c r="AC97" s="16"/>
-      <c r="AD97" s="16"/>
-      <c r="AE97" s="16"/>
       <c r="AG97" s="16"/>
       <c r="AH97" s="16"/>
+      <c r="AI97" s="16"/>
+      <c r="AJ97" s="16"/>
+      <c r="AK97" s="16"/>
+      <c r="AL97" s="16"/>
+      <c r="AM97" s="16"/>
+      <c r="AN97" s="16"/>
       <c r="AO97" s="16"/>
-      <c r="AP97" s="16"/>
       <c r="AQ97" s="16"/>
       <c r="AR97" s="16"/>
-      <c r="AS97" s="16"/>
-      <c r="BN97" s="19"/>
-    </row>
-    <row r="98" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="AY97" s="16"/>
+      <c r="AZ97" s="16"/>
+      <c r="BA97" s="16"/>
+      <c r="BB97" s="16"/>
+      <c r="CA97" s="46"/>
+      <c r="CB97" s="46"/>
+      <c r="CC97" s="46"/>
+      <c r="CD97" s="46"/>
+      <c r="CE97" s="46"/>
+      <c r="CF97" s="46"/>
+      <c r="CG97" s="46"/>
+      <c r="CH97" s="59"/>
+      <c r="CI97" s="59"/>
+      <c r="CJ97" s="59"/>
+      <c r="CK97" s="59"/>
+      <c r="CL97" s="61"/>
+    </row>
+    <row r="98" spans="3:218" x14ac:dyDescent="0.25">
       <c r="D98" s="18"/>
-      <c r="W98" s="16"/>
-      <c r="X98" s="16"/>
-      <c r="Y98" s="16"/>
-      <c r="Z98" s="16"/>
-      <c r="AA98" s="16"/>
-      <c r="AB98" s="16"/>
-      <c r="AC98" s="16"/>
-      <c r="AD98" s="16"/>
-      <c r="AE98" s="16"/>
       <c r="AG98" s="16"/>
       <c r="AH98" s="16"/>
+      <c r="AI98" s="16"/>
+      <c r="AJ98" s="16"/>
+      <c r="AK98" s="16"/>
+      <c r="AL98" s="16"/>
+      <c r="AM98" s="16"/>
+      <c r="AN98" s="16"/>
       <c r="AO98" s="16"/>
-      <c r="AP98" s="16"/>
       <c r="AQ98" s="16"/>
       <c r="AR98" s="16"/>
-      <c r="AS98" s="16"/>
-      <c r="BN98" s="19"/>
-    </row>
-    <row r="99" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="AY98" s="16"/>
+      <c r="AZ98" s="16"/>
+      <c r="BA98" s="16"/>
+      <c r="BB98" s="16"/>
+      <c r="CA98" s="46"/>
+      <c r="CB98" s="46"/>
+      <c r="CC98" s="46"/>
+      <c r="CD98" s="46"/>
+      <c r="CE98" s="46"/>
+      <c r="CF98" s="46"/>
+      <c r="CG98" s="46"/>
+      <c r="CH98" s="59"/>
+      <c r="CI98" s="59"/>
+      <c r="CJ98" s="59"/>
+      <c r="CK98" s="59"/>
+      <c r="CL98" s="61"/>
+    </row>
+    <row r="99" spans="3:218" x14ac:dyDescent="0.25">
       <c r="D99" s="18"/>
-      <c r="W99" s="16"/>
-      <c r="X99" s="16"/>
-      <c r="Y99" s="16"/>
-      <c r="Z99" s="16"/>
-      <c r="AA99" s="16"/>
-      <c r="AB99" s="16"/>
-      <c r="AC99" s="16"/>
-      <c r="AD99" s="16"/>
-      <c r="AE99" s="16"/>
       <c r="AG99" s="16"/>
       <c r="AH99" s="16"/>
+      <c r="AI99" s="16"/>
+      <c r="AJ99" s="16"/>
+      <c r="AK99" s="16"/>
+      <c r="AL99" s="16"/>
+      <c r="AM99" s="16"/>
+      <c r="AN99" s="16"/>
       <c r="AO99" s="16"/>
-      <c r="AP99" s="16"/>
       <c r="AQ99" s="16"/>
       <c r="AR99" s="16"/>
-      <c r="AS99" s="16"/>
-      <c r="BN99" s="19"/>
-    </row>
-    <row r="100" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="AY99" s="16"/>
+      <c r="AZ99" s="16"/>
+      <c r="BA99" s="16"/>
+      <c r="BB99" s="16"/>
+      <c r="CA99" s="46"/>
+      <c r="CB99" s="46"/>
+      <c r="CC99" s="46"/>
+      <c r="CD99" s="46"/>
+      <c r="CE99" s="46"/>
+      <c r="CF99" s="46"/>
+      <c r="CG99" s="46"/>
+      <c r="CL99" s="19"/>
+    </row>
+    <row r="100" spans="3:218" x14ac:dyDescent="0.25">
       <c r="D100" s="18"/>
-      <c r="W100" s="16"/>
-      <c r="X100" s="16"/>
-      <c r="Y100" s="16"/>
-      <c r="Z100" s="16"/>
-      <c r="AA100" s="16"/>
-      <c r="AB100" s="16"/>
-      <c r="AC100" s="16"/>
-      <c r="AD100" s="16"/>
-      <c r="AE100" s="16"/>
+      <c r="AG100" s="16"/>
+      <c r="AH100" s="16"/>
+      <c r="AI100" s="16"/>
+      <c r="AJ100" s="16"/>
+      <c r="AK100" s="16"/>
+      <c r="AL100" s="16"/>
+      <c r="AM100" s="16"/>
+      <c r="AN100" s="16"/>
       <c r="AO100" s="16"/>
-      <c r="AP100" s="16"/>
       <c r="AQ100" s="16"/>
       <c r="AR100" s="16"/>
-      <c r="AS100" s="16"/>
-      <c r="BN100" s="19"/>
-    </row>
-    <row r="101" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="AY100" s="16"/>
+      <c r="AZ100" s="16"/>
+      <c r="BA100" s="16"/>
+      <c r="BB100" s="16"/>
+      <c r="CA100" s="46"/>
+      <c r="CB100" s="46"/>
+      <c r="CC100" s="46"/>
+      <c r="CD100" s="46"/>
+      <c r="CE100" s="46"/>
+      <c r="CF100" s="46"/>
+      <c r="CG100" s="46"/>
+      <c r="CL100" s="19"/>
+    </row>
+    <row r="101" spans="3:218" x14ac:dyDescent="0.25">
       <c r="D101" s="18"/>
-      <c r="F101" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q101" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="W101" s="16"/>
-      <c r="X101" s="16"/>
-      <c r="Y101" s="16"/>
-      <c r="Z101" s="16"/>
-      <c r="AA101" s="16"/>
-      <c r="AB101" s="16"/>
-      <c r="AC101" s="16"/>
-      <c r="AD101" s="16"/>
-      <c r="AE101" s="16"/>
+      <c r="AG101" s="16"/>
+      <c r="AH101" s="16"/>
+      <c r="AI101" s="16"/>
+      <c r="AJ101" s="16"/>
+      <c r="AK101" s="16"/>
+      <c r="AL101" s="16"/>
+      <c r="AM101" s="16"/>
+      <c r="AN101" s="16"/>
       <c r="AO101" s="16"/>
-      <c r="AP101" s="16"/>
-      <c r="AQ101" s="16"/>
-      <c r="AR101" s="16"/>
-      <c r="AS101" s="16"/>
-      <c r="BN101" s="19"/>
-    </row>
-    <row r="102" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="AY101" s="16"/>
+      <c r="AZ101" s="16"/>
+      <c r="BA101" s="16"/>
+      <c r="BB101" s="16"/>
+      <c r="CA101" s="46"/>
+      <c r="CB101" s="46"/>
+      <c r="CC101" s="46"/>
+      <c r="CD101" s="46"/>
+      <c r="CE101" s="46"/>
+      <c r="CF101" s="46"/>
+      <c r="CG101" s="46"/>
+      <c r="CL101" s="19"/>
+    </row>
+    <row r="102" spans="3:218" x14ac:dyDescent="0.25">
       <c r="D102" s="18"/>
-      <c r="W102" s="16"/>
-      <c r="X102" s="16"/>
-      <c r="Y102" s="16"/>
-      <c r="Z102" s="16"/>
-      <c r="AA102" s="16"/>
-      <c r="AB102" s="16"/>
-      <c r="AC102" s="16"/>
-      <c r="AD102" s="16"/>
-      <c r="AE102" s="16"/>
+      <c r="AA102" s="3"/>
+      <c r="AG102" s="16"/>
+      <c r="AH102" s="16"/>
+      <c r="AI102" s="16"/>
+      <c r="AJ102" s="16"/>
+      <c r="AK102" s="16"/>
+      <c r="AL102" s="16"/>
+      <c r="AM102" s="16"/>
+      <c r="AN102" s="16"/>
       <c r="AO102" s="16"/>
-      <c r="AP102" s="16"/>
-      <c r="AQ102" s="16"/>
-      <c r="AR102" s="16"/>
-      <c r="AS102" s="16"/>
-      <c r="BN102" s="19"/>
-    </row>
-    <row r="103" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="AY102" s="16"/>
+      <c r="AZ102" s="16"/>
+      <c r="BA102" s="16"/>
+      <c r="BB102" s="16"/>
+      <c r="CA102" s="46"/>
+      <c r="CB102" s="46"/>
+      <c r="CC102" s="46"/>
+      <c r="CD102" s="46"/>
+      <c r="CE102" s="46"/>
+      <c r="CF102" s="46"/>
+      <c r="CG102" s="46"/>
+      <c r="CL102" s="19"/>
+    </row>
+    <row r="103" spans="3:218" x14ac:dyDescent="0.25">
       <c r="D103" s="18"/>
-      <c r="W103" s="16"/>
-      <c r="X103" s="16"/>
-      <c r="Y103" s="16"/>
-      <c r="Z103" s="16"/>
-      <c r="AA103" s="16"/>
-      <c r="AB103" s="16"/>
-      <c r="AC103" s="16"/>
-      <c r="AD103" s="16"/>
-      <c r="AE103" s="16"/>
-      <c r="AH103" s="3" t="s">
-        <v>25</v>
-      </c>
+      <c r="AG103" s="16"/>
+      <c r="AH103" s="16"/>
+      <c r="AI103" s="16"/>
+      <c r="AJ103" s="16"/>
+      <c r="AK103" s="16"/>
+      <c r="AL103" s="16"/>
+      <c r="AM103" s="16"/>
+      <c r="AN103" s="16"/>
       <c r="AO103" s="16"/>
-      <c r="AP103" s="16"/>
-      <c r="AQ103" s="16"/>
-      <c r="AR103" s="16"/>
-      <c r="AS103" s="16"/>
-      <c r="BN103" s="19"/>
-    </row>
-    <row r="104" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="AY103" s="16"/>
+      <c r="AZ103" s="16"/>
+      <c r="BA103" s="16"/>
+      <c r="BB103" s="16"/>
+      <c r="CL103" s="19"/>
+    </row>
+    <row r="104" spans="3:218" x14ac:dyDescent="0.25">
       <c r="D104" s="18"/>
-      <c r="AB104" s="16"/>
-      <c r="AC104" s="16"/>
-      <c r="AD104" s="16"/>
-      <c r="AE104" s="16"/>
+      <c r="AG104" s="16"/>
+      <c r="AH104" s="16"/>
+      <c r="AI104" s="16"/>
+      <c r="AJ104" s="16"/>
+      <c r="AK104" s="16"/>
+      <c r="AL104" s="16"/>
+      <c r="AM104" s="16"/>
+      <c r="AN104" s="16"/>
       <c r="AO104" s="16"/>
-      <c r="AP104" s="16"/>
-      <c r="AQ104" s="16"/>
-      <c r="AR104" s="16"/>
-      <c r="AS104" s="16"/>
-      <c r="BN104" s="19"/>
-    </row>
-    <row r="105" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="AY104" s="16"/>
+      <c r="AZ104" s="16"/>
+      <c r="BA104" s="16"/>
+      <c r="BB104" s="16"/>
+      <c r="CL104" s="19"/>
+    </row>
+    <row r="105" spans="3:218" x14ac:dyDescent="0.25">
       <c r="D105" s="18"/>
-      <c r="AB105" s="16"/>
-      <c r="AC105" s="16"/>
-      <c r="AD105" s="16"/>
-      <c r="AE105" s="16"/>
+      <c r="AL105" s="16"/>
+      <c r="AM105" s="16"/>
+      <c r="AN105" s="16"/>
       <c r="AO105" s="16"/>
-      <c r="AP105" s="16"/>
-      <c r="AQ105" s="16"/>
-      <c r="AR105" s="16"/>
-      <c r="AS105" s="16"/>
-      <c r="BN105" s="19"/>
-    </row>
-    <row r="106" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="AY105" s="16"/>
+      <c r="AZ105" s="16"/>
+      <c r="BA105" s="16"/>
+      <c r="BB105" s="16"/>
+      <c r="CL105" s="19"/>
+    </row>
+    <row r="106" spans="3:218" x14ac:dyDescent="0.25">
       <c r="D106" s="18"/>
-      <c r="AB106" s="16"/>
-      <c r="AC106" s="16"/>
-      <c r="AD106" s="16"/>
-      <c r="AE106" s="16"/>
+      <c r="AL106" s="16"/>
+      <c r="AM106" s="16"/>
+      <c r="AN106" s="16"/>
       <c r="AO106" s="16"/>
-      <c r="AP106" s="16"/>
-      <c r="AQ106" s="16"/>
-      <c r="AR106" s="16"/>
-      <c r="AS106" s="16"/>
-      <c r="BN106" s="19"/>
-    </row>
-    <row r="107" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="AY106" s="16"/>
+      <c r="AZ106" s="16"/>
+      <c r="BA106" s="16"/>
+      <c r="BB106" s="16"/>
+      <c r="CL106" s="19"/>
+    </row>
+    <row r="107" spans="3:218" x14ac:dyDescent="0.25">
       <c r="D107" s="18"/>
-      <c r="AB107" s="16"/>
-      <c r="AC107" s="16"/>
-      <c r="AD107" s="16"/>
-      <c r="AE107" s="16"/>
+      <c r="AL107" s="16"/>
+      <c r="AM107" s="16"/>
+      <c r="AN107" s="16"/>
       <c r="AO107" s="16"/>
-      <c r="AP107" s="16"/>
-      <c r="AQ107" s="16"/>
-      <c r="AR107" s="16"/>
-      <c r="AS107" s="16"/>
-      <c r="BN107" s="19"/>
-    </row>
-    <row r="108" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="AY107" s="16"/>
+      <c r="AZ107" s="16"/>
+      <c r="BA107" s="16"/>
+      <c r="BB107" s="16"/>
+      <c r="CL107" s="19"/>
+    </row>
+    <row r="108" spans="3:218" x14ac:dyDescent="0.25">
       <c r="D108" s="18"/>
-      <c r="AB108" s="16"/>
-      <c r="AC108" s="16"/>
-      <c r="AD108" s="16"/>
-      <c r="AE108" s="16"/>
+      <c r="AL108" s="16"/>
+      <c r="AM108" s="16"/>
+      <c r="AN108" s="16"/>
       <c r="AO108" s="16"/>
-      <c r="AP108" s="16"/>
-      <c r="AQ108" s="16"/>
-      <c r="AR108" s="16"/>
-      <c r="AS108" s="16"/>
-      <c r="BN108" s="19"/>
-    </row>
-    <row r="109" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="AY108" s="16"/>
+      <c r="AZ108" s="16"/>
+      <c r="BA108" s="16"/>
+      <c r="BB108" s="16"/>
+      <c r="CL108" s="19"/>
+    </row>
+    <row r="109" spans="3:218" x14ac:dyDescent="0.25">
       <c r="D109" s="18"/>
       <c r="E109" s="16"/>
       <c r="F109" s="16"/>
@@ -6754,9 +8360,10 @@
       <c r="AQ109" s="16"/>
       <c r="AR109" s="16"/>
       <c r="AS109" s="16"/>
-      <c r="BN109" s="19"/>
-    </row>
-    <row r="110" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="BB109" s="16"/>
+      <c r="CL109" s="19"/>
+    </row>
+    <row r="110" spans="3:218" x14ac:dyDescent="0.25">
       <c r="D110" s="18"/>
       <c r="E110" s="16"/>
       <c r="F110" s="16"/>
@@ -6774,74 +8381,100 @@
       <c r="AQ110" s="16"/>
       <c r="AR110" s="16"/>
       <c r="AS110" s="16"/>
-      <c r="BN110" s="19"/>
-    </row>
-    <row r="111" spans="3:66" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D111" s="20"/>
-      <c r="E111" s="21"/>
-      <c r="F111" s="21"/>
-      <c r="G111" s="21"/>
-      <c r="H111" s="21"/>
-      <c r="I111" s="21"/>
-      <c r="J111" s="21"/>
-      <c r="K111" s="21"/>
-      <c r="L111" s="21"/>
-      <c r="M111" s="21"/>
-      <c r="N111" s="21"/>
-      <c r="O111" s="21"/>
-      <c r="P111" s="21"/>
-      <c r="Q111" s="21"/>
-      <c r="R111" s="21"/>
-      <c r="S111" s="21"/>
-      <c r="T111" s="21"/>
-      <c r="U111" s="21"/>
-      <c r="V111" s="21"/>
-      <c r="W111" s="21"/>
-      <c r="X111" s="21"/>
-      <c r="Y111" s="21"/>
-      <c r="Z111" s="21"/>
-      <c r="AA111" s="21"/>
-      <c r="AB111" s="21"/>
-      <c r="AC111" s="21"/>
-      <c r="AD111" s="21"/>
-      <c r="AE111" s="21"/>
-      <c r="AF111" s="21"/>
-      <c r="AG111" s="21"/>
-      <c r="AH111" s="21"/>
-      <c r="AI111" s="21"/>
-      <c r="AJ111" s="21"/>
-      <c r="AK111" s="21"/>
-      <c r="AL111" s="21"/>
-      <c r="AM111" s="21"/>
-      <c r="AN111" s="21"/>
-      <c r="AO111" s="21"/>
-      <c r="AP111" s="21"/>
-      <c r="AQ111" s="21"/>
-      <c r="AR111" s="21"/>
-      <c r="AS111" s="21"/>
-      <c r="AT111" s="21"/>
-      <c r="AU111" s="21"/>
-      <c r="AV111" s="21"/>
-      <c r="AW111" s="21"/>
-      <c r="AX111" s="21"/>
-      <c r="AY111" s="21"/>
-      <c r="AZ111" s="21"/>
-      <c r="BA111" s="21"/>
-      <c r="BB111" s="21"/>
-      <c r="BC111" s="21"/>
-      <c r="BD111" s="21"/>
-      <c r="BE111" s="21"/>
-      <c r="BF111" s="21"/>
-      <c r="BG111" s="21"/>
-      <c r="BH111" s="21"/>
-      <c r="BI111" s="21"/>
-      <c r="BJ111" s="21"/>
-      <c r="BK111" s="21"/>
-      <c r="BL111" s="21"/>
-      <c r="BM111" s="21"/>
-      <c r="BN111" s="22"/>
-    </row>
-    <row r="112" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="BB110" s="16"/>
+      <c r="CL110" s="19"/>
+    </row>
+    <row r="111" spans="3:218" x14ac:dyDescent="0.25">
+      <c r="C111" s="19"/>
+      <c r="D111" s="16"/>
+      <c r="E111" s="16"/>
+      <c r="F111" s="16"/>
+      <c r="G111" s="16"/>
+      <c r="H111" s="16"/>
+      <c r="I111" s="16"/>
+      <c r="J111" s="16"/>
+      <c r="K111" s="16"/>
+      <c r="L111" s="16"/>
+      <c r="M111" s="16"/>
+      <c r="N111" s="16"/>
+      <c r="O111" s="16"/>
+      <c r="P111" s="16"/>
+      <c r="Q111" s="16"/>
+      <c r="R111" s="16"/>
+      <c r="S111" s="16"/>
+      <c r="T111" s="16"/>
+      <c r="U111" s="16"/>
+      <c r="V111" s="16"/>
+      <c r="W111" s="16"/>
+      <c r="X111" s="16"/>
+      <c r="Y111" s="16"/>
+      <c r="Z111" s="16"/>
+      <c r="AA111" s="16"/>
+      <c r="AB111" s="16"/>
+      <c r="AC111" s="16"/>
+      <c r="AD111" s="16"/>
+      <c r="AE111" s="16"/>
+      <c r="AF111" s="16"/>
+      <c r="AG111" s="16"/>
+      <c r="AH111" s="16"/>
+      <c r="AI111" s="16"/>
+      <c r="AJ111" s="16"/>
+      <c r="AK111" s="16"/>
+      <c r="AL111" s="16"/>
+      <c r="AM111" s="16"/>
+      <c r="AN111" s="16"/>
+      <c r="AO111" s="16"/>
+      <c r="AP111" s="16"/>
+      <c r="AQ111" s="16"/>
+      <c r="AR111" s="16"/>
+      <c r="AS111" s="16"/>
+      <c r="AT111" s="16"/>
+      <c r="AU111" s="16"/>
+      <c r="AV111" s="16"/>
+      <c r="AW111" s="16"/>
+      <c r="AX111" s="16"/>
+      <c r="AY111" s="16"/>
+      <c r="AZ111" s="16"/>
+      <c r="BA111" s="16"/>
+      <c r="BB111" s="16"/>
+      <c r="BC111" s="16"/>
+      <c r="BD111" s="16"/>
+      <c r="BE111" s="16"/>
+      <c r="BF111" s="16"/>
+      <c r="BG111" s="16"/>
+      <c r="BH111" s="16"/>
+      <c r="BI111" s="16"/>
+      <c r="BJ111" s="16"/>
+      <c r="BK111" s="16"/>
+      <c r="BL111" s="16"/>
+      <c r="BM111" s="16"/>
+      <c r="BN111" s="16"/>
+      <c r="BO111" s="16"/>
+      <c r="BP111" s="16"/>
+      <c r="BQ111" s="16"/>
+      <c r="BR111" s="16"/>
+      <c r="BS111" s="16"/>
+      <c r="BT111" s="16"/>
+      <c r="BU111" s="16"/>
+      <c r="BV111" s="16"/>
+      <c r="BW111" s="16"/>
+      <c r="BX111" s="16"/>
+      <c r="BY111" s="16"/>
+      <c r="BZ111" s="16"/>
+      <c r="CA111" s="16"/>
+      <c r="CB111" s="16"/>
+      <c r="CC111" s="16"/>
+      <c r="CD111" s="16"/>
+      <c r="CE111" s="16"/>
+      <c r="CF111" s="16"/>
+      <c r="CG111" s="16"/>
+      <c r="CH111" s="16"/>
+      <c r="CI111" s="16"/>
+      <c r="CJ111" s="16"/>
+      <c r="CK111" s="16"/>
+      <c r="CL111" s="19"/>
+    </row>
+    <row r="112" spans="3:218" x14ac:dyDescent="0.25">
       <c r="C112" s="19"/>
       <c r="D112" s="16"/>
       <c r="E112" s="16"/>
@@ -6854,13 +8487,212 @@
       <c r="L112" s="16"/>
       <c r="M112" s="16"/>
       <c r="N112" s="16"/>
+      <c r="O112" s="16"/>
+      <c r="P112" s="16"/>
+      <c r="Q112" s="16"/>
+      <c r="R112" s="16"/>
+      <c r="S112" s="16"/>
+      <c r="T112" s="16"/>
+      <c r="U112" s="16"/>
+      <c r="V112" s="16"/>
+      <c r="W112" s="16"/>
+      <c r="X112" s="16"/>
+      <c r="Y112" s="16"/>
+      <c r="Z112" s="16"/>
+      <c r="AA112" s="16"/>
       <c r="AB112" s="16"/>
       <c r="AC112" s="16"/>
       <c r="AD112" s="16"/>
       <c r="AE112" s="16"/>
-      <c r="BN112" s="19"/>
-    </row>
-    <row r="113" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="AF112" s="16"/>
+      <c r="AG112" s="16"/>
+      <c r="AH112" s="16"/>
+      <c r="AI112" s="16"/>
+      <c r="AJ112" s="16"/>
+      <c r="AK112" s="16"/>
+      <c r="AL112" s="16"/>
+      <c r="AM112" s="16"/>
+      <c r="AN112" s="16"/>
+      <c r="AO112" s="16"/>
+      <c r="AP112" s="16"/>
+      <c r="AQ112" s="16"/>
+      <c r="AR112" s="16"/>
+      <c r="AS112" s="16"/>
+      <c r="AT112" s="16"/>
+      <c r="AU112" s="16"/>
+      <c r="AV112" s="16"/>
+      <c r="AW112" s="16"/>
+      <c r="AX112" s="16"/>
+      <c r="AY112" s="16"/>
+      <c r="AZ112" s="16"/>
+      <c r="BA112" s="16"/>
+      <c r="BB112" s="16"/>
+      <c r="BC112" s="16"/>
+      <c r="BD112" s="16"/>
+      <c r="BE112" s="16"/>
+      <c r="BF112" s="16"/>
+      <c r="BG112" s="16"/>
+      <c r="BH112" s="16"/>
+      <c r="BI112" s="16"/>
+      <c r="BJ112" s="16"/>
+      <c r="BK112" s="16"/>
+      <c r="BL112" s="16"/>
+      <c r="BM112" s="16"/>
+      <c r="BN112" s="16"/>
+      <c r="BO112" s="16"/>
+      <c r="BP112" s="16"/>
+      <c r="BQ112" s="16"/>
+      <c r="BR112" s="16"/>
+      <c r="BS112" s="16"/>
+      <c r="BT112" s="16"/>
+      <c r="BU112" s="16"/>
+      <c r="BV112" s="16"/>
+      <c r="BW112" s="16"/>
+      <c r="BX112" s="16"/>
+      <c r="BY112" s="16"/>
+      <c r="BZ112" s="16"/>
+      <c r="CA112" s="16"/>
+      <c r="CB112" s="16"/>
+      <c r="CC112" s="16"/>
+      <c r="CD112" s="16"/>
+      <c r="CE112" s="16"/>
+      <c r="CF112" s="16"/>
+      <c r="CG112" s="16"/>
+      <c r="CH112" s="16"/>
+      <c r="CI112" s="16"/>
+      <c r="CJ112" s="16"/>
+      <c r="CK112" s="16"/>
+      <c r="CL112" s="16"/>
+      <c r="CM112" s="16"/>
+      <c r="CN112" s="16"/>
+      <c r="CO112" s="16"/>
+      <c r="CP112" s="16"/>
+      <c r="CQ112" s="16"/>
+      <c r="CR112" s="16"/>
+      <c r="CS112" s="16"/>
+      <c r="CT112" s="16"/>
+      <c r="CU112" s="16"/>
+      <c r="CV112" s="16"/>
+      <c r="CW112" s="16"/>
+      <c r="CX112" s="16"/>
+      <c r="CY112" s="16"/>
+      <c r="CZ112" s="16"/>
+      <c r="DA112" s="16"/>
+      <c r="DB112" s="16"/>
+      <c r="DC112" s="16"/>
+      <c r="DD112" s="16"/>
+      <c r="DE112" s="16"/>
+      <c r="DF112" s="16"/>
+      <c r="DG112" s="16"/>
+      <c r="DH112" s="16"/>
+      <c r="DI112" s="16"/>
+      <c r="DJ112" s="16"/>
+      <c r="DK112" s="16"/>
+      <c r="DL112" s="16"/>
+      <c r="DM112" s="16"/>
+      <c r="DN112" s="16"/>
+      <c r="DO112" s="16"/>
+      <c r="DP112" s="16"/>
+      <c r="DQ112" s="16"/>
+      <c r="DR112" s="16"/>
+      <c r="DS112" s="16"/>
+      <c r="DT112" s="16"/>
+      <c r="DU112" s="16"/>
+      <c r="DV112" s="16"/>
+      <c r="DW112" s="16"/>
+      <c r="DX112" s="16"/>
+      <c r="DY112" s="16"/>
+      <c r="DZ112" s="16"/>
+      <c r="EA112" s="16"/>
+      <c r="EB112" s="16"/>
+      <c r="EC112" s="16"/>
+      <c r="ED112" s="16"/>
+      <c r="EE112" s="16"/>
+      <c r="EF112" s="16"/>
+      <c r="EG112" s="16"/>
+      <c r="EH112" s="16"/>
+      <c r="EI112" s="16"/>
+      <c r="EJ112" s="16"/>
+      <c r="EK112" s="16"/>
+      <c r="EL112" s="16"/>
+      <c r="EM112" s="16"/>
+      <c r="EN112" s="16"/>
+      <c r="EO112" s="16"/>
+      <c r="EP112" s="16"/>
+      <c r="EQ112" s="16"/>
+      <c r="ER112" s="16"/>
+      <c r="ES112" s="16"/>
+      <c r="ET112" s="16"/>
+      <c r="EU112" s="16"/>
+      <c r="EV112" s="16"/>
+      <c r="EW112" s="16"/>
+      <c r="EX112" s="16"/>
+      <c r="EY112" s="16"/>
+      <c r="EZ112" s="16"/>
+      <c r="FA112" s="16"/>
+      <c r="FB112" s="16"/>
+      <c r="FC112" s="16"/>
+      <c r="FD112" s="16"/>
+      <c r="FE112" s="16"/>
+      <c r="FF112" s="16"/>
+      <c r="FG112" s="16"/>
+      <c r="FH112" s="16"/>
+      <c r="FI112" s="16"/>
+      <c r="FJ112" s="16"/>
+      <c r="FK112" s="16"/>
+      <c r="FL112" s="16"/>
+      <c r="FM112" s="16"/>
+      <c r="FN112" s="16"/>
+      <c r="FO112" s="16"/>
+      <c r="FP112" s="16"/>
+      <c r="FQ112" s="16"/>
+      <c r="FR112" s="16"/>
+      <c r="FS112" s="16"/>
+      <c r="FT112" s="16"/>
+      <c r="FU112" s="16"/>
+      <c r="FV112" s="16"/>
+      <c r="FW112" s="16"/>
+      <c r="FX112" s="16"/>
+      <c r="FY112" s="16"/>
+      <c r="FZ112" s="16"/>
+      <c r="GA112" s="16"/>
+      <c r="GB112" s="16"/>
+      <c r="GC112" s="16"/>
+      <c r="GD112" s="16"/>
+      <c r="GE112" s="16"/>
+      <c r="GF112" s="16"/>
+      <c r="GG112" s="16"/>
+      <c r="GH112" s="16"/>
+      <c r="GI112" s="16"/>
+      <c r="GJ112" s="16"/>
+      <c r="GK112" s="16"/>
+      <c r="GL112" s="16"/>
+      <c r="GM112" s="16"/>
+      <c r="GN112" s="16"/>
+      <c r="GO112" s="16"/>
+      <c r="GP112" s="16"/>
+      <c r="GQ112" s="16"/>
+      <c r="GR112" s="16"/>
+      <c r="GS112" s="16"/>
+      <c r="GT112" s="16"/>
+      <c r="GU112" s="16"/>
+      <c r="GV112" s="16"/>
+      <c r="GW112" s="16"/>
+      <c r="GX112" s="16"/>
+      <c r="GY112" s="16"/>
+      <c r="GZ112" s="16"/>
+      <c r="HA112" s="16"/>
+      <c r="HB112" s="16"/>
+      <c r="HC112" s="16"/>
+      <c r="HD112" s="16"/>
+      <c r="HE112" s="16"/>
+      <c r="HF112" s="16"/>
+      <c r="HG112" s="16"/>
+      <c r="HH112" s="16"/>
+      <c r="HI112" s="16"/>
+      <c r="HJ112" s="16"/>
+    </row>
+    <row r="113" spans="3:90" x14ac:dyDescent="0.25">
       <c r="C113" s="19"/>
       <c r="E113" s="16"/>
       <c r="F113" s="16"/>
@@ -6876,9 +8708,9 @@
       <c r="AC113" s="16"/>
       <c r="AD113" s="16"/>
       <c r="AE113" s="16"/>
-      <c r="BN113" s="19"/>
-    </row>
-    <row r="114" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="BN113" s="16"/>
+    </row>
+    <row r="114" spans="3:90" x14ac:dyDescent="0.25">
       <c r="C114" s="19"/>
       <c r="E114" s="16"/>
       <c r="F114" s="16"/>
@@ -6894,9 +8726,9 @@
       <c r="AC114" s="16"/>
       <c r="AD114" s="16"/>
       <c r="AE114" s="16"/>
-      <c r="BN114" s="19"/>
-    </row>
-    <row r="115" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="BN114" s="16"/>
+    </row>
+    <row r="115" spans="3:90" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C115" s="19"/>
       <c r="E115" s="16"/>
       <c r="F115" s="16"/>
@@ -6906,513 +8738,666 @@
       <c r="J115" s="16"/>
       <c r="K115" s="16"/>
       <c r="L115" s="16"/>
-      <c r="M115" s="16"/>
-      <c r="N115" s="16"/>
+      <c r="N115" s="69" t="s">
+        <v>50</v>
+      </c>
       <c r="AB115" s="16"/>
       <c r="AC115" s="16"/>
       <c r="AD115" s="16"/>
       <c r="AE115" s="16"/>
-      <c r="BN115" s="19"/>
-    </row>
-    <row r="116" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="AN115" s="69" t="s">
+        <v>25</v>
+      </c>
+      <c r="BN115" s="16"/>
+    </row>
+    <row r="116" spans="3:90" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C116" s="19"/>
-      <c r="D116" s="39" t="s">
-        <v>33</v>
-      </c>
-      <c r="E116" s="39"/>
-      <c r="F116" s="39"/>
-      <c r="G116" s="39"/>
-      <c r="AB116" s="16"/>
-      <c r="AC116" s="16"/>
-      <c r="AD116" s="16"/>
-      <c r="AE116" s="16"/>
-      <c r="BN116" s="19"/>
-    </row>
-    <row r="117" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="D116" s="20"/>
+      <c r="E116" s="21"/>
+      <c r="F116" s="21"/>
+      <c r="G116" s="21"/>
+      <c r="H116" s="21"/>
+      <c r="I116" s="21"/>
+      <c r="J116" s="21"/>
+      <c r="K116" s="21"/>
+      <c r="L116" s="21"/>
+      <c r="M116" s="21"/>
+      <c r="N116" s="21"/>
+      <c r="O116" s="21"/>
+      <c r="P116" s="21"/>
+      <c r="Q116" s="21"/>
+      <c r="R116" s="21"/>
+      <c r="S116" s="21"/>
+      <c r="T116" s="21"/>
+      <c r="U116" s="21"/>
+      <c r="V116" s="21"/>
+      <c r="W116" s="21"/>
+      <c r="X116" s="21"/>
+      <c r="Y116" s="21"/>
+      <c r="Z116" s="21"/>
+      <c r="AA116" s="21"/>
+      <c r="AB116" s="21"/>
+      <c r="AC116" s="21"/>
+      <c r="AD116" s="21"/>
+      <c r="AE116" s="21"/>
+      <c r="AF116" s="21"/>
+      <c r="AG116" s="21"/>
+      <c r="AH116" s="21"/>
+      <c r="AI116" s="21"/>
+      <c r="AJ116" s="21"/>
+      <c r="AK116" s="21"/>
+      <c r="AL116" s="21"/>
+      <c r="AM116" s="21"/>
+      <c r="AN116" s="21"/>
+      <c r="AO116" s="21"/>
+      <c r="AP116" s="21"/>
+      <c r="AQ116" s="21"/>
+      <c r="AR116" s="21"/>
+      <c r="AS116" s="21"/>
+      <c r="AT116" s="21"/>
+      <c r="AU116" s="21"/>
+      <c r="AV116" s="21"/>
+      <c r="AW116" s="21"/>
+      <c r="AX116" s="21"/>
+      <c r="AY116" s="21"/>
+      <c r="AZ116" s="21"/>
+      <c r="BA116" s="21"/>
+      <c r="BB116" s="21"/>
+      <c r="BC116" s="21"/>
+      <c r="BD116" s="21"/>
+      <c r="BE116" s="21"/>
+      <c r="BF116" s="21"/>
+      <c r="BG116" s="21"/>
+      <c r="BH116" s="21"/>
+      <c r="BI116" s="21"/>
+      <c r="BJ116" s="21"/>
+      <c r="BK116" s="21"/>
+      <c r="BL116" s="21"/>
+      <c r="BM116" s="21"/>
+      <c r="BN116" s="21"/>
+      <c r="BO116" s="21"/>
+      <c r="BP116" s="21"/>
+      <c r="BQ116" s="21"/>
+      <c r="BR116" s="21"/>
+      <c r="BS116" s="21"/>
+      <c r="BT116" s="21"/>
+      <c r="BU116" s="21"/>
+      <c r="BV116" s="21"/>
+      <c r="BW116" s="21"/>
+      <c r="BX116" s="21"/>
+      <c r="BY116" s="21"/>
+      <c r="BZ116" s="21"/>
+      <c r="CA116" s="21"/>
+      <c r="CB116" s="21"/>
+      <c r="CC116" s="21"/>
+      <c r="CD116" s="21"/>
+      <c r="CE116" s="21"/>
+      <c r="CF116" s="21"/>
+      <c r="CG116" s="21"/>
+      <c r="CH116" s="21"/>
+      <c r="CI116" s="21"/>
+      <c r="CJ116" s="21"/>
+      <c r="CK116" s="21"/>
+      <c r="CL116" s="21"/>
+    </row>
+    <row r="117" spans="3:90" x14ac:dyDescent="0.25">
       <c r="C117" s="19"/>
       <c r="AB117" s="16"/>
       <c r="AC117" s="16"/>
       <c r="AD117" s="16"/>
       <c r="AE117" s="16"/>
-      <c r="BN117" s="19"/>
-    </row>
-    <row r="118" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="BN117" s="16"/>
+    </row>
+    <row r="118" spans="3:90" x14ac:dyDescent="0.25">
       <c r="C118" s="19"/>
       <c r="AB118" s="16"/>
       <c r="AC118" s="16"/>
       <c r="AD118" s="16"/>
       <c r="AE118" s="16"/>
-      <c r="BN118" s="19"/>
-    </row>
-    <row r="119" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="BN118" s="16"/>
+    </row>
+    <row r="119" spans="3:90" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C119" s="19"/>
+      <c r="D119" s="62" t="s">
+        <v>30</v>
+      </c>
+      <c r="E119" s="62"/>
+      <c r="F119" s="62"/>
+      <c r="G119" s="62"/>
       <c r="AB119" s="16"/>
       <c r="AC119" s="16"/>
       <c r="AD119" s="16"/>
       <c r="AE119" s="16"/>
-      <c r="BN119" s="19"/>
-    </row>
-    <row r="120" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="BN119" s="16"/>
+    </row>
+    <row r="120" spans="3:90" x14ac:dyDescent="0.25">
       <c r="C120" s="19"/>
       <c r="AB120" s="16"/>
       <c r="AC120" s="16"/>
       <c r="AD120" s="16"/>
       <c r="AE120" s="16"/>
-      <c r="BN120" s="19"/>
-    </row>
-    <row r="121" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="BN120" s="16"/>
+    </row>
+    <row r="121" spans="3:90" x14ac:dyDescent="0.25">
       <c r="C121" s="19"/>
-      <c r="AB121" s="16"/>
-      <c r="AC121" s="16"/>
-      <c r="AD121" s="16"/>
-      <c r="AE121" s="16"/>
-      <c r="BN121" s="19"/>
-    </row>
-    <row r="122" spans="3:66" x14ac:dyDescent="0.25">
+    </row>
+    <row r="122" spans="3:90" x14ac:dyDescent="0.25">
       <c r="C122" s="19"/>
-      <c r="AB122" s="16"/>
-      <c r="AC122" s="16"/>
-      <c r="AD122" s="16"/>
-      <c r="AE122" s="16"/>
-      <c r="BN122" s="19"/>
-    </row>
-    <row r="123" spans="3:66" x14ac:dyDescent="0.25">
+    </row>
+    <row r="123" spans="3:90" ht="24" x14ac:dyDescent="0.25">
       <c r="C123" s="19"/>
-      <c r="AB123" s="16"/>
-      <c r="AC123" s="16"/>
-      <c r="AD123" s="16"/>
-      <c r="AE123" s="16"/>
-      <c r="BN123" s="19"/>
-    </row>
-    <row r="124" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="E123" s="49" t="s">
+        <v>31</v>
+      </c>
+      <c r="F123" s="49"/>
+      <c r="G123" s="49"/>
+      <c r="H123" s="49"/>
+      <c r="I123" s="50"/>
+      <c r="J123" s="50"/>
+    </row>
+    <row r="124" spans="3:90" x14ac:dyDescent="0.25">
       <c r="C124" s="19"/>
-      <c r="AB124" s="16"/>
-      <c r="AC124" s="16"/>
-      <c r="AD124" s="16"/>
-      <c r="AE124" s="16"/>
-      <c r="BN124" s="19"/>
-    </row>
-    <row r="125" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="E124" s="49"/>
+      <c r="F124" s="49"/>
+      <c r="G124" s="49"/>
+      <c r="H124" s="49"/>
+    </row>
+    <row r="125" spans="3:90" x14ac:dyDescent="0.25">
       <c r="C125" s="19"/>
-      <c r="AB125" s="16"/>
-      <c r="AC125" s="16"/>
-      <c r="AD125" s="16"/>
-      <c r="AE125" s="16"/>
-      <c r="BN125" s="19"/>
-    </row>
-    <row r="126" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="F125" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="G125" s="46"/>
+      <c r="H125" s="46"/>
+      <c r="I125" s="46"/>
+      <c r="J125" s="46"/>
+      <c r="K125" s="46"/>
+      <c r="L125" s="46"/>
+      <c r="M125" s="46"/>
+      <c r="N125" s="46"/>
+      <c r="O125" s="46"/>
+      <c r="P125" s="46"/>
+      <c r="Q125" s="46"/>
+      <c r="R125" s="46"/>
+      <c r="S125" s="46"/>
+      <c r="T125" s="46"/>
+      <c r="W125" s="47" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="126" spans="3:90" x14ac:dyDescent="0.25">
       <c r="C126" s="19"/>
-      <c r="AB126" s="16"/>
-      <c r="AC126" s="16"/>
-      <c r="AD126" s="16"/>
-      <c r="AE126" s="16"/>
-      <c r="BN126" s="19"/>
-    </row>
-    <row r="127" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="F126" s="46"/>
+      <c r="G126" s="46"/>
+      <c r="H126" s="46"/>
+      <c r="I126" s="46"/>
+      <c r="J126" s="46"/>
+      <c r="K126" s="46"/>
+      <c r="L126" s="46"/>
+      <c r="M126" s="46"/>
+      <c r="N126" s="46"/>
+      <c r="O126" s="46"/>
+      <c r="P126" s="46"/>
+      <c r="Q126" s="46"/>
+      <c r="R126" s="46"/>
+      <c r="S126" s="46"/>
+      <c r="T126" s="46"/>
+      <c r="X126" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y126" s="48"/>
+      <c r="Z126" s="48"/>
+      <c r="AA126" s="48"/>
+      <c r="AB126" s="48"/>
+      <c r="AC126" s="48"/>
+      <c r="AD126" s="48"/>
+      <c r="AE126" s="48"/>
+      <c r="AF126" s="48"/>
+      <c r="AG126" s="48"/>
+      <c r="AH126" s="48"/>
+      <c r="AI126" s="48"/>
+      <c r="AJ126" s="48"/>
+    </row>
+    <row r="127" spans="3:90" x14ac:dyDescent="0.25">
       <c r="C127" s="19"/>
-      <c r="AB127" s="16"/>
-      <c r="AC127" s="16"/>
-      <c r="AD127" s="16"/>
-      <c r="AE127" s="16"/>
-      <c r="BN127" s="19"/>
-    </row>
-    <row r="128" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="F127" s="46"/>
+      <c r="G127" s="46"/>
+      <c r="H127" s="46"/>
+      <c r="I127" s="46"/>
+      <c r="J127" s="46"/>
+      <c r="K127" s="46"/>
+      <c r="L127" s="46"/>
+      <c r="M127" s="46"/>
+      <c r="N127" s="46"/>
+      <c r="O127" s="46"/>
+      <c r="P127" s="46"/>
+      <c r="Q127" s="46"/>
+      <c r="R127" s="46"/>
+      <c r="S127" s="46"/>
+      <c r="T127" s="46"/>
+      <c r="X127" s="48"/>
+      <c r="Y127" s="48"/>
+      <c r="Z127" s="48"/>
+      <c r="AA127" s="48"/>
+      <c r="AB127" s="48"/>
+      <c r="AC127" s="48"/>
+      <c r="AD127" s="48"/>
+      <c r="AE127" s="48"/>
+      <c r="AF127" s="48"/>
+      <c r="AG127" s="48"/>
+      <c r="AH127" s="48"/>
+      <c r="AI127" s="48"/>
+      <c r="AJ127" s="48"/>
+    </row>
+    <row r="128" spans="3:90" x14ac:dyDescent="0.25">
       <c r="C128" s="19"/>
-      <c r="AB128" s="16"/>
-      <c r="AC128" s="16"/>
-      <c r="AD128" s="16"/>
-      <c r="AE128" s="16"/>
-      <c r="BN128" s="19"/>
-    </row>
-    <row r="129" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="F128" s="46"/>
+      <c r="G128" s="46"/>
+      <c r="H128" s="46"/>
+      <c r="I128" s="46"/>
+      <c r="J128" s="46"/>
+      <c r="K128" s="46"/>
+      <c r="L128" s="46"/>
+      <c r="M128" s="46"/>
+      <c r="N128" s="46"/>
+      <c r="O128" s="46"/>
+      <c r="P128" s="46"/>
+      <c r="Q128" s="46"/>
+      <c r="R128" s="46"/>
+      <c r="S128" s="46"/>
+      <c r="T128" s="46"/>
+      <c r="X128" s="48"/>
+      <c r="Y128" s="48"/>
+      <c r="Z128" s="48"/>
+      <c r="AA128" s="48"/>
+      <c r="AB128" s="48"/>
+      <c r="AC128" s="48"/>
+      <c r="AD128" s="48"/>
+      <c r="AE128" s="48"/>
+      <c r="AF128" s="48"/>
+      <c r="AG128" s="48"/>
+      <c r="AH128" s="48"/>
+      <c r="AI128" s="48"/>
+      <c r="AJ128" s="48"/>
+    </row>
+    <row r="129" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C129" s="19"/>
-      <c r="AB129" s="16"/>
-      <c r="AC129" s="16"/>
-      <c r="AD129" s="16"/>
-      <c r="AE129" s="16"/>
-      <c r="BN129" s="19"/>
-    </row>
-    <row r="130" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="F129" s="46"/>
+      <c r="G129" s="46"/>
+      <c r="H129" s="46"/>
+      <c r="I129" s="46"/>
+      <c r="J129" s="46"/>
+      <c r="K129" s="46"/>
+      <c r="L129" s="46"/>
+      <c r="M129" s="46"/>
+      <c r="N129" s="46"/>
+      <c r="O129" s="46"/>
+      <c r="P129" s="46"/>
+      <c r="Q129" s="46"/>
+      <c r="R129" s="46"/>
+      <c r="S129" s="46"/>
+      <c r="T129" s="46"/>
+      <c r="X129" s="48"/>
+      <c r="Y129" s="48"/>
+      <c r="Z129" s="48"/>
+      <c r="AA129" s="48"/>
+      <c r="AB129" s="48"/>
+      <c r="AC129" s="48"/>
+      <c r="AD129" s="48"/>
+      <c r="AE129" s="48"/>
+      <c r="AF129" s="48"/>
+      <c r="AG129" s="48"/>
+      <c r="AH129" s="48"/>
+      <c r="AI129" s="48"/>
+      <c r="AJ129" s="48"/>
+    </row>
+    <row r="130" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C130" s="19"/>
-      <c r="AB130" s="16"/>
-      <c r="AC130" s="16"/>
-      <c r="AD130" s="16"/>
-      <c r="AE130" s="16"/>
-      <c r="BN130" s="19"/>
-    </row>
-    <row r="131" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="F130" s="47" t="s">
+        <v>56</v>
+      </c>
+      <c r="X130" s="48"/>
+      <c r="Y130" s="48"/>
+      <c r="Z130" s="48"/>
+      <c r="AA130" s="48"/>
+      <c r="AB130" s="48"/>
+      <c r="AC130" s="48"/>
+      <c r="AD130" s="48"/>
+      <c r="AE130" s="48"/>
+      <c r="AF130" s="48"/>
+      <c r="AG130" s="48"/>
+      <c r="AH130" s="48"/>
+      <c r="AI130" s="48"/>
+      <c r="AJ130" s="48"/>
+    </row>
+    <row r="131" spans="3:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C131" s="19"/>
-      <c r="AB131" s="16"/>
-      <c r="AC131" s="16"/>
-      <c r="AD131" s="16"/>
-      <c r="AE131" s="16"/>
-      <c r="BN131" s="19"/>
-    </row>
-    <row r="132" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="G131" s="64" t="s">
+        <v>57</v>
+      </c>
+      <c r="H131" s="64"/>
+      <c r="I131" s="64"/>
+      <c r="J131" s="64"/>
+      <c r="K131" s="64"/>
+      <c r="L131" s="64"/>
+      <c r="M131" s="64"/>
+      <c r="N131" s="64"/>
+      <c r="O131" s="64"/>
+      <c r="P131" s="64"/>
+      <c r="Q131" s="64"/>
+      <c r="R131" s="64"/>
+      <c r="S131" s="64"/>
+      <c r="T131" s="64"/>
+      <c r="X131" s="48"/>
+      <c r="Y131" s="48"/>
+      <c r="Z131" s="48"/>
+      <c r="AA131" s="48"/>
+      <c r="AB131" s="48"/>
+      <c r="AC131" s="48"/>
+      <c r="AD131" s="48"/>
+      <c r="AE131" s="48"/>
+      <c r="AF131" s="48"/>
+      <c r="AG131" s="48"/>
+      <c r="AH131" s="48"/>
+      <c r="AI131" s="48"/>
+      <c r="AJ131" s="48"/>
+    </row>
+    <row r="132" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C132" s="19"/>
-      <c r="W132" s="16"/>
-      <c r="X132" s="16"/>
-      <c r="Y132" s="16"/>
-      <c r="Z132" s="16"/>
-      <c r="AA132" s="16"/>
-      <c r="AB132" s="16"/>
-      <c r="AC132" s="16"/>
-      <c r="AD132" s="16"/>
-      <c r="AE132" s="16"/>
-      <c r="BN132" s="19"/>
-    </row>
-    <row r="133" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="G132" s="63" t="s">
+        <v>58</v>
+      </c>
+      <c r="X132" s="48"/>
+      <c r="Y132" s="48"/>
+      <c r="Z132" s="48"/>
+      <c r="AA132" s="48"/>
+      <c r="AB132" s="48"/>
+      <c r="AC132" s="48"/>
+      <c r="AD132" s="48"/>
+      <c r="AE132" s="48"/>
+      <c r="AF132" s="48"/>
+      <c r="AG132" s="48"/>
+      <c r="AH132" s="48"/>
+      <c r="AI132" s="48"/>
+      <c r="AJ132" s="48"/>
+    </row>
+    <row r="133" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C133" s="19"/>
-      <c r="W133" s="16"/>
-      <c r="X133" s="16"/>
-      <c r="Y133" s="16"/>
-      <c r="Z133" s="16"/>
-      <c r="AA133" s="16"/>
-      <c r="AB133" s="16"/>
-      <c r="AC133" s="16"/>
-      <c r="AD133" s="16"/>
-      <c r="AE133" s="16"/>
-      <c r="BN133" s="19"/>
-    </row>
-    <row r="134" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="G133" t="s">
+        <v>59</v>
+      </c>
+      <c r="X133" s="48"/>
+      <c r="Y133" s="48"/>
+      <c r="Z133" s="48"/>
+      <c r="AA133" s="48"/>
+      <c r="AB133" s="48"/>
+      <c r="AC133" s="48"/>
+      <c r="AD133" s="48"/>
+      <c r="AE133" s="48"/>
+      <c r="AF133" s="48"/>
+      <c r="AG133" s="48"/>
+      <c r="AH133" s="48"/>
+      <c r="AI133" s="48"/>
+      <c r="AJ133" s="48"/>
+    </row>
+    <row r="134" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C134" s="19"/>
-      <c r="W134" s="16"/>
-      <c r="X134" s="16"/>
-      <c r="Y134" s="16"/>
-      <c r="Z134" s="16"/>
-      <c r="AA134" s="16"/>
-      <c r="AB134" s="16"/>
-      <c r="AC134" s="16"/>
-      <c r="AD134" s="16"/>
-      <c r="AE134" s="16"/>
-      <c r="BN134" s="19"/>
-    </row>
-    <row r="135" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="G134" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="135" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C135" s="19"/>
-      <c r="W135" s="16"/>
-      <c r="X135" s="16"/>
-      <c r="Y135" s="16"/>
-      <c r="Z135" s="16"/>
-      <c r="AA135" s="16"/>
-      <c r="AB135" s="16"/>
-      <c r="AC135" s="16"/>
-      <c r="AD135" s="16"/>
-      <c r="AE135" s="16"/>
-      <c r="BN135" s="19"/>
-    </row>
-    <row r="136" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="G135" s="63" t="s">
+        <v>61</v>
+      </c>
+      <c r="X135" s="44" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y135" s="58"/>
+      <c r="Z135" s="58"/>
+      <c r="AA135" s="58"/>
+      <c r="AB135" s="58"/>
+      <c r="AC135" s="58"/>
+      <c r="AD135" s="58"/>
+      <c r="AE135" s="58"/>
+      <c r="AF135" s="58"/>
+      <c r="AG135" s="58"/>
+      <c r="AH135" s="58"/>
+      <c r="AI135" s="58"/>
+      <c r="AJ135" s="58"/>
+    </row>
+    <row r="136" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C136" s="19"/>
-      <c r="W136" s="16"/>
-      <c r="X136" s="16"/>
-      <c r="Y136" s="16"/>
-      <c r="Z136" s="16"/>
-      <c r="AA136" s="16"/>
-      <c r="AB136" s="16"/>
-      <c r="AC136" s="16"/>
-      <c r="AD136" s="16"/>
-      <c r="AE136" s="16"/>
-      <c r="BN136" s="19"/>
-    </row>
-    <row r="137" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="X136" s="58"/>
+      <c r="Y136" s="58"/>
+      <c r="Z136" s="58"/>
+      <c r="AA136" s="58"/>
+      <c r="AB136" s="58"/>
+      <c r="AC136" s="58"/>
+      <c r="AD136" s="58"/>
+      <c r="AE136" s="58"/>
+      <c r="AF136" s="58"/>
+      <c r="AG136" s="58"/>
+      <c r="AH136" s="58"/>
+      <c r="AI136" s="58"/>
+      <c r="AJ136" s="58"/>
+    </row>
+    <row r="137" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C137" s="19"/>
-      <c r="W137" s="16"/>
-      <c r="X137" s="16"/>
-      <c r="Y137" s="16"/>
-      <c r="Z137" s="16"/>
-      <c r="AA137" s="16"/>
-      <c r="AB137" s="16"/>
-      <c r="AC137" s="16"/>
-      <c r="AD137" s="16"/>
-      <c r="AE137" s="16"/>
-      <c r="BN137" s="19"/>
-    </row>
-    <row r="138" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="X137" s="58"/>
+      <c r="Y137" s="58"/>
+      <c r="Z137" s="58"/>
+      <c r="AA137" s="58"/>
+      <c r="AB137" s="58"/>
+      <c r="AC137" s="58"/>
+      <c r="AD137" s="58"/>
+      <c r="AE137" s="58"/>
+      <c r="AF137" s="58"/>
+      <c r="AG137" s="58"/>
+      <c r="AH137" s="58"/>
+      <c r="AI137" s="58"/>
+      <c r="AJ137" s="58"/>
+    </row>
+    <row r="138" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C138" s="19"/>
-      <c r="W138" s="16"/>
-      <c r="X138" s="16"/>
-      <c r="Y138" s="16"/>
-      <c r="Z138" s="16"/>
-      <c r="AA138" s="16"/>
-      <c r="AB138" s="16"/>
-      <c r="AC138" s="16"/>
-      <c r="AD138" s="16"/>
-      <c r="AE138" s="16"/>
-      <c r="BN138" s="19"/>
-    </row>
-    <row r="139" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="X138" s="58"/>
+      <c r="Y138" s="58"/>
+      <c r="Z138" s="58"/>
+      <c r="AA138" s="58"/>
+      <c r="AB138" s="58"/>
+      <c r="AC138" s="58"/>
+      <c r="AD138" s="58"/>
+      <c r="AE138" s="58"/>
+      <c r="AF138" s="58"/>
+      <c r="AG138" s="58"/>
+      <c r="AH138" s="58"/>
+      <c r="AI138" s="58"/>
+      <c r="AJ138" s="58"/>
+    </row>
+    <row r="139" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C139" s="19"/>
-      <c r="W139" s="16"/>
-      <c r="X139" s="16"/>
-      <c r="Y139" s="16"/>
-      <c r="Z139" s="16"/>
-      <c r="AA139" s="16"/>
-      <c r="AB139" s="16"/>
-      <c r="AC139" s="16"/>
-      <c r="AD139" s="16"/>
-      <c r="AE139" s="16"/>
-      <c r="BN139" s="19"/>
-    </row>
-    <row r="140" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="X139" s="58"/>
+      <c r="Y139" s="58"/>
+      <c r="Z139" s="58"/>
+      <c r="AA139" s="58"/>
+      <c r="AB139" s="58"/>
+      <c r="AC139" s="58"/>
+      <c r="AD139" s="58"/>
+      <c r="AE139" s="58"/>
+      <c r="AF139" s="58"/>
+      <c r="AG139" s="58"/>
+      <c r="AH139" s="58"/>
+      <c r="AI139" s="58"/>
+      <c r="AJ139" s="58"/>
+    </row>
+    <row r="140" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C140" s="19"/>
-      <c r="W140" s="16"/>
-      <c r="X140" s="16"/>
-      <c r="Y140" s="16"/>
-      <c r="Z140" s="16"/>
-      <c r="AA140" s="16"/>
-      <c r="AB140" s="16"/>
-      <c r="AC140" s="16"/>
-      <c r="AD140" s="16"/>
-      <c r="AE140" s="16"/>
-      <c r="BN140" s="19"/>
-    </row>
-    <row r="141" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="X140" s="58"/>
+      <c r="Y140" s="58"/>
+      <c r="Z140" s="58"/>
+      <c r="AA140" s="58"/>
+      <c r="AB140" s="58"/>
+      <c r="AC140" s="58"/>
+      <c r="AD140" s="58"/>
+      <c r="AE140" s="58"/>
+      <c r="AF140" s="58"/>
+      <c r="AG140" s="58"/>
+      <c r="AH140" s="58"/>
+      <c r="AI140" s="58"/>
+      <c r="AJ140" s="58"/>
+    </row>
+    <row r="141" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C141" s="19"/>
-      <c r="W141" s="16"/>
-      <c r="X141" s="16"/>
-      <c r="Y141" s="16"/>
-      <c r="Z141" s="16"/>
-      <c r="AA141" s="16"/>
-      <c r="AB141" s="16"/>
-      <c r="AC141" s="16"/>
-      <c r="AD141" s="16"/>
-      <c r="AE141" s="16"/>
-      <c r="BN141" s="19"/>
-    </row>
-    <row r="142" spans="3:66" x14ac:dyDescent="0.25">
+    </row>
+    <row r="142" spans="3:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C142" s="19"/>
-      <c r="W142" s="16"/>
-      <c r="X142" s="16"/>
-      <c r="Y142" s="16"/>
-      <c r="Z142" s="16"/>
-      <c r="AA142" s="16"/>
-      <c r="AB142" s="16"/>
-      <c r="AC142" s="16"/>
-      <c r="AD142" s="16"/>
-      <c r="AE142" s="16"/>
-      <c r="BN142" s="19"/>
-    </row>
-    <row r="143" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="X142" s="44" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y142" s="44"/>
+      <c r="Z142" s="44"/>
+      <c r="AA142" s="44"/>
+      <c r="AB142" s="44"/>
+      <c r="AC142" s="44"/>
+      <c r="AD142" s="44"/>
+      <c r="AE142" s="44"/>
+      <c r="AF142" s="44"/>
+      <c r="AG142" s="44"/>
+      <c r="AH142" s="44"/>
+      <c r="AI142" s="44"/>
+      <c r="AJ142" s="44"/>
+    </row>
+    <row r="143" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C143" s="19"/>
-      <c r="W143" s="16"/>
-      <c r="X143" s="16"/>
-      <c r="Y143" s="16"/>
-      <c r="Z143" s="16"/>
-      <c r="AA143" s="16"/>
-      <c r="AB143" s="16"/>
-      <c r="AC143" s="16"/>
-      <c r="AD143" s="16"/>
-      <c r="AE143" s="16"/>
-      <c r="BN143" s="19"/>
-    </row>
-    <row r="144" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="X143" s="44"/>
+      <c r="Y143" s="44"/>
+      <c r="Z143" s="44"/>
+      <c r="AA143" s="44"/>
+      <c r="AB143" s="44"/>
+      <c r="AC143" s="44"/>
+      <c r="AD143" s="44"/>
+      <c r="AE143" s="44"/>
+      <c r="AF143" s="44"/>
+      <c r="AG143" s="44"/>
+      <c r="AH143" s="44"/>
+      <c r="AI143" s="44"/>
+      <c r="AJ143" s="44"/>
+    </row>
+    <row r="144" spans="3:36" x14ac:dyDescent="0.25">
       <c r="C144" s="19"/>
-      <c r="W144" s="16"/>
-      <c r="X144" s="16"/>
-      <c r="Y144" s="16"/>
-      <c r="Z144" s="16"/>
-      <c r="AA144" s="16"/>
-      <c r="AB144" s="16"/>
-      <c r="AC144" s="16"/>
-      <c r="AD144" s="16"/>
-      <c r="AE144" s="16"/>
-      <c r="BN144" s="19"/>
-    </row>
-    <row r="145" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="X144" s="44"/>
+      <c r="Y144" s="44"/>
+      <c r="Z144" s="44"/>
+      <c r="AA144" s="44"/>
+      <c r="AB144" s="44"/>
+      <c r="AC144" s="44"/>
+      <c r="AD144" s="44"/>
+      <c r="AE144" s="44"/>
+      <c r="AF144" s="44"/>
+      <c r="AG144" s="44"/>
+      <c r="AH144" s="44"/>
+      <c r="AI144" s="44"/>
+      <c r="AJ144" s="44"/>
+    </row>
+    <row r="145" spans="3:67" x14ac:dyDescent="0.25">
       <c r="C145" s="19"/>
-      <c r="W145" s="16"/>
-      <c r="X145" s="16"/>
-      <c r="Y145" s="16"/>
-      <c r="Z145" s="16"/>
-      <c r="AA145" s="16"/>
-      <c r="AB145" s="16"/>
-      <c r="AC145" s="16"/>
-      <c r="AD145" s="16"/>
-      <c r="AE145" s="16"/>
-      <c r="BN145" s="19"/>
-    </row>
-    <row r="146" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="X145" s="44"/>
+      <c r="Y145" s="44"/>
+      <c r="Z145" s="44"/>
+      <c r="AA145" s="44"/>
+      <c r="AB145" s="44"/>
+      <c r="AC145" s="44"/>
+      <c r="AD145" s="44"/>
+      <c r="AE145" s="44"/>
+      <c r="AF145" s="44"/>
+      <c r="AG145" s="44"/>
+      <c r="AH145" s="44"/>
+      <c r="AI145" s="44"/>
+      <c r="AJ145" s="44"/>
+    </row>
+    <row r="146" spans="3:67" x14ac:dyDescent="0.25">
       <c r="C146" s="19"/>
-      <c r="W146" s="16"/>
-      <c r="X146" s="16"/>
-      <c r="Y146" s="16"/>
-      <c r="Z146" s="16"/>
-      <c r="AA146" s="16"/>
-      <c r="AB146" s="16"/>
-      <c r="AC146" s="16"/>
-      <c r="AD146" s="16"/>
-      <c r="AE146" s="16"/>
-      <c r="BN146" s="19"/>
-    </row>
-    <row r="147" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="X146" s="44"/>
+      <c r="Y146" s="44"/>
+      <c r="Z146" s="44"/>
+      <c r="AA146" s="44"/>
+      <c r="AB146" s="44"/>
+      <c r="AC146" s="44"/>
+      <c r="AD146" s="44"/>
+      <c r="AE146" s="44"/>
+      <c r="AF146" s="44"/>
+      <c r="AG146" s="44"/>
+      <c r="AH146" s="44"/>
+      <c r="AI146" s="44"/>
+      <c r="AJ146" s="44"/>
+    </row>
+    <row r="147" spans="3:67" x14ac:dyDescent="0.25">
       <c r="C147" s="19"/>
-      <c r="W147" s="16"/>
-      <c r="X147" s="16"/>
-      <c r="Y147" s="16"/>
-      <c r="Z147" s="16"/>
-      <c r="AA147" s="16"/>
-      <c r="AB147" s="16"/>
-      <c r="AC147" s="16"/>
-      <c r="AD147" s="16"/>
-      <c r="AE147" s="16"/>
-      <c r="BN147" s="19"/>
-    </row>
-    <row r="148" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="X147" s="44"/>
+      <c r="Y147" s="44"/>
+      <c r="Z147" s="44"/>
+      <c r="AA147" s="44"/>
+      <c r="AB147" s="44"/>
+      <c r="AC147" s="44"/>
+      <c r="AD147" s="44"/>
+      <c r="AE147" s="44"/>
+      <c r="AF147" s="44"/>
+      <c r="AG147" s="44"/>
+      <c r="AH147" s="44"/>
+      <c r="AI147" s="44"/>
+      <c r="AJ147" s="44"/>
+    </row>
+    <row r="148" spans="3:67" x14ac:dyDescent="0.25">
       <c r="C148" s="19"/>
-      <c r="W148" s="16"/>
-      <c r="X148" s="16"/>
-      <c r="Y148" s="16"/>
-      <c r="Z148" s="16"/>
-      <c r="AA148" s="16"/>
-      <c r="AB148" s="16"/>
-      <c r="AC148" s="16"/>
-      <c r="AD148" s="16"/>
-      <c r="AE148" s="16"/>
-      <c r="BN148" s="19"/>
-    </row>
-    <row r="149" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="X148" s="59"/>
+      <c r="Y148" s="59"/>
+      <c r="Z148" s="59"/>
+      <c r="AA148" s="59"/>
+      <c r="AB148" s="59"/>
+      <c r="AC148" s="59"/>
+      <c r="AD148" s="59"/>
+      <c r="AE148" s="59"/>
+      <c r="AF148" s="59"/>
+      <c r="AG148" s="59"/>
+      <c r="AH148" s="59"/>
+      <c r="AI148" s="59"/>
+      <c r="AJ148" s="59"/>
+    </row>
+    <row r="149" spans="3:67" x14ac:dyDescent="0.25">
       <c r="C149" s="19"/>
-      <c r="W149" s="16"/>
-      <c r="X149" s="16"/>
-      <c r="Y149" s="16"/>
-      <c r="Z149" s="16"/>
-      <c r="AA149" s="16"/>
-      <c r="AB149" s="16"/>
-      <c r="AC149" s="16"/>
-      <c r="AD149" s="16"/>
-      <c r="AE149" s="16"/>
-      <c r="BN149" s="19"/>
-    </row>
-    <row r="150" spans="3:66" x14ac:dyDescent="0.25">
+    </row>
+    <row r="150" spans="3:67" x14ac:dyDescent="0.25">
       <c r="C150" s="19"/>
-      <c r="W150" s="16"/>
-      <c r="X150" s="16"/>
-      <c r="Y150" s="16"/>
-      <c r="Z150" s="16"/>
-      <c r="AA150" s="16"/>
-      <c r="AB150" s="16"/>
-      <c r="AC150" s="16"/>
-      <c r="AD150" s="16"/>
-      <c r="AE150" s="16"/>
-      <c r="BN150" s="19"/>
-    </row>
-    <row r="151" spans="3:66" x14ac:dyDescent="0.25">
+    </row>
+    <row r="151" spans="3:67" x14ac:dyDescent="0.25">
       <c r="C151" s="19"/>
-      <c r="W151" s="16"/>
-      <c r="X151" s="16"/>
-      <c r="Y151" s="16"/>
-      <c r="Z151" s="16"/>
-      <c r="AA151" s="16"/>
-      <c r="AB151" s="16"/>
-      <c r="AC151" s="16"/>
-      <c r="AD151" s="16"/>
-      <c r="AE151" s="16"/>
-      <c r="BN151" s="19"/>
-    </row>
-    <row r="152" spans="3:66" x14ac:dyDescent="0.25">
+    </row>
+    <row r="152" spans="3:67" x14ac:dyDescent="0.25">
       <c r="C152" s="19"/>
-      <c r="W152" s="16"/>
-      <c r="X152" s="16"/>
-      <c r="Y152" s="16"/>
-      <c r="Z152" s="16"/>
-      <c r="AA152" s="16"/>
-      <c r="AB152" s="16"/>
-      <c r="AC152" s="16"/>
-      <c r="AD152" s="16"/>
-      <c r="AE152" s="16"/>
-      <c r="BN152" s="19"/>
-    </row>
-    <row r="153" spans="3:66" x14ac:dyDescent="0.25">
+    </row>
+    <row r="153" spans="3:67" x14ac:dyDescent="0.25">
       <c r="C153" s="19"/>
-      <c r="W153" s="16"/>
-      <c r="X153" s="16"/>
-      <c r="Y153" s="16"/>
-      <c r="Z153" s="16"/>
-      <c r="AA153" s="16"/>
-      <c r="AB153" s="16"/>
-      <c r="AC153" s="16"/>
-      <c r="AD153" s="16"/>
-      <c r="AE153" s="16"/>
-      <c r="BN153" s="19"/>
-    </row>
-    <row r="154" spans="3:66" x14ac:dyDescent="0.25">
+    </row>
+    <row r="154" spans="3:67" x14ac:dyDescent="0.25">
       <c r="C154" s="19"/>
-      <c r="W154" s="16"/>
-      <c r="X154" s="16"/>
-      <c r="Y154" s="16"/>
-      <c r="Z154" s="16"/>
-      <c r="AA154" s="16"/>
-      <c r="AB154" s="16"/>
-      <c r="AC154" s="16"/>
-      <c r="AD154" s="16"/>
-      <c r="AE154" s="16"/>
-      <c r="BN154" s="19"/>
-    </row>
-    <row r="155" spans="3:66" x14ac:dyDescent="0.25">
+    </row>
+    <row r="155" spans="3:67" x14ac:dyDescent="0.25">
       <c r="C155" s="19"/>
-      <c r="W155" s="16"/>
-      <c r="X155" s="16"/>
-      <c r="Y155" s="16"/>
-      <c r="Z155" s="16"/>
-      <c r="AA155" s="16"/>
-      <c r="AB155" s="16"/>
-      <c r="AC155" s="16"/>
-      <c r="AD155" s="16"/>
-      <c r="AE155" s="16"/>
-      <c r="BN155" s="19"/>
-    </row>
-    <row r="156" spans="3:66" x14ac:dyDescent="0.25">
+    </row>
+    <row r="156" spans="3:67" x14ac:dyDescent="0.25">
       <c r="C156" s="19"/>
-      <c r="W156" s="16"/>
-      <c r="X156" s="16"/>
-      <c r="Y156" s="16"/>
-      <c r="Z156" s="16"/>
-      <c r="AA156" s="16"/>
-      <c r="AB156" s="16"/>
-      <c r="AC156" s="16"/>
-      <c r="AD156" s="16"/>
-      <c r="AE156" s="16"/>
-      <c r="BN156" s="19"/>
-    </row>
-    <row r="157" spans="3:66" x14ac:dyDescent="0.25">
+    </row>
+    <row r="157" spans="3:67" x14ac:dyDescent="0.25">
       <c r="C157" s="19"/>
-      <c r="W157" s="16"/>
-      <c r="X157" s="16"/>
-      <c r="Y157" s="16"/>
-      <c r="Z157" s="16"/>
-      <c r="AA157" s="16"/>
-      <c r="AB157" s="16"/>
-      <c r="AC157" s="16"/>
-      <c r="AD157" s="16"/>
-      <c r="AE157" s="16"/>
-      <c r="BN157" s="19"/>
-    </row>
-    <row r="158" spans="3:66" x14ac:dyDescent="0.25">
+    </row>
+    <row r="158" spans="3:67" x14ac:dyDescent="0.25">
       <c r="C158" s="19"/>
-      <c r="W158" s="16"/>
-      <c r="X158" s="16"/>
-      <c r="Y158" s="16"/>
-      <c r="Z158" s="16"/>
-      <c r="AA158" s="16"/>
-      <c r="AB158" s="16"/>
-      <c r="AC158" s="16"/>
-      <c r="AD158" s="16"/>
-      <c r="AE158" s="16"/>
-      <c r="BN158" s="19"/>
-    </row>
-    <row r="159" spans="3:66" x14ac:dyDescent="0.25">
+    </row>
+    <row r="159" spans="3:67" x14ac:dyDescent="0.25">
       <c r="C159" s="19"/>
-      <c r="W159" s="16"/>
-      <c r="X159" s="16"/>
-      <c r="Y159" s="16"/>
-      <c r="Z159" s="16"/>
-      <c r="AA159" s="16"/>
-      <c r="AB159" s="16"/>
-      <c r="AC159" s="16"/>
-      <c r="AD159" s="16"/>
-      <c r="AE159" s="16"/>
-      <c r="BN159" s="19"/>
-    </row>
-    <row r="160" spans="3:66" x14ac:dyDescent="0.25">
+    </row>
+    <row r="160" spans="3:67" x14ac:dyDescent="0.25">
       <c r="C160" s="19"/>
       <c r="W160" s="16"/>
       <c r="X160" s="16"/>
@@ -7423,9 +9408,10 @@
       <c r="AC160" s="16"/>
       <c r="AD160" s="16"/>
       <c r="AE160" s="16"/>
-      <c r="BN160" s="19"/>
-    </row>
-    <row r="161" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="BN160" s="16"/>
+      <c r="BO160" s="16"/>
+    </row>
+    <row r="161" spans="3:67" x14ac:dyDescent="0.25">
       <c r="C161" s="19"/>
       <c r="W161" s="16"/>
       <c r="X161" s="16"/>
@@ -7436,9 +9422,10 @@
       <c r="AC161" s="16"/>
       <c r="AD161" s="16"/>
       <c r="AE161" s="16"/>
-      <c r="BN161" s="19"/>
-    </row>
-    <row r="162" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="BN161" s="16"/>
+      <c r="BO161" s="16"/>
+    </row>
+    <row r="162" spans="3:67" x14ac:dyDescent="0.25">
       <c r="C162" s="19"/>
       <c r="W162" s="16"/>
       <c r="X162" s="16"/>
@@ -7449,152 +9436,106 @@
       <c r="AC162" s="16"/>
       <c r="AD162" s="16"/>
       <c r="AE162" s="16"/>
-      <c r="BN162" s="19"/>
-    </row>
-    <row r="163" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="BN162" s="16"/>
+      <c r="BO162" s="16"/>
+    </row>
+    <row r="163" spans="3:67" x14ac:dyDescent="0.25">
       <c r="C163" s="19"/>
-      <c r="W163" s="16"/>
-      <c r="X163" s="16"/>
-      <c r="Y163" s="16"/>
-      <c r="Z163" s="16"/>
-      <c r="AA163" s="16"/>
       <c r="AB163" s="16"/>
       <c r="AC163" s="16"/>
       <c r="AD163" s="16"/>
       <c r="AE163" s="16"/>
-      <c r="BN163" s="19"/>
-    </row>
-    <row r="164" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="BN163" s="16"/>
+    </row>
+    <row r="164" spans="3:67" x14ac:dyDescent="0.25">
       <c r="C164" s="19"/>
-      <c r="W164" s="16"/>
-      <c r="X164" s="16"/>
-      <c r="Y164" s="16"/>
-      <c r="Z164" s="16"/>
-      <c r="AA164" s="16"/>
       <c r="AB164" s="16"/>
       <c r="AC164" s="16"/>
       <c r="AD164" s="16"/>
       <c r="AE164" s="16"/>
-      <c r="BN164" s="19"/>
-    </row>
-    <row r="165" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="BN164" s="16"/>
+    </row>
+    <row r="165" spans="3:67" x14ac:dyDescent="0.25">
       <c r="C165" s="19"/>
-      <c r="W165" s="16"/>
-      <c r="X165" s="16"/>
-      <c r="Y165" s="16"/>
-      <c r="Z165" s="16"/>
-      <c r="AA165" s="16"/>
       <c r="AB165" s="16"/>
       <c r="AC165" s="16"/>
       <c r="AD165" s="16"/>
       <c r="AE165" s="16"/>
-      <c r="BN165" s="19"/>
-    </row>
-    <row r="166" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="BN165" s="16"/>
+    </row>
+    <row r="166" spans="3:67" x14ac:dyDescent="0.25">
       <c r="C166" s="19"/>
-      <c r="W166" s="16"/>
-      <c r="X166" s="16"/>
-      <c r="Y166" s="16"/>
-      <c r="Z166" s="16"/>
-      <c r="AA166" s="16"/>
       <c r="AB166" s="16"/>
       <c r="AC166" s="16"/>
       <c r="AD166" s="16"/>
       <c r="AE166" s="16"/>
-      <c r="BN166" s="19"/>
-    </row>
-    <row r="167" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="BN166" s="16"/>
+      <c r="BO166" s="16"/>
+    </row>
+    <row r="167" spans="3:67" x14ac:dyDescent="0.25">
       <c r="C167" s="19"/>
-      <c r="W167" s="16"/>
-      <c r="X167" s="16"/>
-      <c r="Y167" s="16"/>
-      <c r="Z167" s="16"/>
-      <c r="AA167" s="16"/>
       <c r="AB167" s="16"/>
       <c r="AC167" s="16"/>
       <c r="AD167" s="16"/>
       <c r="AE167" s="16"/>
-      <c r="BN167" s="19"/>
-    </row>
-    <row r="168" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="BN167" s="16"/>
+      <c r="BO167" s="16"/>
+    </row>
+    <row r="168" spans="3:67" x14ac:dyDescent="0.25">
       <c r="C168" s="19"/>
-      <c r="W168" s="16"/>
-      <c r="X168" s="16"/>
-      <c r="Y168" s="16"/>
-      <c r="Z168" s="16"/>
-      <c r="AA168" s="16"/>
       <c r="AB168" s="16"/>
       <c r="AC168" s="16"/>
       <c r="AD168" s="16"/>
       <c r="AE168" s="16"/>
-      <c r="BN168" s="19"/>
-    </row>
-    <row r="169" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="BN168" s="16"/>
+      <c r="BO168" s="16"/>
+    </row>
+    <row r="169" spans="3:67" x14ac:dyDescent="0.25">
       <c r="C169" s="19"/>
-      <c r="W169" s="16"/>
-      <c r="X169" s="16"/>
-      <c r="Y169" s="16"/>
-      <c r="Z169" s="16"/>
-      <c r="AA169" s="16"/>
       <c r="AB169" s="16"/>
       <c r="AC169" s="16"/>
       <c r="AD169" s="16"/>
       <c r="AE169" s="16"/>
-      <c r="BN169" s="19"/>
-    </row>
-    <row r="170" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="BN169" s="16"/>
+      <c r="BO169" s="16"/>
+    </row>
+    <row r="170" spans="3:67" x14ac:dyDescent="0.25">
       <c r="C170" s="19"/>
-      <c r="W170" s="16"/>
-      <c r="X170" s="16"/>
-      <c r="Y170" s="16"/>
-      <c r="Z170" s="16"/>
-      <c r="AA170" s="16"/>
       <c r="AB170" s="16"/>
       <c r="AC170" s="16"/>
       <c r="AD170" s="16"/>
       <c r="AE170" s="16"/>
-      <c r="BN170" s="19"/>
-    </row>
-    <row r="171" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="BN170" s="16"/>
+      <c r="BO170" s="16"/>
+    </row>
+    <row r="171" spans="3:67" x14ac:dyDescent="0.25">
       <c r="C171" s="19"/>
-      <c r="W171" s="16"/>
-      <c r="X171" s="16"/>
-      <c r="Y171" s="16"/>
-      <c r="Z171" s="16"/>
-      <c r="AA171" s="16"/>
       <c r="AB171" s="16"/>
       <c r="AC171" s="16"/>
       <c r="AD171" s="16"/>
       <c r="AE171" s="16"/>
-      <c r="BN171" s="19"/>
-    </row>
-    <row r="172" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="BN171" s="16"/>
+      <c r="BO171" s="16"/>
+    </row>
+    <row r="172" spans="3:67" x14ac:dyDescent="0.25">
       <c r="C172" s="19"/>
-      <c r="W172" s="16"/>
-      <c r="X172" s="16"/>
-      <c r="Y172" s="16"/>
-      <c r="Z172" s="16"/>
-      <c r="AA172" s="16"/>
       <c r="AB172" s="16"/>
       <c r="AC172" s="16"/>
       <c r="AD172" s="16"/>
       <c r="AE172" s="16"/>
-      <c r="BN172" s="19"/>
-    </row>
-    <row r="173" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="BN172" s="16"/>
+      <c r="BO172" s="16"/>
+    </row>
+    <row r="173" spans="3:67" x14ac:dyDescent="0.25">
       <c r="C173" s="19"/>
-      <c r="W173" s="16"/>
-      <c r="X173" s="16"/>
-      <c r="Y173" s="16"/>
-      <c r="Z173" s="16"/>
-      <c r="AA173" s="16"/>
       <c r="AB173" s="16"/>
       <c r="AC173" s="16"/>
       <c r="AD173" s="16"/>
       <c r="AE173" s="16"/>
-      <c r="BN173" s="19"/>
-    </row>
-    <row r="174" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="BN173" s="16"/>
+      <c r="BO173" s="16"/>
+    </row>
+    <row r="174" spans="3:67" x14ac:dyDescent="0.25">
       <c r="C174" s="19"/>
       <c r="W174" s="16"/>
       <c r="X174" s="16"/>
@@ -7605,9 +9546,10 @@
       <c r="AC174" s="16"/>
       <c r="AD174" s="16"/>
       <c r="AE174" s="16"/>
-      <c r="BN174" s="19"/>
-    </row>
-    <row r="175" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="BN174" s="16"/>
+      <c r="BO174" s="16"/>
+    </row>
+    <row r="175" spans="3:67" x14ac:dyDescent="0.25">
       <c r="C175" s="19"/>
       <c r="W175" s="16"/>
       <c r="X175" s="16"/>
@@ -7618,9 +9560,10 @@
       <c r="AC175" s="16"/>
       <c r="AD175" s="16"/>
       <c r="AE175" s="16"/>
-      <c r="BN175" s="19"/>
-    </row>
-    <row r="176" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="BN175" s="16"/>
+      <c r="BO175" s="16"/>
+    </row>
+    <row r="176" spans="3:67" x14ac:dyDescent="0.25">
       <c r="C176" s="19"/>
       <c r="W176" s="16"/>
       <c r="X176" s="16"/>
@@ -7631,9 +9574,10 @@
       <c r="AC176" s="16"/>
       <c r="AD176" s="16"/>
       <c r="AE176" s="16"/>
-      <c r="BN176" s="19"/>
-    </row>
-    <row r="177" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="BN176" s="16"/>
+      <c r="BO176" s="16"/>
+    </row>
+    <row r="177" spans="3:104" x14ac:dyDescent="0.25">
       <c r="C177" s="19"/>
       <c r="W177" s="16"/>
       <c r="X177" s="16"/>
@@ -7644,22 +9588,114 @@
       <c r="AC177" s="16"/>
       <c r="AD177" s="16"/>
       <c r="AE177" s="16"/>
-      <c r="BN177" s="19"/>
-    </row>
-    <row r="178" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="BN177" s="16"/>
+      <c r="BO177" s="16"/>
+    </row>
+    <row r="178" spans="3:104" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C178" s="19"/>
-      <c r="W178" s="16"/>
-      <c r="X178" s="16"/>
-      <c r="Y178" s="16"/>
-      <c r="Z178" s="16"/>
-      <c r="AA178" s="16"/>
-      <c r="AB178" s="16"/>
-      <c r="AC178" s="16"/>
-      <c r="AD178" s="16"/>
-      <c r="AE178" s="16"/>
-      <c r="BN178" s="19"/>
-    </row>
-    <row r="179" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="D178" s="20"/>
+      <c r="E178" s="21"/>
+      <c r="F178" s="21"/>
+      <c r="G178" s="21"/>
+      <c r="H178" s="21"/>
+      <c r="I178" s="21"/>
+      <c r="J178" s="21"/>
+      <c r="K178" s="21"/>
+      <c r="L178" s="21"/>
+      <c r="M178" s="21"/>
+      <c r="N178" s="21"/>
+      <c r="O178" s="21"/>
+      <c r="P178" s="21"/>
+      <c r="Q178" s="21"/>
+      <c r="R178" s="21"/>
+      <c r="S178" s="21"/>
+      <c r="T178" s="21"/>
+      <c r="U178" s="21"/>
+      <c r="V178" s="21"/>
+      <c r="W178" s="21"/>
+      <c r="X178" s="21"/>
+      <c r="Y178" s="21"/>
+      <c r="Z178" s="21"/>
+      <c r="AA178" s="21"/>
+      <c r="AB178" s="21"/>
+      <c r="AC178" s="21"/>
+      <c r="AD178" s="21"/>
+      <c r="AE178" s="21"/>
+      <c r="AF178" s="21"/>
+      <c r="AG178" s="21"/>
+      <c r="AH178" s="21"/>
+      <c r="AI178" s="21"/>
+      <c r="AJ178" s="21"/>
+      <c r="AK178" s="21"/>
+      <c r="AL178" s="21"/>
+      <c r="AM178" s="21"/>
+      <c r="AN178" s="21"/>
+      <c r="AO178" s="21"/>
+      <c r="AP178" s="21"/>
+      <c r="AQ178" s="21"/>
+      <c r="AR178" s="21"/>
+      <c r="AS178" s="21"/>
+      <c r="AT178" s="21"/>
+      <c r="AU178" s="21"/>
+      <c r="AV178" s="21"/>
+      <c r="AW178" s="21"/>
+      <c r="AX178" s="21"/>
+      <c r="AY178" s="21"/>
+      <c r="AZ178" s="21"/>
+      <c r="BA178" s="21"/>
+      <c r="BB178" s="21"/>
+      <c r="BC178" s="21"/>
+      <c r="BD178" s="21"/>
+      <c r="BE178" s="21"/>
+      <c r="BF178" s="21"/>
+      <c r="BG178" s="21"/>
+      <c r="BH178" s="21"/>
+      <c r="BI178" s="21"/>
+      <c r="BJ178" s="21"/>
+      <c r="BK178" s="21"/>
+      <c r="BL178" s="21"/>
+      <c r="BM178" s="21"/>
+      <c r="BN178" s="21"/>
+      <c r="BO178" s="21"/>
+      <c r="BP178" s="21"/>
+      <c r="BQ178" s="21"/>
+      <c r="BR178" s="21"/>
+      <c r="BS178" s="21"/>
+      <c r="BT178" s="21"/>
+      <c r="BU178" s="21"/>
+      <c r="BV178" s="21"/>
+      <c r="BW178" s="21"/>
+      <c r="BX178" s="21"/>
+      <c r="BY178" s="21"/>
+      <c r="BZ178" s="21"/>
+      <c r="CA178" s="21"/>
+      <c r="CB178" s="21"/>
+      <c r="CC178" s="21"/>
+      <c r="CD178" s="21"/>
+      <c r="CE178" s="21"/>
+      <c r="CF178" s="21"/>
+      <c r="CG178" s="21"/>
+      <c r="CH178" s="21"/>
+      <c r="CI178" s="21"/>
+      <c r="CJ178" s="21"/>
+      <c r="CK178" s="21"/>
+      <c r="CL178" s="21"/>
+      <c r="CM178" s="21"/>
+      <c r="CN178" s="21"/>
+      <c r="CO178" s="21"/>
+      <c r="CP178" s="21"/>
+      <c r="CQ178" s="21"/>
+      <c r="CR178" s="21"/>
+      <c r="CS178" s="21"/>
+      <c r="CT178" s="21"/>
+      <c r="CU178" s="21"/>
+      <c r="CV178" s="21"/>
+      <c r="CW178" s="21"/>
+      <c r="CX178" s="21"/>
+      <c r="CY178" s="21"/>
+      <c r="CZ178" s="21"/>
+    </row>
+    <row r="179" spans="3:104" x14ac:dyDescent="0.25">
       <c r="C179" s="19"/>
       <c r="W179" s="16"/>
       <c r="X179" s="16"/>
@@ -7670,9 +9706,10 @@
       <c r="AC179" s="16"/>
       <c r="AD179" s="16"/>
       <c r="AE179" s="16"/>
-      <c r="BN179" s="19"/>
-    </row>
-    <row r="180" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="BN179" s="16"/>
+      <c r="BO179" s="16"/>
+    </row>
+    <row r="180" spans="3:104" x14ac:dyDescent="0.25">
       <c r="C180" s="19"/>
       <c r="W180" s="16"/>
       <c r="X180" s="16"/>
@@ -7683,9 +9720,10 @@
       <c r="AC180" s="16"/>
       <c r="AD180" s="16"/>
       <c r="AE180" s="16"/>
-      <c r="BN180" s="19"/>
-    </row>
-    <row r="181" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="BN180" s="16"/>
+      <c r="BO180" s="16"/>
+    </row>
+    <row r="181" spans="3:104" x14ac:dyDescent="0.25">
       <c r="C181" s="19"/>
       <c r="W181" s="16"/>
       <c r="X181" s="16"/>
@@ -7696,9 +9734,10 @@
       <c r="AC181" s="16"/>
       <c r="AD181" s="16"/>
       <c r="AE181" s="16"/>
-      <c r="BN181" s="19"/>
-    </row>
-    <row r="182" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="BN181" s="16"/>
+      <c r="BO181" s="16"/>
+    </row>
+    <row r="182" spans="3:104" x14ac:dyDescent="0.25">
       <c r="C182" s="19"/>
       <c r="W182" s="16"/>
       <c r="X182" s="16"/>
@@ -7709,9 +9748,10 @@
       <c r="AC182" s="16"/>
       <c r="AD182" s="16"/>
       <c r="AE182" s="16"/>
-      <c r="BN182" s="19"/>
-    </row>
-    <row r="183" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="BN182" s="16"/>
+      <c r="BO182" s="16"/>
+    </row>
+    <row r="183" spans="3:104" x14ac:dyDescent="0.25">
       <c r="C183" s="19"/>
       <c r="W183" s="16"/>
       <c r="X183" s="16"/>
@@ -7722,9 +9762,10 @@
       <c r="AC183" s="16"/>
       <c r="AD183" s="16"/>
       <c r="AE183" s="16"/>
-      <c r="BN183" s="19"/>
-    </row>
-    <row r="184" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="BN183" s="16"/>
+      <c r="BO183" s="16"/>
+    </row>
+    <row r="184" spans="3:104" x14ac:dyDescent="0.25">
       <c r="C184" s="19"/>
       <c r="W184" s="16"/>
       <c r="X184" s="16"/>
@@ -7735,9 +9776,10 @@
       <c r="AC184" s="16"/>
       <c r="AD184" s="16"/>
       <c r="AE184" s="16"/>
-      <c r="BN184" s="19"/>
-    </row>
-    <row r="185" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="BN184" s="16"/>
+      <c r="BO184" s="16"/>
+    </row>
+    <row r="185" spans="3:104" x14ac:dyDescent="0.25">
       <c r="C185" s="19"/>
       <c r="W185" s="16"/>
       <c r="X185" s="16"/>
@@ -7748,9 +9790,10 @@
       <c r="AC185" s="16"/>
       <c r="AD185" s="16"/>
       <c r="AE185" s="16"/>
-      <c r="BN185" s="19"/>
-    </row>
-    <row r="186" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="BN185" s="16"/>
+      <c r="BO185" s="16"/>
+    </row>
+    <row r="186" spans="3:104" x14ac:dyDescent="0.25">
       <c r="C186" s="19"/>
       <c r="W186" s="16"/>
       <c r="X186" s="16"/>
@@ -7761,9 +9804,10 @@
       <c r="AC186" s="16"/>
       <c r="AD186" s="16"/>
       <c r="AE186" s="16"/>
-      <c r="BN186" s="19"/>
-    </row>
-    <row r="187" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="BN186" s="16"/>
+      <c r="BO186" s="16"/>
+    </row>
+    <row r="187" spans="3:104" x14ac:dyDescent="0.25">
       <c r="C187" s="19"/>
       <c r="W187" s="16"/>
       <c r="X187" s="16"/>
@@ -7774,9 +9818,10 @@
       <c r="AC187" s="16"/>
       <c r="AD187" s="16"/>
       <c r="AE187" s="16"/>
-      <c r="BN187" s="19"/>
-    </row>
-    <row r="188" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="BN187" s="16"/>
+      <c r="BO187" s="16"/>
+    </row>
+    <row r="188" spans="3:104" x14ac:dyDescent="0.25">
       <c r="C188" s="19"/>
       <c r="W188" s="16"/>
       <c r="X188" s="16"/>
@@ -7787,9 +9832,10 @@
       <c r="AC188" s="16"/>
       <c r="AD188" s="16"/>
       <c r="AE188" s="16"/>
-      <c r="BN188" s="19"/>
-    </row>
-    <row r="189" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="BN188" s="16"/>
+      <c r="BO188" s="16"/>
+    </row>
+    <row r="189" spans="3:104" x14ac:dyDescent="0.25">
       <c r="C189" s="19"/>
       <c r="W189" s="16"/>
       <c r="X189" s="16"/>
@@ -7800,9 +9846,10 @@
       <c r="AC189" s="16"/>
       <c r="AD189" s="16"/>
       <c r="AE189" s="16"/>
-      <c r="BN189" s="19"/>
-    </row>
-    <row r="190" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="BN189" s="16"/>
+      <c r="BO189" s="16"/>
+    </row>
+    <row r="190" spans="3:104" x14ac:dyDescent="0.25">
       <c r="C190" s="19"/>
       <c r="W190" s="16"/>
       <c r="X190" s="16"/>
@@ -7813,9 +9860,10 @@
       <c r="AC190" s="16"/>
       <c r="AD190" s="16"/>
       <c r="AE190" s="16"/>
-      <c r="BN190" s="19"/>
-    </row>
-    <row r="191" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="BN190" s="16"/>
+      <c r="BO190" s="16"/>
+    </row>
+    <row r="191" spans="3:104" x14ac:dyDescent="0.25">
       <c r="C191" s="19"/>
       <c r="W191" s="16"/>
       <c r="X191" s="16"/>
@@ -7826,9 +9874,10 @@
       <c r="AC191" s="16"/>
       <c r="AD191" s="16"/>
       <c r="AE191" s="16"/>
-      <c r="BN191" s="19"/>
-    </row>
-    <row r="192" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="BN191" s="16"/>
+      <c r="BO191" s="16"/>
+    </row>
+    <row r="192" spans="3:104" x14ac:dyDescent="0.25">
       <c r="C192" s="19"/>
       <c r="W192" s="16"/>
       <c r="X192" s="16"/>
@@ -7839,9 +9888,10 @@
       <c r="AC192" s="16"/>
       <c r="AD192" s="16"/>
       <c r="AE192" s="16"/>
-      <c r="BN192" s="19"/>
-    </row>
-    <row r="193" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="BN192" s="16"/>
+      <c r="BO192" s="16"/>
+    </row>
+    <row r="193" spans="3:67" x14ac:dyDescent="0.25">
       <c r="C193" s="19"/>
       <c r="W193" s="16"/>
       <c r="X193" s="16"/>
@@ -7852,9 +9902,10 @@
       <c r="AC193" s="16"/>
       <c r="AD193" s="16"/>
       <c r="AE193" s="16"/>
-      <c r="BN193" s="19"/>
-    </row>
-    <row r="194" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="BN193" s="16"/>
+      <c r="BO193" s="16"/>
+    </row>
+    <row r="194" spans="3:67" x14ac:dyDescent="0.25">
       <c r="C194" s="19"/>
       <c r="W194" s="16"/>
       <c r="X194" s="16"/>
@@ -7865,9 +9916,10 @@
       <c r="AC194" s="16"/>
       <c r="AD194" s="16"/>
       <c r="AE194" s="16"/>
-      <c r="BN194" s="19"/>
-    </row>
-    <row r="195" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="BN194" s="16"/>
+      <c r="BO194" s="16"/>
+    </row>
+    <row r="195" spans="3:67" x14ac:dyDescent="0.25">
       <c r="C195" s="19"/>
       <c r="W195" s="16"/>
       <c r="X195" s="16"/>
@@ -7878,10 +9930,10 @@
       <c r="AC195" s="16"/>
       <c r="AD195" s="16"/>
       <c r="AE195" s="16"/>
-      <c r="BN195" s="19"/>
-    </row>
-    <row r="196" spans="3:66" x14ac:dyDescent="0.25">
-      <c r="C196" s="19"/>
+      <c r="BN195" s="16"/>
+      <c r="BO195" s="16"/>
+    </row>
+    <row r="196" spans="3:67" x14ac:dyDescent="0.25">
       <c r="W196" s="16"/>
       <c r="X196" s="16"/>
       <c r="Y196" s="16"/>
@@ -7891,9 +9943,10 @@
       <c r="AC196" s="16"/>
       <c r="AD196" s="16"/>
       <c r="AE196" s="16"/>
-      <c r="BN196" s="19"/>
-    </row>
-    <row r="197" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="BN196" s="16"/>
+      <c r="BO196" s="16"/>
+    </row>
+    <row r="197" spans="3:67" x14ac:dyDescent="0.25">
       <c r="W197" s="16"/>
       <c r="X197" s="16"/>
       <c r="Y197" s="16"/>
@@ -7903,9 +9956,10 @@
       <c r="AC197" s="16"/>
       <c r="AD197" s="16"/>
       <c r="AE197" s="16"/>
-      <c r="BN197" s="19"/>
-    </row>
-    <row r="198" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="BN197" s="16"/>
+      <c r="BO197" s="16"/>
+    </row>
+    <row r="198" spans="3:67" x14ac:dyDescent="0.25">
       <c r="W198" s="16"/>
       <c r="X198" s="16"/>
       <c r="Y198" s="16"/>
@@ -7915,9 +9969,10 @@
       <c r="AC198" s="16"/>
       <c r="AD198" s="16"/>
       <c r="AE198" s="16"/>
-      <c r="BN198" s="19"/>
-    </row>
-    <row r="199" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="BN198" s="16"/>
+      <c r="BO198" s="16"/>
+    </row>
+    <row r="199" spans="3:67" x14ac:dyDescent="0.25">
       <c r="W199" s="16"/>
       <c r="X199" s="16"/>
       <c r="Y199" s="16"/>
@@ -7927,9 +9982,10 @@
       <c r="AC199" s="16"/>
       <c r="AD199" s="16"/>
       <c r="AE199" s="16"/>
-      <c r="BN199" s="19"/>
-    </row>
-    <row r="200" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="BN199" s="16"/>
+      <c r="BO199" s="16"/>
+    </row>
+    <row r="200" spans="3:67" x14ac:dyDescent="0.25">
       <c r="W200" s="16"/>
       <c r="X200" s="16"/>
       <c r="Y200" s="16"/>
@@ -7939,9 +9995,10 @@
       <c r="AC200" s="16"/>
       <c r="AD200" s="16"/>
       <c r="AE200" s="16"/>
-      <c r="BN200" s="19"/>
-    </row>
-    <row r="201" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="BN200" s="16"/>
+      <c r="BO200" s="16"/>
+    </row>
+    <row r="201" spans="3:67" x14ac:dyDescent="0.25">
       <c r="W201" s="16"/>
       <c r="X201" s="16"/>
       <c r="Y201" s="16"/>
@@ -7951,9 +10008,10 @@
       <c r="AC201" s="16"/>
       <c r="AD201" s="16"/>
       <c r="AE201" s="16"/>
-      <c r="BN201" s="19"/>
-    </row>
-    <row r="202" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="BN201" s="16"/>
+      <c r="BO201" s="16"/>
+    </row>
+    <row r="202" spans="3:67" x14ac:dyDescent="0.25">
       <c r="W202" s="16"/>
       <c r="X202" s="16"/>
       <c r="Y202" s="16"/>
@@ -7963,9 +10021,10 @@
       <c r="AC202" s="16"/>
       <c r="AD202" s="16"/>
       <c r="AE202" s="16"/>
-      <c r="BN202" s="19"/>
-    </row>
-    <row r="203" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="BN202" s="16"/>
+      <c r="BO202" s="16"/>
+    </row>
+    <row r="203" spans="3:67" x14ac:dyDescent="0.25">
       <c r="W203" s="16"/>
       <c r="X203" s="16"/>
       <c r="Y203" s="16"/>
@@ -7975,9 +10034,10 @@
       <c r="AC203" s="16"/>
       <c r="AD203" s="16"/>
       <c r="AE203" s="16"/>
-      <c r="BN203" s="19"/>
-    </row>
-    <row r="204" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="BN203" s="16"/>
+      <c r="BO203" s="16"/>
+    </row>
+    <row r="204" spans="3:67" x14ac:dyDescent="0.25">
       <c r="W204" s="16"/>
       <c r="X204" s="16"/>
       <c r="Y204" s="16"/>
@@ -7987,9 +10047,10 @@
       <c r="AC204" s="16"/>
       <c r="AD204" s="16"/>
       <c r="AE204" s="16"/>
-      <c r="BN204" s="19"/>
-    </row>
-    <row r="205" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="BN204" s="16"/>
+      <c r="BO204" s="16"/>
+    </row>
+    <row r="205" spans="3:67" x14ac:dyDescent="0.25">
       <c r="W205" s="16"/>
       <c r="X205" s="16"/>
       <c r="Y205" s="16"/>
@@ -7999,9 +10060,10 @@
       <c r="AC205" s="16"/>
       <c r="AD205" s="16"/>
       <c r="AE205" s="16"/>
-      <c r="BN205" s="19"/>
-    </row>
-    <row r="206" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="BN205" s="16"/>
+      <c r="BO205" s="16"/>
+    </row>
+    <row r="206" spans="3:67" x14ac:dyDescent="0.25">
       <c r="W206" s="16"/>
       <c r="X206" s="16"/>
       <c r="Y206" s="16"/>
@@ -8011,9 +10073,10 @@
       <c r="AC206" s="16"/>
       <c r="AD206" s="16"/>
       <c r="AE206" s="16"/>
-      <c r="BN206" s="19"/>
-    </row>
-    <row r="207" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="BN206" s="16"/>
+      <c r="BO206" s="16"/>
+    </row>
+    <row r="207" spans="3:67" x14ac:dyDescent="0.25">
       <c r="W207" s="16"/>
       <c r="X207" s="16"/>
       <c r="Y207" s="16"/>
@@ -8023,9 +10086,10 @@
       <c r="AC207" s="16"/>
       <c r="AD207" s="16"/>
       <c r="AE207" s="16"/>
-      <c r="BN207" s="19"/>
-    </row>
-    <row r="208" spans="3:66" x14ac:dyDescent="0.25">
+      <c r="BN207" s="16"/>
+      <c r="BO207" s="16"/>
+    </row>
+    <row r="208" spans="3:67" x14ac:dyDescent="0.25">
       <c r="W208" s="16"/>
       <c r="X208" s="16"/>
       <c r="Y208" s="16"/>
@@ -8035,9 +10099,10 @@
       <c r="AC208" s="16"/>
       <c r="AD208" s="16"/>
       <c r="AE208" s="16"/>
-      <c r="BN208" s="19"/>
-    </row>
-    <row r="209" spans="23:66" x14ac:dyDescent="0.25">
+      <c r="BN208" s="16"/>
+      <c r="BO208" s="16"/>
+    </row>
+    <row r="209" spans="23:67" x14ac:dyDescent="0.25">
       <c r="W209" s="16"/>
       <c r="X209" s="16"/>
       <c r="Y209" s="16"/>
@@ -8047,9 +10112,10 @@
       <c r="AC209" s="16"/>
       <c r="AD209" s="16"/>
       <c r="AE209" s="16"/>
-      <c r="BN209" s="19"/>
-    </row>
-    <row r="210" spans="23:66" x14ac:dyDescent="0.25">
+      <c r="BN209" s="16"/>
+      <c r="BO209" s="16"/>
+    </row>
+    <row r="210" spans="23:67" x14ac:dyDescent="0.25">
       <c r="W210" s="16"/>
       <c r="X210" s="16"/>
       <c r="Y210" s="16"/>
@@ -8059,9 +10125,10 @@
       <c r="AC210" s="16"/>
       <c r="AD210" s="16"/>
       <c r="AE210" s="16"/>
-      <c r="BN210" s="19"/>
-    </row>
-    <row r="211" spans="23:66" x14ac:dyDescent="0.25">
+      <c r="BN210" s="16"/>
+      <c r="BO210" s="16"/>
+    </row>
+    <row r="211" spans="23:67" x14ac:dyDescent="0.25">
       <c r="W211" s="16"/>
       <c r="X211" s="16"/>
       <c r="Y211" s="16"/>
@@ -8071,9 +10138,10 @@
       <c r="AC211" s="16"/>
       <c r="AD211" s="16"/>
       <c r="AE211" s="16"/>
-      <c r="BN211" s="19"/>
-    </row>
-    <row r="212" spans="23:66" x14ac:dyDescent="0.25">
+      <c r="BN211" s="16"/>
+      <c r="BO211" s="16"/>
+    </row>
+    <row r="212" spans="23:67" x14ac:dyDescent="0.25">
       <c r="W212" s="16"/>
       <c r="X212" s="16"/>
       <c r="Y212" s="16"/>
@@ -8083,9 +10151,10 @@
       <c r="AC212" s="16"/>
       <c r="AD212" s="16"/>
       <c r="AE212" s="16"/>
-      <c r="BN212" s="19"/>
-    </row>
-    <row r="213" spans="23:66" x14ac:dyDescent="0.25">
+      <c r="BN212" s="16"/>
+      <c r="BO212" s="16"/>
+    </row>
+    <row r="213" spans="23:67" x14ac:dyDescent="0.25">
       <c r="W213" s="16"/>
       <c r="X213" s="16"/>
       <c r="Y213" s="16"/>
@@ -8095,9 +10164,10 @@
       <c r="AC213" s="16"/>
       <c r="AD213" s="16"/>
       <c r="AE213" s="16"/>
-      <c r="BN213" s="19"/>
-    </row>
-    <row r="214" spans="23:66" x14ac:dyDescent="0.25">
+      <c r="BN213" s="16"/>
+      <c r="BO213" s="16"/>
+    </row>
+    <row r="214" spans="23:67" x14ac:dyDescent="0.25">
       <c r="W214" s="16"/>
       <c r="X214" s="16"/>
       <c r="Y214" s="16"/>
@@ -8107,9 +10177,10 @@
       <c r="AC214" s="16"/>
       <c r="AD214" s="16"/>
       <c r="AE214" s="16"/>
-      <c r="BN214" s="19"/>
-    </row>
-    <row r="215" spans="23:66" x14ac:dyDescent="0.25">
+      <c r="BN214" s="16"/>
+      <c r="BO214" s="16"/>
+    </row>
+    <row r="215" spans="23:67" x14ac:dyDescent="0.25">
       <c r="W215" s="16"/>
       <c r="X215" s="16"/>
       <c r="Y215" s="16"/>
@@ -8119,9 +10190,10 @@
       <c r="AC215" s="16"/>
       <c r="AD215" s="16"/>
       <c r="AE215" s="16"/>
-      <c r="BN215" s="19"/>
-    </row>
-    <row r="216" spans="23:66" x14ac:dyDescent="0.25">
+      <c r="BN215" s="16"/>
+      <c r="BO215" s="16"/>
+    </row>
+    <row r="216" spans="23:67" x14ac:dyDescent="0.25">
       <c r="W216" s="16"/>
       <c r="X216" s="16"/>
       <c r="Y216" s="16"/>
@@ -8131,9 +10203,10 @@
       <c r="AC216" s="16"/>
       <c r="AD216" s="16"/>
       <c r="AE216" s="16"/>
-      <c r="BN216" s="19"/>
-    </row>
-    <row r="217" spans="23:66" x14ac:dyDescent="0.25">
+      <c r="BN216" s="16"/>
+      <c r="BO216" s="16"/>
+    </row>
+    <row r="217" spans="23:67" x14ac:dyDescent="0.25">
       <c r="W217" s="16"/>
       <c r="X217" s="16"/>
       <c r="Y217" s="16"/>
@@ -8143,9 +10216,10 @@
       <c r="AC217" s="16"/>
       <c r="AD217" s="16"/>
       <c r="AE217" s="16"/>
-      <c r="BN217" s="19"/>
-    </row>
-    <row r="218" spans="23:66" x14ac:dyDescent="0.25">
+      <c r="BN217" s="16"/>
+      <c r="BO217" s="16"/>
+    </row>
+    <row r="218" spans="23:67" x14ac:dyDescent="0.25">
       <c r="W218" s="16"/>
       <c r="X218" s="16"/>
       <c r="Y218" s="16"/>
@@ -8155,9 +10229,10 @@
       <c r="AC218" s="16"/>
       <c r="AD218" s="16"/>
       <c r="AE218" s="16"/>
-      <c r="BN218" s="19"/>
-    </row>
-    <row r="219" spans="23:66" x14ac:dyDescent="0.25">
+      <c r="BN218" s="16"/>
+      <c r="BO218" s="16"/>
+    </row>
+    <row r="219" spans="23:67" x14ac:dyDescent="0.25">
       <c r="W219" s="16"/>
       <c r="X219" s="16"/>
       <c r="Y219" s="16"/>
@@ -8167,9 +10242,10 @@
       <c r="AC219" s="16"/>
       <c r="AD219" s="16"/>
       <c r="AE219" s="16"/>
-      <c r="BN219" s="19"/>
-    </row>
-    <row r="220" spans="23:66" x14ac:dyDescent="0.25">
+      <c r="BN219" s="16"/>
+      <c r="BO219" s="16"/>
+    </row>
+    <row r="220" spans="23:67" x14ac:dyDescent="0.25">
       <c r="W220" s="16"/>
       <c r="X220" s="16"/>
       <c r="Y220" s="16"/>
@@ -8179,9 +10255,10 @@
       <c r="AC220" s="16"/>
       <c r="AD220" s="16"/>
       <c r="AE220" s="16"/>
-      <c r="BN220" s="19"/>
-    </row>
-    <row r="221" spans="23:66" x14ac:dyDescent="0.25">
+      <c r="BN220" s="16"/>
+      <c r="BO220" s="16"/>
+    </row>
+    <row r="221" spans="23:67" x14ac:dyDescent="0.25">
       <c r="W221" s="16"/>
       <c r="X221" s="16"/>
       <c r="Y221" s="16"/>
@@ -8191,9 +10268,10 @@
       <c r="AC221" s="16"/>
       <c r="AD221" s="16"/>
       <c r="AE221" s="16"/>
-      <c r="BN221" s="19"/>
-    </row>
-    <row r="222" spans="23:66" x14ac:dyDescent="0.25">
+      <c r="BN221" s="16"/>
+      <c r="BO221" s="16"/>
+    </row>
+    <row r="222" spans="23:67" x14ac:dyDescent="0.25">
       <c r="W222" s="16"/>
       <c r="X222" s="16"/>
       <c r="Y222" s="16"/>
@@ -8203,9 +10281,10 @@
       <c r="AC222" s="16"/>
       <c r="AD222" s="16"/>
       <c r="AE222" s="16"/>
-      <c r="BN222" s="19"/>
-    </row>
-    <row r="223" spans="23:66" x14ac:dyDescent="0.25">
+      <c r="BN222" s="16"/>
+      <c r="BO222" s="16"/>
+    </row>
+    <row r="223" spans="23:67" x14ac:dyDescent="0.25">
       <c r="W223" s="16"/>
       <c r="X223" s="16"/>
       <c r="Y223" s="16"/>
@@ -8215,9 +10294,10 @@
       <c r="AC223" s="16"/>
       <c r="AD223" s="16"/>
       <c r="AE223" s="16"/>
-      <c r="BN223" s="19"/>
-    </row>
-    <row r="224" spans="23:66" x14ac:dyDescent="0.25">
+      <c r="BN223" s="16"/>
+      <c r="BO223" s="16"/>
+    </row>
+    <row r="224" spans="23:67" x14ac:dyDescent="0.25">
       <c r="W224" s="16"/>
       <c r="X224" s="16"/>
       <c r="Y224" s="16"/>
@@ -8227,9 +10307,10 @@
       <c r="AC224" s="16"/>
       <c r="AD224" s="16"/>
       <c r="AE224" s="16"/>
-      <c r="BN224" s="19"/>
-    </row>
-    <row r="225" spans="23:66" x14ac:dyDescent="0.25">
+      <c r="BN224" s="16"/>
+      <c r="BO224" s="16"/>
+    </row>
+    <row r="225" spans="23:67" x14ac:dyDescent="0.25">
       <c r="W225" s="16"/>
       <c r="X225" s="16"/>
       <c r="Y225" s="16"/>
@@ -8239,9 +10320,10 @@
       <c r="AC225" s="16"/>
       <c r="AD225" s="16"/>
       <c r="AE225" s="16"/>
-      <c r="BN225" s="19"/>
-    </row>
-    <row r="226" spans="23:66" x14ac:dyDescent="0.25">
+      <c r="BN225" s="16"/>
+      <c r="BO225" s="16"/>
+    </row>
+    <row r="226" spans="23:67" x14ac:dyDescent="0.25">
       <c r="W226" s="16"/>
       <c r="X226" s="16"/>
       <c r="Y226" s="16"/>
@@ -8251,9 +10333,10 @@
       <c r="AC226" s="16"/>
       <c r="AD226" s="16"/>
       <c r="AE226" s="16"/>
-      <c r="BN226" s="19"/>
-    </row>
-    <row r="227" spans="23:66" x14ac:dyDescent="0.25">
+      <c r="BN226" s="16"/>
+      <c r="BO226" s="16"/>
+    </row>
+    <row r="227" spans="23:67" x14ac:dyDescent="0.25">
       <c r="W227" s="16"/>
       <c r="X227" s="16"/>
       <c r="Y227" s="16"/>
@@ -8263,9 +10346,10 @@
       <c r="AC227" s="16"/>
       <c r="AD227" s="16"/>
       <c r="AE227" s="16"/>
-      <c r="BN227" s="19"/>
-    </row>
-    <row r="228" spans="23:66" x14ac:dyDescent="0.25">
+      <c r="BN227" s="16"/>
+      <c r="BO227" s="16"/>
+    </row>
+    <row r="228" spans="23:67" x14ac:dyDescent="0.25">
       <c r="W228" s="16"/>
       <c r="X228" s="16"/>
       <c r="Y228" s="16"/>
@@ -8275,9 +10359,10 @@
       <c r="AC228" s="16"/>
       <c r="AD228" s="16"/>
       <c r="AE228" s="16"/>
-      <c r="BN228" s="19"/>
-    </row>
-    <row r="229" spans="23:66" x14ac:dyDescent="0.25">
+      <c r="BN228" s="16"/>
+      <c r="BO228" s="16"/>
+    </row>
+    <row r="229" spans="23:67" x14ac:dyDescent="0.25">
       <c r="W229" s="16"/>
       <c r="X229" s="16"/>
       <c r="Y229" s="16"/>
@@ -8287,9 +10372,10 @@
       <c r="AC229" s="16"/>
       <c r="AD229" s="16"/>
       <c r="AE229" s="16"/>
-      <c r="BN229" s="19"/>
-    </row>
-    <row r="230" spans="23:66" x14ac:dyDescent="0.25">
+      <c r="BN229" s="16"/>
+      <c r="BO229" s="16"/>
+    </row>
+    <row r="230" spans="23:67" x14ac:dyDescent="0.25">
       <c r="W230" s="16"/>
       <c r="X230" s="16"/>
       <c r="Y230" s="16"/>
@@ -8299,9 +10385,10 @@
       <c r="AC230" s="16"/>
       <c r="AD230" s="16"/>
       <c r="AE230" s="16"/>
-      <c r="BN230" s="19"/>
-    </row>
-    <row r="231" spans="23:66" x14ac:dyDescent="0.25">
+      <c r="BN230" s="16"/>
+      <c r="BO230" s="16"/>
+    </row>
+    <row r="231" spans="23:67" x14ac:dyDescent="0.25">
       <c r="W231" s="16"/>
       <c r="X231" s="16"/>
       <c r="Y231" s="16"/>
@@ -8311,9 +10398,10 @@
       <c r="AC231" s="16"/>
       <c r="AD231" s="16"/>
       <c r="AE231" s="16"/>
-      <c r="BN231" s="19"/>
-    </row>
-    <row r="232" spans="23:66" x14ac:dyDescent="0.25">
+      <c r="BN231" s="16"/>
+      <c r="BO231" s="16"/>
+    </row>
+    <row r="232" spans="23:67" x14ac:dyDescent="0.25">
       <c r="W232" s="16"/>
       <c r="X232" s="16"/>
       <c r="Y232" s="16"/>
@@ -8323,388 +10411,787 @@
       <c r="AC232" s="16"/>
       <c r="AD232" s="16"/>
       <c r="AE232" s="16"/>
-      <c r="BN232" s="19"/>
-    </row>
-    <row r="233" spans="23:66" x14ac:dyDescent="0.25">
-      <c r="W233" s="16"/>
-      <c r="X233" s="16"/>
-      <c r="Y233" s="16"/>
-      <c r="Z233" s="16"/>
-      <c r="AA233" s="16"/>
-      <c r="AB233" s="16"/>
-      <c r="AC233" s="16"/>
-      <c r="AD233" s="16"/>
-      <c r="AE233" s="16"/>
-      <c r="BN233" s="19"/>
-    </row>
-    <row r="234" spans="23:66" x14ac:dyDescent="0.25">
-      <c r="BN234" s="19"/>
-    </row>
-    <row r="235" spans="23:66" x14ac:dyDescent="0.25">
-      <c r="BN235" s="19"/>
-    </row>
-    <row r="236" spans="23:66" x14ac:dyDescent="0.25">
-      <c r="BN236" s="19"/>
-    </row>
-    <row r="237" spans="23:66" x14ac:dyDescent="0.25">
-      <c r="BN237" s="19"/>
-    </row>
-    <row r="238" spans="23:66" x14ac:dyDescent="0.25">
-      <c r="BN238" s="19"/>
-    </row>
-    <row r="239" spans="23:66" x14ac:dyDescent="0.25">
-      <c r="BN239" s="19"/>
-    </row>
-    <row r="240" spans="23:66" x14ac:dyDescent="0.25">
-      <c r="BN240" s="19"/>
-    </row>
-    <row r="241" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN241" s="19"/>
-    </row>
-    <row r="242" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN242" s="19"/>
-    </row>
-    <row r="243" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN243" s="19"/>
-    </row>
-    <row r="244" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN244" s="19"/>
-    </row>
-    <row r="245" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN245" s="19"/>
-    </row>
-    <row r="246" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN246" s="19"/>
-    </row>
-    <row r="247" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN247" s="19"/>
-    </row>
-    <row r="248" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN248" s="19"/>
-    </row>
-    <row r="249" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN249" s="19"/>
-    </row>
-    <row r="250" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN250" s="19"/>
-    </row>
-    <row r="251" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN251" s="19"/>
-    </row>
-    <row r="252" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN252" s="19"/>
-    </row>
-    <row r="253" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN253" s="19"/>
-    </row>
-    <row r="254" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN254" s="19"/>
-    </row>
-    <row r="255" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN255" s="19"/>
-    </row>
-    <row r="256" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN256" s="19"/>
-    </row>
-    <row r="257" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN257" s="19"/>
-    </row>
-    <row r="258" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN258" s="19"/>
-    </row>
-    <row r="259" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN259" s="19"/>
-    </row>
-    <row r="260" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN260" s="19"/>
-    </row>
-    <row r="261" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN261" s="19"/>
-    </row>
-    <row r="262" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN262" s="19"/>
-    </row>
-    <row r="263" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN263" s="19"/>
-    </row>
-    <row r="264" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN264" s="19"/>
-    </row>
-    <row r="265" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN265" s="19"/>
-    </row>
-    <row r="266" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN266" s="19"/>
-    </row>
-    <row r="267" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN267" s="19"/>
-    </row>
-    <row r="268" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN268" s="19"/>
-    </row>
-    <row r="269" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN269" s="19"/>
-    </row>
-    <row r="270" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN270" s="19"/>
-    </row>
-    <row r="271" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN271" s="19"/>
-    </row>
-    <row r="272" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN272" s="19"/>
-    </row>
-    <row r="273" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN273" s="19"/>
-    </row>
-    <row r="274" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN274" s="19"/>
-    </row>
-    <row r="275" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN275" s="19"/>
-    </row>
-    <row r="276" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN276" s="19"/>
-    </row>
-    <row r="277" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN277" s="19"/>
-    </row>
-    <row r="278" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN278" s="19"/>
-    </row>
-    <row r="279" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN279" s="19"/>
-    </row>
-    <row r="280" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN280" s="19"/>
-    </row>
-    <row r="281" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN281" s="19"/>
-    </row>
-    <row r="282" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN282" s="19"/>
-    </row>
-    <row r="283" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN283" s="19"/>
-    </row>
-    <row r="284" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN284" s="19"/>
-    </row>
-    <row r="285" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN285" s="19"/>
-    </row>
-    <row r="286" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN286" s="19"/>
-    </row>
-    <row r="287" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN287" s="19"/>
-    </row>
-    <row r="288" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN288" s="19"/>
-    </row>
-    <row r="289" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN289" s="19"/>
-    </row>
-    <row r="290" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN290" s="19"/>
-    </row>
-    <row r="291" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN291" s="19"/>
-    </row>
-    <row r="292" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN292" s="19"/>
-    </row>
-    <row r="293" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN293" s="19"/>
-    </row>
-    <row r="294" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN294" s="19"/>
-    </row>
-    <row r="295" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN295" s="19"/>
-    </row>
-    <row r="296" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN296" s="19"/>
-    </row>
-    <row r="297" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN297" s="19"/>
-    </row>
-    <row r="298" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN298" s="19"/>
-    </row>
-    <row r="299" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN299" s="19"/>
-    </row>
-    <row r="300" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN300" s="19"/>
-    </row>
-    <row r="301" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN301" s="19"/>
-    </row>
-    <row r="302" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN302" s="19"/>
-    </row>
-    <row r="303" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN303" s="19"/>
-    </row>
-    <row r="304" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN304" s="19"/>
-    </row>
-    <row r="305" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN305" s="19"/>
-    </row>
-    <row r="306" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN306" s="19"/>
-    </row>
-    <row r="307" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN307" s="19"/>
-    </row>
-    <row r="308" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN308" s="19"/>
-    </row>
-    <row r="309" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN309" s="19"/>
-    </row>
-    <row r="310" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN310" s="19"/>
-    </row>
-    <row r="311" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN311" s="19"/>
-    </row>
-    <row r="312" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN312" s="19"/>
-    </row>
-    <row r="313" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN313" s="19"/>
-    </row>
-    <row r="314" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN314" s="19"/>
-    </row>
-    <row r="315" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN315" s="19"/>
-    </row>
-    <row r="316" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN316" s="19"/>
-    </row>
-    <row r="317" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN317" s="19"/>
-    </row>
-    <row r="318" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN318" s="19"/>
-    </row>
-    <row r="319" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN319" s="19"/>
-    </row>
-    <row r="320" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN320" s="19"/>
-    </row>
-    <row r="321" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN321" s="19"/>
-    </row>
-    <row r="322" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN322" s="19"/>
-    </row>
-    <row r="323" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN323" s="19"/>
-    </row>
-    <row r="324" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN324" s="19"/>
-    </row>
-    <row r="325" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN325" s="19"/>
-    </row>
-    <row r="326" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN326" s="19"/>
-    </row>
-    <row r="327" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN327" s="19"/>
-    </row>
-    <row r="328" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN328" s="19"/>
-    </row>
-    <row r="329" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN329" s="19"/>
-    </row>
-    <row r="330" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN330" s="19"/>
-    </row>
-    <row r="331" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN331" s="19"/>
-    </row>
-    <row r="332" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN332" s="19"/>
-    </row>
-    <row r="333" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN333" s="19"/>
-    </row>
-    <row r="334" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN334" s="19"/>
-    </row>
-    <row r="335" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN335" s="19"/>
-    </row>
-    <row r="336" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN336" s="19"/>
-    </row>
-    <row r="337" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN337" s="19"/>
-    </row>
-    <row r="338" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN338" s="19"/>
-    </row>
-    <row r="339" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN339" s="19"/>
-    </row>
-    <row r="340" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN340" s="19"/>
-    </row>
-    <row r="341" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN341" s="19"/>
-    </row>
-    <row r="342" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN342" s="19"/>
-    </row>
-    <row r="343" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN343" s="19"/>
-    </row>
-    <row r="344" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN344" s="19"/>
-    </row>
-    <row r="345" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN345" s="19"/>
-    </row>
-    <row r="346" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN346" s="19"/>
-    </row>
-    <row r="347" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN347" s="19"/>
-    </row>
-    <row r="348" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN348" s="19"/>
-    </row>
-    <row r="349" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN349" s="19"/>
-    </row>
-    <row r="350" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN350" s="19"/>
-    </row>
-    <row r="351" spans="66:66" x14ac:dyDescent="0.25">
-      <c r="BN351" s="19"/>
+      <c r="BN232" s="16"/>
+      <c r="BO232" s="16"/>
+    </row>
+    <row r="233" spans="23:67" x14ac:dyDescent="0.25">
+      <c r="BN233" s="16"/>
+      <c r="BO233" s="16"/>
+    </row>
+    <row r="234" spans="23:67" x14ac:dyDescent="0.25">
+      <c r="BN234" s="16"/>
+      <c r="BO234" s="16"/>
+    </row>
+    <row r="235" spans="23:67" x14ac:dyDescent="0.25">
+      <c r="BN235" s="16"/>
+      <c r="BO235" s="16"/>
+    </row>
+    <row r="236" spans="23:67" x14ac:dyDescent="0.25">
+      <c r="BN236" s="16"/>
+      <c r="BO236" s="16"/>
+    </row>
+    <row r="237" spans="23:67" x14ac:dyDescent="0.25">
+      <c r="BN237" s="16"/>
+      <c r="BO237" s="16"/>
+    </row>
+    <row r="238" spans="23:67" x14ac:dyDescent="0.25">
+      <c r="BN238" s="16"/>
+      <c r="BO238" s="16"/>
+    </row>
+    <row r="239" spans="23:67" x14ac:dyDescent="0.25">
+      <c r="BN239" s="16"/>
+      <c r="BO239" s="16"/>
+    </row>
+    <row r="240" spans="23:67" x14ac:dyDescent="0.25">
+      <c r="BN240" s="16"/>
+      <c r="BO240" s="16"/>
+    </row>
+    <row r="241" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN241" s="16"/>
+      <c r="BO241" s="16"/>
+    </row>
+    <row r="242" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN242" s="16"/>
+      <c r="BO242" s="16"/>
+    </row>
+    <row r="243" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN243" s="16"/>
+      <c r="BO243" s="16"/>
+    </row>
+    <row r="244" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN244" s="16"/>
+      <c r="BO244" s="16"/>
+    </row>
+    <row r="245" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN245" s="16"/>
+      <c r="BO245" s="16"/>
+    </row>
+    <row r="246" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN246" s="16"/>
+      <c r="BO246" s="16"/>
+    </row>
+    <row r="247" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN247" s="16"/>
+      <c r="BO247" s="16"/>
+    </row>
+    <row r="248" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN248" s="16"/>
+      <c r="BO248" s="16"/>
+    </row>
+    <row r="249" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN249" s="16"/>
+      <c r="BO249" s="16"/>
+    </row>
+    <row r="250" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN250" s="16"/>
+      <c r="BO250" s="16"/>
+    </row>
+    <row r="251" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN251" s="16"/>
+      <c r="BO251" s="16"/>
+    </row>
+    <row r="252" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN252" s="16"/>
+      <c r="BO252" s="16"/>
+    </row>
+    <row r="253" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN253" s="16"/>
+      <c r="BO253" s="16"/>
+    </row>
+    <row r="254" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN254" s="16"/>
+      <c r="BO254" s="16"/>
+    </row>
+    <row r="255" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN255" s="16"/>
+      <c r="BO255" s="16"/>
+    </row>
+    <row r="256" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN256" s="16"/>
+      <c r="BO256" s="16"/>
+    </row>
+    <row r="257" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN257" s="16"/>
+      <c r="BO257" s="16"/>
+    </row>
+    <row r="258" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN258" s="16"/>
+      <c r="BO258" s="16"/>
+    </row>
+    <row r="259" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN259" s="16"/>
+      <c r="BO259" s="16"/>
+    </row>
+    <row r="260" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN260" s="16"/>
+      <c r="BO260" s="16"/>
+    </row>
+    <row r="261" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN261" s="16"/>
+      <c r="BO261" s="16"/>
+    </row>
+    <row r="262" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN262" s="16"/>
+      <c r="BO262" s="16"/>
+    </row>
+    <row r="263" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN263" s="16"/>
+      <c r="BO263" s="16"/>
+    </row>
+    <row r="264" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN264" s="16"/>
+      <c r="BO264" s="16"/>
+    </row>
+    <row r="265" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN265" s="16"/>
+      <c r="BO265" s="16"/>
+    </row>
+    <row r="266" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN266" s="16"/>
+      <c r="BO266" s="16"/>
+    </row>
+    <row r="267" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN267" s="16"/>
+      <c r="BO267" s="16"/>
+    </row>
+    <row r="268" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN268" s="16"/>
+      <c r="BO268" s="16"/>
+    </row>
+    <row r="269" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN269" s="16"/>
+      <c r="BO269" s="16"/>
+    </row>
+    <row r="270" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN270" s="16"/>
+      <c r="BO270" s="16"/>
+    </row>
+    <row r="271" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN271" s="16"/>
+      <c r="BO271" s="16"/>
+    </row>
+    <row r="272" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN272" s="16"/>
+      <c r="BO272" s="16"/>
+    </row>
+    <row r="273" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN273" s="16"/>
+      <c r="BO273" s="16"/>
+    </row>
+    <row r="274" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN274" s="16"/>
+      <c r="BO274" s="16"/>
+    </row>
+    <row r="275" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN275" s="16"/>
+      <c r="BO275" s="16"/>
+    </row>
+    <row r="276" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN276" s="16"/>
+      <c r="BO276" s="16"/>
+    </row>
+    <row r="277" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN277" s="16"/>
+      <c r="BO277" s="16"/>
+    </row>
+    <row r="278" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN278" s="16"/>
+      <c r="BO278" s="16"/>
+    </row>
+    <row r="279" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN279" s="16"/>
+      <c r="BO279" s="16"/>
+    </row>
+    <row r="280" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN280" s="16"/>
+      <c r="BO280" s="16"/>
+    </row>
+    <row r="281" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN281" s="16"/>
+      <c r="BO281" s="16"/>
+    </row>
+    <row r="282" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN282" s="16"/>
+      <c r="BO282" s="16"/>
+    </row>
+    <row r="283" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN283" s="16"/>
+      <c r="BO283" s="16"/>
+    </row>
+    <row r="284" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN284" s="16"/>
+      <c r="BO284" s="16"/>
+    </row>
+    <row r="285" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN285" s="16"/>
+      <c r="BO285" s="16"/>
+    </row>
+    <row r="286" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN286" s="16"/>
+      <c r="BO286" s="16"/>
+    </row>
+    <row r="287" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN287" s="16"/>
+      <c r="BO287" s="16"/>
+    </row>
+    <row r="288" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN288" s="16"/>
+      <c r="BO288" s="16"/>
+    </row>
+    <row r="289" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN289" s="16"/>
+      <c r="BO289" s="16"/>
+    </row>
+    <row r="290" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN290" s="16"/>
+      <c r="BO290" s="16"/>
+    </row>
+    <row r="291" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN291" s="16"/>
+      <c r="BO291" s="16"/>
+    </row>
+    <row r="292" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN292" s="16"/>
+      <c r="BO292" s="16"/>
+    </row>
+    <row r="293" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN293" s="16"/>
+      <c r="BO293" s="16"/>
+    </row>
+    <row r="294" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN294" s="16"/>
+      <c r="BO294" s="16"/>
+    </row>
+    <row r="295" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN295" s="16"/>
+      <c r="BO295" s="16"/>
+    </row>
+    <row r="296" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN296" s="16"/>
+      <c r="BO296" s="16"/>
+    </row>
+    <row r="297" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN297" s="16"/>
+      <c r="BO297" s="16"/>
+    </row>
+    <row r="298" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN298" s="16"/>
+      <c r="BO298" s="16"/>
+    </row>
+    <row r="299" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN299" s="16"/>
+      <c r="BO299" s="16"/>
+    </row>
+    <row r="300" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN300" s="16"/>
+      <c r="BO300" s="16"/>
+    </row>
+    <row r="301" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN301" s="16"/>
+      <c r="BO301" s="16"/>
+    </row>
+    <row r="302" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN302" s="16"/>
+      <c r="BO302" s="16"/>
+    </row>
+    <row r="303" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN303" s="16"/>
+      <c r="BO303" s="16"/>
+    </row>
+    <row r="304" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN304" s="16"/>
+      <c r="BO304" s="16"/>
+    </row>
+    <row r="305" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN305" s="16"/>
+      <c r="BO305" s="16"/>
+    </row>
+    <row r="306" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN306" s="16"/>
+      <c r="BO306" s="16"/>
+    </row>
+    <row r="307" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN307" s="16"/>
+      <c r="BO307" s="16"/>
+    </row>
+    <row r="308" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN308" s="16"/>
+      <c r="BO308" s="16"/>
+    </row>
+    <row r="309" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN309" s="16"/>
+      <c r="BO309" s="16"/>
+    </row>
+    <row r="310" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN310" s="16"/>
+      <c r="BO310" s="16"/>
+    </row>
+    <row r="311" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN311" s="16"/>
+      <c r="BO311" s="16"/>
+    </row>
+    <row r="312" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN312" s="16"/>
+      <c r="BO312" s="16"/>
+    </row>
+    <row r="313" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN313" s="16"/>
+      <c r="BO313" s="16"/>
+    </row>
+    <row r="314" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN314" s="16"/>
+      <c r="BO314" s="16"/>
+    </row>
+    <row r="315" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN315" s="16"/>
+      <c r="BO315" s="16"/>
+    </row>
+    <row r="316" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN316" s="16"/>
+      <c r="BO316" s="16"/>
+    </row>
+    <row r="317" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN317" s="16"/>
+      <c r="BO317" s="16"/>
+    </row>
+    <row r="318" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN318" s="16"/>
+      <c r="BO318" s="16"/>
+    </row>
+    <row r="319" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN319" s="16"/>
+      <c r="BO319" s="16"/>
+    </row>
+    <row r="320" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN320" s="16"/>
+      <c r="BO320" s="16"/>
+    </row>
+    <row r="321" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN321" s="16"/>
+      <c r="BO321" s="16"/>
+    </row>
+    <row r="322" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN322" s="16"/>
+      <c r="BO322" s="16"/>
+    </row>
+    <row r="323" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN323" s="16"/>
+      <c r="BO323" s="16"/>
+    </row>
+    <row r="324" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN324" s="16"/>
+      <c r="BO324" s="16"/>
+    </row>
+    <row r="325" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN325" s="16"/>
+      <c r="BO325" s="16"/>
+    </row>
+    <row r="326" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN326" s="16"/>
+      <c r="BO326" s="16"/>
+    </row>
+    <row r="327" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN327" s="16"/>
+      <c r="BO327" s="16"/>
+    </row>
+    <row r="328" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN328" s="16"/>
+      <c r="BO328" s="16"/>
+    </row>
+    <row r="329" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN329" s="16"/>
+      <c r="BO329" s="16"/>
+    </row>
+    <row r="330" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN330" s="16"/>
+      <c r="BO330" s="16"/>
+    </row>
+    <row r="331" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN331" s="16"/>
+      <c r="BO331" s="16"/>
+    </row>
+    <row r="332" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN332" s="16"/>
+      <c r="BO332" s="16"/>
+    </row>
+    <row r="333" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN333" s="16"/>
+      <c r="BO333" s="16"/>
+    </row>
+    <row r="334" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN334" s="16"/>
+      <c r="BO334" s="16"/>
+    </row>
+    <row r="335" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN335" s="16"/>
+      <c r="BO335" s="16"/>
+    </row>
+    <row r="336" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN336" s="16"/>
+      <c r="BO336" s="16"/>
+    </row>
+    <row r="337" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN337" s="16"/>
+      <c r="BO337" s="16"/>
+    </row>
+    <row r="338" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN338" s="16"/>
+      <c r="BO338" s="16"/>
+    </row>
+    <row r="339" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN339" s="16"/>
+      <c r="BO339" s="16"/>
+    </row>
+    <row r="340" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN340" s="16"/>
+      <c r="BO340" s="16"/>
+    </row>
+    <row r="341" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN341" s="16"/>
+      <c r="BO341" s="16"/>
+    </row>
+    <row r="342" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN342" s="16"/>
+      <c r="BO342" s="16"/>
+    </row>
+    <row r="343" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN343" s="16"/>
+      <c r="BO343" s="16"/>
+    </row>
+    <row r="344" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN344" s="16"/>
+      <c r="BO344" s="16"/>
+    </row>
+    <row r="345" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN345" s="16"/>
+      <c r="BO345" s="16"/>
+    </row>
+    <row r="346" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN346" s="16"/>
+      <c r="BO346" s="16"/>
+    </row>
+    <row r="347" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN347" s="16"/>
+      <c r="BO347" s="16"/>
+    </row>
+    <row r="348" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN348" s="16"/>
+      <c r="BO348" s="16"/>
+    </row>
+    <row r="349" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN349" s="16"/>
+      <c r="BO349" s="16"/>
+    </row>
+    <row r="350" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BN350" s="16"/>
+      <c r="BO350" s="16"/>
+    </row>
+    <row r="351" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BO351" s="16"/>
+    </row>
+    <row r="352" spans="66:67" x14ac:dyDescent="0.25">
+      <c r="BO352" s="16"/>
+    </row>
+    <row r="353" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO353" s="16"/>
+    </row>
+    <row r="354" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO354" s="16"/>
+    </row>
+    <row r="355" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO355" s="16"/>
+    </row>
+    <row r="356" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO356" s="16"/>
+    </row>
+    <row r="357" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO357" s="16"/>
+    </row>
+    <row r="358" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO358" s="16"/>
+    </row>
+    <row r="359" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO359" s="16"/>
+    </row>
+    <row r="360" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO360" s="16"/>
+    </row>
+    <row r="361" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO361" s="16"/>
+    </row>
+    <row r="362" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO362" s="16"/>
+    </row>
+    <row r="363" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO363" s="16"/>
+    </row>
+    <row r="364" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO364" s="16"/>
+    </row>
+    <row r="365" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO365" s="16"/>
+    </row>
+    <row r="366" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO366" s="16"/>
+    </row>
+    <row r="367" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO367" s="16"/>
+    </row>
+    <row r="368" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO368" s="16"/>
+    </row>
+    <row r="369" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO369" s="16"/>
+    </row>
+    <row r="370" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO370" s="16"/>
+    </row>
+    <row r="371" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO371" s="16"/>
+    </row>
+    <row r="372" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO372" s="16"/>
+    </row>
+    <row r="373" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO373" s="16"/>
+    </row>
+    <row r="374" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO374" s="16"/>
+    </row>
+    <row r="375" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO375" s="16"/>
+    </row>
+    <row r="376" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO376" s="16"/>
+    </row>
+    <row r="377" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO377" s="16"/>
+    </row>
+    <row r="378" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO378" s="16"/>
+    </row>
+    <row r="379" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO379" s="16"/>
+    </row>
+    <row r="380" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO380" s="16"/>
+    </row>
+    <row r="381" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO381" s="16"/>
+    </row>
+    <row r="382" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO382" s="16"/>
+    </row>
+    <row r="383" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO383" s="16"/>
+    </row>
+    <row r="384" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO384" s="16"/>
+    </row>
+    <row r="385" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO385" s="16"/>
+    </row>
+    <row r="386" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO386" s="16"/>
+    </row>
+    <row r="387" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO387" s="16"/>
+    </row>
+    <row r="388" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO388" s="16"/>
+    </row>
+    <row r="389" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO389" s="16"/>
+    </row>
+    <row r="390" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO390" s="16"/>
+    </row>
+    <row r="391" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO391" s="16"/>
+    </row>
+    <row r="392" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO392" s="16"/>
+    </row>
+    <row r="393" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO393" s="16"/>
+    </row>
+    <row r="394" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO394" s="16"/>
+    </row>
+    <row r="395" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO395" s="16"/>
+    </row>
+    <row r="396" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO396" s="16"/>
+    </row>
+    <row r="397" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO397" s="16"/>
+    </row>
+    <row r="398" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO398" s="16"/>
+    </row>
+    <row r="399" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO399" s="16"/>
+    </row>
+    <row r="400" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO400" s="16"/>
+    </row>
+    <row r="401" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO401" s="16"/>
+    </row>
+    <row r="402" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO402" s="16"/>
+    </row>
+    <row r="403" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO403" s="16"/>
+    </row>
+    <row r="404" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO404" s="16"/>
+    </row>
+    <row r="405" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO405" s="16"/>
+    </row>
+    <row r="406" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO406" s="16"/>
+    </row>
+    <row r="407" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO407" s="16"/>
+    </row>
+    <row r="408" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO408" s="16"/>
+    </row>
+    <row r="409" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO409" s="16"/>
+    </row>
+    <row r="410" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO410" s="16"/>
+    </row>
+    <row r="411" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO411" s="16"/>
+    </row>
+    <row r="412" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO412" s="16"/>
+    </row>
+    <row r="413" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO413" s="16"/>
+    </row>
+    <row r="414" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO414" s="16"/>
+    </row>
+    <row r="415" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO415" s="16"/>
+    </row>
+    <row r="416" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO416" s="16"/>
+    </row>
+    <row r="417" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO417" s="16"/>
+    </row>
+    <row r="418" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO418" s="16"/>
+    </row>
+    <row r="419" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO419" s="16"/>
+    </row>
+    <row r="420" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO420" s="16"/>
+    </row>
+    <row r="421" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO421" s="16"/>
+    </row>
+    <row r="422" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO422" s="16"/>
+    </row>
+    <row r="423" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO423" s="16"/>
+    </row>
+    <row r="424" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO424" s="16"/>
+    </row>
+    <row r="425" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO425" s="16"/>
+    </row>
+    <row r="426" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO426" s="16"/>
+    </row>
+    <row r="427" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO427" s="16"/>
+    </row>
+    <row r="428" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO428" s="16"/>
+    </row>
+    <row r="429" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO429" s="16"/>
+    </row>
+    <row r="430" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO430" s="16"/>
+    </row>
+    <row r="431" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO431" s="16"/>
+    </row>
+    <row r="432" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO432" s="16"/>
+    </row>
+    <row r="433" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO433" s="16"/>
+    </row>
+    <row r="434" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO434" s="16"/>
+    </row>
+    <row r="435" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO435" s="16"/>
+    </row>
+    <row r="436" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO436" s="16"/>
+    </row>
+    <row r="437" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO437" s="16"/>
+    </row>
+    <row r="438" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO438" s="16"/>
+    </row>
+    <row r="439" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO439" s="16"/>
+    </row>
+    <row r="440" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO440" s="16"/>
+    </row>
+    <row r="441" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO441" s="16"/>
+    </row>
+    <row r="442" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO442" s="16"/>
+    </row>
+    <row r="443" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO443" s="16"/>
+    </row>
+    <row r="444" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO444" s="16"/>
+    </row>
+    <row r="445" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO445" s="16"/>
+    </row>
+    <row r="446" spans="67:67" x14ac:dyDescent="0.25">
+      <c r="BO446" s="16"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="M59:V60"/>
-    <mergeCell ref="M62:V63"/>
-    <mergeCell ref="AI13:AL15"/>
+  <mergeCells count="21">
+    <mergeCell ref="X126:AJ133"/>
+    <mergeCell ref="X135:AJ140"/>
+    <mergeCell ref="X142:AJ147"/>
+    <mergeCell ref="CA91:CG102"/>
+    <mergeCell ref="E76:H77"/>
+    <mergeCell ref="E123:H124"/>
+    <mergeCell ref="F125:T129"/>
+    <mergeCell ref="Y83:AH84"/>
+    <mergeCell ref="Y86:AH87"/>
     <mergeCell ref="W15:AA15"/>
-    <mergeCell ref="AJ17:AX21"/>
-    <mergeCell ref="M55:V57"/>
+    <mergeCell ref="W17:AH18"/>
+    <mergeCell ref="F78:T82"/>
+    <mergeCell ref="Y79:AH81"/>
     <mergeCell ref="E14:I15"/>
-    <mergeCell ref="W17:AD18"/>
-    <mergeCell ref="W20:AD21"/>
-    <mergeCell ref="W23:AD24"/>
     <mergeCell ref="W26:AD27"/>
-    <mergeCell ref="D116:G116"/>
+    <mergeCell ref="D119:G119"/>
     <mergeCell ref="W29:AD30"/>
     <mergeCell ref="W32:AD33"/>
     <mergeCell ref="W35:AD36"/>
@@ -8712,10 +11199,19 @@
     <mergeCell ref="D72:G72"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="F55" location="'AUTOMATION CONTROL'!D62" display="1. Automate Webpages " xr:uid="{D0968135-C58E-46C6-9C10-12729229DAC1}"/>
+    <hyperlink ref="F65" location="'AUTOMATION CONTROL'!D62" display="1. Automate Webpages " xr:uid="{D0968135-C58E-46C6-9C10-12729229DAC1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="256" orientation="portrait" horizontalDpi="4294967292" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="256" scale="12" orientation="landscape" horizontalDpi="4294967292" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87AD3438-72F6-475D-88AE-27A01DC42CF4}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>